--- a/Financial Analysis/ROKU.xlsx
+++ b/Financial Analysis/ROKU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3648D3D4-D40F-4101-B28A-95D0CD4B655F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280EB0B3-26F9-4CCF-9CB6-5FBD3F20EA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{D7866C78-17E7-487E-8035-32073BE9C199}"/>
   </bookViews>
@@ -271,7 +271,7 @@
     <t>hard to value</t>
   </si>
   <si>
-    <t>Slightly overvalued</t>
+    <t>Overvalued</t>
   </si>
 </sst>
 </file>
@@ -797,14 +797,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="11">
-        <v>59.53</v>
+        <v>70.45</v>
       </c>
       <c r="E3" s="4">
-        <v>45783</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45783</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="4">
         <v>45869</v>
@@ -828,7 +828,7 @@
       </c>
       <c r="D5" s="5">
         <f>D4*D3</f>
-        <v>8727.098</v>
+        <v>10327.969999999999</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -869,7 +869,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>6470.9979999999996</v>
+        <v>8071.869999999999</v>
       </c>
     </row>
   </sheetData>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="BD31" s="11">
         <f>Main!D3</f>
-        <v>59.53</v>
+        <v>70.45</v>
       </c>
     </row>
     <row r="32" spans="2:163" x14ac:dyDescent="0.3">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="BD32" s="10">
         <f>BD30/BD31-1</f>
-        <v>-0.2009046635940247</v>
+        <v>-0.324767276419479</v>
       </c>
     </row>
     <row r="33" spans="2:56" x14ac:dyDescent="0.3">

--- a/Financial Analysis/ROKU.xlsx
+++ b/Financial Analysis/ROKU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280EB0B3-26F9-4CCF-9CB6-5FBD3F20EA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A217F5-ED1C-47FE-9422-919409341BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{D7866C78-17E7-487E-8035-32073BE9C199}"/>
   </bookViews>
@@ -374,13 +374,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>31</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
@@ -398,7 +398,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19575780" y="0"/>
+          <a:off x="20185380" y="0"/>
           <a:ext cx="0" cy="6134100"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -797,17 +797,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="11">
-        <v>70.45</v>
+        <v>89.5</v>
       </c>
       <c r="E3" s="4">
-        <v>45804</v>
+        <v>45870</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45870</v>
       </c>
       <c r="G3" s="4">
-        <v>45869</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -815,8 +815,8 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>129.5+17.1</f>
-        <v>146.6</v>
+        <f>146.9</f>
+        <v>146.9</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>76</v>
@@ -828,7 +828,7 @@
       </c>
       <c r="D5" s="5">
         <f>D4*D3</f>
-        <v>10327.969999999999</v>
+        <v>13147.550000000001</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -836,11 +836,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>2256.1</f>
-        <v>2256.1</v>
+        <f>2253.3</f>
+        <v>2253.3000000000002</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -860,7 +860,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>2256.1</v>
+        <v>2253.3000000000002</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -869,7 +869,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>8071.869999999999</v>
+        <v>10894.25</v>
       </c>
     </row>
   </sheetData>
@@ -1133,16 +1133,15 @@
         <v>880.8</v>
       </c>
       <c r="AF3" s="7">
-        <f>AB3*1.15</f>
-        <v>947.94499999999982</v>
+        <v>975.5</v>
       </c>
       <c r="AG3" s="7">
         <f>AC3*1.13</f>
         <v>1026.2659999999998</v>
       </c>
       <c r="AH3" s="7">
-        <f>AD3*1.1</f>
-        <v>1138.8300000000002</v>
+        <f>AD3*1.11</f>
+        <v>1149.183</v>
       </c>
       <c r="AI3" s="8"/>
       <c r="AJ3" s="5">
@@ -1175,47 +1174,47 @@
       </c>
       <c r="AQ3" s="5">
         <f>SUM(AE3:AH3)</f>
-        <v>3993.8409999999994</v>
+        <v>4031.7489999999998</v>
       </c>
       <c r="AR3" s="5">
-        <f>AQ3*1.1</f>
-        <v>4393.2250999999997</v>
+        <f>AQ3*1.11</f>
+        <v>4475.2413900000001</v>
       </c>
       <c r="AS3" s="5">
         <f>AR3*1.08</f>
-        <v>4744.6831080000002</v>
+        <v>4833.2607012000008</v>
       </c>
       <c r="AT3" s="5">
         <f>AS3*1.06</f>
-        <v>5029.3640944800009</v>
+        <v>5123.2563432720008</v>
       </c>
       <c r="AU3" s="5">
         <f>AT3*1.04</f>
-        <v>5230.5386582592009</v>
+        <v>5328.1865970028812</v>
       </c>
       <c r="AV3" s="5">
         <f t="shared" ref="AV3" si="0">AU3*1.03</f>
-        <v>5387.4548180069769</v>
+        <v>5488.0321949129675</v>
       </c>
       <c r="AW3" s="5">
         <f>AV3*1.02</f>
-        <v>5495.2039143671163</v>
+        <v>5597.7928388112268</v>
       </c>
       <c r="AX3" s="5">
         <f t="shared" ref="AX3:BA3" si="1">AW3*1.02</f>
-        <v>5605.1079926544589</v>
+        <v>5709.748695587451</v>
       </c>
       <c r="AY3" s="5">
         <f t="shared" si="1"/>
-        <v>5717.2101525075486</v>
+        <v>5823.9436694992</v>
       </c>
       <c r="AZ3" s="5">
         <f t="shared" si="1"/>
-        <v>5831.5543555576996</v>
+        <v>5940.4225428891841</v>
       </c>
       <c r="BA3" s="5">
         <f t="shared" si="1"/>
-        <v>5948.1854426688533</v>
+        <v>6059.2309937469681</v>
       </c>
     </row>
     <row r="4" spans="2:53" x14ac:dyDescent="0.3">
@@ -1310,16 +1309,15 @@
         <v>139.9</v>
       </c>
       <c r="AF4" s="7">
-        <f>AB4*1.07</f>
-        <v>153.86600000000001</v>
+        <v>135.6</v>
       </c>
       <c r="AG4" s="7">
-        <f>AC4*1.03</f>
-        <v>158.62</v>
+        <f>AC4*1.01</f>
+        <v>155.54</v>
       </c>
       <c r="AH4" s="7">
-        <f t="shared" ref="AH4" si="2">AD4*1.03</f>
-        <v>170.67099999999999</v>
+        <f>AD4*1.02</f>
+        <v>169.01399999999998</v>
       </c>
       <c r="AI4" s="8"/>
       <c r="AJ4" s="5">
@@ -1352,47 +1350,47 @@
       </c>
       <c r="AQ4" s="5">
         <f>SUM(AE4:AH4)</f>
-        <v>623.05700000000002</v>
+        <v>600.05399999999997</v>
       </c>
       <c r="AR4" s="5">
-        <f>AQ4*1.04</f>
-        <v>647.97928000000002</v>
+        <f>AQ4*1.03</f>
+        <v>618.05561999999998</v>
       </c>
       <c r="AS4" s="5">
         <f>AR4*1.03</f>
-        <v>667.41865840000003</v>
+        <v>636.59728859999996</v>
       </c>
       <c r="AT4" s="5">
-        <f t="shared" ref="AT4:AV4" si="3">AS4*1.02</f>
-        <v>680.76703156799999</v>
+        <f t="shared" ref="AT4:AV4" si="2">AS4*1.02</f>
+        <v>649.32923437199997</v>
       </c>
       <c r="AU4" s="5">
-        <f t="shared" si="3"/>
-        <v>694.38237219936002</v>
+        <f t="shared" si="2"/>
+        <v>662.31581905943995</v>
       </c>
       <c r="AV4" s="5">
-        <f t="shared" si="3"/>
-        <v>708.27001964334727</v>
+        <f t="shared" si="2"/>
+        <v>675.56213544062871</v>
       </c>
       <c r="AW4" s="5">
         <f>AV4*1.01</f>
-        <v>715.35271983978078</v>
+        <v>682.31775679503505</v>
       </c>
       <c r="AX4" s="5">
-        <f t="shared" ref="AX4:BA4" si="4">AW4*1.01</f>
-        <v>722.50624703817857</v>
+        <f t="shared" ref="AX4:BA4" si="3">AW4*1.01</f>
+        <v>689.14093436298538</v>
       </c>
       <c r="AY4" s="5">
-        <f t="shared" si="4"/>
-        <v>729.73130950856034</v>
+        <f t="shared" si="3"/>
+        <v>696.03234370661528</v>
       </c>
       <c r="AZ4" s="5">
-        <f t="shared" si="4"/>
-        <v>737.028622603646</v>
+        <f t="shared" si="3"/>
+        <v>702.99266714368139</v>
       </c>
       <c r="BA4" s="5">
-        <f t="shared" si="4"/>
-        <v>744.39890882968245</v>
+        <f t="shared" si="3"/>
+        <v>710.02259381511817</v>
       </c>
     </row>
     <row r="5" spans="2:53" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1400,205 +1398,205 @@
         <v>10</v>
       </c>
       <c r="C5" s="8">
-        <f t="shared" ref="C5:L5" si="5">C3+C4</f>
+        <f t="shared" ref="C5:L5" si="4">C3+C4</f>
         <v>136.6</v>
       </c>
       <c r="D5" s="8">
+        <f t="shared" si="4"/>
+        <v>156.80000000000001</v>
+      </c>
+      <c r="E5" s="8">
+        <f t="shared" si="4"/>
+        <v>173.39999999999998</v>
+      </c>
+      <c r="F5" s="8">
+        <f t="shared" si="4"/>
+        <v>275.7</v>
+      </c>
+      <c r="G5" s="8">
+        <f t="shared" si="4"/>
+        <v>206.7</v>
+      </c>
+      <c r="H5" s="8">
+        <f t="shared" si="4"/>
+        <v>250.1</v>
+      </c>
+      <c r="I5" s="8">
+        <f t="shared" si="4"/>
+        <v>260.89999999999998</v>
+      </c>
+      <c r="J5" s="8">
+        <f t="shared" si="4"/>
+        <v>411.20000000000005</v>
+      </c>
+      <c r="K5" s="8">
+        <f t="shared" si="4"/>
+        <v>320.8</v>
+      </c>
+      <c r="L5" s="8">
+        <f t="shared" si="4"/>
+        <v>356.1</v>
+      </c>
+      <c r="M5" s="8">
+        <f t="shared" ref="M5:AL5" si="5">M3+M4</f>
+        <v>451.6</v>
+      </c>
+      <c r="N5" s="8">
         <f t="shared" si="5"/>
-        <v>156.80000000000001</v>
-      </c>
-      <c r="E5" s="8">
+        <v>649.9</v>
+      </c>
+      <c r="O5" s="8">
         <f t="shared" si="5"/>
-        <v>173.39999999999998</v>
-      </c>
-      <c r="F5" s="8">
+        <v>574.20000000000005</v>
+      </c>
+      <c r="P5" s="8">
+        <f t="shared" ref="P5:Q5" si="6">P3+P4</f>
+        <v>645.09999999999991</v>
+      </c>
+      <c r="Q5" s="8">
+        <f t="shared" si="6"/>
+        <v>679.9</v>
+      </c>
+      <c r="R5" s="8">
         <f t="shared" si="5"/>
-        <v>275.7</v>
-      </c>
-      <c r="G5" s="8">
-        <f t="shared" si="5"/>
-        <v>206.7</v>
-      </c>
-      <c r="H5" s="8">
-        <f t="shared" si="5"/>
-        <v>250.1</v>
-      </c>
-      <c r="I5" s="8">
-        <f t="shared" si="5"/>
-        <v>260.89999999999998</v>
-      </c>
-      <c r="J5" s="8">
-        <f t="shared" si="5"/>
-        <v>411.20000000000005</v>
-      </c>
-      <c r="K5" s="8">
-        <f t="shared" si="5"/>
-        <v>320.8</v>
-      </c>
-      <c r="L5" s="8">
-        <f t="shared" si="5"/>
-        <v>356.1</v>
-      </c>
-      <c r="M5" s="8">
-        <f t="shared" ref="M5:AL5" si="6">M3+M4</f>
-        <v>451.6</v>
-      </c>
-      <c r="N5" s="8">
-        <f t="shared" si="6"/>
-        <v>649.9</v>
-      </c>
-      <c r="O5" s="8">
-        <f t="shared" si="6"/>
-        <v>574.20000000000005</v>
-      </c>
-      <c r="P5" s="8">
-        <f t="shared" ref="P5:Q5" si="7">P3+P4</f>
-        <v>645.09999999999991</v>
-      </c>
-      <c r="Q5" s="8">
+        <v>865.3</v>
+      </c>
+      <c r="S5" s="8">
+        <f t="shared" ref="S5:T5" si="7">S3+S4</f>
+        <v>733.69999999999993</v>
+      </c>
+      <c r="T5" s="8">
         <f t="shared" si="7"/>
-        <v>679.9</v>
-      </c>
-      <c r="R5" s="8">
-        <f t="shared" si="6"/>
-        <v>865.3</v>
-      </c>
-      <c r="S5" s="8">
-        <f t="shared" ref="S5:T5" si="8">S3+S4</f>
-        <v>733.69999999999993</v>
-      </c>
-      <c r="T5" s="8">
-        <f t="shared" si="8"/>
         <v>764.5</v>
       </c>
       <c r="U5" s="8">
-        <f t="shared" ref="U5" si="9">U3+U4</f>
+        <f t="shared" ref="U5" si="8">U3+U4</f>
         <v>761.40000000000009</v>
       </c>
       <c r="V5" s="8">
-        <f t="shared" ref="V5" si="10">V3+V4</f>
+        <f t="shared" ref="V5" si="9">V3+V4</f>
         <v>867.09999999999991</v>
       </c>
       <c r="W5" s="8">
-        <f t="shared" ref="W5:X5" si="11">W3+W4</f>
+        <f t="shared" ref="W5:X5" si="10">W3+W4</f>
         <v>741</v>
       </c>
       <c r="X5" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>847.3</v>
       </c>
       <c r="Y5" s="8">
-        <f t="shared" ref="Y5" si="12">Y3+Y4</f>
+        <f t="shared" ref="Y5" si="11">Y3+Y4</f>
         <v>912</v>
       </c>
       <c r="Z5" s="8">
-        <f t="shared" ref="Z5:AH5" si="13">Z3+Z4</f>
+        <f t="shared" ref="Z5:AH5" si="12">Z3+Z4</f>
         <v>984.5</v>
       </c>
       <c r="AA5" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>881.4</v>
       </c>
       <c r="AB5" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>968.09999999999991</v>
       </c>
       <c r="AC5" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1062.2</v>
       </c>
       <c r="AD5" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1201</v>
       </c>
       <c r="AE5" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1020.6999999999999</v>
       </c>
       <c r="AF5" s="8">
-        <f t="shared" si="13"/>
-        <v>1101.8109999999999</v>
+        <f t="shared" si="12"/>
+        <v>1111.0999999999999</v>
       </c>
       <c r="AG5" s="8">
-        <f t="shared" si="13"/>
-        <v>1184.886</v>
+        <f t="shared" si="12"/>
+        <v>1181.8059999999998</v>
       </c>
       <c r="AH5" s="8">
-        <f t="shared" si="13"/>
-        <v>1309.5010000000002</v>
+        <f t="shared" si="12"/>
+        <v>1318.1969999999999</v>
       </c>
       <c r="AI5" s="8"/>
       <c r="AJ5" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>742.5</v>
       </c>
       <c r="AK5" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1128.9000000000001</v>
       </c>
       <c r="AL5" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1778.3999999999999</v>
       </c>
       <c r="AM5" s="8">
-        <f t="shared" ref="AM5" si="14">AM3+AM4</f>
+        <f t="shared" ref="AM5" si="13">AM3+AM4</f>
         <v>2764.5</v>
       </c>
       <c r="AN5" s="8">
-        <f t="shared" ref="AN5" si="15">AN3+AN4</f>
+        <f t="shared" ref="AN5" si="14">AN3+AN4</f>
         <v>3126.7</v>
       </c>
       <c r="AO5" s="8">
-        <f t="shared" ref="AO5" si="16">AO3+AO4</f>
+        <f t="shared" ref="AO5" si="15">AO3+AO4</f>
         <v>3484.8</v>
       </c>
       <c r="AP5" s="8">
-        <f t="shared" ref="AP5" si="17">AP3+AP4</f>
+        <f t="shared" ref="AP5" si="16">AP3+AP4</f>
         <v>4112.7</v>
       </c>
       <c r="AQ5" s="8">
-        <f t="shared" ref="AQ5" si="18">AQ3+AQ4</f>
-        <v>4616.8979999999992</v>
+        <f t="shared" ref="AQ5" si="17">AQ3+AQ4</f>
+        <v>4631.8029999999999</v>
       </c>
       <c r="AR5" s="8">
-        <f t="shared" ref="AR5" si="19">AR3+AR4</f>
-        <v>5041.2043799999992</v>
+        <f t="shared" ref="AR5" si="18">AR3+AR4</f>
+        <v>5093.2970100000002</v>
       </c>
       <c r="AS5" s="8">
-        <f t="shared" ref="AS5" si="20">AS3+AS4</f>
-        <v>5412.1017664000001</v>
+        <f t="shared" ref="AS5" si="19">AS3+AS4</f>
+        <v>5469.8579898000007</v>
       </c>
       <c r="AT5" s="8">
-        <f t="shared" ref="AT5" si="21">AT3+AT4</f>
-        <v>5710.1311260480006</v>
+        <f t="shared" ref="AT5" si="20">AT3+AT4</f>
+        <v>5772.5855776440003</v>
       </c>
       <c r="AU5" s="8">
-        <f t="shared" ref="AU5" si="22">AU3+AU4</f>
-        <v>5924.9210304585613</v>
+        <f t="shared" ref="AU5" si="21">AU3+AU4</f>
+        <v>5990.5024160623216</v>
       </c>
       <c r="AV5" s="8">
-        <f t="shared" ref="AV5:AW5" si="23">AV3+AV4</f>
-        <v>6095.7248376503239</v>
+        <f t="shared" ref="AV5:AW5" si="22">AV3+AV4</f>
+        <v>6163.594330353596</v>
       </c>
       <c r="AW5" s="8">
+        <f t="shared" si="22"/>
+        <v>6280.110595606262</v>
+      </c>
+      <c r="AX5" s="8">
+        <f t="shared" ref="AX5:BA5" si="23">AX3+AX4</f>
+        <v>6398.8896299504368</v>
+      </c>
+      <c r="AY5" s="8">
         <f t="shared" si="23"/>
-        <v>6210.5566342068969</v>
-      </c>
-      <c r="AX5" s="8">
-        <f t="shared" ref="AX5:BA5" si="24">AX3+AX4</f>
-        <v>6327.6142396926371</v>
-      </c>
-      <c r="AY5" s="8">
-        <f t="shared" si="24"/>
-        <v>6446.9414620161087</v>
+        <v>6519.9760132058154</v>
       </c>
       <c r="AZ5" s="8">
-        <f t="shared" si="24"/>
-        <v>6568.5829781613456</v>
+        <f t="shared" si="23"/>
+        <v>6643.4152100328656</v>
       </c>
       <c r="BA5" s="8">
-        <f t="shared" si="24"/>
-        <v>6692.5843514985354</v>
+        <f t="shared" si="23"/>
+        <v>6769.2535875620861</v>
       </c>
     </row>
     <row r="6" spans="2:53" x14ac:dyDescent="0.3">
@@ -1693,8 +1691,7 @@
         <v>416.5</v>
       </c>
       <c r="AF6" s="5">
-        <f>AF3*0.47</f>
-        <v>445.5341499999999</v>
+        <v>477.8</v>
       </c>
       <c r="AG6" s="5">
         <f>AG3*0.46</f>
@@ -1702,7 +1699,7 @@
       </c>
       <c r="AH6" s="5">
         <f>AH3*0.46</f>
-        <v>523.86180000000013</v>
+        <v>528.62418000000002</v>
       </c>
       <c r="AJ6" s="5">
         <f>SUM(C6:F6)</f>
@@ -1734,47 +1731,47 @@
       </c>
       <c r="AQ6" s="5">
         <f>SUM(AE6:AH6)</f>
-        <v>1857.97831</v>
+        <v>1895.0065399999999</v>
       </c>
       <c r="AR6" s="5">
         <f>AR3*0.45</f>
-        <v>1976.9512949999998</v>
+        <v>2013.8586255</v>
       </c>
       <c r="AS6" s="5">
-        <f t="shared" ref="AS6:BA6" si="25">AS3*0.45</f>
-        <v>2135.1073986000001</v>
+        <f t="shared" ref="AS6:BA6" si="24">AS3*0.45</f>
+        <v>2174.9673155400005</v>
       </c>
       <c r="AT6" s="5">
-        <f t="shared" si="25"/>
-        <v>2263.2138425160006</v>
+        <f t="shared" si="24"/>
+        <v>2305.4653544724006</v>
       </c>
       <c r="AU6" s="5">
-        <f t="shared" si="25"/>
-        <v>2353.7423962166404</v>
+        <f t="shared" si="24"/>
+        <v>2397.6839686512967</v>
       </c>
       <c r="AV6" s="5">
-        <f t="shared" si="25"/>
-        <v>2424.3546681031398</v>
+        <f t="shared" si="24"/>
+        <v>2469.6144877108354</v>
       </c>
       <c r="AW6" s="5">
-        <f t="shared" si="25"/>
-        <v>2472.8417614652026</v>
+        <f t="shared" si="24"/>
+        <v>2519.006777465052</v>
       </c>
       <c r="AX6" s="5">
-        <f t="shared" si="25"/>
-        <v>2522.2985966945066</v>
+        <f t="shared" si="24"/>
+        <v>2569.386913014353</v>
       </c>
       <c r="AY6" s="5">
-        <f t="shared" si="25"/>
-        <v>2572.7445686283968</v>
+        <f t="shared" si="24"/>
+        <v>2620.7746512746403</v>
       </c>
       <c r="AZ6" s="5">
-        <f t="shared" si="25"/>
-        <v>2624.1994600009648</v>
+        <f t="shared" si="24"/>
+        <v>2673.1901443001329</v>
       </c>
       <c r="BA6" s="5">
-        <f t="shared" si="25"/>
-        <v>2676.6834492009839</v>
+        <f t="shared" si="24"/>
+        <v>2726.6539471861356</v>
       </c>
     </row>
     <row r="7" spans="2:53" x14ac:dyDescent="0.3">
@@ -1869,16 +1866,15 @@
         <v>159.1</v>
       </c>
       <c r="AF7" s="5">
-        <f t="shared" ref="AF7" si="26">AF4*1.07</f>
-        <v>164.63662000000002</v>
+        <v>135.6</v>
       </c>
       <c r="AG7" s="5">
         <f>AG4*1.09</f>
-        <v>172.89580000000001</v>
+        <v>169.5386</v>
       </c>
       <c r="AH7" s="5">
         <f>AH4*1.2</f>
-        <v>204.80519999999999</v>
+        <v>202.81679999999997</v>
       </c>
       <c r="AJ7" s="5">
         <f>SUM(C7:F7)</f>
@@ -1910,47 +1906,47 @@
       </c>
       <c r="AQ7" s="5">
         <f>SUM(AE7:AH7)</f>
-        <v>701.43762000000004</v>
+        <v>667.05539999999996</v>
       </c>
       <c r="AR7" s="5">
         <f>AR4*1.05</f>
-        <v>680.378244</v>
+        <v>648.95840099999998</v>
       </c>
       <c r="AS7" s="5">
         <f>AS4*1.01</f>
-        <v>674.09284498400007</v>
+        <v>642.96326148599996</v>
       </c>
       <c r="AT7" s="5">
         <f>AT4*0.99</f>
-        <v>673.95936125232004</v>
+        <v>642.83594202827999</v>
       </c>
       <c r="AU7" s="5">
-        <f t="shared" ref="AU7:BA7" si="27">AU4*0.99</f>
-        <v>687.43854847736645</v>
+        <f t="shared" ref="AU7:BA7" si="25">AU4*0.99</f>
+        <v>655.69266086884556</v>
       </c>
       <c r="AV7" s="5">
-        <f t="shared" si="27"/>
-        <v>701.18731944691376</v>
+        <f t="shared" si="25"/>
+        <v>668.80651408622236</v>
       </c>
       <c r="AW7" s="5">
-        <f t="shared" si="27"/>
-        <v>708.19919264138298</v>
+        <f t="shared" si="25"/>
+        <v>675.49457922708473</v>
       </c>
       <c r="AX7" s="5">
-        <f t="shared" si="27"/>
-        <v>715.2811845677968</v>
+        <f t="shared" si="25"/>
+        <v>682.24952501935547</v>
       </c>
       <c r="AY7" s="5">
-        <f t="shared" si="27"/>
-        <v>722.43399641347469</v>
+        <f t="shared" si="25"/>
+        <v>689.07202026954917</v>
       </c>
       <c r="AZ7" s="5">
-        <f t="shared" si="27"/>
-        <v>729.65833637760954</v>
+        <f t="shared" si="25"/>
+        <v>695.9627404722446</v>
       </c>
       <c r="BA7" s="5">
-        <f t="shared" si="27"/>
-        <v>736.95491974138565</v>
+        <f t="shared" si="25"/>
+        <v>702.92236787696697</v>
       </c>
     </row>
     <row r="8" spans="2:53" x14ac:dyDescent="0.3">
@@ -1958,204 +1954,204 @@
         <v>26</v>
       </c>
       <c r="C8" s="5">
-        <f t="shared" ref="C8:L8" si="28">C6+C7</f>
+        <f t="shared" ref="C8:L8" si="26">C6+C7</f>
         <v>73.5</v>
       </c>
       <c r="D8" s="5">
+        <f t="shared" si="26"/>
+        <v>79</v>
+      </c>
+      <c r="E8" s="5">
+        <f t="shared" si="26"/>
+        <v>94.4</v>
+      </c>
+      <c r="F8" s="5">
+        <f t="shared" si="26"/>
+        <v>163.4</v>
+      </c>
+      <c r="G8" s="5">
+        <f t="shared" si="26"/>
+        <v>105.80000000000001</v>
+      </c>
+      <c r="H8" s="5">
+        <f t="shared" si="26"/>
+        <v>135.9</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="26"/>
+        <v>142.5</v>
+      </c>
+      <c r="J8" s="5">
+        <f t="shared" si="26"/>
+        <v>249.5</v>
+      </c>
+      <c r="K8" s="5">
+        <f t="shared" si="26"/>
+        <v>179.60000000000002</v>
+      </c>
+      <c r="L8" s="5">
+        <f t="shared" si="26"/>
+        <v>209.2</v>
+      </c>
+      <c r="M8" s="5">
+        <f t="shared" ref="M8:AL8" si="27">M6+M7</f>
+        <v>236.89999999999998</v>
+      </c>
+      <c r="N8" s="5">
+        <f t="shared" si="27"/>
+        <v>344.4</v>
+      </c>
+      <c r="O8" s="5">
+        <f t="shared" ref="O8:R8" si="28">O6+O7</f>
+        <v>247.39999999999998</v>
+      </c>
+      <c r="P8" s="5">
+        <f t="shared" ref="P8:Q8" si="29">P6+P7</f>
+        <v>306.8</v>
+      </c>
+      <c r="Q8" s="5">
+        <f t="shared" si="29"/>
+        <v>316</v>
+      </c>
+      <c r="R8" s="5">
         <f t="shared" si="28"/>
-        <v>79</v>
-      </c>
-      <c r="E8" s="5">
-        <f t="shared" si="28"/>
-        <v>94.4</v>
-      </c>
-      <c r="F8" s="5">
-        <f t="shared" si="28"/>
-        <v>163.4</v>
-      </c>
-      <c r="G8" s="5">
-        <f t="shared" si="28"/>
-        <v>105.80000000000001</v>
-      </c>
-      <c r="H8" s="5">
-        <f t="shared" si="28"/>
-        <v>135.9</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="28"/>
-        <v>142.5</v>
-      </c>
-      <c r="J8" s="5">
-        <f t="shared" si="28"/>
-        <v>249.5</v>
-      </c>
-      <c r="K8" s="5">
-        <f t="shared" si="28"/>
-        <v>179.60000000000002</v>
-      </c>
-      <c r="L8" s="5">
-        <f t="shared" si="28"/>
-        <v>209.2</v>
-      </c>
-      <c r="M8" s="5">
-        <f t="shared" ref="M8:AL8" si="29">M6+M7</f>
-        <v>236.89999999999998</v>
-      </c>
-      <c r="N8" s="5">
-        <f t="shared" si="29"/>
-        <v>344.4</v>
-      </c>
-      <c r="O8" s="5">
-        <f t="shared" ref="O8:R8" si="30">O6+O7</f>
-        <v>247.39999999999998</v>
-      </c>
-      <c r="P8" s="5">
-        <f t="shared" ref="P8:Q8" si="31">P6+P7</f>
-        <v>306.8</v>
-      </c>
-      <c r="Q8" s="5">
-        <f t="shared" si="31"/>
-        <v>316</v>
-      </c>
-      <c r="R8" s="5">
+        <v>485.7</v>
+      </c>
+      <c r="S8" s="5">
+        <f t="shared" ref="S8:T8" si="30">S6+S7</f>
+        <v>368.9</v>
+      </c>
+      <c r="T8" s="5">
         <f t="shared" si="30"/>
-        <v>485.7</v>
-      </c>
-      <c r="S8" s="5">
-        <f t="shared" ref="S8:T8" si="32">S6+S7</f>
-        <v>368.9</v>
-      </c>
-      <c r="T8" s="5">
-        <f t="shared" si="32"/>
         <v>409.3</v>
       </c>
       <c r="U8" s="5">
-        <f t="shared" ref="U8" si="33">U6+U7</f>
+        <f t="shared" ref="U8" si="31">U6+U7</f>
         <v>404.6</v>
       </c>
       <c r="V8" s="5">
-        <f t="shared" ref="V8" si="34">V6+V7</f>
+        <f t="shared" ref="V8" si="32">V6+V7</f>
         <v>502.70000000000005</v>
       </c>
       <c r="W8" s="5">
-        <f t="shared" ref="W8:X8" si="35">W6+W7</f>
+        <f t="shared" ref="W8:X8" si="33">W6+W7</f>
         <v>403.40000000000003</v>
       </c>
       <c r="X8" s="5">
+        <f t="shared" si="33"/>
+        <v>468.9</v>
+      </c>
+      <c r="Y8" s="5">
+        <f t="shared" ref="Y8" si="34">Y6+Y7</f>
+        <v>543.20000000000005</v>
+      </c>
+      <c r="Z8" s="5">
+        <f t="shared" ref="Z8:AA8" si="35">Z6+Z7</f>
+        <v>546.5</v>
+      </c>
+      <c r="AA8" s="5">
         <f t="shared" si="35"/>
-        <v>468.9</v>
-      </c>
-      <c r="Y8" s="5">
-        <f t="shared" ref="Y8" si="36">Y6+Y7</f>
-        <v>543.20000000000005</v>
-      </c>
-      <c r="Z8" s="5">
-        <f t="shared" ref="Z8:AA8" si="37">Z6+Z7</f>
-        <v>546.5</v>
-      </c>
-      <c r="AA8" s="5">
+        <v>493.20000000000005</v>
+      </c>
+      <c r="AB8" s="5">
+        <f t="shared" ref="AB8:AD8" si="36">AB6+AB7</f>
+        <v>543.5</v>
+      </c>
+      <c r="AC8" s="5">
+        <f t="shared" si="36"/>
+        <v>582.09999999999991</v>
+      </c>
+      <c r="AD8" s="5">
+        <f t="shared" si="36"/>
+        <v>688.5</v>
+      </c>
+      <c r="AE8" s="5">
+        <f t="shared" ref="AE8:AH8" si="37">AE6+AE7</f>
+        <v>575.6</v>
+      </c>
+      <c r="AF8" s="5">
         <f t="shared" si="37"/>
-        <v>493.20000000000005</v>
-      </c>
-      <c r="AB8" s="5">
-        <f t="shared" ref="AB8:AD8" si="38">AB6+AB7</f>
-        <v>543.5</v>
-      </c>
-      <c r="AC8" s="5">
-        <f t="shared" si="38"/>
-        <v>582.09999999999991</v>
-      </c>
-      <c r="AD8" s="5">
-        <f t="shared" si="38"/>
-        <v>688.5</v>
-      </c>
-      <c r="AE8" s="5">
-        <f t="shared" ref="AE8:AH8" si="39">AE6+AE7</f>
-        <v>575.6</v>
-      </c>
-      <c r="AF8" s="5">
-        <f t="shared" si="39"/>
-        <v>610.17076999999995</v>
+        <v>613.4</v>
       </c>
       <c r="AG8" s="5">
-        <f t="shared" si="39"/>
-        <v>644.97815999999989</v>
+        <f t="shared" si="37"/>
+        <v>641.62095999999997</v>
       </c>
       <c r="AH8" s="5">
-        <f t="shared" si="39"/>
-        <v>728.66700000000014</v>
+        <f t="shared" si="37"/>
+        <v>731.44097999999997</v>
       </c>
       <c r="AJ8" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>410.3</v>
       </c>
       <c r="AK8" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>633.70000000000005</v>
       </c>
       <c r="AL8" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>970.09999999999991</v>
       </c>
       <c r="AM8" s="5">
-        <f t="shared" ref="AM8" si="40">AM6+AM7</f>
+        <f t="shared" ref="AM8" si="38">AM6+AM7</f>
         <v>1355.9</v>
       </c>
       <c r="AN8" s="5">
-        <f t="shared" ref="AN8" si="41">AN6+AN7</f>
+        <f t="shared" ref="AN8" si="39">AN6+AN7</f>
         <v>1685.5</v>
       </c>
       <c r="AO8" s="5">
-        <f t="shared" ref="AO8" si="42">AO6+AO7</f>
+        <f t="shared" ref="AO8" si="40">AO6+AO7</f>
         <v>1962</v>
       </c>
       <c r="AP8" s="5">
-        <f t="shared" ref="AP8" si="43">AP6+AP7</f>
+        <f t="shared" ref="AP8" si="41">AP6+AP7</f>
         <v>2307.3000000000002</v>
       </c>
       <c r="AQ8" s="5">
-        <f t="shared" ref="AQ8" si="44">AQ6+AQ7</f>
-        <v>2559.4159300000001</v>
+        <f t="shared" ref="AQ8" si="42">AQ6+AQ7</f>
+        <v>2562.0619399999996</v>
       </c>
       <c r="AR8" s="5">
-        <f t="shared" ref="AR8" si="45">AR6+AR7</f>
-        <v>2657.3295389999998</v>
+        <f t="shared" ref="AR8" si="43">AR6+AR7</f>
+        <v>2662.8170264999999</v>
       </c>
       <c r="AS8" s="5">
-        <f t="shared" ref="AS8" si="46">AS6+AS7</f>
-        <v>2809.2002435840004</v>
+        <f t="shared" ref="AS8" si="44">AS6+AS7</f>
+        <v>2817.9305770260007</v>
       </c>
       <c r="AT8" s="5">
-        <f t="shared" ref="AT8" si="47">AT6+AT7</f>
-        <v>2937.1732037683205</v>
+        <f t="shared" ref="AT8" si="45">AT6+AT7</f>
+        <v>2948.3012965006806</v>
       </c>
       <c r="AU8" s="5">
-        <f t="shared" ref="AU8" si="48">AU6+AU7</f>
-        <v>3041.1809446940069</v>
+        <f t="shared" ref="AU8" si="46">AU6+AU7</f>
+        <v>3053.3766295201422</v>
       </c>
       <c r="AV8" s="5">
-        <f t="shared" ref="AV8:AW8" si="49">AV6+AV7</f>
-        <v>3125.5419875500538</v>
+        <f t="shared" ref="AV8:AW8" si="47">AV6+AV7</f>
+        <v>3138.4210017970577</v>
       </c>
       <c r="AW8" s="5">
-        <f t="shared" si="49"/>
-        <v>3181.0409541065856</v>
+        <f t="shared" si="47"/>
+        <v>3194.5013566921366</v>
       </c>
       <c r="AX8" s="5">
-        <f t="shared" ref="AX8:BA8" si="50">AX6+AX7</f>
-        <v>3237.5797812623032</v>
+        <f t="shared" ref="AX8:BA8" si="48">AX6+AX7</f>
+        <v>3251.6364380337086</v>
       </c>
       <c r="AY8" s="5">
-        <f t="shared" si="50"/>
-        <v>3295.1785650418715</v>
+        <f t="shared" si="48"/>
+        <v>3309.8466715441896</v>
       </c>
       <c r="AZ8" s="5">
-        <f t="shared" si="50"/>
-        <v>3353.8577963785742</v>
+        <f t="shared" si="48"/>
+        <v>3369.1528847723775</v>
       </c>
       <c r="BA8" s="5">
-        <f t="shared" si="50"/>
-        <v>3413.6383689423697</v>
+        <f t="shared" si="48"/>
+        <v>3429.5763150631028</v>
       </c>
     </row>
     <row r="9" spans="2:53" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2163,204 +2159,204 @@
         <v>27</v>
       </c>
       <c r="C9" s="8">
-        <f t="shared" ref="C9:L9" si="51">C5-C8</f>
+        <f t="shared" ref="C9:L9" si="49">C5-C8</f>
         <v>63.099999999999994</v>
       </c>
       <c r="D9" s="8">
+        <f t="shared" si="49"/>
+        <v>77.800000000000011</v>
+      </c>
+      <c r="E9" s="8">
+        <f t="shared" si="49"/>
+        <v>78.999999999999972</v>
+      </c>
+      <c r="F9" s="8">
+        <f t="shared" si="49"/>
+        <v>112.29999999999998</v>
+      </c>
+      <c r="G9" s="8">
+        <f t="shared" si="49"/>
+        <v>100.89999999999998</v>
+      </c>
+      <c r="H9" s="8">
+        <f t="shared" si="49"/>
+        <v>114.19999999999999</v>
+      </c>
+      <c r="I9" s="8">
+        <f t="shared" si="49"/>
+        <v>118.39999999999998</v>
+      </c>
+      <c r="J9" s="8">
+        <f t="shared" si="49"/>
+        <v>161.70000000000005</v>
+      </c>
+      <c r="K9" s="8">
+        <f t="shared" si="49"/>
+        <v>141.19999999999999</v>
+      </c>
+      <c r="L9" s="8">
+        <f t="shared" si="49"/>
+        <v>146.90000000000003</v>
+      </c>
+      <c r="M9" s="8">
+        <f t="shared" ref="M9:AL9" si="50">M5-M8</f>
+        <v>214.70000000000005</v>
+      </c>
+      <c r="N9" s="8">
+        <f t="shared" si="50"/>
+        <v>305.5</v>
+      </c>
+      <c r="O9" s="8">
+        <f t="shared" ref="O9:R9" si="51">O5-O8</f>
+        <v>326.80000000000007</v>
+      </c>
+      <c r="P9" s="8">
+        <f t="shared" ref="P9:Q9" si="52">P5-P8</f>
+        <v>338.2999999999999</v>
+      </c>
+      <c r="Q9" s="8">
+        <f t="shared" si="52"/>
+        <v>363.9</v>
+      </c>
+      <c r="R9" s="8">
         <f t="shared" si="51"/>
-        <v>77.800000000000011</v>
-      </c>
-      <c r="E9" s="8">
-        <f t="shared" si="51"/>
-        <v>78.999999999999972</v>
-      </c>
-      <c r="F9" s="8">
-        <f t="shared" si="51"/>
-        <v>112.29999999999998</v>
-      </c>
-      <c r="G9" s="8">
-        <f t="shared" si="51"/>
-        <v>100.89999999999998</v>
-      </c>
-      <c r="H9" s="8">
-        <f t="shared" si="51"/>
-        <v>114.19999999999999</v>
-      </c>
-      <c r="I9" s="8">
-        <f t="shared" si="51"/>
-        <v>118.39999999999998</v>
-      </c>
-      <c r="J9" s="8">
-        <f t="shared" si="51"/>
-        <v>161.70000000000005</v>
-      </c>
-      <c r="K9" s="8">
-        <f t="shared" si="51"/>
-        <v>141.19999999999999</v>
-      </c>
-      <c r="L9" s="8">
-        <f t="shared" si="51"/>
-        <v>146.90000000000003</v>
-      </c>
-      <c r="M9" s="8">
-        <f t="shared" ref="M9:AL9" si="52">M5-M8</f>
-        <v>214.70000000000005</v>
-      </c>
-      <c r="N9" s="8">
-        <f t="shared" si="52"/>
-        <v>305.5</v>
-      </c>
-      <c r="O9" s="8">
-        <f t="shared" ref="O9:R9" si="53">O5-O8</f>
-        <v>326.80000000000007</v>
-      </c>
-      <c r="P9" s="8">
-        <f t="shared" ref="P9:Q9" si="54">P5-P8</f>
-        <v>338.2999999999999</v>
-      </c>
-      <c r="Q9" s="8">
-        <f t="shared" si="54"/>
-        <v>363.9</v>
-      </c>
-      <c r="R9" s="8">
+        <v>379.59999999999997</v>
+      </c>
+      <c r="S9" s="8">
+        <f t="shared" ref="S9:T9" si="53">S5-S8</f>
+        <v>364.79999999999995</v>
+      </c>
+      <c r="T9" s="8">
         <f t="shared" si="53"/>
-        <v>379.59999999999997</v>
-      </c>
-      <c r="S9" s="8">
-        <f t="shared" ref="S9:T9" si="55">S5-S8</f>
-        <v>364.79999999999995</v>
-      </c>
-      <c r="T9" s="8">
-        <f t="shared" si="55"/>
         <v>355.2</v>
       </c>
       <c r="U9" s="8">
-        <f t="shared" ref="U9" si="56">U5-U8</f>
+        <f t="shared" ref="U9" si="54">U5-U8</f>
         <v>356.80000000000007</v>
       </c>
       <c r="V9" s="8">
-        <f t="shared" ref="V9" si="57">V5-V8</f>
+        <f t="shared" ref="V9" si="55">V5-V8</f>
         <v>364.39999999999986</v>
       </c>
       <c r="W9" s="8">
-        <f t="shared" ref="W9:X9" si="58">W5-W8</f>
+        <f t="shared" ref="W9:X9" si="56">W5-W8</f>
         <v>337.59999999999997</v>
       </c>
       <c r="X9" s="8">
+        <f t="shared" si="56"/>
+        <v>378.4</v>
+      </c>
+      <c r="Y9" s="8">
+        <f t="shared" ref="Y9" si="57">Y5-Y8</f>
+        <v>368.79999999999995</v>
+      </c>
+      <c r="Z9" s="8">
+        <f t="shared" ref="Z9:AA9" si="58">Z5-Z8</f>
+        <v>438</v>
+      </c>
+      <c r="AA9" s="8">
         <f t="shared" si="58"/>
-        <v>378.4</v>
-      </c>
-      <c r="Y9" s="8">
-        <f t="shared" ref="Y9" si="59">Y5-Y8</f>
-        <v>368.79999999999995</v>
-      </c>
-      <c r="Z9" s="8">
-        <f t="shared" ref="Z9:AA9" si="60">Z5-Z8</f>
-        <v>438</v>
-      </c>
-      <c r="AA9" s="8">
+        <v>388.19999999999993</v>
+      </c>
+      <c r="AB9" s="8">
+        <f t="shared" ref="AB9:AD9" si="59">AB5-AB8</f>
+        <v>424.59999999999991</v>
+      </c>
+      <c r="AC9" s="8">
+        <f t="shared" si="59"/>
+        <v>480.10000000000014</v>
+      </c>
+      <c r="AD9" s="8">
+        <f t="shared" si="59"/>
+        <v>512.5</v>
+      </c>
+      <c r="AE9" s="8">
+        <f t="shared" ref="AE9:AH9" si="60">AE5-AE8</f>
+        <v>445.09999999999991</v>
+      </c>
+      <c r="AF9" s="8">
         <f t="shared" si="60"/>
-        <v>388.19999999999993</v>
-      </c>
-      <c r="AB9" s="8">
-        <f t="shared" ref="AB9:AD9" si="61">AB5-AB8</f>
-        <v>424.59999999999991</v>
-      </c>
-      <c r="AC9" s="8">
-        <f t="shared" si="61"/>
-        <v>480.10000000000014</v>
-      </c>
-      <c r="AD9" s="8">
-        <f t="shared" si="61"/>
-        <v>512.5</v>
-      </c>
-      <c r="AE9" s="8">
-        <f t="shared" ref="AE9:AH9" si="62">AE5-AE8</f>
-        <v>445.09999999999991</v>
-      </c>
-      <c r="AF9" s="8">
-        <f t="shared" si="62"/>
-        <v>491.64022999999997</v>
+        <v>497.69999999999993</v>
       </c>
       <c r="AG9" s="8">
-        <f t="shared" si="62"/>
-        <v>539.90784000000008</v>
+        <f t="shared" si="60"/>
+        <v>540.18503999999984</v>
       </c>
       <c r="AH9" s="8">
-        <f t="shared" si="62"/>
-        <v>580.83400000000006</v>
+        <f t="shared" si="60"/>
+        <v>586.75601999999992</v>
       </c>
       <c r="AJ9" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>332.2</v>
       </c>
       <c r="AK9" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>495.20000000000005</v>
       </c>
       <c r="AL9" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>808.3</v>
       </c>
       <c r="AM9" s="8">
-        <f t="shared" ref="AM9" si="63">AM5-AM8</f>
+        <f t="shared" ref="AM9" si="61">AM5-AM8</f>
         <v>1408.6</v>
       </c>
       <c r="AN9" s="8">
-        <f t="shared" ref="AN9" si="64">AN5-AN8</f>
+        <f t="shared" ref="AN9" si="62">AN5-AN8</f>
         <v>1441.1999999999998</v>
       </c>
       <c r="AO9" s="8">
-        <f t="shared" ref="AO9" si="65">AO5-AO8</f>
+        <f t="shared" ref="AO9" si="63">AO5-AO8</f>
         <v>1522.8000000000002</v>
       </c>
       <c r="AP9" s="8">
-        <f t="shared" ref="AP9" si="66">AP5-AP8</f>
+        <f t="shared" ref="AP9" si="64">AP5-AP8</f>
         <v>1805.3999999999996</v>
       </c>
       <c r="AQ9" s="8">
-        <f t="shared" ref="AQ9" si="67">AQ5-AQ8</f>
-        <v>2057.4820699999991</v>
+        <f t="shared" ref="AQ9" si="65">AQ5-AQ8</f>
+        <v>2069.7410600000003</v>
       </c>
       <c r="AR9" s="8">
-        <f t="shared" ref="AR9" si="68">AR5-AR8</f>
-        <v>2383.8748409999994</v>
+        <f t="shared" ref="AR9" si="66">AR5-AR8</f>
+        <v>2430.4799835000003</v>
       </c>
       <c r="AS9" s="8">
-        <f t="shared" ref="AS9" si="69">AS5-AS8</f>
-        <v>2602.9015228159997</v>
+        <f t="shared" ref="AS9" si="67">AS5-AS8</f>
+        <v>2651.927412774</v>
       </c>
       <c r="AT9" s="8">
-        <f t="shared" ref="AT9" si="70">AT5-AT8</f>
-        <v>2772.9579222796801</v>
+        <f t="shared" ref="AT9" si="68">AT5-AT8</f>
+        <v>2824.2842811433197</v>
       </c>
       <c r="AU9" s="8">
-        <f t="shared" ref="AU9" si="71">AU5-AU8</f>
-        <v>2883.7400857645544</v>
+        <f t="shared" ref="AU9" si="69">AU5-AU8</f>
+        <v>2937.1257865421794</v>
       </c>
       <c r="AV9" s="8">
-        <f t="shared" ref="AV9:AW9" si="72">AV5-AV8</f>
-        <v>2970.1828501002701</v>
+        <f t="shared" ref="AV9:AW9" si="70">AV5-AV8</f>
+        <v>3025.1733285565383</v>
       </c>
       <c r="AW9" s="8">
-        <f t="shared" si="72"/>
-        <v>3029.5156801003113</v>
+        <f t="shared" si="70"/>
+        <v>3085.6092389141254</v>
       </c>
       <c r="AX9" s="8">
-        <f t="shared" ref="AX9:BA9" si="73">AX5-AX8</f>
-        <v>3090.0344584303339</v>
+        <f t="shared" ref="AX9:BA9" si="71">AX5-AX8</f>
+        <v>3147.2531919167282</v>
       </c>
       <c r="AY9" s="8">
-        <f t="shared" si="73"/>
-        <v>3151.7628969742373</v>
+        <f t="shared" si="71"/>
+        <v>3210.1293416616259</v>
       </c>
       <c r="AZ9" s="8">
-        <f t="shared" si="73"/>
-        <v>3214.7251817827714</v>
+        <f t="shared" si="71"/>
+        <v>3274.2623252604881</v>
       </c>
       <c r="BA9" s="8">
-        <f t="shared" si="73"/>
-        <v>3278.9459825561657</v>
+        <f t="shared" si="71"/>
+        <v>3339.6772724989833</v>
       </c>
     </row>
     <row r="10" spans="2:53" x14ac:dyDescent="0.3">
@@ -2455,15 +2451,14 @@
         <v>184.6</v>
       </c>
       <c r="AF10" s="5">
-        <f>AB10*1.07</f>
-        <v>187.78500000000003</v>
+        <v>178</v>
       </c>
       <c r="AG10" s="5">
         <f>AC10*1.06</f>
         <v>189.52800000000002</v>
       </c>
       <c r="AH10" s="5">
-        <f t="shared" ref="AH10" si="74">AD10*1.03</f>
+        <f t="shared" ref="AH10" si="72">AD10*1.03</f>
         <v>190.96200000000002</v>
       </c>
       <c r="AJ10" s="5">
@@ -2496,47 +2491,47 @@
       </c>
       <c r="AQ10" s="5">
         <f>SUM(AE10:AH10)</f>
-        <v>752.875</v>
+        <v>743.09</v>
       </c>
       <c r="AR10" s="5">
         <f>AQ10*1.02</f>
-        <v>767.9325</v>
+        <v>757.95180000000005</v>
       </c>
       <c r="AS10" s="5">
         <f>AR10*1.01</f>
-        <v>775.61182500000007</v>
+        <v>765.53131800000006</v>
       </c>
       <c r="AT10" s="5">
-        <f t="shared" ref="AT10:BA10" si="75">AS10*1.01</f>
-        <v>783.36794325000005</v>
+        <f t="shared" ref="AT10:BA10" si="73">AS10*1.01</f>
+        <v>773.18663118000006</v>
       </c>
       <c r="AU10" s="5">
-        <f t="shared" si="75"/>
-        <v>791.2016226825001</v>
+        <f t="shared" si="73"/>
+        <v>780.91849749180005</v>
       </c>
       <c r="AV10" s="5">
-        <f t="shared" si="75"/>
-        <v>799.11363890932512</v>
+        <f t="shared" si="73"/>
+        <v>788.72768246671808</v>
       </c>
       <c r="AW10" s="5">
-        <f t="shared" si="75"/>
-        <v>807.10477529841842</v>
+        <f t="shared" si="73"/>
+        <v>796.61495929138528</v>
       </c>
       <c r="AX10" s="5">
-        <f t="shared" si="75"/>
-        <v>815.17582305140263</v>
+        <f t="shared" si="73"/>
+        <v>804.58110888429917</v>
       </c>
       <c r="AY10" s="5">
-        <f t="shared" si="75"/>
-        <v>823.32758128191665</v>
+        <f t="shared" si="73"/>
+        <v>812.62691997314221</v>
       </c>
       <c r="AZ10" s="5">
-        <f t="shared" si="75"/>
-        <v>831.56085709473587</v>
+        <f t="shared" si="73"/>
+        <v>820.75318917287359</v>
       </c>
       <c r="BA10" s="5">
-        <f t="shared" si="75"/>
-        <v>839.87646566568321</v>
+        <f t="shared" si="73"/>
+        <v>828.96072106460235</v>
       </c>
     </row>
     <row r="11" spans="2:53" x14ac:dyDescent="0.3">
@@ -2631,16 +2626,15 @@
         <v>223.7</v>
       </c>
       <c r="AF11" s="5">
-        <f t="shared" ref="AF11:AH11" si="76">AF5*0.22</f>
-        <v>242.39841999999999</v>
+        <v>243.3</v>
       </c>
       <c r="AG11" s="5">
-        <f t="shared" si="76"/>
-        <v>260.67491999999999</v>
+        <f t="shared" ref="AF11:AH11" si="74">AG5*0.22</f>
+        <v>259.99731999999995</v>
       </c>
       <c r="AH11" s="5">
-        <f t="shared" si="76"/>
-        <v>288.09022000000004</v>
+        <f t="shared" si="74"/>
+        <v>290.00333999999998</v>
       </c>
       <c r="AJ11" s="5">
         <f>SUM(C11:F11)</f>
@@ -2672,47 +2666,47 @@
       </c>
       <c r="AQ11" s="5">
         <f>SUM(AE11:AH11)</f>
-        <v>1014.86356</v>
+        <v>1017.0006599999999</v>
       </c>
       <c r="AR11" s="5">
         <f>AR5*0.21</f>
-        <v>1058.6529197999998</v>
+        <v>1069.5923720999999</v>
       </c>
       <c r="AS11" s="5">
         <f>AS5*0.2</f>
-        <v>1082.42035328</v>
+        <v>1093.9715979600003</v>
       </c>
       <c r="AT11" s="5">
         <f>AT5*0.19</f>
-        <v>1084.9249139491201</v>
+        <v>1096.79125975236</v>
       </c>
       <c r="AU11" s="5">
-        <f t="shared" ref="AU11:BA11" si="77">AU5*0.19</f>
-        <v>1125.7349957871268</v>
+        <f t="shared" ref="AU11:BA11" si="75">AU5*0.19</f>
+        <v>1138.195459051841</v>
       </c>
       <c r="AV11" s="5">
-        <f t="shared" si="77"/>
-        <v>1158.1877191535616</v>
+        <f t="shared" si="75"/>
+        <v>1171.0829227671832</v>
       </c>
       <c r="AW11" s="5">
-        <f t="shared" si="77"/>
-        <v>1180.0057604993103</v>
+        <f t="shared" si="75"/>
+        <v>1193.2210131651898</v>
       </c>
       <c r="AX11" s="5">
-        <f t="shared" si="77"/>
-        <v>1202.2467055416012</v>
+        <f t="shared" si="75"/>
+        <v>1215.789029690583</v>
       </c>
       <c r="AY11" s="5">
-        <f t="shared" si="77"/>
-        <v>1224.9188777830607</v>
+        <f t="shared" si="75"/>
+        <v>1238.795442509105</v>
       </c>
       <c r="AZ11" s="5">
-        <f t="shared" si="77"/>
-        <v>1248.0307658506556</v>
+        <f t="shared" si="75"/>
+        <v>1262.2488899062446</v>
       </c>
       <c r="BA11" s="5">
-        <f t="shared" si="77"/>
-        <v>1271.5910267847216</v>
+        <f t="shared" si="75"/>
+        <v>1286.1581816367964</v>
       </c>
     </row>
     <row r="12" spans="2:53" x14ac:dyDescent="0.3">
@@ -2807,15 +2801,14 @@
         <v>94.5</v>
       </c>
       <c r="AF12" s="5">
-        <f t="shared" ref="AF12:AH12" si="78">AB12*1.03</f>
-        <v>101.764</v>
+        <v>99.7</v>
       </c>
       <c r="AG12" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" ref="AF12:AH12" si="76">AC12*1.03</f>
         <v>103</v>
       </c>
       <c r="AH12" s="5">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>97.232000000000014</v>
       </c>
       <c r="AI12" s="9"/>
@@ -2849,47 +2842,47 @@
       </c>
       <c r="AQ12" s="5">
         <f>SUM(AE12:AH12)</f>
-        <v>396.49600000000004</v>
+        <v>394.43200000000002</v>
       </c>
       <c r="AR12" s="5">
-        <f t="shared" ref="AR12:BA12" si="79">AQ12*1.02</f>
-        <v>404.42592000000002</v>
+        <f t="shared" ref="AR12:BA12" si="77">AQ12*1.02</f>
+        <v>402.32064000000003</v>
       </c>
       <c r="AS12" s="5">
-        <f t="shared" si="79"/>
-        <v>412.51443840000002</v>
+        <f t="shared" si="77"/>
+        <v>410.36705280000001</v>
       </c>
       <c r="AT12" s="5">
-        <f t="shared" si="79"/>
-        <v>420.76472716800004</v>
+        <f t="shared" si="77"/>
+        <v>418.57439385600003</v>
       </c>
       <c r="AU12" s="5">
-        <f t="shared" si="79"/>
-        <v>429.18002171136004</v>
+        <f t="shared" si="77"/>
+        <v>426.94588173312002</v>
       </c>
       <c r="AV12" s="5">
-        <f t="shared" si="79"/>
-        <v>437.76362214558725</v>
+        <f t="shared" si="77"/>
+        <v>435.48479936778244</v>
       </c>
       <c r="AW12" s="5">
-        <f t="shared" si="79"/>
-        <v>446.51889458849899</v>
+        <f t="shared" si="77"/>
+        <v>444.19449535513809</v>
       </c>
       <c r="AX12" s="5">
-        <f t="shared" si="79"/>
-        <v>455.44927248026897</v>
+        <f t="shared" si="77"/>
+        <v>453.07838526224083</v>
       </c>
       <c r="AY12" s="5">
-        <f t="shared" si="79"/>
-        <v>464.55825792987434</v>
+        <f t="shared" si="77"/>
+        <v>462.13995296748567</v>
       </c>
       <c r="AZ12" s="5">
-        <f t="shared" si="79"/>
-        <v>473.84942308847184</v>
+        <f t="shared" si="77"/>
+        <v>471.38275202683542</v>
       </c>
       <c r="BA12" s="5">
-        <f t="shared" si="79"/>
-        <v>483.32641155024129</v>
+        <f t="shared" si="77"/>
+        <v>480.81040706737213</v>
       </c>
     </row>
     <row r="13" spans="2:53" x14ac:dyDescent="0.3">
@@ -2897,204 +2890,204 @@
         <v>31</v>
       </c>
       <c r="C13" s="5">
-        <f t="shared" ref="C13:L13" si="80">C10+C11+C12</f>
+        <f t="shared" ref="C13:L13" si="78">C10+C11+C12</f>
         <v>70</v>
       </c>
       <c r="D13" s="5">
+        <f t="shared" si="78"/>
+        <v>77.900000000000006</v>
+      </c>
+      <c r="E13" s="5">
+        <f t="shared" si="78"/>
+        <v>90.8</v>
+      </c>
+      <c r="F13" s="5">
+        <f t="shared" si="78"/>
+        <v>106.8</v>
+      </c>
+      <c r="G13" s="5">
+        <f t="shared" si="78"/>
+        <v>111.6</v>
+      </c>
+      <c r="H13" s="5">
+        <f t="shared" si="78"/>
+        <v>124.6</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="78"/>
+        <v>145.1</v>
+      </c>
+      <c r="J13" s="5">
+        <f t="shared" si="78"/>
+        <v>179</v>
+      </c>
+      <c r="K13" s="5">
+        <f t="shared" si="78"/>
+        <v>196.2</v>
+      </c>
+      <c r="L13" s="5">
+        <f t="shared" si="78"/>
+        <v>189.10000000000002</v>
+      </c>
+      <c r="M13" s="5">
+        <f t="shared" ref="M13:AL13" si="79">M10+M11+M12</f>
+        <v>202.9</v>
+      </c>
+      <c r="N13" s="5">
+        <f t="shared" si="79"/>
+        <v>240.3</v>
+      </c>
+      <c r="O13" s="5">
+        <f t="shared" si="79"/>
+        <v>251</v>
+      </c>
+      <c r="P13" s="5">
+        <f t="shared" ref="P13:Q13" si="80">P10+P11+P12</f>
+        <v>269.2</v>
+      </c>
+      <c r="Q13" s="5">
         <f t="shared" si="80"/>
-        <v>77.900000000000006</v>
-      </c>
-      <c r="E13" s="5">
-        <f t="shared" si="80"/>
-        <v>90.8</v>
-      </c>
-      <c r="F13" s="5">
-        <f t="shared" si="80"/>
-        <v>106.8</v>
-      </c>
-      <c r="G13" s="5">
-        <f t="shared" si="80"/>
-        <v>111.6</v>
-      </c>
-      <c r="H13" s="5">
-        <f t="shared" si="80"/>
-        <v>124.6</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="80"/>
-        <v>145.1</v>
-      </c>
-      <c r="J13" s="5">
-        <f t="shared" si="80"/>
-        <v>179</v>
-      </c>
-      <c r="K13" s="5">
-        <f t="shared" si="80"/>
-        <v>196.2</v>
-      </c>
-      <c r="L13" s="5">
-        <f t="shared" si="80"/>
-        <v>189.10000000000002</v>
-      </c>
-      <c r="M13" s="5">
-        <f t="shared" ref="M13:AL13" si="81">M10+M11+M12</f>
-        <v>202.9</v>
-      </c>
-      <c r="N13" s="5">
+        <v>295.10000000000002</v>
+      </c>
+      <c r="R13" s="5">
+        <f t="shared" si="79"/>
+        <v>358.3</v>
+      </c>
+      <c r="S13" s="5">
+        <f t="shared" ref="S13:T13" si="81">S10+S11+S12</f>
+        <v>388.3</v>
+      </c>
+      <c r="T13" s="5">
         <f t="shared" si="81"/>
-        <v>240.3</v>
-      </c>
-      <c r="O13" s="5">
-        <f t="shared" si="81"/>
-        <v>251</v>
-      </c>
-      <c r="P13" s="5">
-        <f t="shared" ref="P13:Q13" si="82">P10+P11+P12</f>
-        <v>269.2</v>
-      </c>
-      <c r="Q13" s="5">
-        <f t="shared" si="82"/>
-        <v>295.10000000000002</v>
-      </c>
-      <c r="R13" s="5">
-        <f t="shared" si="81"/>
-        <v>358.3</v>
-      </c>
-      <c r="S13" s="5">
-        <f t="shared" ref="S13:T13" si="83">S10+S11+S12</f>
-        <v>388.3</v>
-      </c>
-      <c r="T13" s="5">
-        <f t="shared" si="83"/>
         <v>465.70000000000005</v>
       </c>
       <c r="U13" s="5">
-        <f t="shared" ref="U13" si="84">U10+U11+U12</f>
+        <f t="shared" ref="U13" si="82">U10+U11+U12</f>
         <v>503.8</v>
       </c>
       <c r="V13" s="5">
-        <f t="shared" ref="V13" si="85">V10+V11+V12</f>
+        <f t="shared" ref="V13" si="83">V10+V11+V12</f>
         <v>614.29999999999995</v>
       </c>
       <c r="W13" s="5">
-        <f t="shared" ref="W13:X13" si="86">W10+W11+W12</f>
+        <f t="shared" ref="W13:X13" si="84">W10+W11+W12</f>
         <v>550.1</v>
       </c>
       <c r="X13" s="5">
+        <f t="shared" si="84"/>
+        <v>504.3</v>
+      </c>
+      <c r="Y13" s="5">
+        <f t="shared" ref="Y13" si="85">Y10+Y11+Y12</f>
+        <v>718.59999999999991</v>
+      </c>
+      <c r="Z13" s="5">
+        <f t="shared" ref="Z13:AA13" si="86">Z10+Z11+Z12</f>
+        <v>542.1</v>
+      </c>
+      <c r="AA13" s="5">
         <f t="shared" si="86"/>
-        <v>504.3</v>
-      </c>
-      <c r="Y13" s="5">
-        <f t="shared" ref="Y13" si="87">Y10+Y11+Y12</f>
-        <v>718.59999999999991</v>
-      </c>
-      <c r="Z13" s="5">
-        <f t="shared" ref="Z13:AA13" si="88">Z10+Z11+Z12</f>
-        <v>542.1</v>
-      </c>
-      <c r="AA13" s="5">
+        <v>460.2</v>
+      </c>
+      <c r="AB13" s="5">
+        <f t="shared" ref="AB13:AD13" si="87">AB10+AB11+AB12</f>
+        <v>496</v>
+      </c>
+      <c r="AC13" s="5">
+        <f t="shared" si="87"/>
+        <v>515.79999999999995</v>
+      </c>
+      <c r="AD13" s="5">
+        <f t="shared" si="87"/>
+        <v>551.69999999999993</v>
+      </c>
+      <c r="AE13" s="5">
+        <f t="shared" ref="AE13:AH13" si="88">AE10+AE11+AE12</f>
+        <v>502.79999999999995</v>
+      </c>
+      <c r="AF13" s="5">
         <f t="shared" si="88"/>
-        <v>460.2</v>
-      </c>
-      <c r="AB13" s="5">
-        <f t="shared" ref="AB13:AD13" si="89">AB10+AB11+AB12</f>
-        <v>496</v>
-      </c>
-      <c r="AC13" s="5">
-        <f t="shared" si="89"/>
-        <v>515.79999999999995</v>
-      </c>
-      <c r="AD13" s="5">
-        <f t="shared" si="89"/>
-        <v>551.69999999999993</v>
-      </c>
-      <c r="AE13" s="5">
-        <f t="shared" ref="AE13:AH13" si="90">AE10+AE11+AE12</f>
-        <v>502.79999999999995</v>
-      </c>
-      <c r="AF13" s="5">
-        <f t="shared" si="90"/>
-        <v>531.94741999999997</v>
+        <v>521</v>
       </c>
       <c r="AG13" s="5">
-        <f t="shared" si="90"/>
-        <v>553.20291999999995</v>
+        <f t="shared" si="88"/>
+        <v>552.52531999999997</v>
       </c>
       <c r="AH13" s="5">
-        <f t="shared" si="90"/>
-        <v>576.28422</v>
+        <f t="shared" si="88"/>
+        <v>578.19733999999994</v>
       </c>
       <c r="AJ13" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="79"/>
         <v>345.5</v>
       </c>
       <c r="AK13" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="79"/>
         <v>560.29999999999995</v>
       </c>
       <c r="AL13" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="79"/>
         <v>828.5</v>
       </c>
       <c r="AM13" s="5">
-        <f t="shared" ref="AM13" si="91">AM10+AM11+AM12</f>
+        <f t="shared" ref="AM13" si="89">AM10+AM11+AM12</f>
         <v>1173.6000000000001</v>
       </c>
       <c r="AN13" s="5">
-        <f t="shared" ref="AN13" si="92">AN10+AN11+AN12</f>
+        <f t="shared" ref="AN13" si="90">AN10+AN11+AN12</f>
         <v>1972.1000000000001</v>
       </c>
       <c r="AO13" s="5">
-        <f t="shared" ref="AO13" si="93">AO10+AO11+AO12</f>
+        <f t="shared" ref="AO13" si="91">AO10+AO11+AO12</f>
         <v>2315.1</v>
       </c>
       <c r="AP13" s="5">
-        <f t="shared" ref="AP13" si="94">AP10+AP11+AP12</f>
+        <f t="shared" ref="AP13" si="92">AP10+AP11+AP12</f>
         <v>2023.6999999999998</v>
       </c>
       <c r="AQ13" s="5">
-        <f t="shared" ref="AQ13" si="95">AQ10+AQ11+AQ12</f>
-        <v>2164.2345599999999</v>
+        <f t="shared" ref="AQ13" si="93">AQ10+AQ11+AQ12</f>
+        <v>2154.5226599999996</v>
       </c>
       <c r="AR13" s="5">
-        <f t="shared" ref="AR13" si="96">AR10+AR11+AR12</f>
-        <v>2231.0113397999999</v>
+        <f t="shared" ref="AR13" si="94">AR10+AR11+AR12</f>
+        <v>2229.8648121000001</v>
       </c>
       <c r="AS13" s="5">
-        <f t="shared" ref="AS13" si="97">AS10+AS11+AS12</f>
-        <v>2270.5466166800002</v>
+        <f t="shared" ref="AS13" si="95">AS10+AS11+AS12</f>
+        <v>2269.8699687600001</v>
       </c>
       <c r="AT13" s="5">
-        <f t="shared" ref="AT13" si="98">AT10+AT11+AT12</f>
-        <v>2289.0575843671204</v>
+        <f t="shared" ref="AT13" si="96">AT10+AT11+AT12</f>
+        <v>2288.5522847883599</v>
       </c>
       <c r="AU13" s="5">
-        <f t="shared" ref="AU13" si="99">AU10+AU11+AU12</f>
-        <v>2346.1166401809869</v>
+        <f t="shared" ref="AU13" si="97">AU10+AU11+AU12</f>
+        <v>2346.0598382767612</v>
       </c>
       <c r="AV13" s="5">
-        <f t="shared" ref="AV13:AW13" si="100">AV10+AV11+AV12</f>
-        <v>2395.064980208474</v>
+        <f t="shared" ref="AV13:AW13" si="98">AV10+AV11+AV12</f>
+        <v>2395.2954046016839</v>
       </c>
       <c r="AW13" s="5">
-        <f t="shared" si="100"/>
-        <v>2433.6294303862278</v>
+        <f t="shared" si="98"/>
+        <v>2434.0304678117132</v>
       </c>
       <c r="AX13" s="5">
-        <f t="shared" ref="AX13:BA13" si="101">AX10+AX11+AX12</f>
-        <v>2472.8718010732728</v>
+        <f t="shared" ref="AX13:BA13" si="99">AX10+AX11+AX12</f>
+        <v>2473.448523837123</v>
       </c>
       <c r="AY13" s="5">
-        <f t="shared" si="101"/>
-        <v>2512.8047169948518</v>
+        <f t="shared" si="99"/>
+        <v>2513.5623154497325</v>
       </c>
       <c r="AZ13" s="5">
-        <f t="shared" si="101"/>
-        <v>2553.4410460338631</v>
+        <f t="shared" si="99"/>
+        <v>2554.3848311059537</v>
       </c>
       <c r="BA13" s="5">
-        <f t="shared" si="101"/>
-        <v>2594.7939040006459</v>
+        <f t="shared" si="99"/>
+        <v>2595.929309768771</v>
       </c>
     </row>
     <row r="14" spans="2:53" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3102,204 +3095,204 @@
         <v>32</v>
       </c>
       <c r="C14" s="8">
-        <f t="shared" ref="C14:L14" si="102">C9-C13</f>
+        <f t="shared" ref="C14:L14" si="100">C9-C13</f>
         <v>-6.9000000000000057</v>
       </c>
       <c r="D14" s="8">
+        <f t="shared" si="100"/>
+        <v>-9.9999999999994316E-2</v>
+      </c>
+      <c r="E14" s="8">
+        <f t="shared" si="100"/>
+        <v>-11.800000000000026</v>
+      </c>
+      <c r="F14" s="8">
+        <f t="shared" si="100"/>
+        <v>5.4999999999999858</v>
+      </c>
+      <c r="G14" s="8">
+        <f t="shared" si="100"/>
+        <v>-10.700000000000017</v>
+      </c>
+      <c r="H14" s="8">
+        <f t="shared" si="100"/>
+        <v>-10.400000000000006</v>
+      </c>
+      <c r="I14" s="8">
+        <f t="shared" si="100"/>
+        <v>-26.700000000000017</v>
+      </c>
+      <c r="J14" s="8">
+        <f t="shared" si="100"/>
+        <v>-17.299999999999955</v>
+      </c>
+      <c r="K14" s="8">
+        <f t="shared" si="100"/>
+        <v>-55</v>
+      </c>
+      <c r="L14" s="8">
+        <f t="shared" si="100"/>
+        <v>-42.199999999999989</v>
+      </c>
+      <c r="M14" s="8">
+        <f t="shared" ref="M14:AL14" si="101">M9-M13</f>
+        <v>11.80000000000004</v>
+      </c>
+      <c r="N14" s="8">
+        <f t="shared" si="101"/>
+        <v>65.199999999999989</v>
+      </c>
+      <c r="O14" s="8">
+        <f t="shared" si="101"/>
+        <v>75.800000000000068</v>
+      </c>
+      <c r="P14" s="8">
+        <f t="shared" ref="P14:Q14" si="102">P9-P13</f>
+        <v>69.099999999999909</v>
+      </c>
+      <c r="Q14" s="8">
         <f t="shared" si="102"/>
-        <v>-9.9999999999994316E-2</v>
-      </c>
-      <c r="E14" s="8">
-        <f t="shared" si="102"/>
-        <v>-11.800000000000026</v>
-      </c>
-      <c r="F14" s="8">
-        <f t="shared" si="102"/>
-        <v>5.4999999999999858</v>
-      </c>
-      <c r="G14" s="8">
-        <f t="shared" si="102"/>
-        <v>-10.700000000000017</v>
-      </c>
-      <c r="H14" s="8">
-        <f t="shared" si="102"/>
-        <v>-10.400000000000006</v>
-      </c>
-      <c r="I14" s="8">
-        <f t="shared" si="102"/>
-        <v>-26.700000000000017</v>
-      </c>
-      <c r="J14" s="8">
-        <f t="shared" si="102"/>
-        <v>-17.299999999999955</v>
-      </c>
-      <c r="K14" s="8">
-        <f t="shared" si="102"/>
-        <v>-55</v>
-      </c>
-      <c r="L14" s="8">
-        <f t="shared" si="102"/>
-        <v>-42.199999999999989</v>
-      </c>
-      <c r="M14" s="8">
-        <f t="shared" ref="M14:AL14" si="103">M9-M13</f>
-        <v>11.80000000000004</v>
-      </c>
-      <c r="N14" s="8">
+        <v>68.799999999999955</v>
+      </c>
+      <c r="R14" s="8">
+        <f t="shared" si="101"/>
+        <v>21.299999999999955</v>
+      </c>
+      <c r="S14" s="8">
+        <f t="shared" ref="S14:T14" si="103">S9-S13</f>
+        <v>-23.500000000000057</v>
+      </c>
+      <c r="T14" s="8">
         <f t="shared" si="103"/>
-        <v>65.199999999999989</v>
-      </c>
-      <c r="O14" s="8">
-        <f t="shared" si="103"/>
-        <v>75.800000000000068</v>
-      </c>
-      <c r="P14" s="8">
-        <f t="shared" ref="P14:Q14" si="104">P9-P13</f>
-        <v>69.099999999999909</v>
-      </c>
-      <c r="Q14" s="8">
-        <f t="shared" si="104"/>
-        <v>68.799999999999955</v>
-      </c>
-      <c r="R14" s="8">
-        <f t="shared" si="103"/>
-        <v>21.299999999999955</v>
-      </c>
-      <c r="S14" s="8">
-        <f t="shared" ref="S14:T14" si="105">S9-S13</f>
-        <v>-23.500000000000057</v>
-      </c>
-      <c r="T14" s="8">
-        <f t="shared" si="105"/>
         <v>-110.50000000000006</v>
       </c>
       <c r="U14" s="8">
-        <f t="shared" ref="U14" si="106">U9-U13</f>
+        <f t="shared" ref="U14" si="104">U9-U13</f>
         <v>-146.99999999999994</v>
       </c>
       <c r="V14" s="8">
-        <f t="shared" ref="V14" si="107">V9-V13</f>
+        <f t="shared" ref="V14" si="105">V9-V13</f>
         <v>-249.90000000000009</v>
       </c>
       <c r="W14" s="8">
-        <f t="shared" ref="W14:X14" si="108">W9-W13</f>
+        <f t="shared" ref="W14:X14" si="106">W9-W13</f>
         <v>-212.50000000000006</v>
       </c>
       <c r="X14" s="8">
+        <f t="shared" si="106"/>
+        <v>-125.90000000000003</v>
+      </c>
+      <c r="Y14" s="8">
+        <f t="shared" ref="Y14" si="107">Y9-Y13</f>
+        <v>-349.79999999999995</v>
+      </c>
+      <c r="Z14" s="8">
+        <f t="shared" ref="Z14:AA14" si="108">Z9-Z13</f>
+        <v>-104.10000000000002</v>
+      </c>
+      <c r="AA14" s="8">
         <f t="shared" si="108"/>
-        <v>-125.90000000000003</v>
-      </c>
-      <c r="Y14" s="8">
-        <f t="shared" ref="Y14" si="109">Y9-Y13</f>
-        <v>-349.79999999999995</v>
-      </c>
-      <c r="Z14" s="8">
-        <f t="shared" ref="Z14:AA14" si="110">Z9-Z13</f>
-        <v>-104.10000000000002</v>
-      </c>
-      <c r="AA14" s="8">
+        <v>-72.000000000000057</v>
+      </c>
+      <c r="AB14" s="8">
+        <f t="shared" ref="AB14:AD14" si="109">AB9-AB13</f>
+        <v>-71.400000000000091</v>
+      </c>
+      <c r="AC14" s="8">
+        <f t="shared" si="109"/>
+        <v>-35.699999999999818</v>
+      </c>
+      <c r="AD14" s="8">
+        <f t="shared" si="109"/>
+        <v>-39.199999999999932</v>
+      </c>
+      <c r="AE14" s="8">
+        <f t="shared" ref="AE14:AH14" si="110">AE9-AE13</f>
+        <v>-57.700000000000045</v>
+      </c>
+      <c r="AF14" s="8">
         <f t="shared" si="110"/>
-        <v>-72.000000000000057</v>
-      </c>
-      <c r="AB14" s="8">
-        <f t="shared" ref="AB14:AD14" si="111">AB9-AB13</f>
-        <v>-71.400000000000091</v>
-      </c>
-      <c r="AC14" s="8">
-        <f t="shared" si="111"/>
-        <v>-35.699999999999818</v>
-      </c>
-      <c r="AD14" s="8">
-        <f t="shared" si="111"/>
-        <v>-39.199999999999932</v>
-      </c>
-      <c r="AE14" s="8">
-        <f t="shared" ref="AE14:AH14" si="112">AE9-AE13</f>
-        <v>-57.700000000000045</v>
-      </c>
-      <c r="AF14" s="8">
-        <f t="shared" si="112"/>
-        <v>-40.307189999999991</v>
+        <v>-23.300000000000068</v>
       </c>
       <c r="AG14" s="8">
-        <f t="shared" si="112"/>
-        <v>-13.295079999999871</v>
+        <f t="shared" si="110"/>
+        <v>-12.340280000000121</v>
       </c>
       <c r="AH14" s="8">
-        <f t="shared" si="112"/>
-        <v>4.5497800000000552</v>
+        <f t="shared" si="110"/>
+        <v>8.5586799999999812</v>
       </c>
       <c r="AJ14" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>-13.300000000000011</v>
       </c>
       <c r="AK14" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>-65.099999999999909</v>
       </c>
       <c r="AL14" s="8">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>-20.200000000000045</v>
       </c>
       <c r="AM14" s="8">
-        <f t="shared" ref="AM14" si="113">AM9-AM13</f>
+        <f t="shared" ref="AM14" si="111">AM9-AM13</f>
         <v>234.99999999999977</v>
       </c>
       <c r="AN14" s="8">
-        <f t="shared" ref="AN14" si="114">AN9-AN13</f>
+        <f t="shared" ref="AN14" si="112">AN9-AN13</f>
         <v>-530.90000000000032</v>
       </c>
       <c r="AO14" s="8">
-        <f t="shared" ref="AO14" si="115">AO9-AO13</f>
+        <f t="shared" ref="AO14" si="113">AO9-AO13</f>
         <v>-792.29999999999973</v>
       </c>
       <c r="AP14" s="8">
-        <f t="shared" ref="AP14" si="116">AP9-AP13</f>
+        <f t="shared" ref="AP14" si="114">AP9-AP13</f>
         <v>-218.30000000000018</v>
       </c>
       <c r="AQ14" s="8">
-        <f t="shared" ref="AQ14" si="117">AQ9-AQ13</f>
-        <v>-106.75249000000076</v>
+        <f t="shared" ref="AQ14" si="115">AQ9-AQ13</f>
+        <v>-84.781599999999344</v>
       </c>
       <c r="AR14" s="8">
-        <f t="shared" ref="AR14" si="118">AR9-AR13</f>
-        <v>152.86350119999952</v>
+        <f t="shared" ref="AR14" si="116">AR9-AR13</f>
+        <v>200.61517140000024</v>
       </c>
       <c r="AS14" s="8">
-        <f t="shared" ref="AS14" si="119">AS9-AS13</f>
-        <v>332.3549061359995</v>
+        <f t="shared" ref="AS14" si="117">AS9-AS13</f>
+        <v>382.05744401399988</v>
       </c>
       <c r="AT14" s="8">
-        <f t="shared" ref="AT14" si="120">AT9-AT13</f>
-        <v>483.90033791255973</v>
+        <f t="shared" ref="AT14" si="118">AT9-AT13</f>
+        <v>535.73199635495985</v>
       </c>
       <c r="AU14" s="8">
-        <f t="shared" ref="AU14" si="121">AU9-AU13</f>
-        <v>537.62344558356745</v>
+        <f t="shared" ref="AU14" si="119">AU9-AU13</f>
+        <v>591.06594826541823</v>
       </c>
       <c r="AV14" s="8">
-        <f t="shared" ref="AV14:AW14" si="122">AV9-AV13</f>
-        <v>575.11786989179609</v>
+        <f t="shared" ref="AV14:AW14" si="120">AV9-AV13</f>
+        <v>629.8779239548544</v>
       </c>
       <c r="AW14" s="8">
-        <f t="shared" si="122"/>
-        <v>595.88624971408353</v>
+        <f t="shared" si="120"/>
+        <v>651.57877110241225</v>
       </c>
       <c r="AX14" s="8">
-        <f t="shared" ref="AX14:BA14" si="123">AX9-AX13</f>
-        <v>617.16265735706111</v>
+        <f t="shared" ref="AX14:BA14" si="121">AX9-AX13</f>
+        <v>673.80466807960511</v>
       </c>
       <c r="AY14" s="8">
-        <f t="shared" si="123"/>
-        <v>638.95817997938548</v>
+        <f t="shared" si="121"/>
+        <v>696.56702621189334</v>
       </c>
       <c r="AZ14" s="8">
-        <f t="shared" si="123"/>
-        <v>661.28413574890828</v>
+        <f t="shared" si="121"/>
+        <v>719.87749415453436</v>
       </c>
       <c r="BA14" s="8">
-        <f t="shared" si="123"/>
-        <v>684.15207855551989</v>
+        <f t="shared" si="121"/>
+        <v>743.74796273021229</v>
       </c>
     </row>
     <row r="15" spans="2:53" x14ac:dyDescent="0.3">
@@ -3413,15 +3406,14 @@
         <v>-17.2</v>
       </c>
       <c r="AF15" s="5">
-        <f t="shared" ref="AF15:AH15" si="124">AB15*1.01</f>
-        <v>-28.381</v>
+        <v>-28</v>
       </c>
       <c r="AG15" s="5">
-        <f t="shared" si="124"/>
+        <f t="shared" ref="AF15:AH15" si="122">AC15*1.01</f>
         <v>-31.209</v>
       </c>
       <c r="AH15" s="5">
-        <f t="shared" si="124"/>
+        <f t="shared" si="122"/>
         <v>-13.433000000000002</v>
       </c>
       <c r="AJ15" s="5">
@@ -3454,47 +3446,47 @@
       </c>
       <c r="AQ15" s="5">
         <f>SUM(AE15:AH15)</f>
-        <v>-90.223000000000013</v>
+        <v>-89.842000000000013</v>
       </c>
       <c r="AR15" s="5">
-        <f t="shared" ref="AR15:BA15" si="125">AQ15*1.03</f>
-        <v>-92.929690000000022</v>
+        <f t="shared" ref="AR15:BA15" si="123">AQ15*1.03</f>
+        <v>-92.537260000000018</v>
       </c>
       <c r="AS15" s="5">
-        <f t="shared" si="125"/>
-        <v>-95.717580700000028</v>
+        <f t="shared" si="123"/>
+        <v>-95.313377800000026</v>
       </c>
       <c r="AT15" s="5">
-        <f t="shared" si="125"/>
-        <v>-98.589108121000038</v>
+        <f t="shared" si="123"/>
+        <v>-98.172779134000024</v>
       </c>
       <c r="AU15" s="5">
-        <f t="shared" si="125"/>
-        <v>-101.54678136463004</v>
+        <f t="shared" si="123"/>
+        <v>-101.11796250802003</v>
       </c>
       <c r="AV15" s="5">
-        <f t="shared" si="125"/>
-        <v>-104.59318480556894</v>
+        <f t="shared" si="123"/>
+        <v>-104.15150138326064</v>
       </c>
       <c r="AW15" s="5">
-        <f t="shared" si="125"/>
-        <v>-107.73098034973602</v>
+        <f t="shared" si="123"/>
+        <v>-107.27604642475846</v>
       </c>
       <c r="AX15" s="5">
-        <f t="shared" si="125"/>
-        <v>-110.9629097602281</v>
+        <f t="shared" si="123"/>
+        <v>-110.49432781750122</v>
       </c>
       <c r="AY15" s="5">
-        <f t="shared" si="125"/>
-        <v>-114.29179705303494</v>
+        <f t="shared" si="123"/>
+        <v>-113.80915765202626</v>
       </c>
       <c r="AZ15" s="5">
-        <f t="shared" si="125"/>
-        <v>-117.72055096462599</v>
+        <f t="shared" si="123"/>
+        <v>-117.22343238158705</v>
       </c>
       <c r="BA15" s="5">
-        <f t="shared" si="125"/>
-        <v>-121.25216749356477</v>
+        <f t="shared" si="123"/>
+        <v>-120.74013535303466</v>
       </c>
     </row>
     <row r="16" spans="2:53" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3502,204 +3494,204 @@
         <v>34</v>
       </c>
       <c r="C16" s="8">
-        <f t="shared" ref="C16:L16" si="126">C14-C15</f>
+        <f t="shared" ref="C16:L16" si="124">C14-C15</f>
         <v>-6.5000000000000053</v>
       </c>
       <c r="D16" s="8">
+        <f t="shared" si="124"/>
+        <v>0.20000000000000573</v>
+      </c>
+      <c r="E16" s="8">
+        <f t="shared" si="124"/>
+        <v>-9.7000000000000259</v>
+      </c>
+      <c r="F16" s="8">
+        <f t="shared" si="124"/>
+        <v>6.699999999999986</v>
+      </c>
+      <c r="G16" s="8">
+        <f t="shared" si="124"/>
+        <v>-9.8000000000000167</v>
+      </c>
+      <c r="H16" s="8">
+        <f t="shared" si="124"/>
+        <v>-9.8600000000000065</v>
+      </c>
+      <c r="I16" s="8">
+        <f t="shared" si="124"/>
+        <v>-24.700000000000017</v>
+      </c>
+      <c r="J16" s="8">
+        <f t="shared" si="124"/>
+        <v>-15.999999999999954</v>
+      </c>
+      <c r="K16" s="8">
+        <f t="shared" si="124"/>
+        <v>-54.6</v>
+      </c>
+      <c r="L16" s="8">
+        <f t="shared" si="124"/>
+        <v>-42.599999999999987</v>
+      </c>
+      <c r="M16" s="8">
+        <f t="shared" ref="M16:AL16" si="125">M14-M15</f>
+        <v>12.20000000000004</v>
+      </c>
+      <c r="N16" s="8">
+        <f t="shared" si="125"/>
+        <v>66.649999999999991</v>
+      </c>
+      <c r="O16" s="8">
+        <f t="shared" si="125"/>
+        <v>75.500000000000071</v>
+      </c>
+      <c r="P16" s="8">
+        <f t="shared" ref="P16:Q16" si="126">P14-P15</f>
+        <v>69.899999999999906</v>
+      </c>
+      <c r="Q16" s="8">
         <f t="shared" si="126"/>
-        <v>0.20000000000000573</v>
-      </c>
-      <c r="E16" s="8">
-        <f t="shared" si="126"/>
-        <v>-9.7000000000000259</v>
-      </c>
-      <c r="F16" s="8">
-        <f t="shared" si="126"/>
-        <v>6.699999999999986</v>
-      </c>
-      <c r="G16" s="8">
-        <f t="shared" si="126"/>
-        <v>-9.8000000000000167</v>
-      </c>
-      <c r="H16" s="8">
-        <f t="shared" si="126"/>
-        <v>-9.8600000000000065</v>
-      </c>
-      <c r="I16" s="8">
-        <f t="shared" si="126"/>
-        <v>-24.700000000000017</v>
-      </c>
-      <c r="J16" s="8">
-        <f t="shared" si="126"/>
-        <v>-15.999999999999954</v>
-      </c>
-      <c r="K16" s="8">
-        <f t="shared" si="126"/>
-        <v>-54.6</v>
-      </c>
-      <c r="L16" s="8">
-        <f t="shared" si="126"/>
-        <v>-42.599999999999987</v>
-      </c>
-      <c r="M16" s="8">
-        <f t="shared" ref="M16:AL16" si="127">M14-M15</f>
-        <v>12.20000000000004</v>
-      </c>
-      <c r="N16" s="8">
+        <v>68.599999999999952</v>
+      </c>
+      <c r="R16" s="8">
+        <f t="shared" si="125"/>
+        <v>22.599999999999955</v>
+      </c>
+      <c r="S16" s="8">
+        <f t="shared" ref="S16:T16" si="127">S14-S15</f>
+        <v>-24.200000000000056</v>
+      </c>
+      <c r="T16" s="8">
         <f t="shared" si="127"/>
-        <v>66.649999999999991</v>
-      </c>
-      <c r="O16" s="8">
-        <f t="shared" si="127"/>
-        <v>75.500000000000071</v>
-      </c>
-      <c r="P16" s="8">
-        <f t="shared" ref="P16:Q16" si="128">P14-P15</f>
-        <v>69.899999999999906</v>
-      </c>
-      <c r="Q16" s="8">
-        <f t="shared" si="128"/>
-        <v>68.599999999999952</v>
-      </c>
-      <c r="R16" s="8">
-        <f t="shared" si="127"/>
-        <v>22.599999999999955</v>
-      </c>
-      <c r="S16" s="8">
-        <f t="shared" ref="S16:T16" si="129">S14-S15</f>
-        <v>-24.200000000000056</v>
-      </c>
-      <c r="T16" s="8">
-        <f t="shared" si="129"/>
         <v>-109.80000000000005</v>
       </c>
       <c r="U16" s="8">
-        <f t="shared" ref="U16" si="130">U14-U15</f>
+        <f t="shared" ref="U16" si="128">U14-U15</f>
         <v>-120.29999999999994</v>
       </c>
       <c r="V16" s="8">
-        <f t="shared" ref="V16" si="131">V14-V15</f>
+        <f t="shared" ref="V16" si="129">V14-V15</f>
         <v>-238.2000000000001</v>
       </c>
       <c r="W16" s="8">
-        <f t="shared" ref="W16:X16" si="132">W14-W15</f>
+        <f t="shared" ref="W16:X16" si="130">W14-W15</f>
         <v>-189.50000000000006</v>
       </c>
       <c r="X16" s="8">
+        <f t="shared" si="130"/>
+        <v>-105.90000000000003</v>
+      </c>
+      <c r="Y16" s="8">
+        <f t="shared" ref="Y16" si="131">Y14-Y15</f>
+        <v>-326.89999999999998</v>
+      </c>
+      <c r="Z16" s="8">
+        <f t="shared" ref="Z16:AH16" si="132">Z14-Z15</f>
+        <v>-76.40000000000002</v>
+      </c>
+      <c r="AA16" s="8">
         <f t="shared" si="132"/>
-        <v>-105.90000000000003</v>
-      </c>
-      <c r="Y16" s="8">
-        <f t="shared" ref="Y16" si="133">Y14-Y15</f>
-        <v>-326.89999999999998</v>
-      </c>
-      <c r="Z16" s="8">
-        <f t="shared" ref="Z16:AH16" si="134">Z14-Z15</f>
-        <v>-76.40000000000002</v>
-      </c>
-      <c r="AA16" s="8">
-        <f t="shared" si="134"/>
         <v>-46.000000000000057</v>
       </c>
       <c r="AB16" s="8">
-        <f t="shared" si="134"/>
+        <f t="shared" si="132"/>
         <v>-43.30000000000009</v>
       </c>
       <c r="AC16" s="8">
-        <f t="shared" si="134"/>
+        <f t="shared" si="132"/>
         <v>-4.7999999999998195</v>
       </c>
       <c r="AD16" s="8">
-        <f t="shared" si="134"/>
+        <f t="shared" si="132"/>
         <v>-25.899999999999931</v>
       </c>
       <c r="AE16" s="8">
-        <f t="shared" si="134"/>
+        <f t="shared" si="132"/>
         <v>-40.500000000000043</v>
       </c>
       <c r="AF16" s="8">
-        <f t="shared" si="134"/>
-        <v>-11.926189999999991</v>
+        <f t="shared" si="132"/>
+        <v>4.6999999999999318</v>
       </c>
       <c r="AG16" s="8">
-        <f t="shared" si="134"/>
-        <v>17.913920000000129</v>
+        <f t="shared" si="132"/>
+        <v>18.868719999999879</v>
       </c>
       <c r="AH16" s="8">
-        <f t="shared" si="134"/>
-        <v>17.982780000000055</v>
+        <f t="shared" si="132"/>
+        <v>21.991679999999981</v>
       </c>
       <c r="AJ16" s="8">
-        <f t="shared" si="127"/>
+        <f t="shared" si="125"/>
         <v>-9.3000000000000114</v>
       </c>
       <c r="AK16" s="8">
-        <f t="shared" si="127"/>
+        <f t="shared" si="125"/>
         <v>-60.359999999999907</v>
       </c>
       <c r="AL16" s="8">
-        <f t="shared" si="127"/>
+        <f t="shared" si="125"/>
         <v>-18.350000000000044</v>
       </c>
       <c r="AM16" s="8">
-        <f t="shared" ref="AM16" si="135">AM14-AM15</f>
+        <f t="shared" ref="AM16" si="133">AM14-AM15</f>
         <v>236.59999999999977</v>
       </c>
       <c r="AN16" s="8">
-        <f t="shared" ref="AN16" si="136">AN14-AN15</f>
+        <f t="shared" ref="AN16" si="134">AN14-AN15</f>
         <v>-492.50000000000034</v>
       </c>
       <c r="AO16" s="8">
-        <f t="shared" ref="AO16" si="137">AO14-AO15</f>
+        <f t="shared" ref="AO16" si="135">AO14-AO15</f>
         <v>-698.6999999999997</v>
       </c>
       <c r="AP16" s="8">
-        <f t="shared" ref="AP16" si="138">AP14-AP15</f>
+        <f t="shared" ref="AP16" si="136">AP14-AP15</f>
         <v>-120.00000000000018</v>
       </c>
       <c r="AQ16" s="8">
-        <f t="shared" ref="AQ16" si="139">AQ14-AQ15</f>
-        <v>-16.529490000000749</v>
+        <f t="shared" ref="AQ16" si="137">AQ14-AQ15</f>
+        <v>5.0604000000006693</v>
       </c>
       <c r="AR16" s="8">
-        <f t="shared" ref="AR16" si="140">AR14-AR15</f>
-        <v>245.79319119999954</v>
+        <f t="shared" ref="AR16" si="138">AR14-AR15</f>
+        <v>293.15243140000024</v>
       </c>
       <c r="AS16" s="8">
-        <f t="shared" ref="AS16" si="141">AS14-AS15</f>
-        <v>428.07248683599954</v>
+        <f t="shared" ref="AS16" si="139">AS14-AS15</f>
+        <v>477.3708218139999</v>
       </c>
       <c r="AT16" s="8">
-        <f t="shared" ref="AT16" si="142">AT14-AT15</f>
-        <v>582.48944603355972</v>
+        <f t="shared" ref="AT16" si="140">AT14-AT15</f>
+        <v>633.9047754889599</v>
       </c>
       <c r="AU16" s="8">
-        <f t="shared" ref="AU16" si="143">AU14-AU15</f>
-        <v>639.17022694819752</v>
+        <f t="shared" ref="AU16" si="141">AU14-AU15</f>
+        <v>692.18391077343824</v>
       </c>
       <c r="AV16" s="8">
-        <f t="shared" ref="AV16:AW16" si="144">AV14-AV15</f>
-        <v>679.71105469736506</v>
+        <f t="shared" ref="AV16:AW16" si="142">AV14-AV15</f>
+        <v>734.02942533811506</v>
       </c>
       <c r="AW16" s="8">
-        <f t="shared" si="144"/>
-        <v>703.61723006381953</v>
+        <f t="shared" si="142"/>
+        <v>758.85481752717067</v>
       </c>
       <c r="AX16" s="8">
-        <f t="shared" ref="AX16:BA16" si="145">AX14-AX15</f>
-        <v>728.12556711728917</v>
+        <f t="shared" ref="AX16:BA16" si="143">AX14-AX15</f>
+        <v>784.29899589710635</v>
       </c>
       <c r="AY16" s="8">
-        <f t="shared" si="145"/>
-        <v>753.24997703242047</v>
+        <f t="shared" si="143"/>
+        <v>810.37618386391955</v>
       </c>
       <c r="AZ16" s="8">
-        <f t="shared" si="145"/>
-        <v>779.00468671353428</v>
+        <f t="shared" si="143"/>
+        <v>837.10092653612139</v>
       </c>
       <c r="BA16" s="8">
-        <f t="shared" si="145"/>
-        <v>805.40424604908469</v>
+        <f t="shared" si="143"/>
+        <v>864.488098083247</v>
       </c>
     </row>
     <row r="17" spans="2:163" x14ac:dyDescent="0.3">
@@ -3794,16 +3786,15 @@
         <v>-13.1</v>
       </c>
       <c r="AF17" s="5">
-        <f t="shared" ref="AF17:AH17" si="146">AF16*0.2</f>
-        <v>-2.3852379999999984</v>
+        <v>-5.8</v>
       </c>
       <c r="AG17" s="5">
-        <f t="shared" si="146"/>
-        <v>3.5827840000000259</v>
+        <f t="shared" ref="AF17:AH17" si="144">AG16*0.2</f>
+        <v>3.7737439999999758</v>
       </c>
       <c r="AH17" s="5">
-        <f t="shared" si="146"/>
-        <v>3.5965560000000112</v>
+        <f t="shared" si="144"/>
+        <v>4.398335999999996</v>
       </c>
       <c r="AJ17" s="5">
         <f>SUM(C17:F17)</f>
@@ -3835,47 +3826,47 @@
       </c>
       <c r="AQ17" s="5">
         <f>SUM(AE17:AH17)</f>
-        <v>-8.3058979999999636</v>
+        <v>-10.727920000000026</v>
       </c>
       <c r="AR17" s="5">
         <f>AR16*0.2</f>
-        <v>49.15863823999991</v>
+        <v>58.630486280000049</v>
       </c>
       <c r="AS17" s="5">
-        <f t="shared" ref="AS17:AV17" si="147">AS16*0.2</f>
-        <v>85.614497367199917</v>
+        <f t="shared" ref="AS17:AV17" si="145">AS16*0.2</f>
+        <v>95.474164362799982</v>
       </c>
       <c r="AT17" s="5">
-        <f t="shared" si="147"/>
-        <v>116.49788920671195</v>
+        <f t="shared" si="145"/>
+        <v>126.78095509779199</v>
       </c>
       <c r="AU17" s="5">
-        <f t="shared" si="147"/>
-        <v>127.83404538963951</v>
+        <f t="shared" si="145"/>
+        <v>138.43678215468765</v>
       </c>
       <c r="AV17" s="5">
-        <f t="shared" si="147"/>
-        <v>135.94221093947303</v>
+        <f t="shared" si="145"/>
+        <v>146.80588506762302</v>
       </c>
       <c r="AW17" s="5">
-        <f t="shared" ref="AW17:BA17" si="148">AW16*0.2</f>
-        <v>140.7234460127639</v>
+        <f t="shared" ref="AW17:BA17" si="146">AW16*0.2</f>
+        <v>151.77096350543414</v>
       </c>
       <c r="AX17" s="5">
-        <f t="shared" si="148"/>
-        <v>145.62511342345783</v>
+        <f t="shared" si="146"/>
+        <v>156.85979917942129</v>
       </c>
       <c r="AY17" s="5">
-        <f t="shared" si="148"/>
-        <v>150.64999540648409</v>
+        <f t="shared" si="146"/>
+        <v>162.07523677278391</v>
       </c>
       <c r="AZ17" s="5">
-        <f t="shared" si="148"/>
-        <v>155.80093734270687</v>
+        <f t="shared" si="146"/>
+        <v>167.4201853072243</v>
       </c>
       <c r="BA17" s="5">
-        <f t="shared" si="148"/>
-        <v>161.08084920981696</v>
+        <f t="shared" si="146"/>
+        <v>172.89761961664942</v>
       </c>
     </row>
     <row r="18" spans="2:163" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3883,644 +3874,644 @@
         <v>36</v>
       </c>
       <c r="C18" s="8">
-        <f t="shared" ref="C18:L18" si="149">C16-C17</f>
+        <f t="shared" ref="C18:L18" si="147">C16-C17</f>
         <v>-6.600000000000005</v>
       </c>
       <c r="D18" s="8">
+        <f t="shared" si="147"/>
+        <v>0.60000000000000575</v>
+      </c>
+      <c r="E18" s="8">
+        <f t="shared" si="147"/>
+        <v>-9.5000000000000266</v>
+      </c>
+      <c r="F18" s="8">
+        <f t="shared" si="147"/>
+        <v>6.7999999999999856</v>
+      </c>
+      <c r="G18" s="8">
+        <f t="shared" si="147"/>
+        <v>-9.7000000000000171</v>
+      </c>
+      <c r="H18" s="8">
+        <f t="shared" si="147"/>
+        <v>-9.4600000000000062</v>
+      </c>
+      <c r="I18" s="8">
+        <f t="shared" si="147"/>
+        <v>-24.600000000000016</v>
+      </c>
+      <c r="J18" s="8">
+        <f t="shared" si="147"/>
+        <v>-15.599999999999953</v>
+      </c>
+      <c r="K18" s="8">
+        <f t="shared" si="147"/>
+        <v>-54.4</v>
+      </c>
+      <c r="L18" s="8">
+        <f t="shared" si="147"/>
+        <v>-43.099999999999987</v>
+      </c>
+      <c r="M18" s="8">
+        <f t="shared" ref="M18:AL18" si="148">M16-M17</f>
+        <v>13.20000000000004</v>
+      </c>
+      <c r="N18" s="8">
+        <f t="shared" si="148"/>
+        <v>67.349999999999994</v>
+      </c>
+      <c r="O18" s="8">
+        <f t="shared" ref="O18:R18" si="149">O16-O17</f>
+        <v>76.300000000000068</v>
+      </c>
+      <c r="P18" s="8">
+        <f t="shared" ref="P18:Q18" si="150">P16-P17</f>
+        <v>73.499999999999901</v>
+      </c>
+      <c r="Q18" s="8">
+        <f t="shared" si="150"/>
+        <v>68.899999999999949</v>
+      </c>
+      <c r="R18" s="8">
         <f t="shared" si="149"/>
-        <v>0.60000000000000575</v>
-      </c>
-      <c r="E18" s="8">
-        <f t="shared" si="149"/>
-        <v>-9.5000000000000266</v>
-      </c>
-      <c r="F18" s="8">
-        <f t="shared" si="149"/>
-        <v>6.7999999999999856</v>
-      </c>
-      <c r="G18" s="8">
-        <f t="shared" si="149"/>
-        <v>-9.7000000000000171</v>
-      </c>
-      <c r="H18" s="8">
-        <f t="shared" si="149"/>
-        <v>-9.4600000000000062</v>
-      </c>
-      <c r="I18" s="8">
-        <f t="shared" si="149"/>
-        <v>-24.600000000000016</v>
-      </c>
-      <c r="J18" s="8">
-        <f t="shared" si="149"/>
-        <v>-15.599999999999953</v>
-      </c>
-      <c r="K18" s="8">
-        <f t="shared" si="149"/>
-        <v>-54.4</v>
-      </c>
-      <c r="L18" s="8">
-        <f t="shared" si="149"/>
-        <v>-43.099999999999987</v>
-      </c>
-      <c r="M18" s="8">
-        <f t="shared" ref="M18:AL18" si="150">M16-M17</f>
-        <v>13.20000000000004</v>
-      </c>
-      <c r="N18" s="8">
-        <f t="shared" si="150"/>
-        <v>67.349999999999994</v>
-      </c>
-      <c r="O18" s="8">
-        <f t="shared" ref="O18:R18" si="151">O16-O17</f>
-        <v>76.300000000000068</v>
-      </c>
-      <c r="P18" s="8">
-        <f t="shared" ref="P18:Q18" si="152">P16-P17</f>
-        <v>73.499999999999901</v>
-      </c>
-      <c r="Q18" s="8">
-        <f t="shared" si="152"/>
-        <v>68.899999999999949</v>
-      </c>
-      <c r="R18" s="8">
+        <v>23.699999999999957</v>
+      </c>
+      <c r="S18" s="8">
+        <f t="shared" ref="S18:T18" si="151">S16-S17</f>
+        <v>-26.400000000000055</v>
+      </c>
+      <c r="T18" s="8">
         <f t="shared" si="151"/>
-        <v>23.699999999999957</v>
-      </c>
-      <c r="S18" s="8">
-        <f t="shared" ref="S18:T18" si="153">S16-S17</f>
-        <v>-26.400000000000055</v>
-      </c>
-      <c r="T18" s="8">
-        <f t="shared" si="153"/>
         <v>-112.40000000000005</v>
       </c>
       <c r="U18" s="8">
-        <f t="shared" ref="U18" si="154">U16-U17</f>
+        <f t="shared" ref="U18" si="152">U16-U17</f>
         <v>-122.29999999999994</v>
       </c>
       <c r="V18" s="8">
-        <f t="shared" ref="V18" si="155">V16-V17</f>
+        <f t="shared" ref="V18" si="153">V16-V17</f>
         <v>-237.2000000000001</v>
       </c>
       <c r="W18" s="8">
-        <f t="shared" ref="W18:X18" si="156">W16-W17</f>
+        <f t="shared" ref="W18:X18" si="154">W16-W17</f>
         <v>-193.10000000000005</v>
       </c>
       <c r="X18" s="8">
+        <f t="shared" si="154"/>
+        <v>-107.50000000000003</v>
+      </c>
+      <c r="Y18" s="8">
+        <f t="shared" ref="Y18" si="155">Y16-Y17</f>
+        <v>-330.09999999999997</v>
+      </c>
+      <c r="Z18" s="8">
+        <f t="shared" ref="Z18:AA18" si="156">Z16-Z17</f>
+        <v>-78.200000000000017</v>
+      </c>
+      <c r="AA18" s="8">
         <f t="shared" si="156"/>
-        <v>-107.50000000000003</v>
-      </c>
-      <c r="Y18" s="8">
-        <f t="shared" ref="Y18" si="157">Y16-Y17</f>
-        <v>-330.09999999999997</v>
-      </c>
-      <c r="Z18" s="8">
-        <f t="shared" ref="Z18:AA18" si="158">Z16-Z17</f>
-        <v>-78.200000000000017</v>
-      </c>
-      <c r="AA18" s="8">
+        <v>-50.800000000000054</v>
+      </c>
+      <c r="AB18" s="8">
+        <f t="shared" ref="AB18:AD18" si="157">AB16-AB17</f>
+        <v>-34.100000000000094</v>
+      </c>
+      <c r="AC18" s="8">
+        <f t="shared" si="157"/>
+        <v>-8.8999999999998192</v>
+      </c>
+      <c r="AD18" s="8">
+        <f t="shared" si="157"/>
+        <v>-35.59999999999993</v>
+      </c>
+      <c r="AE18" s="8">
+        <f t="shared" ref="AE18:AH18" si="158">AE16-AE17</f>
+        <v>-27.400000000000041</v>
+      </c>
+      <c r="AF18" s="8">
         <f t="shared" si="158"/>
-        <v>-50.800000000000054</v>
-      </c>
-      <c r="AB18" s="8">
-        <f t="shared" ref="AB18:AD18" si="159">AB16-AB17</f>
-        <v>-34.100000000000094</v>
-      </c>
-      <c r="AC18" s="8">
-        <f t="shared" si="159"/>
-        <v>-8.8999999999998192</v>
-      </c>
-      <c r="AD18" s="8">
-        <f t="shared" si="159"/>
-        <v>-35.59999999999993</v>
-      </c>
-      <c r="AE18" s="8">
-        <f t="shared" ref="AE18:AH18" si="160">AE16-AE17</f>
-        <v>-27.400000000000041</v>
-      </c>
-      <c r="AF18" s="8">
-        <f t="shared" si="160"/>
-        <v>-9.5409519999999937</v>
+        <v>10.499999999999932</v>
       </c>
       <c r="AG18" s="8">
-        <f t="shared" si="160"/>
-        <v>14.331136000000104</v>
+        <f t="shared" si="158"/>
+        <v>15.094975999999903</v>
       </c>
       <c r="AH18" s="8">
-        <f t="shared" si="160"/>
-        <v>14.386224000000045</v>
+        <f t="shared" si="158"/>
+        <v>17.593343999999984</v>
       </c>
       <c r="AJ18" s="8">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>-8.7000000000000117</v>
       </c>
       <c r="AK18" s="8">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>-59.359999999999907</v>
       </c>
       <c r="AL18" s="8">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>-16.950000000000045</v>
       </c>
       <c r="AM18" s="8">
-        <f t="shared" ref="AM18" si="161">AM16-AM17</f>
+        <f t="shared" ref="AM18" si="159">AM16-AM17</f>
         <v>242.39999999999978</v>
       </c>
       <c r="AN18" s="8">
-        <f t="shared" ref="AN18" si="162">AN16-AN17</f>
+        <f t="shared" ref="AN18" si="160">AN16-AN17</f>
         <v>-498.30000000000035</v>
       </c>
       <c r="AO18" s="8">
-        <f t="shared" ref="AO18" si="163">AO16-AO17</f>
+        <f t="shared" ref="AO18" si="161">AO16-AO17</f>
         <v>-708.89999999999975</v>
       </c>
       <c r="AP18" s="8">
-        <f t="shared" ref="AP18" si="164">AP16-AP17</f>
+        <f t="shared" ref="AP18" si="162">AP16-AP17</f>
         <v>-129.40000000000018</v>
       </c>
       <c r="AQ18" s="8">
-        <f t="shared" ref="AQ18" si="165">AQ16-AQ17</f>
-        <v>-8.2235920000007852</v>
+        <f t="shared" ref="AQ18" si="163">AQ16-AQ17</f>
+        <v>15.788320000000695</v>
       </c>
       <c r="AR18" s="8">
-        <f t="shared" ref="AR18" si="166">AR16-AR17</f>
-        <v>196.63455295999964</v>
+        <f t="shared" ref="AR18" si="164">AR16-AR17</f>
+        <v>234.5219451200002</v>
       </c>
       <c r="AS18" s="8">
-        <f t="shared" ref="AS18" si="167">AS16-AS17</f>
-        <v>342.45798946879961</v>
+        <f t="shared" ref="AS18" si="165">AS16-AS17</f>
+        <v>381.89665745119993</v>
       </c>
       <c r="AT18" s="8">
-        <f t="shared" ref="AT18" si="168">AT16-AT17</f>
-        <v>465.99155682684778</v>
+        <f t="shared" ref="AT18" si="166">AT16-AT17</f>
+        <v>507.1238203911679</v>
       </c>
       <c r="AU18" s="8">
-        <f t="shared" ref="AU18" si="169">AU16-AU17</f>
-        <v>511.336181558558</v>
+        <f t="shared" ref="AU18" si="167">AU16-AU17</f>
+        <v>553.74712861875059</v>
       </c>
       <c r="AV18" s="8">
-        <f t="shared" ref="AV18:AW18" si="170">AV16-AV17</f>
-        <v>543.768843757892</v>
+        <f t="shared" ref="AV18:AW18" si="168">AV16-AV17</f>
+        <v>587.22354027049209</v>
       </c>
       <c r="AW18" s="8">
-        <f t="shared" si="170"/>
-        <v>562.8937840510556</v>
+        <f t="shared" si="168"/>
+        <v>607.08385402173656</v>
       </c>
       <c r="AX18" s="8">
-        <f t="shared" ref="AX18:BA18" si="171">AX16-AX17</f>
-        <v>582.50045369383133</v>
+        <f t="shared" ref="AX18:BA18" si="169">AX16-AX17</f>
+        <v>627.43919671768504</v>
       </c>
       <c r="AY18" s="8">
-        <f t="shared" si="171"/>
-        <v>602.59998162593638</v>
+        <f t="shared" si="169"/>
+        <v>648.30094709113564</v>
       </c>
       <c r="AZ18" s="8">
-        <f t="shared" si="171"/>
-        <v>623.20374937082738</v>
+        <f t="shared" si="169"/>
+        <v>669.68074122889709</v>
       </c>
       <c r="BA18" s="8">
-        <f t="shared" si="171"/>
-        <v>644.32339683926773</v>
+        <f t="shared" si="169"/>
+        <v>691.59047846659757</v>
       </c>
       <c r="BB18" s="1">
         <f>BA18*(1+$BD$25)</f>
-        <v>637.8801628708751</v>
+        <v>684.67457368193163</v>
       </c>
       <c r="BC18" s="1">
-        <f t="shared" ref="BC18:DN18" si="172">BB18*(1+$BD$25)</f>
-        <v>631.50136124216635</v>
+        <f t="shared" ref="BC18:DN18" si="170">BB18*(1+$BD$25)</f>
+        <v>677.82782794511229</v>
       </c>
       <c r="BD18" s="1">
-        <f t="shared" si="172"/>
-        <v>625.18634762974466</v>
+        <f t="shared" si="170"/>
+        <v>671.04954966566117</v>
       </c>
       <c r="BE18" s="1">
-        <f t="shared" si="172"/>
-        <v>618.93448415344722</v>
+        <f t="shared" si="170"/>
+        <v>664.33905416900461</v>
       </c>
       <c r="BF18" s="1">
-        <f t="shared" si="172"/>
-        <v>612.74513931191279</v>
+        <f t="shared" si="170"/>
+        <v>657.69566362731462</v>
       </c>
       <c r="BG18" s="1">
-        <f t="shared" si="172"/>
-        <v>606.61768791879365</v>
+        <f t="shared" si="170"/>
+        <v>651.11870699104145</v>
       </c>
       <c r="BH18" s="1">
-        <f t="shared" si="172"/>
-        <v>600.55151103960566</v>
+        <f t="shared" si="170"/>
+        <v>644.60751992113103</v>
       </c>
       <c r="BI18" s="1">
-        <f t="shared" si="172"/>
-        <v>594.54599592920954</v>
+        <f t="shared" si="170"/>
+        <v>638.16144472191968</v>
       </c>
       <c r="BJ18" s="1">
-        <f t="shared" si="172"/>
-        <v>588.60053596991747</v>
+        <f t="shared" si="170"/>
+        <v>631.77983027470043</v>
       </c>
       <c r="BK18" s="1">
-        <f t="shared" si="172"/>
-        <v>582.71453061021828</v>
+        <f t="shared" si="170"/>
+        <v>625.46203197195337</v>
       </c>
       <c r="BL18" s="1">
-        <f t="shared" si="172"/>
-        <v>576.88738530411604</v>
+        <f t="shared" si="170"/>
+        <v>619.20741165223387</v>
       </c>
       <c r="BM18" s="1">
-        <f t="shared" si="172"/>
-        <v>571.11851145107482</v>
+        <f t="shared" si="170"/>
+        <v>613.01533753571152</v>
       </c>
       <c r="BN18" s="1">
-        <f t="shared" si="172"/>
-        <v>565.4073263365641</v>
+        <f t="shared" si="170"/>
+        <v>606.88518416035436</v>
       </c>
       <c r="BO18" s="1">
-        <f t="shared" si="172"/>
-        <v>559.75325307319849</v>
+        <f t="shared" si="170"/>
+        <v>600.81633231875082</v>
       </c>
       <c r="BP18" s="1">
-        <f t="shared" si="172"/>
-        <v>554.1557205424665</v>
+        <f t="shared" si="170"/>
+        <v>594.80816899556328</v>
       </c>
       <c r="BQ18" s="1">
-        <f t="shared" si="172"/>
-        <v>548.61416333704187</v>
+        <f t="shared" si="170"/>
+        <v>588.86008730560764</v>
       </c>
       <c r="BR18" s="1">
-        <f t="shared" si="172"/>
-        <v>543.12802170367149</v>
+        <f t="shared" si="170"/>
+        <v>582.9714864325515</v>
       </c>
       <c r="BS18" s="1">
-        <f t="shared" si="172"/>
-        <v>537.69674148663478</v>
+        <f t="shared" si="170"/>
+        <v>577.14177156822598</v>
       </c>
       <c r="BT18" s="1">
-        <f t="shared" si="172"/>
-        <v>532.31977407176839</v>
+        <f t="shared" si="170"/>
+        <v>571.37035385254376</v>
       </c>
       <c r="BU18" s="1">
-        <f t="shared" si="172"/>
-        <v>526.99657633105073</v>
+        <f t="shared" si="170"/>
+        <v>565.65665031401829</v>
       </c>
       <c r="BV18" s="1">
-        <f t="shared" si="172"/>
-        <v>521.72661056774018</v>
+        <f t="shared" si="170"/>
+        <v>560.0000838108781</v>
       </c>
       <c r="BW18" s="1">
-        <f t="shared" si="172"/>
-        <v>516.50934446206281</v>
+        <f t="shared" si="170"/>
+        <v>554.40008297276927</v>
       </c>
       <c r="BX18" s="1">
-        <f t="shared" si="172"/>
-        <v>511.34425101744216</v>
+        <f t="shared" si="170"/>
+        <v>548.85608214304159</v>
       </c>
       <c r="BY18" s="1">
-        <f t="shared" si="172"/>
-        <v>506.23080850726774</v>
+        <f t="shared" si="170"/>
+        <v>543.36752132161121</v>
       </c>
       <c r="BZ18" s="1">
-        <f t="shared" si="172"/>
-        <v>501.16850042219505</v>
+        <f t="shared" si="170"/>
+        <v>537.93384610839507</v>
       </c>
       <c r="CA18" s="1">
-        <f t="shared" si="172"/>
-        <v>496.15681541797312</v>
+        <f t="shared" si="170"/>
+        <v>532.55450764731108</v>
       </c>
       <c r="CB18" s="1">
-        <f t="shared" si="172"/>
-        <v>491.19524726379336</v>
+        <f t="shared" si="170"/>
+        <v>527.22896257083801</v>
       </c>
       <c r="CC18" s="1">
-        <f t="shared" si="172"/>
-        <v>486.28329479115541</v>
+        <f t="shared" si="170"/>
+        <v>521.95667294512964</v>
       </c>
       <c r="CD18" s="1">
-        <f t="shared" si="172"/>
-        <v>481.42046184324386</v>
+        <f t="shared" si="170"/>
+        <v>516.7371062156783</v>
       </c>
       <c r="CE18" s="1">
-        <f t="shared" si="172"/>
-        <v>476.60625722481143</v>
+        <f t="shared" si="170"/>
+        <v>511.56973515352149</v>
       </c>
       <c r="CF18" s="1">
-        <f t="shared" si="172"/>
-        <v>471.8401946525633</v>
+        <f t="shared" si="170"/>
+        <v>506.45403780198626</v>
       </c>
       <c r="CG18" s="1">
-        <f t="shared" si="172"/>
-        <v>467.12179270603764</v>
+        <f t="shared" si="170"/>
+        <v>501.38949742396642</v>
       </c>
       <c r="CH18" s="1">
-        <f t="shared" si="172"/>
-        <v>462.45057477897728</v>
+        <f t="shared" si="170"/>
+        <v>496.37560244972673</v>
       </c>
       <c r="CI18" s="1">
-        <f t="shared" si="172"/>
-        <v>457.8260690311875</v>
+        <f t="shared" si="170"/>
+        <v>491.41184642522944</v>
       </c>
       <c r="CJ18" s="1">
-        <f t="shared" si="172"/>
-        <v>453.24780834087562</v>
+        <f t="shared" si="170"/>
+        <v>486.49772796097716</v>
       </c>
       <c r="CK18" s="1">
-        <f t="shared" si="172"/>
-        <v>448.71533025746686</v>
+        <f t="shared" si="170"/>
+        <v>481.63275068136738</v>
       </c>
       <c r="CL18" s="1">
-        <f t="shared" si="172"/>
-        <v>444.22817695489221</v>
+        <f t="shared" si="170"/>
+        <v>476.81642317455373</v>
       </c>
       <c r="CM18" s="1">
-        <f t="shared" si="172"/>
-        <v>439.78589518534329</v>
+        <f t="shared" si="170"/>
+        <v>472.04825894280822</v>
       </c>
       <c r="CN18" s="1">
-        <f t="shared" si="172"/>
-        <v>435.38803623348986</v>
+        <f t="shared" si="170"/>
+        <v>467.32777635338016</v>
       </c>
       <c r="CO18" s="1">
-        <f t="shared" si="172"/>
-        <v>431.03415587115495</v>
+        <f t="shared" si="170"/>
+        <v>462.65449858984636</v>
       </c>
       <c r="CP18" s="1">
-        <f t="shared" si="172"/>
-        <v>426.72381431244338</v>
+        <f t="shared" si="170"/>
+        <v>458.02795360394788</v>
       </c>
       <c r="CQ18" s="1">
-        <f t="shared" si="172"/>
-        <v>422.45657616931896</v>
+        <f t="shared" si="170"/>
+        <v>453.44767406790839</v>
       </c>
       <c r="CR18" s="1">
-        <f t="shared" si="172"/>
-        <v>418.23201040762575</v>
+        <f t="shared" si="170"/>
+        <v>448.91319732722928</v>
       </c>
       <c r="CS18" s="1">
-        <f t="shared" si="172"/>
-        <v>414.04969030354948</v>
+        <f t="shared" si="170"/>
+        <v>444.42406535395696</v>
       </c>
       <c r="CT18" s="1">
-        <f t="shared" si="172"/>
-        <v>409.90919340051397</v>
+        <f t="shared" si="170"/>
+        <v>439.9798247004174</v>
       </c>
       <c r="CU18" s="1">
-        <f t="shared" si="172"/>
-        <v>405.81010146650885</v>
+        <f t="shared" si="170"/>
+        <v>435.58002645341321</v>
       </c>
       <c r="CV18" s="1">
-        <f t="shared" si="172"/>
-        <v>401.75200045184374</v>
+        <f t="shared" si="170"/>
+        <v>431.22422618887907</v>
       </c>
       <c r="CW18" s="1">
-        <f t="shared" si="172"/>
-        <v>397.73448044732532</v>
+        <f t="shared" si="170"/>
+        <v>426.91198392699027</v>
       </c>
       <c r="CX18" s="1">
-        <f t="shared" si="172"/>
-        <v>393.75713564285206</v>
+        <f t="shared" si="170"/>
+        <v>422.64286408772034</v>
       </c>
       <c r="CY18" s="1">
-        <f t="shared" si="172"/>
-        <v>389.81956428642354</v>
+        <f t="shared" si="170"/>
+        <v>418.41643544684314</v>
       </c>
       <c r="CZ18" s="1">
-        <f t="shared" si="172"/>
-        <v>385.92136864355928</v>
+        <f t="shared" si="170"/>
+        <v>414.23227109237473</v>
       </c>
       <c r="DA18" s="1">
-        <f t="shared" si="172"/>
-        <v>382.06215495712365</v>
+        <f t="shared" si="170"/>
+        <v>410.08994838145099</v>
       </c>
       <c r="DB18" s="1">
-        <f t="shared" si="172"/>
-        <v>378.24153340755242</v>
+        <f t="shared" si="170"/>
+        <v>405.98904889763651</v>
       </c>
       <c r="DC18" s="1">
-        <f t="shared" si="172"/>
-        <v>374.45911807347687</v>
+        <f t="shared" si="170"/>
+        <v>401.92915840866016</v>
       </c>
       <c r="DD18" s="1">
-        <f t="shared" si="172"/>
-        <v>370.71452689274213</v>
+        <f t="shared" si="170"/>
+        <v>397.90986682457356</v>
       </c>
       <c r="DE18" s="1">
-        <f t="shared" si="172"/>
-        <v>367.00738162381469</v>
+        <f t="shared" si="170"/>
+        <v>393.93076815632782</v>
       </c>
       <c r="DF18" s="1">
-        <f t="shared" si="172"/>
-        <v>363.33730780757656</v>
+        <f t="shared" si="170"/>
+        <v>389.99146047476455</v>
       </c>
       <c r="DG18" s="1">
-        <f t="shared" si="172"/>
-        <v>359.70393472950082</v>
+        <f t="shared" si="170"/>
+        <v>386.09154587001689</v>
       </c>
       <c r="DH18" s="1">
-        <f t="shared" si="172"/>
-        <v>356.10689538220578</v>
+        <f t="shared" si="170"/>
+        <v>382.23063041131672</v>
       </c>
       <c r="DI18" s="1">
-        <f t="shared" si="172"/>
-        <v>352.54582642838369</v>
+        <f t="shared" si="170"/>
+        <v>378.40832410720355</v>
       </c>
       <c r="DJ18" s="1">
-        <f t="shared" si="172"/>
-        <v>349.02036816409986</v>
+        <f t="shared" si="170"/>
+        <v>374.62424086613152</v>
       </c>
       <c r="DK18" s="1">
-        <f t="shared" si="172"/>
-        <v>345.53016448245887</v>
+        <f t="shared" si="170"/>
+        <v>370.8779984574702</v>
       </c>
       <c r="DL18" s="1">
-        <f t="shared" si="172"/>
-        <v>342.07486283763427</v>
+        <f t="shared" si="170"/>
+        <v>367.16921847289547</v>
       </c>
       <c r="DM18" s="1">
-        <f t="shared" si="172"/>
-        <v>338.6541142092579</v>
+        <f t="shared" si="170"/>
+        <v>363.49752628816651</v>
       </c>
       <c r="DN18" s="1">
-        <f t="shared" si="172"/>
-        <v>335.2675730671653</v>
+        <f t="shared" si="170"/>
+        <v>359.86255102528486</v>
       </c>
       <c r="DO18" s="1">
-        <f t="shared" ref="DO18:FG18" si="173">DN18*(1+$BD$25)</f>
-        <v>331.91489733649365</v>
+        <f t="shared" ref="DO18:FG18" si="171">DN18*(1+$BD$25)</f>
+        <v>356.26392551503199</v>
       </c>
       <c r="DP18" s="1">
-        <f t="shared" si="173"/>
-        <v>328.59574836312873</v>
+        <f t="shared" si="171"/>
+        <v>352.70128625988167</v>
       </c>
       <c r="DQ18" s="1">
-        <f t="shared" si="173"/>
-        <v>325.30979087949743</v>
+        <f t="shared" si="171"/>
+        <v>349.17427339728283</v>
       </c>
       <c r="DR18" s="1">
-        <f t="shared" si="173"/>
-        <v>322.05669297070244</v>
+        <f t="shared" si="171"/>
+        <v>345.68253066330999</v>
       </c>
       <c r="DS18" s="1">
-        <f t="shared" si="173"/>
-        <v>318.8361260409954</v>
+        <f t="shared" si="171"/>
+        <v>342.22570535667688</v>
       </c>
       <c r="DT18" s="1">
-        <f t="shared" si="173"/>
-        <v>315.64776478058542</v>
+        <f t="shared" si="171"/>
+        <v>338.80344830311009</v>
       </c>
       <c r="DU18" s="1">
-        <f t="shared" si="173"/>
-        <v>312.49128713277958</v>
+        <f t="shared" si="171"/>
+        <v>335.41541382007898</v>
       </c>
       <c r="DV18" s="1">
-        <f t="shared" si="173"/>
-        <v>309.36637426145177</v>
+        <f t="shared" si="171"/>
+        <v>332.0612596818782</v>
       </c>
       <c r="DW18" s="1">
-        <f t="shared" si="173"/>
-        <v>306.27271051883724</v>
+        <f t="shared" si="171"/>
+        <v>328.74064708505944</v>
       </c>
       <c r="DX18" s="1">
-        <f t="shared" si="173"/>
-        <v>303.20998341364884</v>
+        <f t="shared" si="171"/>
+        <v>325.45324061420882</v>
       </c>
       <c r="DY18" s="1">
-        <f t="shared" si="173"/>
-        <v>300.17788357951235</v>
+        <f t="shared" si="171"/>
+        <v>322.19870820806671</v>
       </c>
       <c r="DZ18" s="1">
-        <f t="shared" si="173"/>
-        <v>297.17610474371725</v>
+        <f t="shared" si="171"/>
+        <v>318.97672112598605</v>
       </c>
       <c r="EA18" s="1">
-        <f t="shared" si="173"/>
-        <v>294.20434369628009</v>
+        <f t="shared" si="171"/>
+        <v>315.78695391472615</v>
       </c>
       <c r="EB18" s="1">
-        <f t="shared" si="173"/>
-        <v>291.26230025931727</v>
+        <f t="shared" si="171"/>
+        <v>312.62908437557888</v>
       </c>
       <c r="EC18" s="1">
-        <f t="shared" si="173"/>
-        <v>288.34967725672408</v>
+        <f t="shared" si="171"/>
+        <v>309.5027935318231</v>
       </c>
       <c r="ED18" s="1">
-        <f t="shared" si="173"/>
-        <v>285.46618048415684</v>
+        <f t="shared" si="171"/>
+        <v>306.40776559650487</v>
       </c>
       <c r="EE18" s="1">
-        <f t="shared" si="173"/>
-        <v>282.61151867931528</v>
+        <f t="shared" si="171"/>
+        <v>303.34368794053984</v>
       </c>
       <c r="EF18" s="1">
-        <f t="shared" si="173"/>
-        <v>279.78540349252211</v>
+        <f t="shared" si="171"/>
+        <v>300.31025106113441</v>
       </c>
       <c r="EG18" s="1">
-        <f t="shared" si="173"/>
-        <v>276.98754945759686</v>
+        <f t="shared" si="171"/>
+        <v>297.30714855052304</v>
       </c>
       <c r="EH18" s="1">
-        <f t="shared" si="173"/>
-        <v>274.2176739630209</v>
+        <f t="shared" si="171"/>
+        <v>294.33407706501782</v>
       </c>
       <c r="EI18" s="1">
-        <f t="shared" si="173"/>
-        <v>271.47549722339068</v>
+        <f t="shared" si="171"/>
+        <v>291.39073629436763</v>
       </c>
       <c r="EJ18" s="1">
-        <f t="shared" si="173"/>
-        <v>268.76074225115678</v>
+        <f t="shared" si="171"/>
+        <v>288.47682893142394</v>
       </c>
       <c r="EK18" s="1">
-        <f t="shared" si="173"/>
-        <v>266.07313482864521</v>
+        <f t="shared" si="171"/>
+        <v>285.59206064210969</v>
       </c>
       <c r="EL18" s="1">
-        <f t="shared" si="173"/>
-        <v>263.41240348035876</v>
+        <f t="shared" si="171"/>
+        <v>282.73614003568861</v>
       </c>
       <c r="EM18" s="1">
-        <f t="shared" si="173"/>
-        <v>260.7782794455552</v>
+        <f t="shared" si="171"/>
+        <v>279.90877863533171</v>
       </c>
       <c r="EN18" s="1">
-        <f t="shared" si="173"/>
-        <v>258.17049665109965</v>
+        <f t="shared" si="171"/>
+        <v>277.1096908489784</v>
       </c>
       <c r="EO18" s="1">
-        <f t="shared" si="173"/>
-        <v>255.58879168458864</v>
+        <f t="shared" si="171"/>
+        <v>274.33859394048864</v>
       </c>
       <c r="EP18" s="1">
-        <f t="shared" si="173"/>
-        <v>253.03290376774277</v>
+        <f t="shared" si="171"/>
+        <v>271.59520800108373</v>
       </c>
       <c r="EQ18" s="1">
-        <f t="shared" si="173"/>
-        <v>250.50257473006533</v>
+        <f t="shared" si="171"/>
+        <v>268.87925592107291</v>
       </c>
       <c r="ER18" s="1">
-        <f t="shared" si="173"/>
-        <v>247.99754898276467</v>
+        <f t="shared" si="171"/>
+        <v>266.19046336186216</v>
       </c>
       <c r="ES18" s="1">
-        <f t="shared" si="173"/>
-        <v>245.51757349293703</v>
+        <f t="shared" si="171"/>
+        <v>263.52855872824352</v>
       </c>
       <c r="ET18" s="1">
-        <f t="shared" si="173"/>
-        <v>243.06239775800765</v>
+        <f t="shared" si="171"/>
+        <v>260.89327314096107</v>
       </c>
       <c r="EU18" s="1">
-        <f t="shared" si="173"/>
-        <v>240.63177378042758</v>
+        <f t="shared" si="171"/>
+        <v>258.28434040955148</v>
       </c>
       <c r="EV18" s="1">
-        <f t="shared" si="173"/>
-        <v>238.22545604262331</v>
+        <f t="shared" si="171"/>
+        <v>255.70149700545596</v>
       </c>
       <c r="EW18" s="1">
-        <f t="shared" si="173"/>
-        <v>235.84320148219706</v>
+        <f t="shared" si="171"/>
+        <v>253.14448203540141</v>
       </c>
       <c r="EX18" s="1">
-        <f t="shared" si="173"/>
-        <v>233.48476946737509</v>
+        <f t="shared" si="171"/>
+        <v>250.6130372150474</v>
       </c>
       <c r="EY18" s="1">
-        <f t="shared" si="173"/>
-        <v>231.14992177270133</v>
+        <f t="shared" si="171"/>
+        <v>248.10690684289693</v>
       </c>
       <c r="EZ18" s="1">
-        <f t="shared" si="173"/>
-        <v>228.83842255497433</v>
+        <f t="shared" si="171"/>
+        <v>245.62583777446795</v>
       </c>
       <c r="FA18" s="1">
-        <f t="shared" si="173"/>
-        <v>226.55003832942458</v>
+        <f t="shared" si="171"/>
+        <v>243.16957939672326</v>
       </c>
       <c r="FB18" s="1">
-        <f t="shared" si="173"/>
-        <v>224.28453794613034</v>
+        <f t="shared" si="171"/>
+        <v>240.73788360275603</v>
       </c>
       <c r="FC18" s="1">
-        <f t="shared" si="173"/>
-        <v>222.04169256666904</v>
+        <f t="shared" si="171"/>
+        <v>238.33050476672847</v>
       </c>
       <c r="FD18" s="1">
-        <f t="shared" si="173"/>
-        <v>219.82127564100236</v>
+        <f t="shared" si="171"/>
+        <v>235.94719971906119</v>
       </c>
       <c r="FE18" s="1">
-        <f t="shared" si="173"/>
-        <v>217.62306288459234</v>
+        <f t="shared" si="171"/>
+        <v>233.58772772187058</v>
       </c>
       <c r="FF18" s="1">
-        <f t="shared" si="173"/>
-        <v>215.44683225574641</v>
+        <f t="shared" si="171"/>
+        <v>231.25185044465186</v>
       </c>
       <c r="FG18" s="1">
-        <f t="shared" si="173"/>
-        <v>213.29236393318894</v>
+        <f t="shared" si="171"/>
+        <v>228.93933194020534</v>
       </c>
     </row>
     <row r="19" spans="2:163" x14ac:dyDescent="0.3">
@@ -4617,16 +4608,16 @@
         <v>146.6</v>
       </c>
       <c r="AF19" s="5">
-        <f>129.5+17.1</f>
-        <v>146.6</v>
+        <f>146.9</f>
+        <v>146.9</v>
       </c>
       <c r="AG19" s="5">
-        <f>129.5+17.1</f>
-        <v>146.6</v>
+        <f>146.9</f>
+        <v>146.9</v>
       </c>
       <c r="AH19" s="5">
-        <f>129.5+17.1</f>
-        <v>146.6</v>
+        <f>146.9</f>
+        <v>146.9</v>
       </c>
       <c r="AJ19">
         <v>125</v>
@@ -4647,52 +4638,52 @@
         <v>125</v>
       </c>
       <c r="AP19" s="5">
-        <f t="shared" ref="AP19" si="174">128.7+17.2</f>
+        <f t="shared" ref="AP19" si="172">128.7+17.2</f>
         <v>145.89999999999998</v>
       </c>
       <c r="AQ19" s="5">
-        <f t="shared" ref="AQ19:BA19" si="175">129.5+17.1</f>
-        <v>146.6</v>
+        <f>146.9</f>
+        <v>146.9</v>
       </c>
       <c r="AR19" s="5">
-        <f t="shared" si="175"/>
-        <v>146.6</v>
+        <f>146.9</f>
+        <v>146.9</v>
       </c>
       <c r="AS19" s="5">
-        <f t="shared" si="175"/>
-        <v>146.6</v>
+        <f>146.9</f>
+        <v>146.9</v>
       </c>
       <c r="AT19" s="5">
-        <f t="shared" si="175"/>
-        <v>146.6</v>
+        <f>146.9</f>
+        <v>146.9</v>
       </c>
       <c r="AU19" s="5">
-        <f t="shared" si="175"/>
-        <v>146.6</v>
+        <f>146.9</f>
+        <v>146.9</v>
       </c>
       <c r="AV19" s="5">
-        <f t="shared" si="175"/>
-        <v>146.6</v>
+        <f>146.9</f>
+        <v>146.9</v>
       </c>
       <c r="AW19" s="5">
-        <f t="shared" si="175"/>
-        <v>146.6</v>
+        <f>146.9</f>
+        <v>146.9</v>
       </c>
       <c r="AX19" s="5">
-        <f t="shared" si="175"/>
-        <v>146.6</v>
+        <f>146.9</f>
+        <v>146.9</v>
       </c>
       <c r="AY19" s="5">
-        <f t="shared" si="175"/>
-        <v>146.6</v>
+        <f>146.9</f>
+        <v>146.9</v>
       </c>
       <c r="AZ19" s="5">
-        <f t="shared" si="175"/>
-        <v>146.6</v>
+        <f>146.9</f>
+        <v>146.9</v>
       </c>
       <c r="BA19" s="5">
-        <f t="shared" si="175"/>
-        <v>146.6</v>
+        <f>146.9</f>
+        <v>146.9</v>
       </c>
     </row>
     <row r="20" spans="2:163" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4700,204 +4691,204 @@
         <v>37</v>
       </c>
       <c r="C20" s="6">
-        <f t="shared" ref="C20:L20" si="176">C18/C19</f>
+        <f t="shared" ref="C20:L20" si="173">C18/C19</f>
         <v>-5.2800000000000041E-2</v>
       </c>
       <c r="D20" s="6">
+        <f t="shared" si="173"/>
+        <v>4.8000000000000464E-3</v>
+      </c>
+      <c r="E20" s="6">
+        <f t="shared" si="173"/>
+        <v>-7.6000000000000206E-2</v>
+      </c>
+      <c r="F20" s="6">
+        <f t="shared" si="173"/>
+        <v>5.4399999999999886E-2</v>
+      </c>
+      <c r="G20" s="6">
+        <f t="shared" si="173"/>
+        <v>-7.7600000000000141E-2</v>
+      </c>
+      <c r="H20" s="6">
+        <f t="shared" si="173"/>
+        <v>-7.5680000000000053E-2</v>
+      </c>
+      <c r="I20" s="6">
+        <f t="shared" si="173"/>
+        <v>-0.19680000000000011</v>
+      </c>
+      <c r="J20" s="6">
+        <f t="shared" si="173"/>
+        <v>-0.12479999999999963</v>
+      </c>
+      <c r="K20" s="6">
+        <f t="shared" si="173"/>
+        <v>-0.43519999999999998</v>
+      </c>
+      <c r="L20" s="6">
+        <f t="shared" si="173"/>
+        <v>-0.34479999999999988</v>
+      </c>
+      <c r="M20" s="6">
+        <f t="shared" ref="M20:AL20" si="174">M18/M19</f>
+        <v>0.10560000000000032</v>
+      </c>
+      <c r="N20" s="6">
+        <f t="shared" si="174"/>
+        <v>0.53879999999999995</v>
+      </c>
+      <c r="O20" s="6">
+        <f t="shared" ref="O20:R20" si="175">O18/O19</f>
+        <v>0.6104000000000005</v>
+      </c>
+      <c r="P20" s="6">
+        <f t="shared" ref="P20:Q20" si="176">P18/P19</f>
+        <v>0.51148225469728537</v>
+      </c>
+      <c r="Q20" s="6">
         <f t="shared" si="176"/>
-        <v>4.8000000000000464E-3</v>
-      </c>
-      <c r="E20" s="6">
-        <f t="shared" si="176"/>
-        <v>-7.6000000000000206E-2</v>
-      </c>
-      <c r="F20" s="6">
-        <f t="shared" si="176"/>
-        <v>5.4399999999999886E-2</v>
-      </c>
-      <c r="G20" s="6">
-        <f t="shared" si="176"/>
-        <v>-7.7600000000000141E-2</v>
-      </c>
-      <c r="H20" s="6">
-        <f t="shared" si="176"/>
-        <v>-7.5680000000000053E-2</v>
-      </c>
-      <c r="I20" s="6">
-        <f t="shared" si="176"/>
-        <v>-0.19680000000000011</v>
-      </c>
-      <c r="J20" s="6">
-        <f t="shared" si="176"/>
-        <v>-0.12479999999999963</v>
-      </c>
-      <c r="K20" s="6">
-        <f t="shared" si="176"/>
-        <v>-0.43519999999999998</v>
-      </c>
-      <c r="L20" s="6">
-        <f t="shared" si="176"/>
-        <v>-0.34479999999999988</v>
-      </c>
-      <c r="M20" s="6">
-        <f t="shared" ref="M20:AL20" si="177">M18/M19</f>
-        <v>0.10560000000000032</v>
-      </c>
-      <c r="N20" s="6">
+        <v>0.47947112038970047</v>
+      </c>
+      <c r="R20" s="6">
+        <f t="shared" si="175"/>
+        <v>0.16492693110647152</v>
+      </c>
+      <c r="S20" s="6">
+        <f t="shared" ref="S20:T20" si="177">S18/S19</f>
+        <v>-0.18371607515657659</v>
+      </c>
+      <c r="T20" s="6">
         <f t="shared" si="177"/>
-        <v>0.53879999999999995</v>
-      </c>
-      <c r="O20" s="6">
-        <f t="shared" ref="O20:R20" si="178">O18/O19</f>
-        <v>0.6104000000000005</v>
-      </c>
-      <c r="P20" s="6">
-        <f t="shared" ref="P20:Q20" si="179">P18/P19</f>
-        <v>0.51148225469728537</v>
-      </c>
-      <c r="Q20" s="6">
-        <f t="shared" si="179"/>
-        <v>0.47947112038970047</v>
-      </c>
-      <c r="R20" s="6">
-        <f t="shared" si="178"/>
-        <v>0.16492693110647152</v>
-      </c>
-      <c r="S20" s="6">
-        <f t="shared" ref="S20:T20" si="180">S18/S19</f>
-        <v>-0.18371607515657659</v>
-      </c>
-      <c r="T20" s="6">
+        <v>-0.78218510786360518</v>
+      </c>
+      <c r="U20" s="6">
+        <f t="shared" ref="U20" si="178">U18/U19</f>
+        <v>-0.85107863604732048</v>
+      </c>
+      <c r="V20" s="6">
+        <f t="shared" ref="V20" si="179">V18/V19</f>
+        <v>-1.650661099512875</v>
+      </c>
+      <c r="W20" s="6">
+        <f t="shared" ref="W20:X20" si="180">W18/W19</f>
+        <v>-1.3437717466945029</v>
+      </c>
+      <c r="X20" s="6">
         <f t="shared" si="180"/>
-        <v>-0.78218510786360518</v>
-      </c>
-      <c r="U20" s="6">
-        <f t="shared" ref="U20" si="181">U18/U19</f>
-        <v>-0.85107863604732048</v>
-      </c>
-      <c r="V20" s="6">
-        <f t="shared" ref="V20" si="182">V18/V19</f>
-        <v>-1.650661099512875</v>
-      </c>
-      <c r="W20" s="6">
-        <f t="shared" ref="W20:X20" si="183">W18/W19</f>
-        <v>-1.3437717466945029</v>
-      </c>
-      <c r="X20" s="6">
+        <v>-0.74808629088378598</v>
+      </c>
+      <c r="Y20" s="6">
+        <f t="shared" ref="Y20" si="181">Y18/Y19</f>
+        <v>-2.2971468336812806</v>
+      </c>
+      <c r="Z20" s="6">
+        <f t="shared" ref="Z20:AA20" si="182">Z18/Z19</f>
+        <v>-0.54418928322894933</v>
+      </c>
+      <c r="AA20" s="6">
+        <f t="shared" si="182"/>
+        <v>-0.35351426583159401</v>
+      </c>
+      <c r="AB20" s="6">
+        <f t="shared" ref="AB20:AD20" si="183">AB18/AB19</f>
+        <v>-0.23729993041057826</v>
+      </c>
+      <c r="AC20" s="6">
         <f t="shared" si="183"/>
-        <v>-0.74808629088378598</v>
-      </c>
-      <c r="Y20" s="6">
-        <f t="shared" ref="Y20" si="184">Y18/Y19</f>
-        <v>-2.2971468336812806</v>
-      </c>
-      <c r="Z20" s="6">
-        <f t="shared" ref="Z20:AA20" si="185">Z18/Z19</f>
-        <v>-0.54418928322894933</v>
-      </c>
-      <c r="AA20" s="6">
-        <f t="shared" si="185"/>
-        <v>-0.35351426583159401</v>
-      </c>
-      <c r="AB20" s="6">
-        <f t="shared" ref="AB20:AD20" si="186">AB18/AB19</f>
-        <v>-0.23729993041057826</v>
-      </c>
-      <c r="AC20" s="6">
-        <f t="shared" si="186"/>
         <v>-6.1421670117321039E-2</v>
       </c>
       <c r="AD20" s="6">
-        <f t="shared" si="186"/>
+        <f t="shared" si="183"/>
         <v>-0.24400274160383781</v>
       </c>
       <c r="AE20" s="6">
-        <f t="shared" ref="AE20:AH20" si="187">AE18/AE19</f>
+        <f t="shared" ref="AE20:AH20" si="184">AE18/AE19</f>
         <v>-0.18690313778990478</v>
       </c>
       <c r="AF20" s="6">
-        <f t="shared" si="187"/>
-        <v>-6.5081527967257802E-2</v>
+        <f t="shared" si="184"/>
+        <v>7.1477195371000224E-2</v>
       </c>
       <c r="AG20" s="6">
-        <f t="shared" si="187"/>
-        <v>9.775672578444819E-2</v>
+        <f t="shared" si="184"/>
+        <v>0.10275681415929137</v>
       </c>
       <c r="AH20" s="6">
-        <f t="shared" si="187"/>
-        <v>9.8132496589359103E-2</v>
+        <f t="shared" si="184"/>
+        <v>0.11976408441116394</v>
       </c>
       <c r="AJ20" s="6">
-        <f t="shared" si="177"/>
+        <f t="shared" si="174"/>
         <v>-6.9600000000000092E-2</v>
       </c>
       <c r="AK20" s="6">
-        <f t="shared" si="177"/>
+        <f t="shared" si="174"/>
         <v>-0.47487999999999925</v>
       </c>
       <c r="AL20" s="6">
-        <f t="shared" si="177"/>
+        <f t="shared" si="174"/>
         <v>-0.13560000000000036</v>
       </c>
       <c r="AM20" s="6">
-        <f t="shared" ref="AM20" si="188">AM18/AM19</f>
+        <f t="shared" ref="AM20" si="185">AM18/AM19</f>
         <v>1.9391999999999983</v>
       </c>
       <c r="AN20" s="6">
-        <f t="shared" ref="AN20" si="189">AN18/AN19</f>
+        <f t="shared" ref="AN20" si="186">AN18/AN19</f>
         <v>-3.9864000000000028</v>
       </c>
       <c r="AO20" s="6">
-        <f t="shared" ref="AO20" si="190">AO18/AO19</f>
+        <f t="shared" ref="AO20" si="187">AO18/AO19</f>
         <v>-5.671199999999998</v>
       </c>
       <c r="AP20" s="6">
-        <f t="shared" ref="AP20" si="191">AP18/AP19</f>
+        <f t="shared" ref="AP20" si="188">AP18/AP19</f>
         <v>-0.88690884167237971</v>
       </c>
       <c r="AQ20" s="6">
-        <f t="shared" ref="AQ20" si="192">AQ18/AQ19</f>
-        <v>-5.6095443383361428E-2</v>
+        <f t="shared" ref="AQ20" si="189">AQ18/AQ19</f>
+        <v>0.10747665078285019</v>
       </c>
       <c r="AR20" s="6">
-        <f t="shared" ref="AR20" si="193">AR18/AR19</f>
-        <v>1.3412998155525215</v>
+        <f t="shared" ref="AR20" si="190">AR18/AR19</f>
+        <v>1.5964734181075575</v>
       </c>
       <c r="AS20" s="6">
-        <f t="shared" ref="AS20" si="194">AS18/AS19</f>
-        <v>2.3360026566766687</v>
+        <f t="shared" ref="AS20" si="191">AS18/AS19</f>
+        <v>2.5997049520163369</v>
       </c>
       <c r="AT20" s="6">
-        <f t="shared" ref="AT20" si="195">AT18/AT19</f>
-        <v>3.1786600056401624</v>
+        <f t="shared" ref="AT20" si="192">AT18/AT19</f>
+        <v>3.4521703226083584</v>
       </c>
       <c r="AU20" s="6">
-        <f t="shared" ref="AU20" si="196">AU18/AU19</f>
-        <v>3.4879684963066713</v>
+        <f t="shared" ref="AU20" si="193">AU18/AU19</f>
+        <v>3.7695515903250549</v>
       </c>
       <c r="AV20" s="6">
-        <f t="shared" ref="AV20:AW20" si="197">AV18/AV19</f>
-        <v>3.709200844187531</v>
+        <f t="shared" ref="AV20:AW20" si="194">AV18/AV19</f>
+        <v>3.9974373061299664</v>
       </c>
       <c r="AW20" s="6">
-        <f t="shared" si="197"/>
-        <v>3.8396574628312115</v>
+        <f t="shared" si="194"/>
+        <v>4.1326334514754022</v>
       </c>
       <c r="AX20" s="6">
-        <f t="shared" ref="AX20:BA20" si="198">AX18/AX19</f>
-        <v>3.9734000934094906</v>
+        <f t="shared" ref="AX20:BA20" si="195">AX18/AX19</f>
+        <v>4.2711994330679719</v>
       </c>
       <c r="AY20" s="6">
-        <f t="shared" si="198"/>
-        <v>4.110504649563004</v>
+        <f t="shared" si="195"/>
+        <v>4.413212709946464</v>
       </c>
       <c r="AZ20" s="6">
-        <f t="shared" si="198"/>
-        <v>4.2510487678774043</v>
+        <f t="shared" si="195"/>
+        <v>4.5587524930489929</v>
       </c>
       <c r="BA20" s="6">
-        <f t="shared" si="198"/>
-        <v>4.3951118474711306</v>
+        <f t="shared" si="195"/>
+        <v>4.7078997853410316</v>
       </c>
     </row>
     <row r="22" spans="2:163" x14ac:dyDescent="0.3">
@@ -4905,116 +4896,116 @@
         <v>45</v>
       </c>
       <c r="G22" s="9">
-        <f t="shared" ref="G22:N22" si="199">G3/C3-1</f>
+        <f t="shared" ref="G22:N22" si="196">G3/C3-1</f>
         <v>0.78695073235685742</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>0.85714285714285698</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>0.79120879120879151</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>0.71466314398943198</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>0.73323397913561861</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>0.45974955277280882</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>0.78025655326268795</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="199"/>
+        <f t="shared" si="196"/>
         <v>0.8151001540832048</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" ref="O22:O24" si="200">O3/K3-1</f>
+        <f t="shared" ref="O22:O24" si="197">O3/K3-1</f>
         <v>1.0055889939810836</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" ref="P22:P24" si="201">P3/L3-1</f>
+        <f t="shared" ref="P22:P24" si="198">P3/L3-1</f>
         <v>1.174428104575163</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" ref="Q22:Q24" si="202">Q3/M3-1</f>
+        <f t="shared" ref="Q22:Q24" si="199">Q3/M3-1</f>
         <v>0.82487468671679198</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" ref="R22:R24" si="203">R3/N3-1</f>
+        <f t="shared" ref="R22:R24" si="200">R3/N3-1</f>
         <v>0.49320882852292036</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" ref="S22:S24" si="204">S3/O3-1</f>
+        <f t="shared" ref="S22:S24" si="201">S3/O3-1</f>
         <v>0.38670953912111461</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" ref="T22:T24" si="205">T3/P3-1</f>
+        <f t="shared" ref="T22:T24" si="202">T3/P3-1</f>
         <v>0.25737366146909646</v>
       </c>
       <c r="U22" s="9">
-        <f t="shared" ref="U22:U24" si="206">U3/Q3-1</f>
+        <f t="shared" ref="U22:U24" si="203">U3/Q3-1</f>
         <v>0.14540772532188839</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" ref="V22:V24" si="207">V3/R3-1</f>
+        <f t="shared" ref="V22:V24" si="204">V3/R3-1</f>
         <v>3.9368959636156831E-2</v>
       </c>
       <c r="W22" s="9">
-        <f t="shared" ref="W22:W24" si="208">W3/S3-1</f>
+        <f t="shared" ref="W22:W24" si="205">W3/S3-1</f>
         <v>-1.9013757922399011E-2</v>
       </c>
       <c r="X22" s="9">
-        <f t="shared" ref="X22:X24" si="209">X3/T3-1</f>
+        <f t="shared" ref="X22:X24" si="206">X3/T3-1</f>
         <v>0.11145973405050058</v>
       </c>
       <c r="Y22" s="9">
-        <f t="shared" ref="Y22:Y24" si="210">Y3/U3-1</f>
+        <f t="shared" ref="Y22:Y24" si="207">Y3/U3-1</f>
         <v>0.1792565947242204</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" ref="Z22:Z24" si="211">Z3/V3-1</f>
+        <f t="shared" ref="Z22:Z24" si="208">Z3/V3-1</f>
         <v>0.13346095993436347</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" ref="AA22:AA24" si="212">AA3/W3-1</f>
+        <f t="shared" ref="AA22:AA24" si="209">AA3/W3-1</f>
         <v>0.18956823195713834</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" ref="AB22:AB24" si="213">AB3/X3-1</f>
+        <f t="shared" ref="AB22:AB24" si="210">AB3/X3-1</f>
         <v>0.10807904288210768</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" ref="AC22:AC24" si="214">AC3/Y3-1</f>
+        <f t="shared" ref="AC22:AC24" si="211">AC3/Y3-1</f>
         <v>0.15429588205388933</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" ref="AD22:AD24" si="215">AD3/Z3-1</f>
+        <f t="shared" ref="AD22:AD24" si="212">AD3/Z3-1</f>
         <v>0.24900470503076355</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" ref="AE22:AE24" si="216">AE3/AA3-1</f>
+        <f t="shared" ref="AE22:AE24" si="213">AE3/AA3-1</f>
         <v>0.16677705656378317</v>
       </c>
       <c r="AF22" s="9">
-        <f t="shared" ref="AF22:AF24" si="217">AF3/AB3-1</f>
-        <v>0.14999999999999991</v>
+        <f t="shared" ref="AF22:AF24" si="214">AF3/AB3-1</f>
+        <v>0.18342836345990543</v>
       </c>
       <c r="AG22" s="9">
-        <f t="shared" ref="AG22:AG24" si="218">AG3/AC3-1</f>
+        <f t="shared" ref="AG22:AG24" si="215">AG3/AC3-1</f>
         <v>0.12999999999999967</v>
       </c>
       <c r="AH22" s="9">
-        <f t="shared" ref="AH22:AH24" si="219">AH3/AD3-1</f>
-        <v>0.10000000000000009</v>
+        <f t="shared" ref="AH22:AH24" si="216">AH3/AD3-1</f>
+        <v>0.1100000000000001</v>
       </c>
       <c r="AK22" s="9">
         <f>AK3/AJ3-1</f>
@@ -5025,63 +5016,63 @@
         <v>0.71139308855291583</v>
       </c>
       <c r="AM22" s="9">
-        <f t="shared" ref="AM22:AW22" si="220">AM3/AL3-1</f>
+        <f t="shared" ref="AM22:AW22" si="217">AM3/AL3-1</f>
         <v>0.80225587632118645</v>
       </c>
       <c r="AN22" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="217"/>
         <v>0.1881045122324827</v>
       </c>
       <c r="AO22" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="217"/>
         <v>0.10295796957306536</v>
       </c>
       <c r="AP22" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="217"/>
         <v>0.17650791530291876</v>
       </c>
       <c r="AQ22" s="9">
-        <f t="shared" si="220"/>
-        <v>0.13374428705254493</v>
+        <f t="shared" si="217"/>
+        <v>0.14450535100916917</v>
       </c>
       <c r="AR22" s="9">
-        <f t="shared" si="220"/>
-        <v>0.10000000000000009</v>
+        <f t="shared" si="217"/>
+        <v>0.1100000000000001</v>
       </c>
       <c r="AS22" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="217"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AT22" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="217"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AU22" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="217"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AV22" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="217"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AW22" s="9">
-        <f t="shared" si="220"/>
+        <f t="shared" si="217"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AX22" s="9">
-        <f t="shared" ref="AX22:AX24" si="221">AX3/AW3-1</f>
+        <f t="shared" ref="AX22:AX24" si="218">AX3/AW3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AY22" s="9">
-        <f t="shared" ref="AY22:AY24" si="222">AY3/AX3-1</f>
+        <f t="shared" ref="AY22:AY24" si="219">AY3/AX3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AZ22" s="9">
-        <f t="shared" ref="AZ22:AZ24" si="223">AZ3/AY3-1</f>
+        <f t="shared" ref="AZ22:AZ24" si="220">AZ3/AY3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BA22" s="9">
-        <f t="shared" ref="BA22:BA24" si="224">BA3/AZ3-1</f>
+        <f t="shared" ref="BA22:BA24" si="221">BA3/AZ3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -5090,183 +5081,183 @@
         <v>46</v>
       </c>
       <c r="G23" s="9">
-        <f t="shared" ref="G23:N23" si="225">G4/C4-1</f>
+        <f t="shared" ref="G23:N23" si="222">G4/C4-1</f>
         <v>0.17886178861788626</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" si="225"/>
+        <f t="shared" si="222"/>
         <v>0.23909774436090236</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" si="225"/>
+        <f t="shared" si="222"/>
         <v>0.11323328785811726</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="225"/>
+        <f t="shared" si="222"/>
         <v>0.21962992759452926</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" si="225"/>
+        <f t="shared" si="222"/>
         <v>0.21655172413793111</v>
       </c>
       <c r="L23" s="9">
-        <f t="shared" si="225"/>
+        <f t="shared" si="222"/>
         <v>0.35072815533980561</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" si="225"/>
+        <f t="shared" si="222"/>
         <v>0.62254901960784337</v>
       </c>
       <c r="N23" s="9">
-        <f t="shared" si="225"/>
+        <f t="shared" si="222"/>
         <v>0.1787598944591029</v>
       </c>
       <c r="O23" s="9">
+        <f t="shared" si="197"/>
+        <v>0.22108843537414957</v>
+      </c>
+      <c r="P23" s="9">
+        <f t="shared" si="198"/>
+        <v>1.3477088948786964E-2</v>
+      </c>
+      <c r="Q23" s="9">
+        <f t="shared" si="199"/>
+        <v>-0.2643504531722054</v>
+      </c>
+      <c r="R23" s="9">
         <f t="shared" si="200"/>
-        <v>0.22108843537414957</v>
-      </c>
-      <c r="P23" s="9">
+        <v>-9.5131505316172316E-2</v>
+      </c>
+      <c r="S23" s="9">
         <f t="shared" si="201"/>
-        <v>1.3477088948786964E-2</v>
-      </c>
-      <c r="Q23" s="9">
+        <v>-0.19405756731662027</v>
+      </c>
+      <c r="T23" s="9">
         <f t="shared" si="202"/>
-        <v>-0.2643504531722054</v>
-      </c>
-      <c r="R23" s="9">
+        <v>-0.15602836879432624</v>
+      </c>
+      <c r="U23" s="9">
         <f t="shared" si="203"/>
-        <v>-9.5131505316172316E-2</v>
-      </c>
-      <c r="S23" s="9">
+        <v>-3.2854209445585258E-2</v>
+      </c>
+      <c r="V23" s="9">
         <f t="shared" si="204"/>
-        <v>-0.19405756731662027</v>
-      </c>
-      <c r="T23" s="9">
+        <v>-0.16017316017316008</v>
+      </c>
+      <c r="W23" s="9">
         <f t="shared" si="205"/>
-        <v>-0.15602836879432624</v>
-      </c>
-      <c r="U23" s="9">
+        <v>0.22580645161290325</v>
+      </c>
+      <c r="X23" s="9">
         <f t="shared" si="206"/>
-        <v>-3.2854209445585258E-2</v>
-      </c>
-      <c r="V23" s="9">
+        <v>8.6134453781512743E-2</v>
+      </c>
+      <c r="Y23" s="9">
         <f t="shared" si="207"/>
-        <v>-0.16017316017316008</v>
-      </c>
-      <c r="W23" s="9">
+        <v>0.32908704883227169</v>
+      </c>
+      <c r="Z23" s="9">
         <f t="shared" si="208"/>
-        <v>0.22580645161290325</v>
-      </c>
-      <c r="X23" s="9">
+        <v>0.14580265095729006</v>
+      </c>
+      <c r="AA23" s="9">
         <f t="shared" si="209"/>
-        <v>8.6134453781512743E-2</v>
-      </c>
-      <c r="Y23" s="9">
+        <v>0.18890977443609014</v>
+      </c>
+      <c r="AB23" s="9">
         <f t="shared" si="210"/>
-        <v>0.32908704883227169</v>
-      </c>
-      <c r="Z23" s="9">
+        <v>0.39071566731141205</v>
+      </c>
+      <c r="AC23" s="9">
         <f t="shared" si="211"/>
-        <v>0.14580265095729006</v>
-      </c>
-      <c r="AA23" s="9">
+        <v>0.23003194888178902</v>
+      </c>
+      <c r="AD23" s="9">
         <f t="shared" si="212"/>
-        <v>0.18890977443609014</v>
-      </c>
-      <c r="AB23" s="9">
+        <v>6.4910025706940822E-2</v>
+      </c>
+      <c r="AE23" s="9">
         <f t="shared" si="213"/>
-        <v>0.39071566731141205</v>
-      </c>
-      <c r="AC23" s="9">
+        <v>0.10592885375494077</v>
+      </c>
+      <c r="AF23" s="9">
         <f t="shared" si="214"/>
-        <v>0.23003194888178902</v>
-      </c>
-      <c r="AD23" s="9">
+        <v>-5.7023643949930536E-2</v>
+      </c>
+      <c r="AG23" s="9">
         <f t="shared" si="215"/>
-        <v>6.4910025706940822E-2</v>
-      </c>
-      <c r="AE23" s="9">
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AH23" s="9">
         <f t="shared" si="216"/>
-        <v>0.10592885375494077</v>
-      </c>
-      <c r="AF23" s="9">
-        <f t="shared" si="217"/>
-        <v>7.0000000000000062E-2</v>
-      </c>
-      <c r="AG23" s="9">
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AK23" s="9">
+        <f t="shared" ref="AK23:AL23" si="223">AK4/AJ4-1</f>
+        <v>0.19195331695331697</v>
+      </c>
+      <c r="AL23" s="9">
+        <f t="shared" si="223"/>
+        <v>0.31564029889203793</v>
+      </c>
+      <c r="AM23" s="9">
+        <f t="shared" ref="AM23:AW23" si="224">AM4/AL4-1</f>
+        <v>-6.0712886799843324E-2</v>
+      </c>
+      <c r="AN23" s="9">
+        <f t="shared" si="224"/>
+        <v>-0.14095079232693908</v>
+      </c>
+      <c r="AO23" s="9">
+        <f t="shared" si="224"/>
+        <v>0.1907766990291262</v>
+      </c>
+      <c r="AP23" s="9">
+        <f t="shared" si="224"/>
+        <v>0.20260905014268227</v>
+      </c>
+      <c r="AQ23" s="9">
+        <f t="shared" si="224"/>
+        <v>1.7040677966101647E-2</v>
+      </c>
+      <c r="AR23" s="9">
+        <f t="shared" si="224"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AS23" s="9">
+        <f t="shared" si="224"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AT23" s="9">
+        <f t="shared" si="224"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AU23" s="9">
+        <f t="shared" si="224"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AV23" s="9">
+        <f t="shared" si="224"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AW23" s="9">
+        <f t="shared" si="224"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AX23" s="9">
         <f t="shared" si="218"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AH23" s="9">
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AY23" s="9">
         <f t="shared" si="219"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AK23" s="9">
-        <f t="shared" ref="AK23:AL23" si="226">AK4/AJ4-1</f>
-        <v>0.19195331695331697</v>
-      </c>
-      <c r="AL23" s="9">
-        <f t="shared" si="226"/>
-        <v>0.31564029889203793</v>
-      </c>
-      <c r="AM23" s="9">
-        <f t="shared" ref="AM23:AW23" si="227">AM4/AL4-1</f>
-        <v>-6.0712886799843324E-2</v>
-      </c>
-      <c r="AN23" s="9">
-        <f t="shared" si="227"/>
-        <v>-0.14095079232693908</v>
-      </c>
-      <c r="AO23" s="9">
-        <f t="shared" si="227"/>
-        <v>0.1907766990291262</v>
-      </c>
-      <c r="AP23" s="9">
-        <f t="shared" si="227"/>
-        <v>0.20260905014268227</v>
-      </c>
-      <c r="AQ23" s="9">
-        <f t="shared" si="227"/>
-        <v>5.6028813559322099E-2</v>
-      </c>
-      <c r="AR23" s="9">
-        <f t="shared" si="227"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="AS23" s="9">
-        <f t="shared" si="227"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AT23" s="9">
-        <f t="shared" si="227"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AU23" s="9">
-        <f t="shared" si="227"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AV23" s="9">
-        <f t="shared" si="227"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AW23" s="9">
-        <f t="shared" si="227"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AX23" s="9">
+      <c r="AZ23" s="9">
+        <f t="shared" si="220"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="BA23" s="9">
         <f t="shared" si="221"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AY23" s="9">
-        <f t="shared" si="222"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AZ23" s="9">
-        <f t="shared" si="223"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="BA23" s="9">
-        <f t="shared" si="224"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -5279,180 +5270,180 @@
         <v>0.51317715959004384</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" ref="H24:N24" si="228">H5/D5-1</f>
+        <f t="shared" ref="H24:N24" si="225">H5/D5-1</f>
         <v>0.59502551020408156</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" si="228"/>
+        <f t="shared" si="225"/>
         <v>0.50461361014994233</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="228"/>
+        <f t="shared" si="225"/>
         <v>0.49147624229234688</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="228"/>
+        <f t="shared" si="225"/>
         <v>0.5520077406869861</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="228"/>
+        <f t="shared" si="225"/>
         <v>0.42383046781287503</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="228"/>
+        <f t="shared" si="225"/>
         <v>0.73093139133767759</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="228"/>
+        <f t="shared" si="225"/>
         <v>0.58049610894941606</v>
       </c>
       <c r="O24" s="9">
+        <f t="shared" si="197"/>
+        <v>0.78990024937655878</v>
+      </c>
+      <c r="P24" s="9">
+        <f t="shared" si="198"/>
+        <v>0.811569783768604</v>
+      </c>
+      <c r="Q24" s="9">
+        <f t="shared" si="199"/>
+        <v>0.50553587245349862</v>
+      </c>
+      <c r="R24" s="9">
         <f t="shared" si="200"/>
-        <v>0.78990024937655878</v>
-      </c>
-      <c r="P24" s="9">
+        <v>0.33143560547776585</v>
+      </c>
+      <c r="S24" s="9">
         <f t="shared" si="201"/>
-        <v>0.811569783768604</v>
-      </c>
-      <c r="Q24" s="9">
+        <v>0.27777777777777746</v>
+      </c>
+      <c r="T24" s="9">
         <f t="shared" si="202"/>
-        <v>0.50553587245349862</v>
-      </c>
-      <c r="R24" s="9">
+        <v>0.18508758332041553</v>
+      </c>
+      <c r="U24" s="9">
         <f t="shared" si="203"/>
-        <v>0.33143560547776585</v>
-      </c>
-      <c r="S24" s="9">
+        <v>0.11987056920135331</v>
+      </c>
+      <c r="V24" s="9">
         <f t="shared" si="204"/>
-        <v>0.27777777777777746</v>
-      </c>
-      <c r="T24" s="9">
+        <v>2.0802033976654588E-3</v>
+      </c>
+      <c r="W24" s="9">
         <f t="shared" si="205"/>
-        <v>0.18508758332041553</v>
-      </c>
-      <c r="U24" s="9">
+        <v>9.9495706692109831E-3</v>
+      </c>
+      <c r="X24" s="9">
         <f t="shared" si="206"/>
-        <v>0.11987056920135331</v>
-      </c>
-      <c r="V24" s="9">
+        <v>0.10830608240680184</v>
+      </c>
+      <c r="Y24" s="9">
         <f t="shared" si="207"/>
-        <v>2.0802033976654588E-3</v>
-      </c>
-      <c r="W24" s="9">
+        <v>0.19779353821907009</v>
+      </c>
+      <c r="Z24" s="9">
         <f t="shared" si="208"/>
-        <v>9.9495706692109831E-3</v>
-      </c>
-      <c r="X24" s="9">
+        <v>0.13539384154076828</v>
+      </c>
+      <c r="AA24" s="9">
         <f t="shared" si="209"/>
-        <v>0.10830608240680184</v>
-      </c>
-      <c r="Y24" s="9">
+        <v>0.18947368421052624</v>
+      </c>
+      <c r="AB24" s="9">
         <f t="shared" si="210"/>
-        <v>0.19779353821907009</v>
-      </c>
-      <c r="Z24" s="9">
+        <v>0.14257051811636967</v>
+      </c>
+      <c r="AC24" s="9">
         <f t="shared" si="211"/>
-        <v>0.13539384154076828</v>
-      </c>
-      <c r="AA24" s="9">
+        <v>0.1646929824561405</v>
+      </c>
+      <c r="AD24" s="9">
         <f t="shared" si="212"/>
-        <v>0.18947368421052624</v>
-      </c>
-      <c r="AB24" s="9">
+        <v>0.21990858303707461</v>
+      </c>
+      <c r="AE24" s="9">
         <f t="shared" si="213"/>
-        <v>0.14257051811636967</v>
-      </c>
-      <c r="AC24" s="9">
+        <v>0.15804402087587932</v>
+      </c>
+      <c r="AF24" s="9">
         <f t="shared" si="214"/>
-        <v>0.1646929824561405</v>
-      </c>
-      <c r="AD24" s="9">
+        <v>0.14771201322177463</v>
+      </c>
+      <c r="AG24" s="9">
         <f t="shared" si="215"/>
-        <v>0.21990858303707461</v>
-      </c>
-      <c r="AE24" s="9">
+        <v>0.11260214648841993</v>
+      </c>
+      <c r="AH24" s="9">
         <f t="shared" si="216"/>
-        <v>0.15804402087587932</v>
-      </c>
-      <c r="AF24" s="9">
-        <f t="shared" si="217"/>
-        <v>0.13811693006920778</v>
-      </c>
-      <c r="AG24" s="9">
+        <v>9.7582847626977332E-2</v>
+      </c>
+      <c r="AK24" s="9">
+        <f t="shared" ref="AK24:AL24" si="226">AK5/AJ5-1</f>
+        <v>0.52040404040404042</v>
+      </c>
+      <c r="AL24" s="9">
+        <f t="shared" si="226"/>
+        <v>0.5753388254052616</v>
+      </c>
+      <c r="AM24" s="9">
+        <f t="shared" ref="AM24:AW24" si="227">AM5/AL5-1</f>
+        <v>0.55448717948717952</v>
+      </c>
+      <c r="AN24" s="9">
+        <f t="shared" si="227"/>
+        <v>0.13101826731777888</v>
+      </c>
+      <c r="AO24" s="9">
+        <f t="shared" si="227"/>
+        <v>0.11452969584546024</v>
+      </c>
+      <c r="AP24" s="9">
+        <f t="shared" si="227"/>
+        <v>0.18018250688705217</v>
+      </c>
+      <c r="AQ24" s="9">
+        <f t="shared" si="227"/>
+        <v>0.1262195151603569</v>
+      </c>
+      <c r="AR24" s="9">
+        <f t="shared" si="227"/>
+        <v>9.9635932270867311E-2</v>
+      </c>
+      <c r="AS24" s="9">
+        <f t="shared" si="227"/>
+        <v>7.3932656795917095E-2</v>
+      </c>
+      <c r="AT24" s="9">
+        <f t="shared" si="227"/>
+        <v>5.5344688730222025E-2</v>
+      </c>
+      <c r="AU24" s="9">
+        <f t="shared" si="227"/>
+        <v>3.7750300188232222E-2</v>
+      </c>
+      <c r="AV24" s="9">
+        <f t="shared" si="227"/>
+        <v>2.8894390197917952E-2</v>
+      </c>
+      <c r="AW24" s="9">
+        <f t="shared" si="227"/>
+        <v>1.8903947762892725E-2</v>
+      </c>
+      <c r="AX24" s="9">
         <f t="shared" si="218"/>
-        <v>0.11550178874035022</v>
-      </c>
-      <c r="AH24" s="9">
+        <v>1.8913525890336347E-2</v>
+      </c>
+      <c r="AY24" s="9">
         <f t="shared" si="219"/>
-        <v>9.0342214820982703E-2</v>
-      </c>
-      <c r="AK24" s="9">
-        <f t="shared" ref="AK24:AL24" si="229">AK5/AJ5-1</f>
-        <v>0.52040404040404042</v>
-      </c>
-      <c r="AL24" s="9">
-        <f t="shared" si="229"/>
-        <v>0.5753388254052616</v>
-      </c>
-      <c r="AM24" s="9">
-        <f t="shared" ref="AM24:AW24" si="230">AM5/AL5-1</f>
-        <v>0.55448717948717952</v>
-      </c>
-      <c r="AN24" s="9">
-        <f t="shared" si="230"/>
-        <v>0.13101826731777888</v>
-      </c>
-      <c r="AO24" s="9">
-        <f t="shared" si="230"/>
-        <v>0.11452969584546024</v>
-      </c>
-      <c r="AP24" s="9">
-        <f t="shared" si="230"/>
-        <v>0.18018250688705217</v>
-      </c>
-      <c r="AQ24" s="9">
-        <f t="shared" si="230"/>
-        <v>0.12259537530089704</v>
-      </c>
-      <c r="AR24" s="9">
-        <f t="shared" si="230"/>
-        <v>9.1902914034488026E-2</v>
-      </c>
-      <c r="AS24" s="9">
-        <f t="shared" si="230"/>
-        <v>7.3573169909846303E-2</v>
-      </c>
-      <c r="AT24" s="9">
-        <f t="shared" si="230"/>
-        <v>5.5067212796747311E-2</v>
-      </c>
-      <c r="AU24" s="9">
-        <f t="shared" si="230"/>
-        <v>3.7615581791239361E-2</v>
-      </c>
-      <c r="AV24" s="9">
-        <f t="shared" si="230"/>
-        <v>2.88280310089708E-2</v>
-      </c>
-      <c r="AW24" s="9">
-        <f t="shared" si="230"/>
-        <v>1.8838087284930083E-2</v>
-      </c>
-      <c r="AX24" s="9">
+        <v>1.8923030440879174E-2</v>
+      </c>
+      <c r="AZ24" s="9">
+        <f t="shared" si="220"/>
+        <v>1.8932461803085054E-2</v>
+      </c>
+      <c r="BA24" s="9">
         <f t="shared" si="221"/>
-        <v>1.8848166497831054E-2</v>
-      </c>
-      <c r="AY24" s="9">
-        <f t="shared" si="222"/>
-        <v>1.8858169572813166E-2</v>
-      </c>
-      <c r="AZ24" s="9">
-        <f t="shared" si="223"/>
-        <v>1.8868096889342212E-2</v>
-      </c>
-      <c r="BA24" s="9">
-        <f t="shared" si="224"/>
-        <v>1.8877948828454949E-2</v>
+        <v>1.8941820366606077E-2</v>
       </c>
     </row>
     <row r="25" spans="2:163" x14ac:dyDescent="0.3">
@@ -5464,199 +5455,199 @@
         <v>0.71105193075898798</v>
       </c>
       <c r="D25" s="9">
-        <f t="shared" ref="D25:N25" si="231">(D3-D6)/D3</f>
+        <f t="shared" ref="D25:N25" si="228">(D3-D6)/D3</f>
         <v>0.69767441860465118</v>
       </c>
       <c r="E25" s="9">
+        <f t="shared" si="228"/>
+        <v>0.70529470529470528</v>
+      </c>
+      <c r="F25" s="9">
+        <f t="shared" si="228"/>
+        <v>0.72258916776750326</v>
+      </c>
+      <c r="G25" s="9">
+        <f t="shared" si="228"/>
+        <v>0.69895678092399394</v>
+      </c>
+      <c r="H25" s="9">
+        <f t="shared" si="228"/>
+        <v>0.654144305307096</v>
+      </c>
+      <c r="I25" s="9">
+        <f t="shared" si="228"/>
+        <v>0.62576687116564422</v>
+      </c>
+      <c r="J25" s="9">
+        <f t="shared" si="228"/>
+        <v>0.62557781201849005</v>
+      </c>
+      <c r="K25" s="9">
+        <f t="shared" si="228"/>
+        <v>0.56190885640584687</v>
+      </c>
+      <c r="L25" s="9">
+        <f t="shared" si="228"/>
+        <v>0.56576797385620914</v>
+      </c>
+      <c r="M25" s="9">
+        <f t="shared" si="228"/>
+        <v>0.60964912280701755</v>
+      </c>
+      <c r="N25" s="9">
+        <f t="shared" si="228"/>
+        <v>0.63858234295415961</v>
+      </c>
+      <c r="O25" s="9">
+        <f t="shared" ref="O25:R25" si="229">(O3-O6)/O3</f>
+        <v>0.66859592711682736</v>
+      </c>
+      <c r="P25" s="9">
+        <f t="shared" si="229"/>
+        <v>0.6481307533345857</v>
+      </c>
+      <c r="Q25" s="9">
+        <f t="shared" si="229"/>
+        <v>0.6497854077253219</v>
+      </c>
+      <c r="R25" s="9">
+        <f t="shared" si="229"/>
+        <v>0.60488914155770324</v>
+      </c>
+      <c r="S25" s="9">
+        <f t="shared" ref="S25:AA25" si="230">(S3-S6)/S3</f>
+        <v>0.58726232802597</v>
+      </c>
+      <c r="T25" s="9">
+        <f t="shared" si="230"/>
+        <v>0.55909158822650529</v>
+      </c>
+      <c r="U25" s="9">
+        <f t="shared" si="230"/>
+        <v>0.55695443645083931</v>
+      </c>
+      <c r="V25" s="9">
+        <f t="shared" si="230"/>
+        <v>0.55791057021742096</v>
+      </c>
+      <c r="W25" s="9">
+        <f t="shared" si="230"/>
+        <v>0.52631578947368418</v>
+      </c>
+      <c r="X25" s="9">
+        <f t="shared" si="230"/>
+        <v>0.532195187525205</v>
+      </c>
+      <c r="Y25" s="9">
+        <f t="shared" si="230"/>
+        <v>0.48068124046771726</v>
+      </c>
+      <c r="Z25" s="9">
+        <f t="shared" si="230"/>
+        <v>0.55314271926649783</v>
+      </c>
+      <c r="AA25" s="9">
+        <f t="shared" si="230"/>
+        <v>0.52232083719697964</v>
+      </c>
+      <c r="AB25" s="9">
+        <f t="shared" ref="AB25:AD25" si="231">(AB3-AB6)/AB3</f>
+        <v>0.53354361276234374</v>
+      </c>
+      <c r="AC25" s="9">
         <f t="shared" si="231"/>
-        <v>0.70529470529470528</v>
-      </c>
-      <c r="F25" s="9">
+        <v>0.54151068046685757</v>
+      </c>
+      <c r="AD25" s="9">
         <f t="shared" si="231"/>
-        <v>0.72258916776750326</v>
-      </c>
-      <c r="G25" s="9">
-        <f t="shared" si="231"/>
-        <v>0.69895678092399394</v>
-      </c>
-      <c r="H25" s="9">
-        <f t="shared" si="231"/>
-        <v>0.654144305307096</v>
-      </c>
-      <c r="I25" s="9">
-        <f t="shared" si="231"/>
-        <v>0.62576687116564422</v>
-      </c>
-      <c r="J25" s="9">
-        <f t="shared" si="231"/>
-        <v>0.62557781201849005</v>
-      </c>
-      <c r="K25" s="9">
-        <f t="shared" si="231"/>
-        <v>0.56190885640584687</v>
-      </c>
-      <c r="L25" s="9">
-        <f t="shared" si="231"/>
-        <v>0.56576797385620914</v>
-      </c>
-      <c r="M25" s="9">
-        <f t="shared" si="231"/>
-        <v>0.60964912280701755</v>
-      </c>
-      <c r="N25" s="9">
-        <f t="shared" si="231"/>
-        <v>0.63858234295415961</v>
-      </c>
-      <c r="O25" s="9">
-        <f t="shared" ref="O25:R25" si="232">(O3-O6)/O3</f>
-        <v>0.66859592711682736</v>
-      </c>
-      <c r="P25" s="9">
+        <v>0.54080942721916347</v>
+      </c>
+      <c r="AE25" s="9">
+        <f t="shared" ref="AE25:AH25" si="232">(AE3-AE6)/AE3</f>
+        <v>0.52713442325158943</v>
+      </c>
+      <c r="AF25" s="9">
         <f t="shared" si="232"/>
-        <v>0.6481307533345857</v>
-      </c>
-      <c r="Q25" s="9">
+        <v>0.51019989748846739</v>
+      </c>
+      <c r="AG25" s="9">
         <f t="shared" si="232"/>
-        <v>0.6497854077253219</v>
-      </c>
-      <c r="R25" s="9">
+        <v>0.54</v>
+      </c>
+      <c r="AH25" s="9">
         <f t="shared" si="232"/>
-        <v>0.60488914155770324</v>
-      </c>
-      <c r="S25" s="9">
-        <f t="shared" ref="S25:AA25" si="233">(S3-S6)/S3</f>
-        <v>0.58726232802597</v>
-      </c>
-      <c r="T25" s="9">
-        <f t="shared" si="233"/>
-        <v>0.55909158822650529</v>
-      </c>
-      <c r="U25" s="9">
-        <f t="shared" si="233"/>
-        <v>0.55695443645083931</v>
-      </c>
-      <c r="V25" s="9">
-        <f t="shared" si="233"/>
-        <v>0.55791057021742096</v>
-      </c>
-      <c r="W25" s="9">
-        <f t="shared" si="233"/>
-        <v>0.52631578947368418</v>
-      </c>
-      <c r="X25" s="9">
-        <f t="shared" si="233"/>
-        <v>0.532195187525205</v>
-      </c>
-      <c r="Y25" s="9">
-        <f t="shared" si="233"/>
-        <v>0.48068124046771726</v>
-      </c>
-      <c r="Z25" s="9">
-        <f t="shared" si="233"/>
-        <v>0.55314271926649783</v>
-      </c>
-      <c r="AA25" s="9">
-        <f t="shared" si="233"/>
-        <v>0.52232083719697964</v>
-      </c>
-      <c r="AB25" s="9">
-        <f t="shared" ref="AB25:AD25" si="234">(AB3-AB6)/AB3</f>
-        <v>0.53354361276234374</v>
-      </c>
-      <c r="AC25" s="9">
+        <v>0.53999999999999992</v>
+      </c>
+      <c r="AJ25" s="9">
+        <f t="shared" ref="AJ25" si="233">(AJ3-AJ6)/AJ3</f>
+        <v>0.71096186135763972</v>
+      </c>
+      <c r="AK25" s="9">
+        <f t="shared" ref="AK25:AL25" si="234">(AK3-AK6)/AK3</f>
+        <v>0.64538336933045359</v>
+      </c>
+      <c r="AL25" s="9">
         <f t="shared" si="234"/>
-        <v>0.54151068046685757</v>
-      </c>
-      <c r="AD25" s="9">
-        <f t="shared" si="234"/>
-        <v>0.54080942721916347</v>
-      </c>
-      <c r="AE25" s="9">
-        <f t="shared" ref="AE25:AH25" si="235">(AE3-AE6)/AE3</f>
-        <v>0.52713442325158943</v>
-      </c>
-      <c r="AF25" s="9">
+        <v>0.60317084713677238</v>
+      </c>
+      <c r="AM25" s="9">
+        <f t="shared" ref="AM25:AV25" si="235">(AM3-AM6)/AM3</f>
+        <v>0.63941529169766731</v>
+      </c>
+      <c r="AN25" s="9">
         <f t="shared" si="235"/>
-        <v>0.53</v>
-      </c>
-      <c r="AG25" s="9">
+        <v>0.56496113751059041</v>
+      </c>
+      <c r="AO25" s="9">
         <f t="shared" si="235"/>
-        <v>0.54</v>
-      </c>
-      <c r="AH25" s="9">
+        <v>0.52321154231514266</v>
+      </c>
+      <c r="AP25" s="9">
         <f t="shared" si="235"/>
-        <v>0.53999999999999992</v>
-      </c>
-      <c r="AJ25" s="9">
-        <f t="shared" ref="AJ25" si="236">(AJ3-AJ6)/AJ3</f>
-        <v>0.71096186135763972</v>
-      </c>
-      <c r="AK25" s="9">
-        <f t="shared" ref="AK25:AL25" si="237">(AK3-AK6)/AK3</f>
-        <v>0.64538336933045359</v>
-      </c>
-      <c r="AL25" s="9">
-        <f t="shared" si="237"/>
-        <v>0.60317084713677238</v>
-      </c>
-      <c r="AM25" s="9">
-        <f t="shared" ref="AM25:AV25" si="238">(AM3-AM6)/AM3</f>
-        <v>0.63941529169766731</v>
-      </c>
-      <c r="AN25" s="9">
-        <f t="shared" si="238"/>
-        <v>0.56496113751059041</v>
-      </c>
-      <c r="AO25" s="9">
-        <f t="shared" si="238"/>
-        <v>0.52321154231514266</v>
-      </c>
-      <c r="AP25" s="9">
-        <f t="shared" si="238"/>
         <v>0.53532801544270014</v>
       </c>
       <c r="AQ25" s="9">
-        <f t="shared" si="238"/>
-        <v>0.53478911403834051</v>
+        <f t="shared" si="235"/>
+        <v>0.52997903887369979</v>
       </c>
       <c r="AR25" s="9">
-        <f t="shared" si="238"/>
+        <f t="shared" si="235"/>
         <v>0.55000000000000004</v>
       </c>
       <c r="AS25" s="9">
-        <f t="shared" si="238"/>
+        <f t="shared" si="235"/>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="AT25" s="9">
+        <f t="shared" si="235"/>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="AU25" s="9">
+        <f t="shared" si="235"/>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="AV25" s="9">
+        <f t="shared" si="235"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="AT25" s="9">
-        <f t="shared" si="238"/>
+      <c r="AW25" s="9">
+        <f t="shared" ref="AW25:BA25" si="236">(AW3-AW6)/AW3</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AX25" s="9">
+        <f t="shared" si="236"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AY25" s="9">
+        <f t="shared" si="236"/>
         <v>0.54999999999999993</v>
       </c>
-      <c r="AU25" s="9">
-        <f t="shared" si="238"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="AV25" s="9">
-        <f t="shared" si="238"/>
+      <c r="AZ25" s="9">
+        <f t="shared" si="236"/>
         <v>0.54999999999999993</v>
       </c>
-      <c r="AW25" s="9">
-        <f t="shared" ref="AW25:BA25" si="239">(AW3-AW6)/AW3</f>
-        <v>0.54999999999999993</v>
-      </c>
-      <c r="AX25" s="9">
-        <f t="shared" si="239"/>
-        <v>0.54999999999999993</v>
-      </c>
-      <c r="AY25" s="9">
-        <f t="shared" si="239"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="AZ25" s="9">
-        <f t="shared" si="239"/>
-        <v>0.55000000000000004</v>
-      </c>
       <c r="BA25" s="9">
-        <f t="shared" si="239"/>
+        <f t="shared" si="236"/>
         <v>0.55000000000000004</v>
       </c>
       <c r="BC25" t="s">
@@ -5671,204 +5662,204 @@
         <v>44</v>
       </c>
       <c r="C26" s="9">
-        <f t="shared" ref="C26:N26" si="240">(C4-C7)/C4</f>
+        <f t="shared" ref="C26:N26" si="237">(C4-C7)/C4</f>
         <v>0.15772357723577241</v>
       </c>
       <c r="D26" s="9">
+        <f t="shared" si="237"/>
+        <v>0.22255639097744356</v>
+      </c>
+      <c r="E26" s="9">
+        <f t="shared" si="237"/>
+        <v>0.11459754433833549</v>
+      </c>
+      <c r="F26" s="9">
+        <f t="shared" si="237"/>
+        <v>2.3330651649235652E-2</v>
+      </c>
+      <c r="G26" s="9">
+        <f t="shared" si="237"/>
+        <v>9.7931034482758542E-2</v>
+      </c>
+      <c r="H26" s="9">
+        <f t="shared" si="237"/>
+        <v>5.461165048543689E-2</v>
+      </c>
+      <c r="I26" s="9">
+        <f t="shared" si="237"/>
+        <v>7.5980392156862614E-2</v>
+      </c>
+      <c r="J26" s="9">
+        <f t="shared" si="237"/>
+        <v>-4.617414248021221E-3</v>
+      </c>
+      <c r="K26" s="9">
+        <f t="shared" si="237"/>
+        <v>0.11904761904761904</v>
+      </c>
+      <c r="L26" s="9">
+        <f t="shared" si="237"/>
+        <v>7.5471698113207475E-2</v>
+      </c>
+      <c r="M26" s="9">
+        <f t="shared" si="237"/>
+        <v>0.15181268882175233</v>
+      </c>
+      <c r="N26" s="9">
+        <f t="shared" si="237"/>
+        <v>2.5741466144376019E-2</v>
+      </c>
+      <c r="O26" s="9">
+        <f t="shared" ref="O26:R26" si="238">(O4-O7)/O4</f>
+        <v>0.13834726090993504</v>
+      </c>
+      <c r="P26" s="9">
+        <f t="shared" si="238"/>
+        <v>-5.9397163120567399E-2</v>
+      </c>
+      <c r="Q26" s="9">
+        <f t="shared" si="238"/>
+        <v>-0.14989733059548249</v>
+      </c>
+      <c r="R26" s="9">
+        <f t="shared" si="238"/>
+        <v>-0.28447742733457021</v>
+      </c>
+      <c r="S26" s="9">
+        <f t="shared" ref="S26:AA26" si="239">(S4-S7)/S4</f>
+        <v>-0.1739631336405531</v>
+      </c>
+      <c r="T26" s="9">
+        <f t="shared" si="239"/>
+        <v>-0.19957983193277309</v>
+      </c>
+      <c r="U26" s="9">
+        <f t="shared" si="239"/>
+        <v>-0.1571125265392781</v>
+      </c>
+      <c r="V26" s="9">
+        <f t="shared" si="239"/>
+        <v>-0.32106038291605293</v>
+      </c>
+      <c r="W26" s="9">
+        <f t="shared" si="239"/>
+        <v>3.3834586466165495E-2</v>
+      </c>
+      <c r="X26" s="9">
+        <f t="shared" si="239"/>
+        <v>-0.16924564796905223</v>
+      </c>
+      <c r="Y26" s="9">
+        <f t="shared" si="239"/>
+        <v>-7.5079872204472778E-2</v>
+      </c>
+      <c r="Z26" s="9">
+        <f t="shared" si="239"/>
+        <v>-0.13174807197943444</v>
+      </c>
+      <c r="AA26" s="9">
+        <f t="shared" si="239"/>
+        <v>-4.8221343873517744E-2</v>
+      </c>
+      <c r="AB26" s="9">
+        <f t="shared" ref="AB26:AD26" si="240">(AB4-AB7)/AB4</f>
+        <v>-0.10570236439499296</v>
+      </c>
+      <c r="AC26" s="9">
         <f t="shared" si="240"/>
-        <v>0.22255639097744356</v>
-      </c>
-      <c r="E26" s="9">
+        <v>-7.5974025974025902E-2</v>
+      </c>
+      <c r="AD26" s="9">
         <f t="shared" si="240"/>
-        <v>0.11459754433833549</v>
-      </c>
-      <c r="F26" s="9">
-        <f t="shared" si="240"/>
-        <v>2.3330651649235652E-2</v>
-      </c>
-      <c r="G26" s="9">
-        <f t="shared" si="240"/>
-        <v>9.7931034482758542E-2</v>
-      </c>
-      <c r="H26" s="9">
-        <f t="shared" si="240"/>
-        <v>5.461165048543689E-2</v>
-      </c>
-      <c r="I26" s="9">
-        <f t="shared" si="240"/>
-        <v>7.5980392156862614E-2</v>
-      </c>
-      <c r="J26" s="9">
-        <f t="shared" si="240"/>
-        <v>-4.617414248021221E-3</v>
-      </c>
-      <c r="K26" s="9">
-        <f t="shared" si="240"/>
-        <v>0.11904761904761904</v>
-      </c>
-      <c r="L26" s="9">
-        <f t="shared" si="240"/>
-        <v>7.5471698113207475E-2</v>
-      </c>
-      <c r="M26" s="9">
-        <f t="shared" si="240"/>
-        <v>0.15181268882175233</v>
-      </c>
-      <c r="N26" s="9">
-        <f t="shared" si="240"/>
-        <v>2.5741466144376019E-2</v>
-      </c>
-      <c r="O26" s="9">
-        <f t="shared" ref="O26:R26" si="241">(O4-O7)/O4</f>
-        <v>0.13834726090993504</v>
-      </c>
-      <c r="P26" s="9">
+        <v>-0.28605914302957158</v>
+      </c>
+      <c r="AE26" s="9">
+        <f t="shared" ref="AE26:AH26" si="241">(AE4-AE7)/AE4</f>
+        <v>-0.1372408863473909</v>
+      </c>
+      <c r="AF26" s="9">
         <f t="shared" si="241"/>
-        <v>-5.9397163120567399E-2</v>
-      </c>
-      <c r="Q26" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="9">
         <f t="shared" si="241"/>
-        <v>-0.14989733059548249</v>
-      </c>
-      <c r="R26" s="9">
+        <v>-9.0000000000000066E-2</v>
+      </c>
+      <c r="AH26" s="9">
         <f t="shared" si="241"/>
-        <v>-0.28447742733457021</v>
-      </c>
-      <c r="S26" s="9">
-        <f t="shared" ref="S26:AA26" si="242">(S4-S7)/S4</f>
-        <v>-0.1739631336405531</v>
-      </c>
-      <c r="T26" s="9">
-        <f t="shared" si="242"/>
-        <v>-0.19957983193277309</v>
-      </c>
-      <c r="U26" s="9">
-        <f t="shared" si="242"/>
-        <v>-0.1571125265392781</v>
-      </c>
-      <c r="V26" s="9">
-        <f t="shared" si="242"/>
-        <v>-0.32106038291605293</v>
-      </c>
-      <c r="W26" s="9">
-        <f t="shared" si="242"/>
-        <v>3.3834586466165495E-2</v>
-      </c>
-      <c r="X26" s="9">
-        <f t="shared" si="242"/>
-        <v>-0.16924564796905223</v>
-      </c>
-      <c r="Y26" s="9">
-        <f t="shared" si="242"/>
-        <v>-7.5079872204472778E-2</v>
-      </c>
-      <c r="Z26" s="9">
-        <f t="shared" si="242"/>
-        <v>-0.13174807197943444</v>
-      </c>
-      <c r="AA26" s="9">
-        <f t="shared" si="242"/>
-        <v>-4.8221343873517744E-2</v>
-      </c>
-      <c r="AB26" s="9">
-        <f t="shared" ref="AB26:AD26" si="243">(AB4-AB7)/AB4</f>
-        <v>-0.10570236439499296</v>
-      </c>
-      <c r="AC26" s="9">
+        <v>-0.19999999999999996</v>
+      </c>
+      <c r="AJ26" s="9">
+        <f t="shared" ref="AJ26" si="242">(AJ4-AJ7)/AJ4</f>
+        <v>0.10995085995085997</v>
+      </c>
+      <c r="AK26" s="9">
+        <f t="shared" ref="AK26:AL26" si="243">(AK4-AK7)/AK4</f>
+        <v>4.4060809069827421E-2</v>
+      </c>
+      <c r="AL26" s="9">
         <f t="shared" si="243"/>
-        <v>-7.5974025974025902E-2</v>
-      </c>
-      <c r="AD26" s="9">
-        <f t="shared" si="243"/>
-        <v>-0.28605914302957158</v>
-      </c>
-      <c r="AE26" s="9">
-        <f t="shared" ref="AE26:AH26" si="244">(AE4-AE7)/AE4</f>
-        <v>-0.1372408863473909</v>
-      </c>
-      <c r="AF26" s="9">
+        <v>8.538973756365055E-2</v>
+      </c>
+      <c r="AM26" s="9">
+        <f t="shared" ref="AM26:AV26" si="244">(AM4-AM7)/AM4</f>
+        <v>-0.10925771476230199</v>
+      </c>
+      <c r="AN26" s="9">
         <f t="shared" si="244"/>
-        <v>-7.0000000000000048E-2</v>
-      </c>
-      <c r="AG26" s="9">
+        <v>-0.22451456310679613</v>
+      </c>
+      <c r="AO26" s="9">
         <f t="shared" si="244"/>
-        <v>-9.0000000000000024E-2</v>
-      </c>
-      <c r="AH26" s="9">
+        <v>-8.92784345699143E-2</v>
+      </c>
+      <c r="AP26" s="9">
         <f t="shared" si="244"/>
-        <v>-0.19999999999999996</v>
-      </c>
-      <c r="AJ26" s="9">
-        <f t="shared" ref="AJ26" si="245">(AJ4-AJ7)/AJ4</f>
-        <v>0.10995085995085997</v>
-      </c>
-      <c r="AK26" s="9">
-        <f t="shared" ref="AK26:AL26" si="246">(AK4-AK7)/AK4</f>
-        <v>4.4060809069827421E-2</v>
-      </c>
-      <c r="AL26" s="9">
-        <f t="shared" si="246"/>
-        <v>8.538973756365055E-2</v>
-      </c>
-      <c r="AM26" s="9">
-        <f t="shared" ref="AM26:AV26" si="247">(AM4-AM7)/AM4</f>
-        <v>-0.10925771476230199</v>
-      </c>
-      <c r="AN26" s="9">
-        <f t="shared" si="247"/>
-        <v>-0.22451456310679613</v>
-      </c>
-      <c r="AO26" s="9">
-        <f t="shared" si="247"/>
-        <v>-8.92784345699143E-2</v>
-      </c>
-      <c r="AP26" s="9">
-        <f t="shared" si="247"/>
         <v>-0.13627118644067793</v>
       </c>
       <c r="AQ26" s="9">
-        <f t="shared" si="247"/>
-        <v>-0.12580007928648587</v>
+        <f t="shared" si="244"/>
+        <v>-0.11165895069443749</v>
       </c>
       <c r="AR26" s="9">
-        <f t="shared" si="247"/>
-        <v>-4.9999999999999968E-2</v>
+        <f t="shared" si="244"/>
+        <v>-5.000000000000001E-2</v>
       </c>
       <c r="AS26" s="9">
-        <f t="shared" si="247"/>
-        <v>-1.0000000000000059E-2</v>
+        <f t="shared" si="244"/>
+        <v>-1.0000000000000014E-2</v>
       </c>
       <c r="AT26" s="9">
-        <f t="shared" si="247"/>
+        <f t="shared" si="244"/>
+        <v>9.9999999999999794E-3</v>
+      </c>
+      <c r="AU26" s="9">
+        <f t="shared" si="244"/>
+        <v>9.9999999999999725E-3</v>
+      </c>
+      <c r="AV26" s="9">
+        <f t="shared" si="244"/>
+        <v>1.0000000000000083E-2</v>
+      </c>
+      <c r="AW26" s="9">
+        <f t="shared" ref="AW26:BA26" si="245">(AW4-AW7)/AW4</f>
+        <v>9.999999999999962E-3</v>
+      </c>
+      <c r="AX26" s="9">
+        <f t="shared" si="245"/>
+        <v>1.0000000000000071E-2</v>
+      </c>
+      <c r="AY26" s="9">
+        <f t="shared" si="245"/>
         <v>9.999999999999936E-3</v>
       </c>
-      <c r="AU26" s="9">
-        <f t="shared" si="247"/>
-        <v>9.9999999999999534E-3</v>
-      </c>
-      <c r="AV26" s="9">
-        <f t="shared" si="247"/>
-        <v>1.0000000000000049E-2</v>
-      </c>
-      <c r="AW26" s="9">
-        <f t="shared" ref="AW26:BA26" si="248">(AW4-AW7)/AW4</f>
-        <v>9.9999999999999846E-3</v>
-      </c>
-      <c r="AX26" s="9">
-        <f t="shared" si="248"/>
-        <v>9.9999999999999811E-3</v>
-      </c>
-      <c r="AY26" s="9">
-        <f t="shared" si="248"/>
-        <v>1.0000000000000071E-2</v>
-      </c>
       <c r="AZ26" s="9">
-        <f t="shared" si="248"/>
-        <v>9.9999999999999933E-3</v>
+        <f t="shared" si="245"/>
+        <v>9.9999999999999568E-3</v>
       </c>
       <c r="BA26" s="9">
-        <f t="shared" si="248"/>
-        <v>9.9999999999999707E-3</v>
+        <f t="shared" si="245"/>
+        <v>1.0000000000000023E-2</v>
       </c>
       <c r="BC26" t="s">
         <v>48</v>
@@ -5886,35 +5877,35 @@
         <v>0.46193265007320644</v>
       </c>
       <c r="D27" s="9">
-        <f t="shared" ref="D27:G27" si="249">D9/D5</f>
+        <f t="shared" ref="D27:G27" si="246">D9/D5</f>
         <v>0.49617346938775514</v>
       </c>
       <c r="E27" s="9">
-        <f t="shared" si="249"/>
+        <f t="shared" si="246"/>
         <v>0.45559400230680497</v>
       </c>
       <c r="F27" s="9">
-        <f t="shared" si="249"/>
+        <f t="shared" si="246"/>
         <v>0.4073268044976423</v>
       </c>
       <c r="G27" s="9">
-        <f t="shared" si="249"/>
+        <f t="shared" si="246"/>
         <v>0.48814707305273336</v>
       </c>
       <c r="H27" s="9">
-        <f t="shared" ref="H27:N27" si="250">H9/H5</f>
+        <f t="shared" ref="H27:N27" si="247">H9/H5</f>
         <v>0.45661735305877643</v>
       </c>
       <c r="I27" s="9">
-        <f t="shared" si="250"/>
+        <f t="shared" si="247"/>
         <v>0.45381372173246448</v>
       </c>
       <c r="J27" s="9">
-        <f t="shared" si="250"/>
+        <f t="shared" si="247"/>
         <v>0.39323929961089499</v>
       </c>
       <c r="K27" s="9">
-        <f t="shared" si="250"/>
+        <f t="shared" si="247"/>
         <v>0.44014962593516205</v>
       </c>
       <c r="L27" s="9">
@@ -5922,171 +5913,171 @@
         <v>0.41252457174950863</v>
       </c>
       <c r="M27" s="9">
+        <f t="shared" si="247"/>
+        <v>0.47542072630646598</v>
+      </c>
+      <c r="N27" s="9">
+        <f t="shared" si="247"/>
+        <v>0.47007231881827977</v>
+      </c>
+      <c r="O27" s="9">
+        <f t="shared" ref="O27:R27" si="248">O9/O5</f>
+        <v>0.56913967258794851</v>
+      </c>
+      <c r="P27" s="9">
+        <f t="shared" si="248"/>
+        <v>0.52441481940784362</v>
+      </c>
+      <c r="Q27" s="9">
+        <f t="shared" si="248"/>
+        <v>0.53522576849536696</v>
+      </c>
+      <c r="R27" s="9">
+        <f t="shared" si="248"/>
+        <v>0.4386917831965792</v>
+      </c>
+      <c r="S27" s="9">
+        <f t="shared" ref="S27:AA27" si="249">S9/S5</f>
+        <v>0.4972059424833038</v>
+      </c>
+      <c r="T27" s="9">
+        <f t="shared" si="249"/>
+        <v>0.46461739699149768</v>
+      </c>
+      <c r="U27" s="9">
+        <f t="shared" si="249"/>
+        <v>0.46861045442605731</v>
+      </c>
+      <c r="V27" s="9">
+        <f t="shared" si="249"/>
+        <v>0.42025141275516076</v>
+      </c>
+      <c r="W27" s="9">
+        <f t="shared" si="249"/>
+        <v>0.45560053981106607</v>
+      </c>
+      <c r="X27" s="9">
+        <f t="shared" si="249"/>
+        <v>0.4465950666824029</v>
+      </c>
+      <c r="Y27" s="9">
+        <f t="shared" si="249"/>
+        <v>0.40438596491228063</v>
+      </c>
+      <c r="Z27" s="9">
+        <f t="shared" si="249"/>
+        <v>0.44489588623666837</v>
+      </c>
+      <c r="AA27" s="9">
+        <f t="shared" si="249"/>
+        <v>0.44043567052416605</v>
+      </c>
+      <c r="AB27" s="9">
+        <f t="shared" ref="AB27:AD27" si="250">AB9/AB5</f>
+        <v>0.43859105464311532</v>
+      </c>
+      <c r="AC27" s="9">
         <f t="shared" si="250"/>
-        <v>0.47542072630646598</v>
-      </c>
-      <c r="N27" s="9">
+        <v>0.45198644323103004</v>
+      </c>
+      <c r="AD27" s="9">
         <f t="shared" si="250"/>
-        <v>0.47007231881827977</v>
-      </c>
-      <c r="O27" s="9">
-        <f t="shared" ref="O27:R27" si="251">O9/O5</f>
-        <v>0.56913967258794851</v>
-      </c>
-      <c r="P27" s="9">
+        <v>0.42672772689425481</v>
+      </c>
+      <c r="AE27" s="9">
+        <f t="shared" ref="AE27:AH27" si="251">AE9/AE5</f>
+        <v>0.4360732830410502</v>
+      </c>
+      <c r="AF27" s="9">
         <f t="shared" si="251"/>
-        <v>0.52441481940784362</v>
-      </c>
-      <c r="Q27" s="9">
+        <v>0.44793447934479341</v>
+      </c>
+      <c r="AG27" s="9">
         <f t="shared" si="251"/>
-        <v>0.53522576849536696</v>
-      </c>
-      <c r="R27" s="9">
+        <v>0.45708436071571806</v>
+      </c>
+      <c r="AH27" s="9">
         <f t="shared" si="251"/>
-        <v>0.4386917831965792</v>
-      </c>
-      <c r="S27" s="9">
-        <f t="shared" ref="S27:AA27" si="252">S9/S5</f>
-        <v>0.4972059424833038</v>
-      </c>
-      <c r="T27" s="9">
-        <f t="shared" si="252"/>
-        <v>0.46461739699149768</v>
-      </c>
-      <c r="U27" s="9">
-        <f t="shared" si="252"/>
-        <v>0.46861045442605731</v>
-      </c>
-      <c r="V27" s="9">
-        <f t="shared" si="252"/>
-        <v>0.42025141275516076</v>
-      </c>
-      <c r="W27" s="9">
-        <f t="shared" si="252"/>
-        <v>0.45560053981106607</v>
-      </c>
-      <c r="X27" s="9">
-        <f t="shared" si="252"/>
-        <v>0.4465950666824029</v>
-      </c>
-      <c r="Y27" s="9">
-        <f t="shared" si="252"/>
-        <v>0.40438596491228063</v>
-      </c>
-      <c r="Z27" s="9">
-        <f t="shared" si="252"/>
-        <v>0.44489588623666837</v>
-      </c>
-      <c r="AA27" s="9">
-        <f t="shared" si="252"/>
-        <v>0.44043567052416605</v>
-      </c>
-      <c r="AB27" s="9">
-        <f t="shared" ref="AB27:AD27" si="253">AB9/AB5</f>
-        <v>0.43859105464311532</v>
-      </c>
-      <c r="AC27" s="9">
+        <v>0.44512012999574418</v>
+      </c>
+      <c r="AJ27" s="9">
+        <f t="shared" ref="AJ27" si="252">AJ9/AJ5</f>
+        <v>0.44740740740740736</v>
+      </c>
+      <c r="AK27" s="9">
+        <f t="shared" ref="AK27:AL27" si="253">AK9/AK5</f>
+        <v>0.4386570998316946</v>
+      </c>
+      <c r="AL27" s="9">
         <f t="shared" si="253"/>
-        <v>0.45198644323103004</v>
-      </c>
-      <c r="AD27" s="9">
-        <f t="shared" si="253"/>
-        <v>0.42672772689425481</v>
-      </c>
-      <c r="AE27" s="9">
-        <f t="shared" ref="AE27:AH27" si="254">AE9/AE5</f>
-        <v>0.4360732830410502</v>
-      </c>
-      <c r="AF27" s="9">
+        <v>0.45450967161493477</v>
+      </c>
+      <c r="AM27" s="9">
+        <f t="shared" ref="AM27:AV27" si="254">AM9/AM5</f>
+        <v>0.50953156086091511</v>
+      </c>
+      <c r="AN27" s="9">
         <f t="shared" si="254"/>
-        <v>0.44621103800924117</v>
-      </c>
-      <c r="AG27" s="9">
+        <v>0.46093325231074295</v>
+      </c>
+      <c r="AO27" s="9">
         <f t="shared" si="254"/>
-        <v>0.45566226624333489</v>
-      </c>
-      <c r="AH27" s="9">
+        <v>0.43698347107438018</v>
+      </c>
+      <c r="AP27" s="9">
         <f t="shared" si="254"/>
-        <v>0.44355368953517404</v>
-      </c>
-      <c r="AJ27" s="9">
-        <f t="shared" ref="AJ27" si="255">AJ9/AJ5</f>
-        <v>0.44740740740740736</v>
-      </c>
-      <c r="AK27" s="9">
-        <f t="shared" ref="AK27:AL27" si="256">AK9/AK5</f>
-        <v>0.4386570998316946</v>
-      </c>
-      <c r="AL27" s="9">
-        <f t="shared" si="256"/>
-        <v>0.45450967161493477</v>
-      </c>
-      <c r="AM27" s="9">
-        <f t="shared" ref="AM27:AV27" si="257">AM9/AM5</f>
-        <v>0.50953156086091511</v>
-      </c>
-      <c r="AN27" s="9">
-        <f t="shared" si="257"/>
-        <v>0.46093325231074295</v>
-      </c>
-      <c r="AO27" s="9">
-        <f t="shared" si="257"/>
-        <v>0.43698347107438018</v>
-      </c>
-      <c r="AP27" s="9">
-        <f t="shared" si="257"/>
         <v>0.43898169086001887</v>
       </c>
       <c r="AQ27" s="9">
-        <f t="shared" si="257"/>
-        <v>0.44564165593435234</v>
+        <f t="shared" si="254"/>
+        <v>0.44685429410534089</v>
       </c>
       <c r="AR27" s="9">
-        <f t="shared" si="257"/>
-        <v>0.47287803891815228</v>
+        <f t="shared" si="254"/>
+        <v>0.47719188155100351</v>
       </c>
       <c r="AS27" s="9">
-        <f t="shared" si="257"/>
-        <v>0.48094097915446021</v>
+        <f t="shared" si="254"/>
+        <v>0.48482564222311098</v>
       </c>
       <c r="AT27" s="9">
-        <f t="shared" si="257"/>
-        <v>0.4856207083634615</v>
+        <f t="shared" si="254"/>
+        <v>0.48925810508226569</v>
       </c>
       <c r="AU27" s="9">
-        <f t="shared" si="257"/>
-        <v>0.48671367448442876</v>
+        <f t="shared" si="254"/>
+        <v>0.49029707068757206</v>
       </c>
       <c r="AV27" s="9">
-        <f t="shared" si="257"/>
-        <v>0.48725671338622389</v>
+        <f t="shared" si="254"/>
+        <v>0.49081317919620265</v>
       </c>
       <c r="AW27" s="9">
-        <f t="shared" ref="AW27:BA27" si="258">AW9/AW5</f>
-        <v>0.48780099088287082</v>
+        <f t="shared" ref="AW27:BA27" si="255">AW9/AW5</f>
+        <v>0.49133039807816481</v>
       </c>
       <c r="AX27" s="9">
-        <f t="shared" si="258"/>
-        <v>0.48834115693191055</v>
+        <f t="shared" si="255"/>
+        <v>0.49184364380748125</v>
       </c>
       <c r="AY27" s="9">
-        <f t="shared" si="258"/>
-        <v>0.48887723202447192</v>
+        <f t="shared" si="255"/>
+        <v>0.49235293736659519</v>
       </c>
       <c r="AZ27" s="9">
-        <f t="shared" si="258"/>
-        <v>0.48940923673657022</v>
+        <f t="shared" si="255"/>
+        <v>0.49285829979672308</v>
       </c>
       <c r="BA27" s="9">
-        <f t="shared" si="258"/>
-        <v>0.4899371917250438</v>
+        <f t="shared" si="255"/>
+        <v>0.49335975219414874</v>
       </c>
       <c r="BC27" t="s">
         <v>49</v>
       </c>
       <c r="BD27" s="5">
         <f>NPV(BD26,AP18:FG18)</f>
-        <v>4717.683312157913</v>
+        <v>5134.237396951924</v>
       </c>
     </row>
     <row r="28" spans="2:163" x14ac:dyDescent="0.3">
@@ -6098,207 +6089,207 @@
         <v>-5.0512445095168418E-2</v>
       </c>
       <c r="D28" s="9">
-        <f t="shared" ref="D28:G28" si="259">D14/D5</f>
+        <f t="shared" ref="D28:G28" si="256">D14/D5</f>
         <v>-6.3775510204078006E-4</v>
       </c>
       <c r="E28" s="9">
+        <f t="shared" si="256"/>
+        <v>-6.8050749711649525E-2</v>
+      </c>
+      <c r="F28" s="9">
+        <f t="shared" si="256"/>
+        <v>1.9949220166847973E-2</v>
+      </c>
+      <c r="G28" s="9">
+        <f t="shared" si="256"/>
+        <v>-5.1765844218674494E-2</v>
+      </c>
+      <c r="H28" s="9">
+        <f t="shared" ref="H28:N28" si="257">H14/H5</f>
+        <v>-4.1583366653338685E-2</v>
+      </c>
+      <c r="I28" s="9">
+        <f t="shared" si="257"/>
+        <v>-0.10233806055960146</v>
+      </c>
+      <c r="J28" s="9">
+        <f t="shared" si="257"/>
+        <v>-4.2071984435797551E-2</v>
+      </c>
+      <c r="K28" s="9">
+        <f t="shared" si="257"/>
+        <v>-0.17144638403990026</v>
+      </c>
+      <c r="L28" s="9">
+        <f t="shared" si="257"/>
+        <v>-0.11850603762987921</v>
+      </c>
+      <c r="M28" s="9">
+        <f t="shared" si="257"/>
+        <v>2.6129317980513815E-2</v>
+      </c>
+      <c r="N28" s="9">
+        <f t="shared" si="257"/>
+        <v>0.10032312663486689</v>
+      </c>
+      <c r="O28" s="9">
+        <f t="shared" ref="O28:R28" si="258">O14/O5</f>
+        <v>0.13200975269940798</v>
+      </c>
+      <c r="P28" s="9">
+        <f t="shared" si="258"/>
+        <v>0.10711517594171434</v>
+      </c>
+      <c r="Q28" s="9">
+        <f t="shared" si="258"/>
+        <v>0.10119135166936308</v>
+      </c>
+      <c r="R28" s="9">
+        <f t="shared" si="258"/>
+        <v>2.461574020570895E-2</v>
+      </c>
+      <c r="S28" s="9">
+        <f t="shared" ref="S28:AA28" si="259">S14/S5</f>
+        <v>-3.2029439825541857E-2</v>
+      </c>
+      <c r="T28" s="9">
         <f t="shared" si="259"/>
-        <v>-6.8050749711649525E-2</v>
-      </c>
-      <c r="F28" s="9">
+        <v>-0.14453891432308705</v>
+      </c>
+      <c r="U28" s="9">
         <f t="shared" si="259"/>
-        <v>1.9949220166847973E-2</v>
-      </c>
-      <c r="G28" s="9">
+        <v>-0.19306540583136317</v>
+      </c>
+      <c r="V28" s="9">
         <f t="shared" si="259"/>
-        <v>-5.1765844218674494E-2</v>
-      </c>
-      <c r="H28" s="9">
-        <f t="shared" ref="H28:N28" si="260">H14/H5</f>
-        <v>-4.1583366653338685E-2</v>
-      </c>
-      <c r="I28" s="9">
+        <v>-0.28820205281974409</v>
+      </c>
+      <c r="W28" s="9">
+        <f t="shared" si="259"/>
+        <v>-0.28677462887989214</v>
+      </c>
+      <c r="X28" s="9">
+        <f t="shared" si="259"/>
+        <v>-0.14858963767260716</v>
+      </c>
+      <c r="Y28" s="9">
+        <f t="shared" si="259"/>
+        <v>-0.38355263157894731</v>
+      </c>
+      <c r="Z28" s="9">
+        <f t="shared" si="259"/>
+        <v>-0.10573895378364655</v>
+      </c>
+      <c r="AA28" s="9">
+        <f t="shared" si="259"/>
+        <v>-8.1688223281143696E-2</v>
+      </c>
+      <c r="AB28" s="9">
+        <f t="shared" ref="AB28:AD28" si="260">AB14/AB5</f>
+        <v>-7.3752711496746309E-2</v>
+      </c>
+      <c r="AC28" s="9">
         <f t="shared" si="260"/>
-        <v>-0.10233806055960146</v>
-      </c>
-      <c r="J28" s="9">
+        <v>-3.3609489738278868E-2</v>
+      </c>
+      <c r="AD28" s="9">
         <f t="shared" si="260"/>
-        <v>-4.2071984435797551E-2</v>
-      </c>
-      <c r="K28" s="9">
-        <f t="shared" si="260"/>
-        <v>-0.17144638403990026</v>
-      </c>
-      <c r="L28" s="9">
-        <f t="shared" si="260"/>
-        <v>-0.11850603762987921</v>
-      </c>
-      <c r="M28" s="9">
-        <f t="shared" si="260"/>
-        <v>2.6129317980513815E-2</v>
-      </c>
-      <c r="N28" s="9">
-        <f t="shared" si="260"/>
-        <v>0.10032312663486689</v>
-      </c>
-      <c r="O28" s="9">
-        <f t="shared" ref="O28:R28" si="261">O14/O5</f>
-        <v>0.13200975269940798</v>
-      </c>
-      <c r="P28" s="9">
+        <v>-3.2639467110740991E-2</v>
+      </c>
+      <c r="AE28" s="9">
+        <f t="shared" ref="AE28:AH28" si="261">AE14/AE5</f>
+        <v>-5.6529832467914223E-2</v>
+      </c>
+      <c r="AF28" s="9">
         <f t="shared" si="261"/>
-        <v>0.10711517594171434</v>
-      </c>
-      <c r="Q28" s="9">
+        <v>-2.0970209702097085E-2</v>
+      </c>
+      <c r="AG28" s="9">
         <f t="shared" si="261"/>
-        <v>0.10119135166936308</v>
-      </c>
-      <c r="R28" s="9">
+        <v>-1.0441883016332735E-2</v>
+      </c>
+      <c r="AH28" s="9">
         <f t="shared" si="261"/>
-        <v>2.461574020570895E-2</v>
-      </c>
-      <c r="S28" s="9">
-        <f t="shared" ref="S28:AA28" si="262">S14/S5</f>
-        <v>-3.2029439825541857E-2</v>
-      </c>
-      <c r="T28" s="9">
-        <f t="shared" si="262"/>
-        <v>-0.14453891432308705</v>
-      </c>
-      <c r="U28" s="9">
-        <f t="shared" si="262"/>
-        <v>-0.19306540583136317</v>
-      </c>
-      <c r="V28" s="9">
-        <f t="shared" si="262"/>
-        <v>-0.28820205281974409</v>
-      </c>
-      <c r="W28" s="9">
-        <f t="shared" si="262"/>
-        <v>-0.28677462887989214</v>
-      </c>
-      <c r="X28" s="9">
-        <f t="shared" si="262"/>
-        <v>-0.14858963767260716</v>
-      </c>
-      <c r="Y28" s="9">
-        <f t="shared" si="262"/>
-        <v>-0.38355263157894731</v>
-      </c>
-      <c r="Z28" s="9">
-        <f t="shared" si="262"/>
-        <v>-0.10573895378364655</v>
-      </c>
-      <c r="AA28" s="9">
-        <f t="shared" si="262"/>
-        <v>-8.1688223281143696E-2</v>
-      </c>
-      <c r="AB28" s="9">
-        <f t="shared" ref="AB28:AD28" si="263">AB14/AB5</f>
-        <v>-7.3752711496746309E-2</v>
-      </c>
-      <c r="AC28" s="9">
+        <v>6.4927169459496432E-3</v>
+      </c>
+      <c r="AJ28" s="9">
+        <f t="shared" ref="AJ28" si="262">AJ14/AJ5</f>
+        <v>-1.7912457912457928E-2</v>
+      </c>
+      <c r="AK28" s="9">
+        <f t="shared" ref="AK28:AL28" si="263">AK14/AK5</f>
+        <v>-5.7666755248471882E-2</v>
+      </c>
+      <c r="AL28" s="9">
         <f t="shared" si="263"/>
-        <v>-3.3609489738278868E-2</v>
-      </c>
-      <c r="AD28" s="9">
-        <f t="shared" si="263"/>
-        <v>-3.2639467110740991E-2</v>
-      </c>
-      <c r="AE28" s="9">
-        <f t="shared" ref="AE28:AH28" si="264">AE14/AE5</f>
-        <v>-5.6529832467914223E-2</v>
-      </c>
-      <c r="AF28" s="9">
+        <v>-1.1358524516419279E-2</v>
+      </c>
+      <c r="AM28" s="9">
+        <f t="shared" ref="AM28:AV28" si="264">AM14/AM5</f>
+        <v>8.5006330258636201E-2</v>
+      </c>
+      <c r="AN28" s="9">
         <f t="shared" si="264"/>
-        <v>-3.6582671619724248E-2</v>
-      </c>
-      <c r="AG28" s="9">
+        <v>-0.16979563117664001</v>
+      </c>
+      <c r="AO28" s="9">
         <f t="shared" si="264"/>
-        <v>-1.1220556239165515E-2</v>
-      </c>
-      <c r="AH28" s="9">
+        <v>-0.22735881542699715</v>
+      </c>
+      <c r="AP28" s="9">
         <f t="shared" si="264"/>
-        <v>3.4744379729378248E-3</v>
-      </c>
-      <c r="AJ28" s="9">
-        <f t="shared" ref="AJ28" si="265">AJ14/AJ5</f>
-        <v>-1.7912457912457928E-2</v>
-      </c>
-      <c r="AK28" s="9">
-        <f t="shared" ref="AK28:AL28" si="266">AK14/AK5</f>
-        <v>-5.7666755248471882E-2</v>
-      </c>
-      <c r="AL28" s="9">
-        <f t="shared" si="266"/>
-        <v>-1.1358524516419279E-2</v>
-      </c>
-      <c r="AM28" s="9">
-        <f t="shared" ref="AM28:AV28" si="267">AM14/AM5</f>
-        <v>8.5006330258636201E-2</v>
-      </c>
-      <c r="AN28" s="9">
-        <f t="shared" si="267"/>
-        <v>-0.16979563117664001</v>
-      </c>
-      <c r="AO28" s="9">
-        <f t="shared" si="267"/>
-        <v>-0.22735881542699715</v>
-      </c>
-      <c r="AP28" s="9">
-        <f t="shared" si="267"/>
         <v>-5.3079485496146134E-2</v>
       </c>
       <c r="AQ28" s="9">
-        <f t="shared" si="267"/>
-        <v>-2.3122124422068839E-2</v>
+        <f t="shared" si="264"/>
+        <v>-1.8304232714560473E-2</v>
       </c>
       <c r="AR28" s="9">
-        <f t="shared" si="267"/>
-        <v>3.0322813692389823E-2</v>
+        <f t="shared" si="264"/>
+        <v>3.9388076329756438E-2</v>
       </c>
       <c r="AS28" s="9">
-        <f t="shared" si="267"/>
-        <v>6.1409581800431295E-2</v>
+        <f t="shared" si="264"/>
+        <v>6.9847781190379571E-2</v>
       </c>
       <c r="AT28" s="9">
-        <f t="shared" si="267"/>
-        <v>8.4744172634695455E-2</v>
+        <f t="shared" si="264"/>
+        <v>9.2806245857962891E-2</v>
       </c>
       <c r="AU28" s="9">
-        <f t="shared" si="267"/>
-        <v>9.073934366716073E-2</v>
+        <f t="shared" si="264"/>
+        <v>9.8667174673128313E-2</v>
       </c>
       <c r="AV28" s="9">
-        <f t="shared" si="267"/>
-        <v>9.4347741279195069E-2</v>
+        <f t="shared" si="264"/>
+        <v>0.10219328044561934</v>
       </c>
       <c r="AW28" s="9">
-        <f t="shared" ref="AW28:BA28" si="268">AW14/AW5</f>
-        <v>9.5947317577304347E-2</v>
+        <f t="shared" ref="AW28:BA28" si="265">AW14/AW5</f>
+        <v>0.10375275422032769</v>
       </c>
       <c r="AX28" s="9">
-        <f t="shared" si="268"/>
-        <v>9.7534810748361886E-2</v>
+        <f t="shared" si="265"/>
+        <v>0.10530024848777149</v>
       </c>
       <c r="AY28" s="9">
-        <f t="shared" si="268"/>
-        <v>9.9110281013714732E-2</v>
+        <f t="shared" si="265"/>
+        <v>0.10683582651240421</v>
       </c>
       <c r="AZ28" s="9">
-        <f t="shared" si="268"/>
-        <v>0.10067378884418274</v>
+        <f t="shared" si="265"/>
+        <v>0.10835955173588692</v>
       </c>
       <c r="BA28" s="9">
-        <f t="shared" si="268"/>
-        <v>0.10222539494811619</v>
+        <f t="shared" si="265"/>
+        <v>0.10987148776591624</v>
       </c>
       <c r="BC28" t="s">
         <v>50</v>
       </c>
       <c r="BD28" s="5">
         <f>Main!D8</f>
-        <v>2256.1</v>
+        <v>2253.3000000000002</v>
       </c>
     </row>
     <row r="29" spans="2:163" x14ac:dyDescent="0.3">
@@ -6310,184 +6301,184 @@
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
       <c r="G29" s="9">
-        <f t="shared" ref="G29:N29" si="269">G10/C10-1</f>
+        <f t="shared" ref="G29:N29" si="266">G10/C10-1</f>
         <v>0.63343108504398837</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" si="269"/>
+        <f t="shared" si="266"/>
         <v>0.54228855721393021</v>
       </c>
       <c r="I29" s="9">
-        <f t="shared" si="269"/>
+        <f t="shared" si="266"/>
         <v>0.50881057268722474</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="269"/>
+        <f t="shared" si="266"/>
         <v>0.54509803921568611</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="269"/>
+        <f t="shared" si="266"/>
         <v>0.58527827648114883</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" si="269"/>
+        <f t="shared" si="266"/>
         <v>0.3612903225806452</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" si="269"/>
+        <f t="shared" si="266"/>
         <v>0.29051094890510964</v>
       </c>
       <c r="N29" s="9">
-        <f t="shared" si="269"/>
+        <f t="shared" si="266"/>
         <v>0.20177664974619303</v>
       </c>
       <c r="O29" s="9">
-        <f t="shared" ref="O29" si="270">O10/K10-1</f>
+        <f t="shared" ref="O29" si="267">O10/K10-1</f>
         <v>0.15062287655719131</v>
       </c>
       <c r="P29" s="9">
-        <f t="shared" ref="P29" si="271">P10/L10-1</f>
+        <f t="shared" ref="P29" si="268">P10/L10-1</f>
         <v>0.3424170616113742</v>
       </c>
       <c r="Q29" s="9">
-        <f t="shared" ref="Q29" si="272">Q10/M10-1</f>
+        <f t="shared" ref="Q29" si="269">Q10/M10-1</f>
         <v>0.36085972850678716</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" ref="R29" si="273">R10/N10-1</f>
+        <f t="shared" ref="R29" si="270">R10/N10-1</f>
         <v>0.33474128827877503</v>
       </c>
       <c r="S29" s="9">
-        <f t="shared" ref="S29" si="274">S10/O10-1</f>
+        <f t="shared" ref="S29" si="271">S10/O10-1</f>
         <v>0.61417322834645671</v>
       </c>
       <c r="T29" s="9">
-        <f t="shared" ref="T29" si="275">T10/P10-1</f>
+        <f t="shared" ref="T29" si="272">T10/P10-1</f>
         <v>0.73521624007060904</v>
       </c>
       <c r="U29" s="9">
-        <f t="shared" ref="U29" si="276">U10/Q10-1</f>
+        <f t="shared" ref="U29" si="273">U10/Q10-1</f>
         <v>0.72568578553615959</v>
       </c>
       <c r="V29" s="9">
-        <f t="shared" ref="V29" si="277">V10/R10-1</f>
+        <f t="shared" ref="V29" si="274">V10/R10-1</f>
         <v>0.74604430379746822</v>
       </c>
       <c r="W29" s="9">
-        <f t="shared" ref="W29" si="278">W10/S10-1</f>
+        <f t="shared" ref="W29" si="275">W10/S10-1</f>
         <v>0.34207317073170729</v>
       </c>
       <c r="X29" s="9">
-        <f t="shared" ref="X29" si="279">X10/T10-1</f>
+        <f t="shared" ref="X29" si="276">X10/T10-1</f>
         <v>-2.1363173957273607E-2</v>
       </c>
       <c r="Y29" s="9">
-        <f t="shared" ref="Y29" si="280">Y10/U10-1</f>
+        <f t="shared" ref="Y29" si="277">Y10/U10-1</f>
         <v>0.359344894026975</v>
       </c>
       <c r="Z29" s="9">
-        <f t="shared" ref="Z29" si="281">Z10/V10-1</f>
+        <f t="shared" ref="Z29" si="278">Z10/V10-1</f>
         <v>-0.16719528772088799</v>
       </c>
       <c r="AA29" s="9">
-        <f t="shared" ref="AA29" si="282">AA10/W10-1</f>
+        <f t="shared" ref="AA29" si="279">AA10/W10-1</f>
         <v>-0.18037255792821438</v>
       </c>
       <c r="AB29" s="9">
-        <f t="shared" ref="AB29" si="283">AB10/X10-1</f>
+        <f t="shared" ref="AB29" si="280">AB10/X10-1</f>
         <v>-8.7837837837837829E-2</v>
       </c>
       <c r="AC29" s="9">
-        <f t="shared" ref="AC29" si="284">AC10/Y10-1</f>
+        <f t="shared" ref="AC29" si="281">AC10/Y10-1</f>
         <v>-0.36640680368532952</v>
       </c>
       <c r="AD29" s="9">
-        <f t="shared" ref="AD29" si="285">AD10/Z10-1</f>
+        <f t="shared" ref="AD29" si="282">AD10/Z10-1</f>
         <v>8.705114254624613E-3</v>
       </c>
       <c r="AE29" s="9">
-        <f t="shared" ref="AE29" si="286">AE10/AA10-1</f>
+        <f t="shared" ref="AE29" si="283">AE10/AA10-1</f>
         <v>2.3281596452328079E-2</v>
       </c>
       <c r="AF29" s="9">
-        <f t="shared" ref="AF29" si="287">AF10/AB10-1</f>
-        <v>7.0000000000000062E-2</v>
+        <f t="shared" ref="AF29" si="284">AF10/AB10-1</f>
+        <v>1.4245014245014342E-2</v>
       </c>
       <c r="AG29" s="9">
-        <f t="shared" ref="AG29" si="288">AG10/AC10-1</f>
+        <f t="shared" ref="AG29" si="285">AG10/AC10-1</f>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AH29" s="9">
-        <f t="shared" ref="AH29" si="289">AH10/AD10-1</f>
+        <f t="shared" ref="AH29" si="286">AH10/AD10-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ29" s="9"/>
       <c r="AK29" s="9">
-        <f t="shared" ref="AK29" si="290">AK10/AJ10-1</f>
+        <f t="shared" ref="AK29" si="287">AK10/AJ10-1</f>
         <v>0.55243116578793194</v>
       </c>
       <c r="AL29" s="9">
-        <f t="shared" ref="AL29" si="291">AL10/AK10-1</f>
+        <f t="shared" ref="AL29" si="288">AL10/AK10-1</f>
         <v>0.34264150943396232</v>
       </c>
       <c r="AM29" s="9">
-        <f t="shared" ref="AM29" si="292">AM10/AL10-1</f>
+        <f t="shared" ref="AM29" si="289">AM10/AL10-1</f>
         <v>0.29735806632939865</v>
       </c>
       <c r="AN29" s="9">
-        <f t="shared" ref="AN29" si="293">AN10/AM10-1</f>
+        <f t="shared" ref="AN29" si="290">AN10/AM10-1</f>
         <v>0.70905545927209723</v>
       </c>
       <c r="AO29" s="9">
-        <f t="shared" ref="AO29" si="294">AO10/AN10-1</f>
+        <f t="shared" ref="AO29" si="291">AO10/AN10-1</f>
         <v>0.11357586512866003</v>
       </c>
       <c r="AP29" s="9">
-        <f t="shared" ref="AP29" si="295">AP10/AO10-1</f>
+        <f t="shared" ref="AP29" si="292">AP10/AO10-1</f>
         <v>-0.18030734206033006</v>
       </c>
       <c r="AQ29" s="9">
-        <f t="shared" ref="AQ29" si="296">AQ10/AP10-1</f>
-        <v>4.5514511873350871E-2</v>
+        <f t="shared" ref="AQ29" si="293">AQ10/AP10-1</f>
+        <v>3.1926121372031657E-2</v>
       </c>
       <c r="AR29" s="9">
-        <f t="shared" ref="AR29" si="297">AR10/AQ10-1</f>
+        <f t="shared" ref="AR29" si="294">AR10/AQ10-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AS29" s="9">
-        <f t="shared" ref="AS29" si="298">AS10/AR10-1</f>
+        <f t="shared" ref="AS29" si="295">AS10/AR10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AT29" s="9">
-        <f t="shared" ref="AT29" si="299">AT10/AS10-1</f>
+        <f t="shared" ref="AT29" si="296">AT10/AS10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AU29" s="9">
-        <f t="shared" ref="AU29" si="300">AU10/AT10-1</f>
+        <f t="shared" ref="AU29" si="297">AU10/AT10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AV29" s="9">
-        <f t="shared" ref="AV29:AW29" si="301">AV10/AU10-1</f>
+        <f t="shared" ref="AV29:AW29" si="298">AV10/AU10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AW29" s="9">
-        <f t="shared" si="301"/>
+        <f t="shared" si="298"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX29" s="9">
-        <f t="shared" ref="AX29" si="302">AX10/AW10-1</f>
+        <f t="shared" ref="AX29" si="299">AX10/AW10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY29" s="9">
-        <f t="shared" ref="AY29" si="303">AY10/AX10-1</f>
+        <f t="shared" ref="AY29" si="300">AY10/AX10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ29" s="9">
-        <f t="shared" ref="AZ29" si="304">AZ10/AY10-1</f>
+        <f t="shared" ref="AZ29" si="301">AZ10/AY10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA29" s="9">
-        <f t="shared" ref="BA29" si="305">BA10/AZ10-1</f>
+        <f t="shared" ref="BA29" si="302">BA10/AZ10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BC29" t="s">
@@ -6495,7 +6486,7 @@
       </c>
       <c r="BD29" s="5">
         <f>BD27+BD28</f>
-        <v>6973.7833121579133</v>
+        <v>7387.5373969519242</v>
       </c>
     </row>
     <row r="30" spans="2:163" x14ac:dyDescent="0.3">
@@ -6507,207 +6498,207 @@
         <v>0.14860907759882871</v>
       </c>
       <c r="D30" s="9">
-        <f t="shared" ref="D30:G30" si="306">D11/D5</f>
+        <f t="shared" ref="D30:G30" si="303">D11/D5</f>
         <v>0.14221938775510204</v>
       </c>
       <c r="E30" s="9">
+        <f t="shared" si="303"/>
+        <v>0.14763552479815459</v>
+      </c>
+      <c r="F30" s="9">
+        <f t="shared" si="303"/>
+        <v>0.12549873050417121</v>
+      </c>
+      <c r="G30" s="9">
+        <f t="shared" si="303"/>
+        <v>0.16352201257861634</v>
+      </c>
+      <c r="H30" s="9">
+        <f t="shared" ref="H30:N30" si="304">H11/H5</f>
+        <v>0.14634146341463417</v>
+      </c>
+      <c r="I30" s="9">
+        <f t="shared" si="304"/>
+        <v>0.17899578382522041</v>
+      </c>
+      <c r="J30" s="9">
+        <f t="shared" si="304"/>
+        <v>0.15029182879377428</v>
+      </c>
+      <c r="K30" s="9">
+        <f t="shared" si="304"/>
+        <v>0.21259351620947631</v>
+      </c>
+      <c r="L30" s="9">
+        <f t="shared" si="304"/>
+        <v>0.18028643639427128</v>
+      </c>
+      <c r="M30" s="9">
+        <f t="shared" si="304"/>
+        <v>0.15721877767936226</v>
+      </c>
+      <c r="N30" s="9">
+        <f t="shared" si="304"/>
+        <v>0.1478689029081397</v>
+      </c>
+      <c r="O30" s="9">
+        <f t="shared" ref="O30:R30" si="305">O11/O5</f>
+        <v>0.15482410309996517</v>
+      </c>
+      <c r="P30" s="9">
+        <f t="shared" si="305"/>
+        <v>0.14524879863587042</v>
+      </c>
+      <c r="Q30" s="9">
+        <f t="shared" si="305"/>
+        <v>0.1613472569495514</v>
+      </c>
+      <c r="R30" s="9">
+        <f t="shared" si="305"/>
+        <v>0.18883624176586156</v>
+      </c>
+      <c r="S30" s="9">
+        <f t="shared" ref="S30:AA30" si="306">S11/S5</f>
+        <v>0.19967289082731363</v>
+      </c>
+      <c r="T30" s="9">
         <f t="shared" si="306"/>
-        <v>0.14763552479815459</v>
-      </c>
-      <c r="F30" s="9">
+        <v>0.2419882275997384</v>
+      </c>
+      <c r="U30" s="9">
         <f t="shared" si="306"/>
-        <v>0.12549873050417121</v>
-      </c>
-      <c r="G30" s="9">
+        <v>0.2750197005516154</v>
+      </c>
+      <c r="V30" s="9">
         <f t="shared" si="306"/>
-        <v>0.16352201257861634</v>
-      </c>
-      <c r="H30" s="9">
-        <f t="shared" ref="H30:N30" si="307">H11/H5</f>
-        <v>0.14634146341463417</v>
-      </c>
-      <c r="I30" s="9">
+        <v>0.34321300888017536</v>
+      </c>
+      <c r="W30" s="9">
+        <f t="shared" si="306"/>
+        <v>0.31565452091767882</v>
+      </c>
+      <c r="X30" s="9">
+        <f t="shared" si="306"/>
+        <v>0.26814587513277471</v>
+      </c>
+      <c r="Y30" s="9">
+        <f t="shared" si="306"/>
+        <v>0.33739035087719299</v>
+      </c>
+      <c r="Z30" s="9">
+        <f t="shared" si="306"/>
+        <v>0.26876587100050792</v>
+      </c>
+      <c r="AA30" s="9">
+        <f t="shared" si="306"/>
+        <v>0.22929430451554345</v>
+      </c>
+      <c r="AB30" s="9">
+        <f t="shared" ref="AB30:AD30" si="307">AB11/AB5</f>
+        <v>0.22900526805082119</v>
+      </c>
+      <c r="AC30" s="9">
         <f t="shared" si="307"/>
-        <v>0.17899578382522041</v>
-      </c>
-      <c r="J30" s="9">
+        <v>0.22312182263227262</v>
+      </c>
+      <c r="AD30" s="9">
         <f t="shared" si="307"/>
-        <v>0.15029182879377428</v>
-      </c>
-      <c r="K30" s="9">
-        <f t="shared" si="307"/>
-        <v>0.21259351620947631</v>
-      </c>
-      <c r="L30" s="9">
-        <f t="shared" si="307"/>
-        <v>0.18028643639427128</v>
-      </c>
-      <c r="M30" s="9">
-        <f t="shared" si="307"/>
-        <v>0.15721877767936226</v>
-      </c>
-      <c r="N30" s="9">
-        <f t="shared" si="307"/>
-        <v>0.1478689029081397</v>
-      </c>
-      <c r="O30" s="9">
-        <f t="shared" ref="O30:R30" si="308">O11/O5</f>
-        <v>0.15482410309996517</v>
-      </c>
-      <c r="P30" s="9">
+        <v>0.22639467110741046</v>
+      </c>
+      <c r="AE30" s="9">
+        <f t="shared" ref="AE30:AH30" si="308">AE11/AE5</f>
+        <v>0.21916331929068286</v>
+      </c>
+      <c r="AF30" s="9">
         <f t="shared" si="308"/>
-        <v>0.14524879863587042</v>
-      </c>
-      <c r="Q30" s="9">
+        <v>0.21897218972189725</v>
+      </c>
+      <c r="AG30" s="9">
         <f t="shared" si="308"/>
-        <v>0.1613472569495514</v>
-      </c>
-      <c r="R30" s="9">
+        <v>0.22</v>
+      </c>
+      <c r="AH30" s="9">
         <f t="shared" si="308"/>
-        <v>0.18883624176586156</v>
-      </c>
-      <c r="S30" s="9">
-        <f t="shared" ref="S30:AA30" si="309">S11/S5</f>
-        <v>0.19967289082731363</v>
-      </c>
-      <c r="T30" s="9">
-        <f t="shared" si="309"/>
-        <v>0.2419882275997384</v>
-      </c>
-      <c r="U30" s="9">
-        <f t="shared" si="309"/>
-        <v>0.2750197005516154</v>
-      </c>
-      <c r="V30" s="9">
-        <f t="shared" si="309"/>
-        <v>0.34321300888017536</v>
-      </c>
-      <c r="W30" s="9">
-        <f t="shared" si="309"/>
-        <v>0.31565452091767882</v>
-      </c>
-      <c r="X30" s="9">
-        <f t="shared" si="309"/>
-        <v>0.26814587513277471</v>
-      </c>
-      <c r="Y30" s="9">
-        <f t="shared" si="309"/>
-        <v>0.33739035087719299</v>
-      </c>
-      <c r="Z30" s="9">
-        <f t="shared" si="309"/>
-        <v>0.26876587100050792</v>
-      </c>
-      <c r="AA30" s="9">
-        <f t="shared" si="309"/>
-        <v>0.22929430451554345</v>
-      </c>
-      <c r="AB30" s="9">
-        <f t="shared" ref="AB30:AD30" si="310">AB11/AB5</f>
-        <v>0.22900526805082119</v>
-      </c>
-      <c r="AC30" s="9">
+        <v>0.22</v>
+      </c>
+      <c r="AJ30" s="9">
+        <f t="shared" ref="AJ30" si="309">AJ11/AJ5</f>
+        <v>0.13845117845117846</v>
+      </c>
+      <c r="AK30" s="9">
+        <f t="shared" ref="AK30:AL30" si="310">AK11/AK5</f>
+        <v>0.15847284967667641</v>
+      </c>
+      <c r="AL30" s="9">
         <f t="shared" si="310"/>
-        <v>0.22312182263227262</v>
-      </c>
-      <c r="AD30" s="9">
-        <f t="shared" si="310"/>
-        <v>0.22639467110741046</v>
-      </c>
-      <c r="AE30" s="9">
-        <f t="shared" ref="AE30:AH30" si="311">AE11/AE5</f>
-        <v>0.21916331929068286</v>
-      </c>
-      <c r="AF30" s="9">
+        <v>0.16840980656770133</v>
+      </c>
+      <c r="AM30" s="9">
+        <f t="shared" ref="AM30:AV30" si="311">AM11/AM5</f>
+        <v>0.16483993488876833</v>
+      </c>
+      <c r="AN30" s="9">
         <f t="shared" si="311"/>
-        <v>0.22</v>
-      </c>
-      <c r="AG30" s="9">
+        <v>0.26817411328237439</v>
+      </c>
+      <c r="AO30" s="9">
         <f t="shared" si="311"/>
-        <v>0.22</v>
-      </c>
-      <c r="AH30" s="9">
+        <v>0.29654499540863177</v>
+      </c>
+      <c r="AP30" s="9">
         <f t="shared" si="311"/>
-        <v>0.22</v>
-      </c>
-      <c r="AJ30" s="9">
-        <f t="shared" ref="AJ30" si="312">AJ11/AJ5</f>
-        <v>0.13845117845117846</v>
-      </c>
-      <c r="AK30" s="9">
-        <f t="shared" ref="AK30:AL30" si="313">AK11/AK5</f>
-        <v>0.15847284967667641</v>
-      </c>
-      <c r="AL30" s="9">
-        <f t="shared" si="313"/>
-        <v>0.16840980656770133</v>
-      </c>
-      <c r="AM30" s="9">
-        <f t="shared" ref="AM30:AV30" si="314">AM11/AM5</f>
-        <v>0.16483993488876833</v>
-      </c>
-      <c r="AN30" s="9">
-        <f t="shared" si="314"/>
-        <v>0.26817411328237439</v>
-      </c>
-      <c r="AO30" s="9">
-        <f t="shared" si="314"/>
-        <v>0.29654499540863177</v>
-      </c>
-      <c r="AP30" s="9">
-        <f t="shared" si="314"/>
         <v>0.22678532351010283</v>
       </c>
       <c r="AQ30" s="9">
-        <f t="shared" si="314"/>
-        <v>0.21981502731920874</v>
+        <f t="shared" si="311"/>
+        <v>0.21956906630096312</v>
       </c>
       <c r="AR30" s="9">
-        <f t="shared" si="314"/>
-        <v>0.21</v>
+        <f t="shared" si="311"/>
+        <v>0.20999999999999996</v>
       </c>
       <c r="AS30" s="9">
-        <f t="shared" si="314"/>
-        <v>0.19999999999999998</v>
+        <f t="shared" si="311"/>
+        <v>0.2</v>
       </c>
       <c r="AT30" s="9">
-        <f t="shared" si="314"/>
+        <f t="shared" si="311"/>
         <v>0.19</v>
       </c>
       <c r="AU30" s="9">
-        <f t="shared" si="314"/>
+        <f t="shared" si="311"/>
+        <v>0.18999999999999997</v>
+      </c>
+      <c r="AV30" s="9">
+        <f t="shared" si="311"/>
+        <v>0.18999999999999997</v>
+      </c>
+      <c r="AW30" s="9">
+        <f t="shared" ref="AW30:BA30" si="312">AW11/AW5</f>
+        <v>0.19</v>
+      </c>
+      <c r="AX30" s="9">
+        <f t="shared" si="312"/>
+        <v>0.19</v>
+      </c>
+      <c r="AY30" s="9">
+        <f t="shared" si="312"/>
+        <v>0.19</v>
+      </c>
+      <c r="AZ30" s="9">
+        <f t="shared" si="312"/>
         <v>0.19000000000000003</v>
       </c>
-      <c r="AV30" s="9">
-        <f t="shared" si="314"/>
+      <c r="BA30" s="9">
+        <f t="shared" si="312"/>
         <v>0.19</v>
-      </c>
-      <c r="AW30" s="9">
-        <f t="shared" ref="AW30:BA30" si="315">AW11/AW5</f>
-        <v>0.18999999999999997</v>
-      </c>
-      <c r="AX30" s="9">
-        <f t="shared" si="315"/>
-        <v>0.19000000000000003</v>
-      </c>
-      <c r="AY30" s="9">
-        <f t="shared" si="315"/>
-        <v>0.19</v>
-      </c>
-      <c r="AZ30" s="9">
-        <f t="shared" si="315"/>
-        <v>0.19</v>
-      </c>
-      <c r="BA30" s="9">
-        <f t="shared" si="315"/>
-        <v>0.18999999999999997</v>
       </c>
       <c r="BC30" t="s">
         <v>52</v>
       </c>
       <c r="BD30" s="11">
         <f>BD29/AV19</f>
-        <v>47.570145376247709</v>
+        <v>50.289567031667282</v>
       </c>
     </row>
     <row r="31" spans="2:163" x14ac:dyDescent="0.3">
@@ -6719,184 +6710,184 @@
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
       <c r="G31" s="9">
-        <f t="shared" ref="G31:N31" si="316">G12/C12-1</f>
+        <f t="shared" ref="G31:N31" si="313">G12/C12-1</f>
         <v>0.41666666666666674</v>
       </c>
       <c r="H31" s="9">
-        <f t="shared" si="316"/>
+        <f t="shared" si="313"/>
         <v>0.68831168831168821</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" si="316"/>
+        <f t="shared" si="313"/>
         <v>0.51010101010100994</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" si="316"/>
+        <f t="shared" si="313"/>
         <v>0.81132075471698117</v>
       </c>
       <c r="K31" s="9">
-        <f t="shared" si="316"/>
+        <f t="shared" si="313"/>
         <v>0.79638009049773761</v>
       </c>
       <c r="L31" s="9">
-        <f t="shared" si="316"/>
+        <f t="shared" si="313"/>
         <v>0.55769230769230771</v>
       </c>
       <c r="M31" s="9">
-        <f t="shared" si="316"/>
+        <f t="shared" si="313"/>
         <v>0.45484949832775934</v>
       </c>
       <c r="N31" s="9">
-        <f t="shared" si="316"/>
+        <f t="shared" si="313"/>
         <v>0.2890625</v>
       </c>
       <c r="O31" s="9">
-        <f t="shared" ref="O31" si="317">O12/K12-1</f>
+        <f t="shared" ref="O31" si="314">O12/K12-1</f>
         <v>0.52392947103274556</v>
       </c>
       <c r="P31" s="9">
-        <f t="shared" ref="P31" si="318">P12/L12-1</f>
+        <f t="shared" ref="P31" si="315">P12/L12-1</f>
         <v>0.53580246913580254</v>
       </c>
       <c r="Q31" s="9">
-        <f t="shared" ref="Q31" si="319">Q12/M12-1</f>
+        <f t="shared" ref="Q31" si="316">Q12/M12-1</f>
         <v>0.49655172413793092</v>
       </c>
       <c r="R31" s="9">
-        <f t="shared" ref="R31" si="320">R12/N12-1</f>
+        <f t="shared" ref="R31" si="317">R12/N12-1</f>
         <v>0.38383838383838387</v>
       </c>
       <c r="S31" s="9">
-        <f t="shared" ref="S31" si="321">S12/O12-1</f>
+        <f t="shared" ref="S31" si="318">S12/O12-1</f>
         <v>0.28595041322314052</v>
       </c>
       <c r="T31" s="9">
-        <f t="shared" ref="T31" si="322">T12/P12-1</f>
+        <f t="shared" ref="T31" si="319">T12/P12-1</f>
         <v>0.35209003215434076</v>
       </c>
       <c r="U31" s="9">
-        <f t="shared" ref="U31" si="323">U12/Q12-1</f>
+        <f t="shared" ref="U31" si="320">U12/Q12-1</f>
         <v>0.33333333333333348</v>
       </c>
       <c r="V31" s="9">
-        <f t="shared" ref="V31" si="324">V12/R12-1</f>
+        <f t="shared" ref="V31" si="321">V12/R12-1</f>
         <v>0.4014598540145986</v>
       </c>
       <c r="W31" s="9">
-        <f t="shared" ref="W31" si="325">W12/S12-1</f>
+        <f t="shared" ref="W31" si="322">W12/S12-1</f>
         <v>0.23521850899742924</v>
       </c>
       <c r="X31" s="9">
-        <f t="shared" ref="X31" si="326">X12/T12-1</f>
+        <f t="shared" ref="X31" si="323">X12/T12-1</f>
         <v>7.1343638525565023E-3</v>
       </c>
       <c r="Y31" s="9">
-        <f t="shared" ref="Y31" si="327">Y12/U12-1</f>
+        <f t="shared" ref="Y31" si="324">Y12/U12-1</f>
         <v>0.48271889400921641</v>
       </c>
       <c r="Z31" s="9">
-        <f t="shared" ref="Z31" si="328">Z12/V12-1</f>
+        <f t="shared" ref="Z31" si="325">Z12/V12-1</f>
         <v>-2.3958333333333304E-2</v>
       </c>
       <c r="AA31" s="9">
-        <f t="shared" ref="AA31" si="329">AA12/W12-1</f>
+        <f t="shared" ref="AA31" si="326">AA12/W12-1</f>
         <v>-0.19146722164412067</v>
       </c>
       <c r="AB31" s="9">
-        <f t="shared" ref="AB31" si="330">AB12/X12-1</f>
+        <f t="shared" ref="AB31" si="327">AB12/X12-1</f>
         <v>0.166469893742621</v>
       </c>
       <c r="AC31" s="9">
-        <f t="shared" ref="AC31" si="331">AC12/Y12-1</f>
+        <f t="shared" ref="AC31" si="328">AC12/Y12-1</f>
         <v>-0.22299922299922292</v>
       </c>
       <c r="AD31" s="9">
-        <f t="shared" ref="AD31" si="332">AD12/Z12-1</f>
+        <f t="shared" ref="AD31" si="329">AD12/Z12-1</f>
         <v>7.4706510138740079E-3</v>
       </c>
       <c r="AE31" s="9">
-        <f t="shared" ref="AE31" si="333">AE12/AA12-1</f>
+        <f t="shared" ref="AE31" si="330">AE12/AA12-1</f>
         <v>0.21621621621621623</v>
       </c>
       <c r="AF31" s="9">
-        <f t="shared" ref="AF31" si="334">AF12/AB12-1</f>
+        <f t="shared" ref="AF31" si="331">AF12/AB12-1</f>
+        <v>9.109311740890691E-3</v>
+      </c>
+      <c r="AG31" s="9">
+        <f t="shared" ref="AG31" si="332">AG12/AC12-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AG31" s="9">
-        <f t="shared" ref="AG31" si="335">AG12/AC12-1</f>
-        <v>3.0000000000000027E-2</v>
-      </c>
       <c r="AH31" s="9">
-        <f t="shared" ref="AH31" si="336">AH12/AD12-1</f>
+        <f t="shared" ref="AH31" si="333">AH12/AD12-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ31" s="9"/>
       <c r="AK31" s="9">
-        <f t="shared" ref="AK31" si="337">AK12/AJ12-1</f>
+        <f t="shared" ref="AK31" si="334">AK12/AJ12-1</f>
         <v>0.6166666666666667</v>
       </c>
       <c r="AL31" s="9">
-        <f t="shared" ref="AL31" si="338">AL12/AK12-1</f>
+        <f t="shared" ref="AL31" si="335">AL12/AK12-1</f>
         <v>0.48797250859106511</v>
       </c>
       <c r="AM31" s="9">
-        <f t="shared" ref="AM31" si="339">AM12/AL12-1</f>
+        <f t="shared" ref="AM31" si="336">AM12/AL12-1</f>
         <v>0.47979214780600477</v>
       </c>
       <c r="AN31" s="9">
-        <f t="shared" ref="AN31" si="340">AN12/AM12-1</f>
+        <f t="shared" ref="AN31" si="337">AN12/AM12-1</f>
         <v>0.34490831057354643</v>
       </c>
       <c r="AO31" s="9">
-        <f t="shared" ref="AO31" si="341">AO12/AN12-1</f>
+        <f t="shared" ref="AO31" si="338">AO12/AN12-1</f>
         <v>0.16971279373368153</v>
       </c>
       <c r="AP31" s="9">
-        <f t="shared" ref="AP31" si="342">AP12/AO12-1</f>
+        <f t="shared" ref="AP31" si="339">AP12/AO12-1</f>
         <v>-8.0109126984126977E-2</v>
       </c>
       <c r="AQ31" s="9">
-        <f t="shared" ref="AQ31" si="343">AQ12/AP12-1</f>
-        <v>6.9010514963602221E-2</v>
+        <f t="shared" ref="AQ31" si="340">AQ12/AP12-1</f>
+        <v>6.3445672688056121E-2</v>
       </c>
       <c r="AR31" s="9">
-        <f t="shared" ref="AR31" si="344">AR12/AQ12-1</f>
+        <f t="shared" ref="AR31" si="341">AR12/AQ12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AS31" s="9">
-        <f t="shared" ref="AS31" si="345">AS12/AR12-1</f>
+        <f t="shared" ref="AS31" si="342">AS12/AR12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AT31" s="9">
-        <f t="shared" ref="AT31" si="346">AT12/AS12-1</f>
+        <f t="shared" ref="AT31" si="343">AT12/AS12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AU31" s="9">
-        <f t="shared" ref="AU31" si="347">AU12/AT12-1</f>
+        <f t="shared" ref="AU31" si="344">AU12/AT12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AV31" s="9">
-        <f t="shared" ref="AV31:AW31" si="348">AV12/AU12-1</f>
+        <f t="shared" ref="AV31:AW31" si="345">AV12/AU12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AW31" s="9">
-        <f t="shared" si="348"/>
+        <f t="shared" si="345"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AX31" s="9">
-        <f t="shared" ref="AX31" si="349">AX12/AW12-1</f>
+        <f t="shared" ref="AX31" si="346">AX12/AW12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AY31" s="9">
-        <f t="shared" ref="AY31" si="350">AY12/AX12-1</f>
+        <f t="shared" ref="AY31" si="347">AY12/AX12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AZ31" s="9">
-        <f t="shared" ref="AZ31" si="351">AZ12/AY12-1</f>
+        <f t="shared" ref="AZ31" si="348">AZ12/AY12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BA31" s="9">
-        <f t="shared" ref="BA31" si="352">BA12/AZ12-1</f>
+        <f t="shared" ref="BA31" si="349">BA12/AZ12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BC31" t="s">
@@ -6904,7 +6895,7 @@
       </c>
       <c r="BD31" s="11">
         <f>Main!D3</f>
-        <v>70.45</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="32" spans="2:163" x14ac:dyDescent="0.3">
@@ -6916,199 +6907,199 @@
         <v>-1.5384615384615373E-2</v>
       </c>
       <c r="D32" s="9">
-        <f t="shared" ref="D32:G32" si="353">D17/D16</f>
+        <f t="shared" ref="D32:G32" si="350">D17/D16</f>
         <v>-1.9999999999999429</v>
       </c>
       <c r="E32" s="9">
+        <f t="shared" si="350"/>
+        <v>2.0618556701030875E-2</v>
+      </c>
+      <c r="F32" s="9">
+        <f t="shared" si="350"/>
+        <v>-1.4925373134328391E-2</v>
+      </c>
+      <c r="G32" s="9">
+        <f t="shared" si="350"/>
+        <v>1.0204081632653045E-2</v>
+      </c>
+      <c r="H32" s="9">
+        <f t="shared" ref="H32:N32" si="351">H17/H16</f>
+        <v>4.0567951318458396E-2</v>
+      </c>
+      <c r="I32" s="9">
+        <f t="shared" si="351"/>
+        <v>4.0485829959514144E-3</v>
+      </c>
+      <c r="J32" s="9">
+        <f t="shared" si="351"/>
+        <v>2.5000000000000074E-2</v>
+      </c>
+      <c r="K32" s="9">
+        <f t="shared" si="351"/>
+        <v>3.663003663003663E-3</v>
+      </c>
+      <c r="L32" s="9">
+        <f t="shared" si="351"/>
+        <v>-1.1737089201877937E-2</v>
+      </c>
+      <c r="M32" s="9">
+        <f t="shared" si="351"/>
+        <v>-8.1967213114753829E-2</v>
+      </c>
+      <c r="N32" s="9">
+        <f t="shared" si="351"/>
+        <v>-1.0502625656414103E-2</v>
+      </c>
+      <c r="O32" s="9">
+        <f t="shared" ref="O32:R32" si="352">O17/O16</f>
+        <v>-1.0596026490066216E-2</v>
+      </c>
+      <c r="P32" s="9">
+        <f t="shared" si="352"/>
+        <v>-5.150214592274685E-2</v>
+      </c>
+      <c r="Q32" s="9">
+        <f t="shared" si="352"/>
+        <v>-4.3731778425656004E-3</v>
+      </c>
+      <c r="R32" s="9">
+        <f t="shared" si="352"/>
+        <v>-4.8672566371681519E-2</v>
+      </c>
+      <c r="S32" s="9">
+        <f t="shared" ref="S32:AA32" si="353">S17/S16</f>
+        <v>-9.0909090909090703E-2</v>
+      </c>
+      <c r="T32" s="9">
         <f t="shared" si="353"/>
-        <v>2.0618556701030875E-2</v>
-      </c>
-      <c r="F32" s="9">
+        <v>-2.3679417122040063E-2</v>
+      </c>
+      <c r="U32" s="9">
         <f t="shared" si="353"/>
-        <v>-1.4925373134328391E-2</v>
-      </c>
-      <c r="G32" s="9">
+        <v>-1.6625103906899426E-2</v>
+      </c>
+      <c r="V32" s="9">
         <f t="shared" si="353"/>
-        <v>1.0204081632653045E-2</v>
-      </c>
-      <c r="H32" s="9">
-        <f t="shared" ref="H32:N32" si="354">H17/H16</f>
-        <v>4.0567951318458396E-2</v>
-      </c>
-      <c r="I32" s="9">
+        <v>4.1981528127623827E-3</v>
+      </c>
+      <c r="W32" s="9">
+        <f t="shared" si="353"/>
+        <v>-1.8997361477572555E-2</v>
+      </c>
+      <c r="X32" s="9">
+        <f t="shared" si="353"/>
+        <v>-1.5108593012275727E-2</v>
+      </c>
+      <c r="Y32" s="9">
+        <f t="shared" si="353"/>
+        <v>-9.7889262771489773E-3</v>
+      </c>
+      <c r="Z32" s="9">
+        <f t="shared" si="353"/>
+        <v>-2.3560209424083763E-2</v>
+      </c>
+      <c r="AA32" s="9">
+        <f t="shared" si="353"/>
+        <v>-0.10434782608695639</v>
+      </c>
+      <c r="AB32" s="9">
+        <f t="shared" ref="AB32:AD32" si="354">AB17/AB16</f>
+        <v>0.21247113163972242</v>
+      </c>
+      <c r="AC32" s="9">
         <f t="shared" si="354"/>
-        <v>4.0485829959514144E-3</v>
-      </c>
-      <c r="J32" s="9">
+        <v>-0.85416666666669872</v>
+      </c>
+      <c r="AD32" s="9">
         <f t="shared" si="354"/>
-        <v>2.5000000000000074E-2</v>
-      </c>
-      <c r="K32" s="9">
-        <f t="shared" si="354"/>
-        <v>3.663003663003663E-3</v>
-      </c>
-      <c r="L32" s="9">
-        <f t="shared" si="354"/>
-        <v>-1.1737089201877937E-2</v>
-      </c>
-      <c r="M32" s="9">
-        <f t="shared" si="354"/>
-        <v>-8.1967213114753829E-2</v>
-      </c>
-      <c r="N32" s="9">
-        <f t="shared" si="354"/>
-        <v>-1.0502625656414103E-2</v>
-      </c>
-      <c r="O32" s="9">
-        <f t="shared" ref="O32:R32" si="355">O17/O16</f>
-        <v>-1.0596026490066216E-2</v>
-      </c>
-      <c r="P32" s="9">
+        <v>-0.37451737451737549</v>
+      </c>
+      <c r="AE32" s="9">
+        <f t="shared" ref="AE32:AH32" si="355">AE17/AE16</f>
+        <v>0.32345679012345646</v>
+      </c>
+      <c r="AF32" s="9">
         <f t="shared" si="355"/>
-        <v>-5.150214592274685E-2</v>
-      </c>
-      <c r="Q32" s="9">
+        <v>-1.2340425531915071</v>
+      </c>
+      <c r="AG32" s="9">
         <f t="shared" si="355"/>
-        <v>-4.3731778425656004E-3</v>
-      </c>
-      <c r="R32" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="AH32" s="9">
         <f t="shared" si="355"/>
-        <v>-4.8672566371681519E-2</v>
-      </c>
-      <c r="S32" s="9">
-        <f t="shared" ref="S32:AA32" si="356">S17/S16</f>
-        <v>-9.0909090909090703E-2</v>
-      </c>
-      <c r="T32" s="9">
-        <f t="shared" si="356"/>
-        <v>-2.3679417122040063E-2</v>
-      </c>
-      <c r="U32" s="9">
-        <f t="shared" si="356"/>
-        <v>-1.6625103906899426E-2</v>
-      </c>
-      <c r="V32" s="9">
-        <f t="shared" si="356"/>
-        <v>4.1981528127623827E-3</v>
-      </c>
-      <c r="W32" s="9">
-        <f t="shared" si="356"/>
-        <v>-1.8997361477572555E-2</v>
-      </c>
-      <c r="X32" s="9">
-        <f t="shared" si="356"/>
-        <v>-1.5108593012275727E-2</v>
-      </c>
-      <c r="Y32" s="9">
-        <f t="shared" si="356"/>
-        <v>-9.7889262771489773E-3</v>
-      </c>
-      <c r="Z32" s="9">
-        <f t="shared" si="356"/>
-        <v>-2.3560209424083763E-2</v>
-      </c>
-      <c r="AA32" s="9">
-        <f t="shared" si="356"/>
-        <v>-0.10434782608695639</v>
-      </c>
-      <c r="AB32" s="9">
-        <f t="shared" ref="AB32:AD32" si="357">AB17/AB16</f>
-        <v>0.21247113163972242</v>
-      </c>
-      <c r="AC32" s="9">
+        <v>0.19999999999999998</v>
+      </c>
+      <c r="AJ32" s="9">
+        <f t="shared" ref="AJ32" si="356">AJ17/AJ16</f>
+        <v>6.4516129032257979E-2</v>
+      </c>
+      <c r="AK32" s="9">
+        <f t="shared" ref="AK32:AL32" si="357">AK17/AK16</f>
+        <v>1.6567263088137864E-2</v>
+      </c>
+      <c r="AL32" s="9">
         <f t="shared" si="357"/>
-        <v>-0.85416666666669872</v>
-      </c>
-      <c r="AD32" s="9">
-        <f t="shared" si="357"/>
-        <v>-0.37451737451737549</v>
-      </c>
-      <c r="AE32" s="9">
-        <f t="shared" ref="AE32:AH32" si="358">AE17/AE16</f>
-        <v>0.32345679012345646</v>
-      </c>
-      <c r="AF32" s="9">
+        <v>7.6294277929155122E-2</v>
+      </c>
+      <c r="AM32" s="9">
+        <f t="shared" ref="AM32:AV32" si="358">AM17/AM16</f>
+        <v>-2.4513947590870694E-2</v>
+      </c>
+      <c r="AN32" s="9">
+        <f t="shared" si="358"/>
+        <v>-1.1776649746192887E-2</v>
+      </c>
+      <c r="AO32" s="9">
+        <f t="shared" si="358"/>
+        <v>-1.459854014598541E-2</v>
+      </c>
+      <c r="AP32" s="9">
+        <f t="shared" si="358"/>
+        <v>-7.8333333333333199E-2</v>
+      </c>
+      <c r="AQ32" s="9">
+        <f t="shared" si="358"/>
+        <v>-2.1199747055565976</v>
+      </c>
+      <c r="AR32" s="9">
         <f t="shared" si="358"/>
         <v>0.2</v>
       </c>
-      <c r="AG32" s="9">
+      <c r="AS32" s="9">
         <f t="shared" si="358"/>
         <v>0.2</v>
       </c>
-      <c r="AH32" s="9">
+      <c r="AT32" s="9">
         <f t="shared" si="358"/>
         <v>0.2</v>
       </c>
-      <c r="AJ32" s="9">
-        <f t="shared" ref="AJ32" si="359">AJ17/AJ16</f>
-        <v>6.4516129032257979E-2</v>
-      </c>
-      <c r="AK32" s="9">
-        <f t="shared" ref="AK32:AL32" si="360">AK17/AK16</f>
-        <v>1.6567263088137864E-2</v>
-      </c>
-      <c r="AL32" s="9">
-        <f t="shared" si="360"/>
-        <v>7.6294277929155122E-2</v>
-      </c>
-      <c r="AM32" s="9">
-        <f t="shared" ref="AM32:AV32" si="361">AM17/AM16</f>
-        <v>-2.4513947590870694E-2</v>
-      </c>
-      <c r="AN32" s="9">
-        <f t="shared" si="361"/>
-        <v>-1.1776649746192887E-2</v>
-      </c>
-      <c r="AO32" s="9">
-        <f t="shared" si="361"/>
-        <v>-1.459854014598541E-2</v>
-      </c>
-      <c r="AP32" s="9">
-        <f t="shared" si="361"/>
-        <v>-7.8333333333333199E-2</v>
-      </c>
-      <c r="AQ32" s="9">
-        <f t="shared" si="361"/>
-        <v>0.50248967149014201</v>
-      </c>
-      <c r="AR32" s="9">
-        <f t="shared" si="361"/>
+      <c r="AU32" s="9">
+        <f t="shared" si="358"/>
         <v>0.2</v>
       </c>
-      <c r="AS32" s="9">
-        <f t="shared" si="361"/>
+      <c r="AV32" s="9">
+        <f t="shared" si="358"/>
         <v>0.2</v>
       </c>
-      <c r="AT32" s="9">
-        <f t="shared" si="361"/>
+      <c r="AW32" s="9">
+        <f t="shared" ref="AW32:BA32" si="359">AW17/AW16</f>
         <v>0.2</v>
       </c>
-      <c r="AU32" s="9">
-        <f t="shared" si="361"/>
+      <c r="AX32" s="9">
+        <f t="shared" si="359"/>
         <v>0.2</v>
       </c>
-      <c r="AV32" s="9">
-        <f t="shared" si="361"/>
+      <c r="AY32" s="9">
+        <f t="shared" si="359"/>
+        <v>0.2</v>
+      </c>
+      <c r="AZ32" s="9">
+        <f t="shared" si="359"/>
         <v>0.20000000000000004</v>
       </c>
-      <c r="AW32" s="9">
-        <f t="shared" ref="AW32:BA32" si="362">AW17/AW16</f>
-        <v>0.19999999999999998</v>
-      </c>
-      <c r="AX32" s="9">
-        <f t="shared" si="362"/>
-        <v>0.2</v>
-      </c>
-      <c r="AY32" s="9">
-        <f t="shared" si="362"/>
-        <v>0.2</v>
-      </c>
-      <c r="AZ32" s="9">
-        <f t="shared" si="362"/>
-        <v>0.2</v>
-      </c>
       <c r="BA32" s="9">
-        <f t="shared" si="362"/>
+        <f t="shared" si="359"/>
         <v>0.20000000000000004</v>
       </c>
       <c r="BC32" s="1" t="s">
@@ -7116,7 +7107,7 @@
       </c>
       <c r="BD32" s="10">
         <f>BD30/BD31-1</f>
-        <v>-0.324767276419479</v>
+        <v>-0.4381053962942203</v>
       </c>
     </row>
     <row r="33" spans="2:56" x14ac:dyDescent="0.3">
@@ -7128,200 +7119,200 @@
         <v>-4.831625183016109E-2</v>
       </c>
       <c r="D33" s="9">
-        <f t="shared" ref="D33:AW33" si="363">D18/D5</f>
+        <f t="shared" ref="D33:AW33" si="360">D18/D5</f>
         <v>3.8265306122449343E-3</v>
       </c>
       <c r="E33" s="9">
+        <f t="shared" si="360"/>
+        <v>-5.4786620530565329E-2</v>
+      </c>
+      <c r="F33" s="9">
+        <f t="shared" si="360"/>
+        <v>2.466449038810296E-2</v>
+      </c>
+      <c r="G33" s="9">
+        <f t="shared" si="360"/>
+        <v>-4.6927914852443242E-2</v>
+      </c>
+      <c r="H33" s="9">
+        <f t="shared" si="360"/>
+        <v>-3.7824870051979237E-2</v>
+      </c>
+      <c r="I33" s="9">
+        <f t="shared" si="360"/>
+        <v>-9.4288999616711458E-2</v>
+      </c>
+      <c r="J33" s="9">
+        <f t="shared" si="360"/>
+        <v>-3.7937743190661365E-2</v>
+      </c>
+      <c r="K33" s="9">
+        <f t="shared" si="360"/>
+        <v>-0.16957605985037405</v>
+      </c>
+      <c r="L33" s="9">
+        <f t="shared" si="360"/>
+        <v>-0.1210334175793316</v>
+      </c>
+      <c r="M33" s="9">
+        <f t="shared" si="360"/>
+        <v>2.9229406554473071E-2</v>
+      </c>
+      <c r="N33" s="9">
+        <f t="shared" si="360"/>
+        <v>0.10363132789659947</v>
+      </c>
+      <c r="O33" s="9">
+        <f t="shared" si="360"/>
+        <v>0.13288052943225367</v>
+      </c>
+      <c r="P33" s="9">
+        <f t="shared" si="360"/>
+        <v>0.11393582390327067</v>
+      </c>
+      <c r="Q33" s="9">
+        <f t="shared" si="360"/>
+        <v>0.10133843212237087</v>
+      </c>
+      <c r="R33" s="9">
+        <f t="shared" si="360"/>
+        <v>2.7389344735929688E-2</v>
+      </c>
+      <c r="S33" s="9">
+        <f t="shared" ref="S33:AA33" si="361">S18/S5</f>
+        <v>-3.5982008995502329E-2</v>
+      </c>
+      <c r="T33" s="9">
+        <f t="shared" si="361"/>
+        <v>-0.14702419882276005</v>
+      </c>
+      <c r="U33" s="9">
+        <f t="shared" si="361"/>
+        <v>-0.16062516417126335</v>
+      </c>
+      <c r="V33" s="9">
+        <f t="shared" si="361"/>
+        <v>-0.27355552992734417</v>
+      </c>
+      <c r="W33" s="9">
+        <f t="shared" si="361"/>
+        <v>-0.26059379217273959</v>
+      </c>
+      <c r="X33" s="9">
+        <f t="shared" si="361"/>
+        <v>-0.12687359848931906</v>
+      </c>
+      <c r="Y33" s="9">
+        <f t="shared" si="361"/>
+        <v>-0.36195175438596489</v>
+      </c>
+      <c r="Z33" s="9">
+        <f t="shared" si="361"/>
+        <v>-7.9431183341797884E-2</v>
+      </c>
+      <c r="AA33" s="9">
+        <f t="shared" si="361"/>
+        <v>-5.7635579759473629E-2</v>
+      </c>
+      <c r="AB33" s="9">
+        <f t="shared" ref="AB33:AD33" si="362">AB18/AB5</f>
+        <v>-3.5223633922115583E-2</v>
+      </c>
+      <c r="AC33" s="9">
+        <f t="shared" si="362"/>
+        <v>-8.3788363773298988E-3</v>
+      </c>
+      <c r="AD33" s="9">
+        <f t="shared" si="362"/>
+        <v>-2.9641965029142323E-2</v>
+      </c>
+      <c r="AE33" s="9">
+        <f t="shared" ref="AE33:AH33" si="363">AE18/AE5</f>
+        <v>-2.6844322523758249E-2</v>
+      </c>
+      <c r="AF33" s="9">
         <f t="shared" si="363"/>
-        <v>-5.4786620530565329E-2</v>
-      </c>
-      <c r="F33" s="9">
+        <v>9.4500945009449496E-3</v>
+      </c>
+      <c r="AG33" s="9">
         <f t="shared" si="363"/>
-        <v>2.466449038810296E-2</v>
-      </c>
-      <c r="G33" s="9">
+        <v>1.2772803658129935E-2</v>
+      </c>
+      <c r="AH33" s="9">
         <f t="shared" si="363"/>
-        <v>-4.6927914852443242E-2</v>
-      </c>
-      <c r="H33" s="9">
-        <f t="shared" si="363"/>
-        <v>-3.7824870051979237E-2</v>
-      </c>
-      <c r="I33" s="9">
-        <f t="shared" si="363"/>
-        <v>-9.4288999616711458E-2</v>
-      </c>
-      <c r="J33" s="9">
-        <f t="shared" si="363"/>
-        <v>-3.7937743190661365E-2</v>
-      </c>
-      <c r="K33" s="9">
-        <f t="shared" si="363"/>
-        <v>-0.16957605985037405</v>
-      </c>
-      <c r="L33" s="9">
-        <f t="shared" si="363"/>
-        <v>-0.1210334175793316</v>
-      </c>
-      <c r="M33" s="9">
-        <f t="shared" si="363"/>
-        <v>2.9229406554473071E-2</v>
-      </c>
-      <c r="N33" s="9">
-        <f t="shared" si="363"/>
-        <v>0.10363132789659947</v>
-      </c>
-      <c r="O33" s="9">
-        <f t="shared" si="363"/>
-        <v>0.13288052943225367</v>
-      </c>
-      <c r="P33" s="9">
-        <f t="shared" si="363"/>
-        <v>0.11393582390327067</v>
-      </c>
-      <c r="Q33" s="9">
-        <f t="shared" si="363"/>
-        <v>0.10133843212237087</v>
-      </c>
-      <c r="R33" s="9">
-        <f t="shared" si="363"/>
-        <v>2.7389344735929688E-2</v>
-      </c>
-      <c r="S33" s="9">
-        <f t="shared" ref="S33:AA33" si="364">S18/S5</f>
-        <v>-3.5982008995502329E-2</v>
-      </c>
-      <c r="T33" s="9">
+        <v>1.3346521043516246E-2</v>
+      </c>
+      <c r="AJ33" s="9">
+        <f t="shared" si="360"/>
+        <v>-1.1717171717171734E-2</v>
+      </c>
+      <c r="AK33" s="9">
+        <f t="shared" si="360"/>
+        <v>-5.2582159624413059E-2</v>
+      </c>
+      <c r="AL33" s="9">
+        <f t="shared" si="360"/>
+        <v>-9.53103913630232E-3</v>
+      </c>
+      <c r="AM33" s="9">
+        <f t="shared" si="360"/>
+        <v>8.7683125339120913E-2</v>
+      </c>
+      <c r="AN33" s="9">
+        <f t="shared" si="360"/>
+        <v>-0.15936930309911421</v>
+      </c>
+      <c r="AO33" s="9">
+        <f t="shared" si="360"/>
+        <v>-0.20342630853994481</v>
+      </c>
+      <c r="AP33" s="9">
+        <f t="shared" si="360"/>
+        <v>-3.1463515452136111E-2</v>
+      </c>
+      <c r="AQ33" s="9">
+        <f t="shared" si="360"/>
+        <v>3.4086769234357973E-3</v>
+      </c>
+      <c r="AR33" s="9">
+        <f t="shared" si="360"/>
+        <v>4.6045212886573872E-2</v>
+      </c>
+      <c r="AS33" s="9">
+        <f t="shared" si="360"/>
+        <v>6.9818386174439528E-2</v>
+      </c>
+      <c r="AT33" s="9">
+        <f t="shared" si="360"/>
+        <v>8.7850377195818619E-2</v>
+      </c>
+      <c r="AU33" s="9">
+        <f t="shared" si="360"/>
+        <v>9.2437510271924705E-2</v>
+      </c>
+      <c r="AV33" s="9">
+        <f t="shared" si="360"/>
+        <v>9.5272905515312201E-2</v>
+      </c>
+      <c r="AW33" s="9">
+        <f t="shared" si="360"/>
+        <v>9.6667701114446794E-2</v>
+      </c>
+      <c r="AX33" s="9">
+        <f t="shared" ref="AX33:BA33" si="364">AX18/AX5</f>
+        <v>9.8054386464319271E-2</v>
+      </c>
+      <c r="AY33" s="9">
         <f t="shared" si="364"/>
-        <v>-0.14702419882276005</v>
-      </c>
-      <c r="U33" s="9">
+        <v>9.9433026406545277E-2</v>
+      </c>
+      <c r="AZ33" s="9">
         <f t="shared" si="364"/>
-        <v>-0.16062516417126335</v>
-      </c>
-      <c r="V33" s="9">
+        <v>0.10080368606459329</v>
+      </c>
+      <c r="BA33" s="9">
         <f t="shared" si="364"/>
-        <v>-0.27355552992734417</v>
-      </c>
-      <c r="W33" s="9">
-        <f t="shared" si="364"/>
-        <v>-0.26059379217273959</v>
-      </c>
-      <c r="X33" s="9">
-        <f t="shared" si="364"/>
-        <v>-0.12687359848931906</v>
-      </c>
-      <c r="Y33" s="9">
-        <f t="shared" si="364"/>
-        <v>-0.36195175438596489</v>
-      </c>
-      <c r="Z33" s="9">
-        <f t="shared" si="364"/>
-        <v>-7.9431183341797884E-2</v>
-      </c>
-      <c r="AA33" s="9">
-        <f t="shared" si="364"/>
-        <v>-5.7635579759473629E-2</v>
-      </c>
-      <c r="AB33" s="9">
-        <f t="shared" ref="AB33:AD33" si="365">AB18/AB5</f>
-        <v>-3.5223633922115583E-2</v>
-      </c>
-      <c r="AC33" s="9">
-        <f t="shared" si="365"/>
-        <v>-8.3788363773298988E-3</v>
-      </c>
-      <c r="AD33" s="9">
-        <f t="shared" si="365"/>
-        <v>-2.9641965029142323E-2</v>
-      </c>
-      <c r="AE33" s="9">
-        <f t="shared" ref="AE33:AH33" si="366">AE18/AE5</f>
-        <v>-2.6844322523758249E-2</v>
-      </c>
-      <c r="AF33" s="9">
-        <f t="shared" si="366"/>
-        <v>-8.6593363108554856E-3</v>
-      </c>
-      <c r="AG33" s="9">
-        <f t="shared" si="366"/>
-        <v>1.2094949218743494E-2</v>
-      </c>
-      <c r="AH33" s="9">
-        <f t="shared" si="366"/>
-        <v>1.0986035138575719E-2</v>
-      </c>
-      <c r="AJ33" s="9">
-        <f t="shared" si="363"/>
-        <v>-1.1717171717171734E-2</v>
-      </c>
-      <c r="AK33" s="9">
-        <f t="shared" si="363"/>
-        <v>-5.2582159624413059E-2</v>
-      </c>
-      <c r="AL33" s="9">
-        <f t="shared" si="363"/>
-        <v>-9.53103913630232E-3</v>
-      </c>
-      <c r="AM33" s="9">
-        <f t="shared" si="363"/>
-        <v>8.7683125339120913E-2</v>
-      </c>
-      <c r="AN33" s="9">
-        <f t="shared" si="363"/>
-        <v>-0.15936930309911421</v>
-      </c>
-      <c r="AO33" s="9">
-        <f t="shared" si="363"/>
-        <v>-0.20342630853994481</v>
-      </c>
-      <c r="AP33" s="9">
-        <f t="shared" si="363"/>
-        <v>-3.1463515452136111E-2</v>
-      </c>
-      <c r="AQ33" s="9">
-        <f t="shared" si="363"/>
-        <v>-1.7811942130843668E-3</v>
-      </c>
-      <c r="AR33" s="9">
-        <f t="shared" si="363"/>
-        <v>3.9005471339370629E-2</v>
-      </c>
-      <c r="AS33" s="9">
-        <f t="shared" si="363"/>
-        <v>6.3276339627404019E-2</v>
-      </c>
-      <c r="AT33" s="9">
-        <f t="shared" si="363"/>
-        <v>8.1607855676225416E-2</v>
-      </c>
-      <c r="AU33" s="9">
-        <f t="shared" si="363"/>
-        <v>8.6302615499836116E-2</v>
-      </c>
-      <c r="AV33" s="9">
-        <f t="shared" si="363"/>
-        <v>8.9204952362563456E-2</v>
-      </c>
-      <c r="AW33" s="9">
-        <f t="shared" si="363"/>
-        <v>9.0634997344797338E-2</v>
-      </c>
-      <c r="AX33" s="9">
-        <f t="shared" ref="AX33:BA33" si="367">AX18/AX5</f>
-        <v>9.2056884574260367E-2</v>
-      </c>
-      <c r="AY33" s="9">
-        <f t="shared" si="367"/>
-        <v>9.3470676781589601E-2</v>
-      </c>
-      <c r="AZ33" s="9">
-        <f t="shared" si="367"/>
-        <v>9.4876437040195896E-2</v>
-      </c>
-      <c r="BA33" s="9">
-        <f t="shared" si="367"/>
-        <v>9.6274228758132477E-2</v>
+        <v>0.10216643083623501</v>
       </c>
       <c r="BC33" t="s">
         <v>55</v>

--- a/Financial Analysis/ROKU.xlsx
+++ b/Financial Analysis/ROKU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A217F5-ED1C-47FE-9422-919409341BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D6F9E71-DE83-4970-A1DA-6426B595BB07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{D7866C78-17E7-487E-8035-32073BE9C199}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="81">
   <si>
     <t>ROKU</t>
   </si>
@@ -266,9 +266,6 @@
   </si>
   <si>
     <t>Q425</t>
-  </si>
-  <si>
-    <t>hard to value</t>
   </si>
   <si>
     <t>Overvalued</t>
@@ -374,14 +371,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
     </xdr:to>
@@ -398,7 +395,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="20185380" y="0"/>
+          <a:off x="20779740" y="0"/>
           <a:ext cx="0" cy="6134100"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -797,17 +794,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="11">
-        <v>89.5</v>
+        <v>94.56</v>
       </c>
       <c r="E3" s="4">
-        <v>45870</v>
+        <v>45961</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45870</v>
+        <v>45961</v>
       </c>
       <c r="G3" s="4">
-        <v>45959</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -815,8 +812,8 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>146.9</f>
-        <v>146.9</v>
+        <f>147.5</f>
+        <v>147.5</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>76</v>
@@ -828,7 +825,7 @@
       </c>
       <c r="D5" s="5">
         <f>D4*D3</f>
-        <v>13147.550000000001</v>
+        <v>13947.6</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -869,7 +866,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>10894.25</v>
+        <v>11694.3</v>
       </c>
     </row>
   </sheetData>
@@ -880,7 +877,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F6321-D042-44C2-A13A-18A1A0821A3D}">
-  <dimension ref="B2:FG35"/>
+  <dimension ref="B2:FG33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
@@ -1136,12 +1133,11 @@
         <v>975.5</v>
       </c>
       <c r="AG3" s="7">
-        <f>AC3*1.13</f>
-        <v>1026.2659999999998</v>
+        <v>1064.5999999999999</v>
       </c>
       <c r="AH3" s="7">
-        <f>AD3*1.11</f>
-        <v>1149.183</v>
+        <f>AD3*1.15</f>
+        <v>1190.5949999999998</v>
       </c>
       <c r="AI3" s="8"/>
       <c r="AJ3" s="5">
@@ -1174,47 +1170,47 @@
       </c>
       <c r="AQ3" s="5">
         <f>SUM(AE3:AH3)</f>
-        <v>4031.7489999999998</v>
+        <v>4111.494999999999</v>
       </c>
       <c r="AR3" s="5">
-        <f>AQ3*1.11</f>
-        <v>4475.2413900000001</v>
+        <f>AQ3*1.12</f>
+        <v>4604.8743999999997</v>
       </c>
       <c r="AS3" s="5">
         <f>AR3*1.08</f>
-        <v>4833.2607012000008</v>
+        <v>4973.2643520000001</v>
       </c>
       <c r="AT3" s="5">
         <f>AS3*1.06</f>
-        <v>5123.2563432720008</v>
+        <v>5271.6602131200007</v>
       </c>
       <c r="AU3" s="5">
         <f>AT3*1.04</f>
-        <v>5328.1865970028812</v>
+        <v>5482.5266216448008</v>
       </c>
       <c r="AV3" s="5">
         <f t="shared" ref="AV3" si="0">AU3*1.03</f>
-        <v>5488.0321949129675</v>
+        <v>5647.0024202941449</v>
       </c>
       <c r="AW3" s="5">
         <f>AV3*1.02</f>
-        <v>5597.7928388112268</v>
+        <v>5759.9424687000283</v>
       </c>
       <c r="AX3" s="5">
         <f t="shared" ref="AX3:BA3" si="1">AW3*1.02</f>
-        <v>5709.748695587451</v>
+        <v>5875.1413180740292</v>
       </c>
       <c r="AY3" s="5">
         <f t="shared" si="1"/>
-        <v>5823.9436694992</v>
+        <v>5992.6441444355096</v>
       </c>
       <c r="AZ3" s="5">
         <f t="shared" si="1"/>
-        <v>5940.4225428891841</v>
+        <v>6112.4970273242197</v>
       </c>
       <c r="BA3" s="5">
         <f t="shared" si="1"/>
-        <v>6059.2309937469681</v>
+        <v>6234.7469678707039</v>
       </c>
     </row>
     <row r="4" spans="2:53" x14ac:dyDescent="0.3">
@@ -1312,12 +1308,11 @@
         <v>135.6</v>
       </c>
       <c r="AG4" s="7">
-        <f>AC4*1.01</f>
-        <v>155.54</v>
+        <v>146</v>
       </c>
       <c r="AH4" s="7">
-        <f>AD4*1.02</f>
-        <v>169.01399999999998</v>
+        <f>AD4*0.97</f>
+        <v>160.72899999999998</v>
       </c>
       <c r="AI4" s="8"/>
       <c r="AJ4" s="5">
@@ -1350,47 +1345,47 @@
       </c>
       <c r="AQ4" s="5">
         <f>SUM(AE4:AH4)</f>
-        <v>600.05399999999997</v>
+        <v>582.22900000000004</v>
       </c>
       <c r="AR4" s="5">
-        <f>AQ4*1.03</f>
-        <v>618.05561999999998</v>
+        <f>AQ4*1.02</f>
+        <v>593.87358000000006</v>
       </c>
       <c r="AS4" s="5">
-        <f>AR4*1.03</f>
-        <v>636.59728859999996</v>
+        <f>AR4*1.02</f>
+        <v>605.7510516000001</v>
       </c>
       <c r="AT4" s="5">
-        <f t="shared" ref="AT4:AV4" si="2">AS4*1.02</f>
-        <v>649.32923437199997</v>
+        <f>AS4*1.01</f>
+        <v>611.80856211600008</v>
       </c>
       <c r="AU4" s="5">
-        <f t="shared" si="2"/>
-        <v>662.31581905943995</v>
+        <f t="shared" ref="AU4:BA4" si="2">AT4*1.01</f>
+        <v>617.92664773716012</v>
       </c>
       <c r="AV4" s="5">
         <f t="shared" si="2"/>
-        <v>675.56213544062871</v>
+        <v>624.10591421453171</v>
       </c>
       <c r="AW4" s="5">
-        <f>AV4*1.01</f>
-        <v>682.31775679503505</v>
+        <f t="shared" si="2"/>
+        <v>630.34697335667704</v>
       </c>
       <c r="AX4" s="5">
-        <f t="shared" ref="AX4:BA4" si="3">AW4*1.01</f>
-        <v>689.14093436298538</v>
+        <f t="shared" si="2"/>
+        <v>636.65044309024381</v>
       </c>
       <c r="AY4" s="5">
-        <f t="shared" si="3"/>
-        <v>696.03234370661528</v>
+        <f t="shared" si="2"/>
+        <v>643.01694752114622</v>
       </c>
       <c r="AZ4" s="5">
-        <f t="shared" si="3"/>
-        <v>702.99266714368139</v>
+        <f t="shared" si="2"/>
+        <v>649.44711699635764</v>
       </c>
       <c r="BA4" s="5">
-        <f t="shared" si="3"/>
-        <v>710.02259381511817</v>
+        <f t="shared" si="2"/>
+        <v>655.94158816632125</v>
       </c>
     </row>
     <row r="5" spans="2:53" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1398,205 +1393,205 @@
         <v>10</v>
       </c>
       <c r="C5" s="8">
-        <f t="shared" ref="C5:L5" si="4">C3+C4</f>
+        <f t="shared" ref="C5:L5" si="3">C3+C4</f>
         <v>136.6</v>
       </c>
       <c r="D5" s="8">
+        <f t="shared" si="3"/>
+        <v>156.80000000000001</v>
+      </c>
+      <c r="E5" s="8">
+        <f t="shared" si="3"/>
+        <v>173.39999999999998</v>
+      </c>
+      <c r="F5" s="8">
+        <f t="shared" si="3"/>
+        <v>275.7</v>
+      </c>
+      <c r="G5" s="8">
+        <f t="shared" si="3"/>
+        <v>206.7</v>
+      </c>
+      <c r="H5" s="8">
+        <f t="shared" si="3"/>
+        <v>250.1</v>
+      </c>
+      <c r="I5" s="8">
+        <f t="shared" si="3"/>
+        <v>260.89999999999998</v>
+      </c>
+      <c r="J5" s="8">
+        <f t="shared" si="3"/>
+        <v>411.20000000000005</v>
+      </c>
+      <c r="K5" s="8">
+        <f t="shared" si="3"/>
+        <v>320.8</v>
+      </c>
+      <c r="L5" s="8">
+        <f t="shared" si="3"/>
+        <v>356.1</v>
+      </c>
+      <c r="M5" s="8">
+        <f t="shared" ref="M5:AL5" si="4">M3+M4</f>
+        <v>451.6</v>
+      </c>
+      <c r="N5" s="8">
         <f t="shared" si="4"/>
-        <v>156.80000000000001</v>
-      </c>
-      <c r="E5" s="8">
+        <v>649.9</v>
+      </c>
+      <c r="O5" s="8">
         <f t="shared" si="4"/>
-        <v>173.39999999999998</v>
-      </c>
-      <c r="F5" s="8">
+        <v>574.20000000000005</v>
+      </c>
+      <c r="P5" s="8">
+        <f t="shared" ref="P5:Q5" si="5">P3+P4</f>
+        <v>645.09999999999991</v>
+      </c>
+      <c r="Q5" s="8">
+        <f t="shared" si="5"/>
+        <v>679.9</v>
+      </c>
+      <c r="R5" s="8">
         <f t="shared" si="4"/>
-        <v>275.7</v>
-      </c>
-      <c r="G5" s="8">
-        <f t="shared" si="4"/>
-        <v>206.7</v>
-      </c>
-      <c r="H5" s="8">
-        <f t="shared" si="4"/>
-        <v>250.1</v>
-      </c>
-      <c r="I5" s="8">
-        <f t="shared" si="4"/>
-        <v>260.89999999999998</v>
-      </c>
-      <c r="J5" s="8">
-        <f t="shared" si="4"/>
-        <v>411.20000000000005</v>
-      </c>
-      <c r="K5" s="8">
-        <f t="shared" si="4"/>
-        <v>320.8</v>
-      </c>
-      <c r="L5" s="8">
-        <f t="shared" si="4"/>
-        <v>356.1</v>
-      </c>
-      <c r="M5" s="8">
-        <f t="shared" ref="M5:AL5" si="5">M3+M4</f>
-        <v>451.6</v>
-      </c>
-      <c r="N5" s="8">
-        <f t="shared" si="5"/>
-        <v>649.9</v>
-      </c>
-      <c r="O5" s="8">
-        <f t="shared" si="5"/>
-        <v>574.20000000000005</v>
-      </c>
-      <c r="P5" s="8">
-        <f t="shared" ref="P5:Q5" si="6">P3+P4</f>
-        <v>645.09999999999991</v>
-      </c>
-      <c r="Q5" s="8">
+        <v>865.3</v>
+      </c>
+      <c r="S5" s="8">
+        <f t="shared" ref="S5:T5" si="6">S3+S4</f>
+        <v>733.69999999999993</v>
+      </c>
+      <c r="T5" s="8">
         <f t="shared" si="6"/>
-        <v>679.9</v>
-      </c>
-      <c r="R5" s="8">
-        <f t="shared" si="5"/>
-        <v>865.3</v>
-      </c>
-      <c r="S5" s="8">
-        <f t="shared" ref="S5:T5" si="7">S3+S4</f>
-        <v>733.69999999999993</v>
-      </c>
-      <c r="T5" s="8">
-        <f t="shared" si="7"/>
         <v>764.5</v>
       </c>
       <c r="U5" s="8">
-        <f t="shared" ref="U5" si="8">U3+U4</f>
+        <f t="shared" ref="U5" si="7">U3+U4</f>
         <v>761.40000000000009</v>
       </c>
       <c r="V5" s="8">
-        <f t="shared" ref="V5" si="9">V3+V4</f>
+        <f t="shared" ref="V5" si="8">V3+V4</f>
         <v>867.09999999999991</v>
       </c>
       <c r="W5" s="8">
-        <f t="shared" ref="W5:X5" si="10">W3+W4</f>
+        <f t="shared" ref="W5:X5" si="9">W3+W4</f>
         <v>741</v>
       </c>
       <c r="X5" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>847.3</v>
       </c>
       <c r="Y5" s="8">
-        <f t="shared" ref="Y5" si="11">Y3+Y4</f>
+        <f t="shared" ref="Y5" si="10">Y3+Y4</f>
         <v>912</v>
       </c>
       <c r="Z5" s="8">
-        <f t="shared" ref="Z5:AH5" si="12">Z3+Z4</f>
+        <f t="shared" ref="Z5:AH5" si="11">Z3+Z4</f>
         <v>984.5</v>
       </c>
       <c r="AA5" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>881.4</v>
       </c>
       <c r="AB5" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>968.09999999999991</v>
       </c>
       <c r="AC5" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1062.2</v>
       </c>
       <c r="AD5" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1201</v>
       </c>
       <c r="AE5" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1020.6999999999999</v>
       </c>
       <c r="AF5" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1111.0999999999999</v>
       </c>
       <c r="AG5" s="8">
-        <f t="shared" si="12"/>
-        <v>1181.8059999999998</v>
+        <f t="shared" si="11"/>
+        <v>1210.5999999999999</v>
       </c>
       <c r="AH5" s="8">
-        <f t="shared" si="12"/>
-        <v>1318.1969999999999</v>
+        <f t="shared" si="11"/>
+        <v>1351.3239999999998</v>
       </c>
       <c r="AI5" s="8"/>
       <c r="AJ5" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>742.5</v>
       </c>
       <c r="AK5" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1128.9000000000001</v>
       </c>
       <c r="AL5" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1778.3999999999999</v>
       </c>
       <c r="AM5" s="8">
-        <f t="shared" ref="AM5" si="13">AM3+AM4</f>
+        <f t="shared" ref="AM5" si="12">AM3+AM4</f>
         <v>2764.5</v>
       </c>
       <c r="AN5" s="8">
-        <f t="shared" ref="AN5" si="14">AN3+AN4</f>
+        <f t="shared" ref="AN5" si="13">AN3+AN4</f>
         <v>3126.7</v>
       </c>
       <c r="AO5" s="8">
-        <f t="shared" ref="AO5" si="15">AO3+AO4</f>
+        <f t="shared" ref="AO5" si="14">AO3+AO4</f>
         <v>3484.8</v>
       </c>
       <c r="AP5" s="8">
-        <f t="shared" ref="AP5" si="16">AP3+AP4</f>
+        <f t="shared" ref="AP5" si="15">AP3+AP4</f>
         <v>4112.7</v>
       </c>
       <c r="AQ5" s="8">
-        <f t="shared" ref="AQ5" si="17">AQ3+AQ4</f>
-        <v>4631.8029999999999</v>
+        <f t="shared" ref="AQ5" si="16">AQ3+AQ4</f>
+        <v>4693.7239999999993</v>
       </c>
       <c r="AR5" s="8">
-        <f t="shared" ref="AR5" si="18">AR3+AR4</f>
-        <v>5093.2970100000002</v>
+        <f t="shared" ref="AR5" si="17">AR3+AR4</f>
+        <v>5198.7479800000001</v>
       </c>
       <c r="AS5" s="8">
-        <f t="shared" ref="AS5" si="19">AS3+AS4</f>
-        <v>5469.8579898000007</v>
+        <f t="shared" ref="AS5" si="18">AS3+AS4</f>
+        <v>5579.0154036000004</v>
       </c>
       <c r="AT5" s="8">
-        <f t="shared" ref="AT5" si="20">AT3+AT4</f>
-        <v>5772.5855776440003</v>
+        <f t="shared" ref="AT5" si="19">AT3+AT4</f>
+        <v>5883.4687752360005</v>
       </c>
       <c r="AU5" s="8">
-        <f t="shared" ref="AU5" si="21">AU3+AU4</f>
-        <v>5990.5024160623216</v>
+        <f t="shared" ref="AU5" si="20">AU3+AU4</f>
+        <v>6100.453269381961</v>
       </c>
       <c r="AV5" s="8">
-        <f t="shared" ref="AV5:AW5" si="22">AV3+AV4</f>
-        <v>6163.594330353596</v>
+        <f t="shared" ref="AV5:AW5" si="21">AV3+AV4</f>
+        <v>6271.1083345086763</v>
       </c>
       <c r="AW5" s="8">
+        <f t="shared" si="21"/>
+        <v>6390.2894420567054</v>
+      </c>
+      <c r="AX5" s="8">
+        <f t="shared" ref="AX5:BA5" si="22">AX3+AX4</f>
+        <v>6511.7917611642733</v>
+      </c>
+      <c r="AY5" s="8">
         <f t="shared" si="22"/>
-        <v>6280.110595606262</v>
-      </c>
-      <c r="AX5" s="8">
-        <f t="shared" ref="AX5:BA5" si="23">AX3+AX4</f>
-        <v>6398.8896299504368</v>
-      </c>
-      <c r="AY5" s="8">
-        <f t="shared" si="23"/>
-        <v>6519.9760132058154</v>
+        <v>6635.6610919566556</v>
       </c>
       <c r="AZ5" s="8">
-        <f t="shared" si="23"/>
-        <v>6643.4152100328656</v>
+        <f t="shared" si="22"/>
+        <v>6761.9441443205778</v>
       </c>
       <c r="BA5" s="8">
-        <f t="shared" si="23"/>
-        <v>6769.2535875620861</v>
+        <f t="shared" si="22"/>
+        <v>6890.6885560370247</v>
       </c>
     </row>
     <row r="6" spans="2:53" x14ac:dyDescent="0.3">
@@ -1694,12 +1689,11 @@
         <v>477.8</v>
       </c>
       <c r="AG6" s="5">
-        <f>AG3*0.46</f>
-        <v>472.08235999999994</v>
+        <v>516.9</v>
       </c>
       <c r="AH6" s="5">
         <f>AH3*0.46</f>
-        <v>528.62418000000002</v>
+        <v>547.67369999999994</v>
       </c>
       <c r="AJ6" s="5">
         <f>SUM(C6:F6)</f>
@@ -1731,47 +1725,47 @@
       </c>
       <c r="AQ6" s="5">
         <f>SUM(AE6:AH6)</f>
-        <v>1895.0065399999999</v>
+        <v>1958.8736999999996</v>
       </c>
       <c r="AR6" s="5">
-        <f>AR3*0.45</f>
-        <v>2013.8586255</v>
+        <f>AR3*0.47</f>
+        <v>2164.2909679999998</v>
       </c>
       <c r="AS6" s="5">
-        <f t="shared" ref="AS6:BA6" si="24">AS3*0.45</f>
-        <v>2174.9673155400005</v>
+        <f>AS3*0.46</f>
+        <v>2287.70160192</v>
       </c>
       <c r="AT6" s="5">
-        <f t="shared" si="24"/>
-        <v>2305.4653544724006</v>
+        <f t="shared" ref="AT6:BA6" si="23">AT3*0.46</f>
+        <v>2424.9636980352002</v>
       </c>
       <c r="AU6" s="5">
-        <f t="shared" si="24"/>
-        <v>2397.6839686512967</v>
+        <f t="shared" si="23"/>
+        <v>2521.9622459566085</v>
       </c>
       <c r="AV6" s="5">
-        <f t="shared" si="24"/>
-        <v>2469.6144877108354</v>
+        <f t="shared" si="23"/>
+        <v>2597.6211133353067</v>
       </c>
       <c r="AW6" s="5">
-        <f t="shared" si="24"/>
-        <v>2519.006777465052</v>
+        <f t="shared" si="23"/>
+        <v>2649.5735356020132</v>
       </c>
       <c r="AX6" s="5">
-        <f t="shared" si="24"/>
-        <v>2569.386913014353</v>
+        <f t="shared" si="23"/>
+        <v>2702.5650063140533</v>
       </c>
       <c r="AY6" s="5">
-        <f t="shared" si="24"/>
-        <v>2620.7746512746403</v>
+        <f t="shared" si="23"/>
+        <v>2756.6163064403345</v>
       </c>
       <c r="AZ6" s="5">
-        <f t="shared" si="24"/>
-        <v>2673.1901443001329</v>
+        <f t="shared" si="23"/>
+        <v>2811.7486325691411</v>
       </c>
       <c r="BA6" s="5">
-        <f t="shared" si="24"/>
-        <v>2726.6539471861356</v>
+        <f t="shared" si="23"/>
+        <v>2867.9836052205237</v>
       </c>
     </row>
     <row r="7" spans="2:53" x14ac:dyDescent="0.3">
@@ -1869,12 +1863,11 @@
         <v>135.6</v>
       </c>
       <c r="AG7" s="5">
-        <f>AG4*1.09</f>
-        <v>169.5386</v>
+        <v>168.9</v>
       </c>
       <c r="AH7" s="5">
         <f>AH4*1.2</f>
-        <v>202.81679999999997</v>
+        <v>192.87479999999996</v>
       </c>
       <c r="AJ7" s="5">
         <f>SUM(C7:F7)</f>
@@ -1906,47 +1899,47 @@
       </c>
       <c r="AQ7" s="5">
         <f>SUM(AE7:AH7)</f>
-        <v>667.05539999999996</v>
+        <v>656.47479999999996</v>
       </c>
       <c r="AR7" s="5">
         <f>AR4*1.05</f>
-        <v>648.95840099999998</v>
+        <v>623.56725900000004</v>
       </c>
       <c r="AS7" s="5">
         <f>AS4*1.01</f>
-        <v>642.96326148599996</v>
+        <v>611.80856211600008</v>
       </c>
       <c r="AT7" s="5">
         <f>AT4*0.99</f>
-        <v>642.83594202827999</v>
+        <v>605.69047649484003</v>
       </c>
       <c r="AU7" s="5">
-        <f t="shared" ref="AU7:BA7" si="25">AU4*0.99</f>
-        <v>655.69266086884556</v>
+        <f t="shared" ref="AU7:BA7" si="24">AU4*0.99</f>
+        <v>611.74738125978854</v>
       </c>
       <c r="AV7" s="5">
-        <f t="shared" si="25"/>
-        <v>668.80651408622236</v>
+        <f t="shared" si="24"/>
+        <v>617.86485507238638</v>
       </c>
       <c r="AW7" s="5">
-        <f t="shared" si="25"/>
-        <v>675.49457922708473</v>
+        <f t="shared" si="24"/>
+        <v>624.04350362311027</v>
       </c>
       <c r="AX7" s="5">
-        <f t="shared" si="25"/>
-        <v>682.24952501935547</v>
+        <f t="shared" si="24"/>
+        <v>630.2839386593414</v>
       </c>
       <c r="AY7" s="5">
-        <f t="shared" si="25"/>
-        <v>689.07202026954917</v>
+        <f t="shared" si="24"/>
+        <v>636.58677804593481</v>
       </c>
       <c r="AZ7" s="5">
-        <f t="shared" si="25"/>
-        <v>695.9627404722446</v>
+        <f t="shared" si="24"/>
+        <v>642.95264582639402</v>
       </c>
       <c r="BA7" s="5">
-        <f t="shared" si="25"/>
-        <v>702.92236787696697</v>
+        <f t="shared" si="24"/>
+        <v>649.38217228465805</v>
       </c>
     </row>
     <row r="8" spans="2:53" x14ac:dyDescent="0.3">
@@ -1954,204 +1947,204 @@
         <v>26</v>
       </c>
       <c r="C8" s="5">
-        <f t="shared" ref="C8:L8" si="26">C6+C7</f>
+        <f t="shared" ref="C8:L8" si="25">C6+C7</f>
         <v>73.5</v>
       </c>
       <c r="D8" s="5">
+        <f t="shared" si="25"/>
+        <v>79</v>
+      </c>
+      <c r="E8" s="5">
+        <f t="shared" si="25"/>
+        <v>94.4</v>
+      </c>
+      <c r="F8" s="5">
+        <f t="shared" si="25"/>
+        <v>163.4</v>
+      </c>
+      <c r="G8" s="5">
+        <f t="shared" si="25"/>
+        <v>105.80000000000001</v>
+      </c>
+      <c r="H8" s="5">
+        <f t="shared" si="25"/>
+        <v>135.9</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="25"/>
+        <v>142.5</v>
+      </c>
+      <c r="J8" s="5">
+        <f t="shared" si="25"/>
+        <v>249.5</v>
+      </c>
+      <c r="K8" s="5">
+        <f t="shared" si="25"/>
+        <v>179.60000000000002</v>
+      </c>
+      <c r="L8" s="5">
+        <f t="shared" si="25"/>
+        <v>209.2</v>
+      </c>
+      <c r="M8" s="5">
+        <f t="shared" ref="M8:AL8" si="26">M6+M7</f>
+        <v>236.89999999999998</v>
+      </c>
+      <c r="N8" s="5">
         <f t="shared" si="26"/>
-        <v>79</v>
-      </c>
-      <c r="E8" s="5">
+        <v>344.4</v>
+      </c>
+      <c r="O8" s="5">
+        <f t="shared" ref="O8:R8" si="27">O6+O7</f>
+        <v>247.39999999999998</v>
+      </c>
+      <c r="P8" s="5">
+        <f t="shared" ref="P8:Q8" si="28">P6+P7</f>
+        <v>306.8</v>
+      </c>
+      <c r="Q8" s="5">
+        <f t="shared" si="28"/>
+        <v>316</v>
+      </c>
+      <c r="R8" s="5">
+        <f t="shared" si="27"/>
+        <v>485.7</v>
+      </c>
+      <c r="S8" s="5">
+        <f t="shared" ref="S8:T8" si="29">S6+S7</f>
+        <v>368.9</v>
+      </c>
+      <c r="T8" s="5">
+        <f t="shared" si="29"/>
+        <v>409.3</v>
+      </c>
+      <c r="U8" s="5">
+        <f t="shared" ref="U8" si="30">U6+U7</f>
+        <v>404.6</v>
+      </c>
+      <c r="V8" s="5">
+        <f t="shared" ref="V8" si="31">V6+V7</f>
+        <v>502.70000000000005</v>
+      </c>
+      <c r="W8" s="5">
+        <f t="shared" ref="W8:X8" si="32">W6+W7</f>
+        <v>403.40000000000003</v>
+      </c>
+      <c r="X8" s="5">
+        <f t="shared" si="32"/>
+        <v>468.9</v>
+      </c>
+      <c r="Y8" s="5">
+        <f t="shared" ref="Y8" si="33">Y6+Y7</f>
+        <v>543.20000000000005</v>
+      </c>
+      <c r="Z8" s="5">
+        <f t="shared" ref="Z8:AA8" si="34">Z6+Z7</f>
+        <v>546.5</v>
+      </c>
+      <c r="AA8" s="5">
+        <f t="shared" si="34"/>
+        <v>493.20000000000005</v>
+      </c>
+      <c r="AB8" s="5">
+        <f t="shared" ref="AB8:AD8" si="35">AB6+AB7</f>
+        <v>543.5</v>
+      </c>
+      <c r="AC8" s="5">
+        <f t="shared" si="35"/>
+        <v>582.09999999999991</v>
+      </c>
+      <c r="AD8" s="5">
+        <f t="shared" si="35"/>
+        <v>688.5</v>
+      </c>
+      <c r="AE8" s="5">
+        <f t="shared" ref="AE8:AH8" si="36">AE6+AE7</f>
+        <v>575.6</v>
+      </c>
+      <c r="AF8" s="5">
+        <f t="shared" si="36"/>
+        <v>613.4</v>
+      </c>
+      <c r="AG8" s="5">
+        <f t="shared" si="36"/>
+        <v>685.8</v>
+      </c>
+      <c r="AH8" s="5">
+        <f t="shared" si="36"/>
+        <v>740.54849999999988</v>
+      </c>
+      <c r="AJ8" s="5">
         <f t="shared" si="26"/>
-        <v>94.4</v>
-      </c>
-      <c r="F8" s="5">
+        <v>410.3</v>
+      </c>
+      <c r="AK8" s="5">
         <f t="shared" si="26"/>
-        <v>163.4</v>
-      </c>
-      <c r="G8" s="5">
+        <v>633.70000000000005</v>
+      </c>
+      <c r="AL8" s="5">
         <f t="shared" si="26"/>
-        <v>105.80000000000001</v>
-      </c>
-      <c r="H8" s="5">
-        <f t="shared" si="26"/>
-        <v>135.9</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="26"/>
-        <v>142.5</v>
-      </c>
-      <c r="J8" s="5">
-        <f t="shared" si="26"/>
-        <v>249.5</v>
-      </c>
-      <c r="K8" s="5">
-        <f t="shared" si="26"/>
-        <v>179.60000000000002</v>
-      </c>
-      <c r="L8" s="5">
-        <f t="shared" si="26"/>
-        <v>209.2</v>
-      </c>
-      <c r="M8" s="5">
-        <f t="shared" ref="M8:AL8" si="27">M6+M7</f>
-        <v>236.89999999999998</v>
-      </c>
-      <c r="N8" s="5">
-        <f t="shared" si="27"/>
-        <v>344.4</v>
-      </c>
-      <c r="O8" s="5">
-        <f t="shared" ref="O8:R8" si="28">O6+O7</f>
-        <v>247.39999999999998</v>
-      </c>
-      <c r="P8" s="5">
-        <f t="shared" ref="P8:Q8" si="29">P6+P7</f>
-        <v>306.8</v>
-      </c>
-      <c r="Q8" s="5">
-        <f t="shared" si="29"/>
-        <v>316</v>
-      </c>
-      <c r="R8" s="5">
-        <f t="shared" si="28"/>
-        <v>485.7</v>
-      </c>
-      <c r="S8" s="5">
-        <f t="shared" ref="S8:T8" si="30">S6+S7</f>
-        <v>368.9</v>
-      </c>
-      <c r="T8" s="5">
-        <f t="shared" si="30"/>
-        <v>409.3</v>
-      </c>
-      <c r="U8" s="5">
-        <f t="shared" ref="U8" si="31">U6+U7</f>
-        <v>404.6</v>
-      </c>
-      <c r="V8" s="5">
-        <f t="shared" ref="V8" si="32">V6+V7</f>
-        <v>502.70000000000005</v>
-      </c>
-      <c r="W8" s="5">
-        <f t="shared" ref="W8:X8" si="33">W6+W7</f>
-        <v>403.40000000000003</v>
-      </c>
-      <c r="X8" s="5">
-        <f t="shared" si="33"/>
-        <v>468.9</v>
-      </c>
-      <c r="Y8" s="5">
-        <f t="shared" ref="Y8" si="34">Y6+Y7</f>
-        <v>543.20000000000005</v>
-      </c>
-      <c r="Z8" s="5">
-        <f t="shared" ref="Z8:AA8" si="35">Z6+Z7</f>
-        <v>546.5</v>
-      </c>
-      <c r="AA8" s="5">
-        <f t="shared" si="35"/>
-        <v>493.20000000000005</v>
-      </c>
-      <c r="AB8" s="5">
-        <f t="shared" ref="AB8:AD8" si="36">AB6+AB7</f>
-        <v>543.5</v>
-      </c>
-      <c r="AC8" s="5">
-        <f t="shared" si="36"/>
-        <v>582.09999999999991</v>
-      </c>
-      <c r="AD8" s="5">
-        <f t="shared" si="36"/>
-        <v>688.5</v>
-      </c>
-      <c r="AE8" s="5">
-        <f t="shared" ref="AE8:AH8" si="37">AE6+AE7</f>
-        <v>575.6</v>
-      </c>
-      <c r="AF8" s="5">
-        <f t="shared" si="37"/>
-        <v>613.4</v>
-      </c>
-      <c r="AG8" s="5">
-        <f t="shared" si="37"/>
-        <v>641.62095999999997</v>
-      </c>
-      <c r="AH8" s="5">
-        <f t="shared" si="37"/>
-        <v>731.44097999999997</v>
-      </c>
-      <c r="AJ8" s="5">
-        <f t="shared" si="27"/>
-        <v>410.3</v>
-      </c>
-      <c r="AK8" s="5">
-        <f t="shared" si="27"/>
-        <v>633.70000000000005</v>
-      </c>
-      <c r="AL8" s="5">
-        <f t="shared" si="27"/>
         <v>970.09999999999991</v>
       </c>
       <c r="AM8" s="5">
-        <f t="shared" ref="AM8" si="38">AM6+AM7</f>
+        <f t="shared" ref="AM8" si="37">AM6+AM7</f>
         <v>1355.9</v>
       </c>
       <c r="AN8" s="5">
-        <f t="shared" ref="AN8" si="39">AN6+AN7</f>
+        <f t="shared" ref="AN8" si="38">AN6+AN7</f>
         <v>1685.5</v>
       </c>
       <c r="AO8" s="5">
-        <f t="shared" ref="AO8" si="40">AO6+AO7</f>
+        <f t="shared" ref="AO8" si="39">AO6+AO7</f>
         <v>1962</v>
       </c>
       <c r="AP8" s="5">
-        <f t="shared" ref="AP8" si="41">AP6+AP7</f>
+        <f t="shared" ref="AP8" si="40">AP6+AP7</f>
         <v>2307.3000000000002</v>
       </c>
       <c r="AQ8" s="5">
-        <f t="shared" ref="AQ8" si="42">AQ6+AQ7</f>
-        <v>2562.0619399999996</v>
+        <f t="shared" ref="AQ8" si="41">AQ6+AQ7</f>
+        <v>2615.3484999999996</v>
       </c>
       <c r="AR8" s="5">
-        <f t="shared" ref="AR8" si="43">AR6+AR7</f>
-        <v>2662.8170264999999</v>
+        <f t="shared" ref="AR8" si="42">AR6+AR7</f>
+        <v>2787.8582269999997</v>
       </c>
       <c r="AS8" s="5">
-        <f t="shared" ref="AS8" si="44">AS6+AS7</f>
-        <v>2817.9305770260007</v>
+        <f t="shared" ref="AS8" si="43">AS6+AS7</f>
+        <v>2899.5101640359999</v>
       </c>
       <c r="AT8" s="5">
-        <f t="shared" ref="AT8" si="45">AT6+AT7</f>
-        <v>2948.3012965006806</v>
+        <f t="shared" ref="AT8" si="44">AT6+AT7</f>
+        <v>3030.6541745300401</v>
       </c>
       <c r="AU8" s="5">
-        <f t="shared" ref="AU8" si="46">AU6+AU7</f>
-        <v>3053.3766295201422</v>
+        <f t="shared" ref="AU8" si="45">AU6+AU7</f>
+        <v>3133.7096272163972</v>
       </c>
       <c r="AV8" s="5">
-        <f t="shared" ref="AV8:AW8" si="47">AV6+AV7</f>
-        <v>3138.4210017970577</v>
+        <f t="shared" ref="AV8:AW8" si="46">AV6+AV7</f>
+        <v>3215.4859684076932</v>
       </c>
       <c r="AW8" s="5">
+        <f t="shared" si="46"/>
+        <v>3273.6170392251233</v>
+      </c>
+      <c r="AX8" s="5">
+        <f t="shared" ref="AX8:BA8" si="47">AX6+AX7</f>
+        <v>3332.8489449733947</v>
+      </c>
+      <c r="AY8" s="5">
         <f t="shared" si="47"/>
-        <v>3194.5013566921366</v>
-      </c>
-      <c r="AX8" s="5">
-        <f t="shared" ref="AX8:BA8" si="48">AX6+AX7</f>
-        <v>3251.6364380337086</v>
-      </c>
-      <c r="AY8" s="5">
-        <f t="shared" si="48"/>
-        <v>3309.8466715441896</v>
+        <v>3393.2030844862693</v>
       </c>
       <c r="AZ8" s="5">
-        <f t="shared" si="48"/>
-        <v>3369.1528847723775</v>
+        <f t="shared" si="47"/>
+        <v>3454.7012783955352</v>
       </c>
       <c r="BA8" s="5">
-        <f t="shared" si="48"/>
-        <v>3429.5763150631028</v>
+        <f t="shared" si="47"/>
+        <v>3517.3657775051815</v>
       </c>
     </row>
     <row r="9" spans="2:53" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2159,204 +2152,204 @@
         <v>27</v>
       </c>
       <c r="C9" s="8">
-        <f t="shared" ref="C9:L9" si="49">C5-C8</f>
+        <f t="shared" ref="C9:L9" si="48">C5-C8</f>
         <v>63.099999999999994</v>
       </c>
       <c r="D9" s="8">
+        <f t="shared" si="48"/>
+        <v>77.800000000000011</v>
+      </c>
+      <c r="E9" s="8">
+        <f t="shared" si="48"/>
+        <v>78.999999999999972</v>
+      </c>
+      <c r="F9" s="8">
+        <f t="shared" si="48"/>
+        <v>112.29999999999998</v>
+      </c>
+      <c r="G9" s="8">
+        <f t="shared" si="48"/>
+        <v>100.89999999999998</v>
+      </c>
+      <c r="H9" s="8">
+        <f t="shared" si="48"/>
+        <v>114.19999999999999</v>
+      </c>
+      <c r="I9" s="8">
+        <f t="shared" si="48"/>
+        <v>118.39999999999998</v>
+      </c>
+      <c r="J9" s="8">
+        <f t="shared" si="48"/>
+        <v>161.70000000000005</v>
+      </c>
+      <c r="K9" s="8">
+        <f t="shared" si="48"/>
+        <v>141.19999999999999</v>
+      </c>
+      <c r="L9" s="8">
+        <f t="shared" si="48"/>
+        <v>146.90000000000003</v>
+      </c>
+      <c r="M9" s="8">
+        <f t="shared" ref="M9:AL9" si="49">M5-M8</f>
+        <v>214.70000000000005</v>
+      </c>
+      <c r="N9" s="8">
         <f t="shared" si="49"/>
-        <v>77.800000000000011</v>
-      </c>
-      <c r="E9" s="8">
+        <v>305.5</v>
+      </c>
+      <c r="O9" s="8">
+        <f t="shared" ref="O9:R9" si="50">O5-O8</f>
+        <v>326.80000000000007</v>
+      </c>
+      <c r="P9" s="8">
+        <f t="shared" ref="P9:Q9" si="51">P5-P8</f>
+        <v>338.2999999999999</v>
+      </c>
+      <c r="Q9" s="8">
+        <f t="shared" si="51"/>
+        <v>363.9</v>
+      </c>
+      <c r="R9" s="8">
+        <f t="shared" si="50"/>
+        <v>379.59999999999997</v>
+      </c>
+      <c r="S9" s="8">
+        <f t="shared" ref="S9:T9" si="52">S5-S8</f>
+        <v>364.79999999999995</v>
+      </c>
+      <c r="T9" s="8">
+        <f t="shared" si="52"/>
+        <v>355.2</v>
+      </c>
+      <c r="U9" s="8">
+        <f t="shared" ref="U9" si="53">U5-U8</f>
+        <v>356.80000000000007</v>
+      </c>
+      <c r="V9" s="8">
+        <f t="shared" ref="V9" si="54">V5-V8</f>
+        <v>364.39999999999986</v>
+      </c>
+      <c r="W9" s="8">
+        <f t="shared" ref="W9:X9" si="55">W5-W8</f>
+        <v>337.59999999999997</v>
+      </c>
+      <c r="X9" s="8">
+        <f t="shared" si="55"/>
+        <v>378.4</v>
+      </c>
+      <c r="Y9" s="8">
+        <f t="shared" ref="Y9" si="56">Y5-Y8</f>
+        <v>368.79999999999995</v>
+      </c>
+      <c r="Z9" s="8">
+        <f t="shared" ref="Z9:AA9" si="57">Z5-Z8</f>
+        <v>438</v>
+      </c>
+      <c r="AA9" s="8">
+        <f t="shared" si="57"/>
+        <v>388.19999999999993</v>
+      </c>
+      <c r="AB9" s="8">
+        <f t="shared" ref="AB9:AD9" si="58">AB5-AB8</f>
+        <v>424.59999999999991</v>
+      </c>
+      <c r="AC9" s="8">
+        <f t="shared" si="58"/>
+        <v>480.10000000000014</v>
+      </c>
+      <c r="AD9" s="8">
+        <f t="shared" si="58"/>
+        <v>512.5</v>
+      </c>
+      <c r="AE9" s="8">
+        <f t="shared" ref="AE9:AH9" si="59">AE5-AE8</f>
+        <v>445.09999999999991</v>
+      </c>
+      <c r="AF9" s="8">
+        <f t="shared" si="59"/>
+        <v>497.69999999999993</v>
+      </c>
+      <c r="AG9" s="8">
+        <f t="shared" si="59"/>
+        <v>524.79999999999995</v>
+      </c>
+      <c r="AH9" s="8">
+        <f t="shared" si="59"/>
+        <v>610.77549999999997</v>
+      </c>
+      <c r="AJ9" s="8">
         <f t="shared" si="49"/>
-        <v>78.999999999999972</v>
-      </c>
-      <c r="F9" s="8">
+        <v>332.2</v>
+      </c>
+      <c r="AK9" s="8">
         <f t="shared" si="49"/>
-        <v>112.29999999999998</v>
-      </c>
-      <c r="G9" s="8">
+        <v>495.20000000000005</v>
+      </c>
+      <c r="AL9" s="8">
         <f t="shared" si="49"/>
-        <v>100.89999999999998</v>
-      </c>
-      <c r="H9" s="8">
-        <f t="shared" si="49"/>
-        <v>114.19999999999999</v>
-      </c>
-      <c r="I9" s="8">
-        <f t="shared" si="49"/>
-        <v>118.39999999999998</v>
-      </c>
-      <c r="J9" s="8">
-        <f t="shared" si="49"/>
-        <v>161.70000000000005</v>
-      </c>
-      <c r="K9" s="8">
-        <f t="shared" si="49"/>
-        <v>141.19999999999999</v>
-      </c>
-      <c r="L9" s="8">
-        <f t="shared" si="49"/>
-        <v>146.90000000000003</v>
-      </c>
-      <c r="M9" s="8">
-        <f t="shared" ref="M9:AL9" si="50">M5-M8</f>
-        <v>214.70000000000005</v>
-      </c>
-      <c r="N9" s="8">
-        <f t="shared" si="50"/>
-        <v>305.5</v>
-      </c>
-      <c r="O9" s="8">
-        <f t="shared" ref="O9:R9" si="51">O5-O8</f>
-        <v>326.80000000000007</v>
-      </c>
-      <c r="P9" s="8">
-        <f t="shared" ref="P9:Q9" si="52">P5-P8</f>
-        <v>338.2999999999999</v>
-      </c>
-      <c r="Q9" s="8">
-        <f t="shared" si="52"/>
-        <v>363.9</v>
-      </c>
-      <c r="R9" s="8">
-        <f t="shared" si="51"/>
-        <v>379.59999999999997</v>
-      </c>
-      <c r="S9" s="8">
-        <f t="shared" ref="S9:T9" si="53">S5-S8</f>
-        <v>364.79999999999995</v>
-      </c>
-      <c r="T9" s="8">
-        <f t="shared" si="53"/>
-        <v>355.2</v>
-      </c>
-      <c r="U9" s="8">
-        <f t="shared" ref="U9" si="54">U5-U8</f>
-        <v>356.80000000000007</v>
-      </c>
-      <c r="V9" s="8">
-        <f t="shared" ref="V9" si="55">V5-V8</f>
-        <v>364.39999999999986</v>
-      </c>
-      <c r="W9" s="8">
-        <f t="shared" ref="W9:X9" si="56">W5-W8</f>
-        <v>337.59999999999997</v>
-      </c>
-      <c r="X9" s="8">
-        <f t="shared" si="56"/>
-        <v>378.4</v>
-      </c>
-      <c r="Y9" s="8">
-        <f t="shared" ref="Y9" si="57">Y5-Y8</f>
-        <v>368.79999999999995</v>
-      </c>
-      <c r="Z9" s="8">
-        <f t="shared" ref="Z9:AA9" si="58">Z5-Z8</f>
-        <v>438</v>
-      </c>
-      <c r="AA9" s="8">
-        <f t="shared" si="58"/>
-        <v>388.19999999999993</v>
-      </c>
-      <c r="AB9" s="8">
-        <f t="shared" ref="AB9:AD9" si="59">AB5-AB8</f>
-        <v>424.59999999999991</v>
-      </c>
-      <c r="AC9" s="8">
-        <f t="shared" si="59"/>
-        <v>480.10000000000014</v>
-      </c>
-      <c r="AD9" s="8">
-        <f t="shared" si="59"/>
-        <v>512.5</v>
-      </c>
-      <c r="AE9" s="8">
-        <f t="shared" ref="AE9:AH9" si="60">AE5-AE8</f>
-        <v>445.09999999999991</v>
-      </c>
-      <c r="AF9" s="8">
-        <f t="shared" si="60"/>
-        <v>497.69999999999993</v>
-      </c>
-      <c r="AG9" s="8">
-        <f t="shared" si="60"/>
-        <v>540.18503999999984</v>
-      </c>
-      <c r="AH9" s="8">
-        <f t="shared" si="60"/>
-        <v>586.75601999999992</v>
-      </c>
-      <c r="AJ9" s="8">
-        <f t="shared" si="50"/>
-        <v>332.2</v>
-      </c>
-      <c r="AK9" s="8">
-        <f t="shared" si="50"/>
-        <v>495.20000000000005</v>
-      </c>
-      <c r="AL9" s="8">
-        <f t="shared" si="50"/>
         <v>808.3</v>
       </c>
       <c r="AM9" s="8">
-        <f t="shared" ref="AM9" si="61">AM5-AM8</f>
+        <f t="shared" ref="AM9" si="60">AM5-AM8</f>
         <v>1408.6</v>
       </c>
       <c r="AN9" s="8">
-        <f t="shared" ref="AN9" si="62">AN5-AN8</f>
+        <f t="shared" ref="AN9" si="61">AN5-AN8</f>
         <v>1441.1999999999998</v>
       </c>
       <c r="AO9" s="8">
-        <f t="shared" ref="AO9" si="63">AO5-AO8</f>
+        <f t="shared" ref="AO9" si="62">AO5-AO8</f>
         <v>1522.8000000000002</v>
       </c>
       <c r="AP9" s="8">
-        <f t="shared" ref="AP9" si="64">AP5-AP8</f>
+        <f t="shared" ref="AP9" si="63">AP5-AP8</f>
         <v>1805.3999999999996</v>
       </c>
       <c r="AQ9" s="8">
-        <f t="shared" ref="AQ9" si="65">AQ5-AQ8</f>
-        <v>2069.7410600000003</v>
+        <f t="shared" ref="AQ9" si="64">AQ5-AQ8</f>
+        <v>2078.3754999999996</v>
       </c>
       <c r="AR9" s="8">
-        <f t="shared" ref="AR9" si="66">AR5-AR8</f>
-        <v>2430.4799835000003</v>
+        <f t="shared" ref="AR9" si="65">AR5-AR8</f>
+        <v>2410.8897530000004</v>
       </c>
       <c r="AS9" s="8">
-        <f t="shared" ref="AS9" si="67">AS5-AS8</f>
-        <v>2651.927412774</v>
+        <f t="shared" ref="AS9" si="66">AS5-AS8</f>
+        <v>2679.5052395640005</v>
       </c>
       <c r="AT9" s="8">
-        <f t="shared" ref="AT9" si="68">AT5-AT8</f>
-        <v>2824.2842811433197</v>
+        <f t="shared" ref="AT9" si="67">AT5-AT8</f>
+        <v>2852.8146007059604</v>
       </c>
       <c r="AU9" s="8">
-        <f t="shared" ref="AU9" si="69">AU5-AU8</f>
-        <v>2937.1257865421794</v>
+        <f t="shared" ref="AU9" si="68">AU5-AU8</f>
+        <v>2966.7436421655639</v>
       </c>
       <c r="AV9" s="8">
-        <f t="shared" ref="AV9:AW9" si="70">AV5-AV8</f>
-        <v>3025.1733285565383</v>
+        <f t="shared" ref="AV9:AW9" si="69">AV5-AV8</f>
+        <v>3055.6223661009831</v>
       </c>
       <c r="AW9" s="8">
+        <f t="shared" si="69"/>
+        <v>3116.6724028315821</v>
+      </c>
+      <c r="AX9" s="8">
+        <f t="shared" ref="AX9:BA9" si="70">AX5-AX8</f>
+        <v>3178.9428161908786</v>
+      </c>
+      <c r="AY9" s="8">
         <f t="shared" si="70"/>
-        <v>3085.6092389141254</v>
-      </c>
-      <c r="AX9" s="8">
-        <f t="shared" ref="AX9:BA9" si="71">AX5-AX8</f>
-        <v>3147.2531919167282</v>
-      </c>
-      <c r="AY9" s="8">
-        <f t="shared" si="71"/>
-        <v>3210.1293416616259</v>
+        <v>3242.4580074703863</v>
       </c>
       <c r="AZ9" s="8">
-        <f t="shared" si="71"/>
-        <v>3274.2623252604881</v>
+        <f t="shared" si="70"/>
+        <v>3307.2428659250427</v>
       </c>
       <c r="BA9" s="8">
-        <f t="shared" si="71"/>
-        <v>3339.6772724989833</v>
+        <f t="shared" si="70"/>
+        <v>3373.3227785318431</v>
       </c>
     </row>
     <row r="10" spans="2:53" x14ac:dyDescent="0.3">
@@ -2454,11 +2447,10 @@
         <v>178</v>
       </c>
       <c r="AG10" s="5">
-        <f>AC10*1.06</f>
-        <v>189.52800000000002</v>
+        <v>182.2</v>
       </c>
       <c r="AH10" s="5">
-        <f t="shared" ref="AH10" si="72">AD10*1.03</f>
+        <f t="shared" ref="AH10" si="71">AD10*1.03</f>
         <v>190.96200000000002</v>
       </c>
       <c r="AJ10" s="5">
@@ -2491,47 +2483,47 @@
       </c>
       <c r="AQ10" s="5">
         <f>SUM(AE10:AH10)</f>
-        <v>743.09</v>
+        <v>735.76199999999994</v>
       </c>
       <c r="AR10" s="5">
         <f>AQ10*1.02</f>
-        <v>757.95180000000005</v>
+        <v>750.47723999999994</v>
       </c>
       <c r="AS10" s="5">
         <f>AR10*1.01</f>
-        <v>765.53131800000006</v>
+        <v>757.98201239999992</v>
       </c>
       <c r="AT10" s="5">
-        <f t="shared" ref="AT10:BA10" si="73">AS10*1.01</f>
-        <v>773.18663118000006</v>
+        <f t="shared" ref="AT10:BA10" si="72">AS10*1.01</f>
+        <v>765.5618325239999</v>
       </c>
       <c r="AU10" s="5">
-        <f t="shared" si="73"/>
-        <v>780.91849749180005</v>
+        <f t="shared" si="72"/>
+        <v>773.21745084923987</v>
       </c>
       <c r="AV10" s="5">
-        <f t="shared" si="73"/>
-        <v>788.72768246671808</v>
+        <f t="shared" si="72"/>
+        <v>780.94962535773232</v>
       </c>
       <c r="AW10" s="5">
-        <f t="shared" si="73"/>
-        <v>796.61495929138528</v>
+        <f t="shared" si="72"/>
+        <v>788.75912161130964</v>
       </c>
       <c r="AX10" s="5">
-        <f t="shared" si="73"/>
-        <v>804.58110888429917</v>
+        <f t="shared" si="72"/>
+        <v>796.64671282742279</v>
       </c>
       <c r="AY10" s="5">
-        <f t="shared" si="73"/>
-        <v>812.62691997314221</v>
+        <f t="shared" si="72"/>
+        <v>804.61317995569698</v>
       </c>
       <c r="AZ10" s="5">
-        <f t="shared" si="73"/>
-        <v>820.75318917287359</v>
+        <f t="shared" si="72"/>
+        <v>812.65931175525395</v>
       </c>
       <c r="BA10" s="5">
-        <f t="shared" si="73"/>
-        <v>828.96072106460235</v>
+        <f t="shared" si="72"/>
+        <v>820.78590487280655</v>
       </c>
     </row>
     <row r="11" spans="2:53" x14ac:dyDescent="0.3">
@@ -2629,12 +2621,11 @@
         <v>243.3</v>
       </c>
       <c r="AG11" s="5">
-        <f t="shared" ref="AF11:AH11" si="74">AG5*0.22</f>
-        <v>259.99731999999995</v>
+        <v>242.1</v>
       </c>
       <c r="AH11" s="5">
-        <f t="shared" si="74"/>
-        <v>290.00333999999998</v>
+        <f>AH5*0.21</f>
+        <v>283.77803999999998</v>
       </c>
       <c r="AJ11" s="5">
         <f>SUM(C11:F11)</f>
@@ -2666,47 +2657,47 @@
       </c>
       <c r="AQ11" s="5">
         <f>SUM(AE11:AH11)</f>
-        <v>1017.0006599999999</v>
+        <v>992.87804000000006</v>
       </c>
       <c r="AR11" s="5">
         <f>AR5*0.21</f>
-        <v>1069.5923720999999</v>
+        <v>1091.7370758</v>
       </c>
       <c r="AS11" s="5">
         <f>AS5*0.2</f>
-        <v>1093.9715979600003</v>
+        <v>1115.80308072</v>
       </c>
       <c r="AT11" s="5">
         <f>AT5*0.19</f>
-        <v>1096.79125975236</v>
+        <v>1117.8590672948401</v>
       </c>
       <c r="AU11" s="5">
-        <f t="shared" ref="AU11:BA11" si="75">AU5*0.19</f>
-        <v>1138.195459051841</v>
+        <f t="shared" ref="AU11:BA11" si="73">AU5*0.19</f>
+        <v>1159.0861211825727</v>
       </c>
       <c r="AV11" s="5">
-        <f t="shared" si="75"/>
-        <v>1171.0829227671832</v>
+        <f t="shared" si="73"/>
+        <v>1191.5105835566485</v>
       </c>
       <c r="AW11" s="5">
-        <f t="shared" si="75"/>
-        <v>1193.2210131651898</v>
+        <f t="shared" si="73"/>
+        <v>1214.1549939907741</v>
       </c>
       <c r="AX11" s="5">
-        <f t="shared" si="75"/>
-        <v>1215.789029690583</v>
+        <f t="shared" si="73"/>
+        <v>1237.240434621212</v>
       </c>
       <c r="AY11" s="5">
-        <f t="shared" si="75"/>
-        <v>1238.795442509105</v>
+        <f t="shared" si="73"/>
+        <v>1260.7756074717645</v>
       </c>
       <c r="AZ11" s="5">
-        <f t="shared" si="75"/>
-        <v>1262.2488899062446</v>
+        <f t="shared" si="73"/>
+        <v>1284.7693874209099</v>
       </c>
       <c r="BA11" s="5">
-        <f t="shared" si="75"/>
-        <v>1286.1581816367964</v>
+        <f t="shared" si="73"/>
+        <v>1309.2308256470346</v>
       </c>
     </row>
     <row r="12" spans="2:53" x14ac:dyDescent="0.3">
@@ -2804,11 +2795,10 @@
         <v>99.7</v>
       </c>
       <c r="AG12" s="5">
-        <f t="shared" ref="AF12:AH12" si="76">AC12*1.03</f>
-        <v>103</v>
+        <v>91.1</v>
       </c>
       <c r="AH12" s="5">
-        <f t="shared" si="76"/>
+        <f t="shared" ref="AG12:AH12" si="74">AD12*1.03</f>
         <v>97.232000000000014</v>
       </c>
       <c r="AI12" s="9"/>
@@ -2842,47 +2832,47 @@
       </c>
       <c r="AQ12" s="5">
         <f>SUM(AE12:AH12)</f>
-        <v>394.43200000000002</v>
+        <v>382.53199999999998</v>
       </c>
       <c r="AR12" s="5">
-        <f t="shared" ref="AR12:BA12" si="77">AQ12*1.02</f>
-        <v>402.32064000000003</v>
+        <f t="shared" ref="AR12:BA12" si="75">AQ12*1.02</f>
+        <v>390.18263999999999</v>
       </c>
       <c r="AS12" s="5">
-        <f t="shared" si="77"/>
-        <v>410.36705280000001</v>
+        <f t="shared" si="75"/>
+        <v>397.9862928</v>
       </c>
       <c r="AT12" s="5">
-        <f t="shared" si="77"/>
-        <v>418.57439385600003</v>
+        <f t="shared" si="75"/>
+        <v>405.94601865600004</v>
       </c>
       <c r="AU12" s="5">
-        <f t="shared" si="77"/>
-        <v>426.94588173312002</v>
+        <f>AT12*1.01</f>
+        <v>410.00547884256002</v>
       </c>
       <c r="AV12" s="5">
-        <f t="shared" si="77"/>
-        <v>435.48479936778244</v>
+        <f t="shared" ref="AV12:BA12" si="76">AU12*1.01</f>
+        <v>414.10553363098563</v>
       </c>
       <c r="AW12" s="5">
-        <f t="shared" si="77"/>
-        <v>444.19449535513809</v>
+        <f t="shared" si="76"/>
+        <v>418.24658896729551</v>
       </c>
       <c r="AX12" s="5">
-        <f t="shared" si="77"/>
-        <v>453.07838526224083</v>
+        <f t="shared" si="76"/>
+        <v>422.42905485696849</v>
       </c>
       <c r="AY12" s="5">
-        <f t="shared" si="77"/>
-        <v>462.13995296748567</v>
+        <f t="shared" si="76"/>
+        <v>426.65334540553818</v>
       </c>
       <c r="AZ12" s="5">
-        <f t="shared" si="77"/>
-        <v>471.38275202683542</v>
+        <f t="shared" si="76"/>
+        <v>430.91987885959355</v>
       </c>
       <c r="BA12" s="5">
-        <f t="shared" si="77"/>
-        <v>480.81040706737213</v>
+        <f t="shared" si="76"/>
+        <v>435.2290776481895</v>
       </c>
     </row>
     <row r="13" spans="2:53" x14ac:dyDescent="0.3">
@@ -2890,204 +2880,204 @@
         <v>31</v>
       </c>
       <c r="C13" s="5">
-        <f t="shared" ref="C13:L13" si="78">C10+C11+C12</f>
+        <f t="shared" ref="C13:L13" si="77">C10+C11+C12</f>
         <v>70</v>
       </c>
       <c r="D13" s="5">
+        <f t="shared" si="77"/>
+        <v>77.900000000000006</v>
+      </c>
+      <c r="E13" s="5">
+        <f t="shared" si="77"/>
+        <v>90.8</v>
+      </c>
+      <c r="F13" s="5">
+        <f t="shared" si="77"/>
+        <v>106.8</v>
+      </c>
+      <c r="G13" s="5">
+        <f t="shared" si="77"/>
+        <v>111.6</v>
+      </c>
+      <c r="H13" s="5">
+        <f t="shared" si="77"/>
+        <v>124.6</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="77"/>
+        <v>145.1</v>
+      </c>
+      <c r="J13" s="5">
+        <f t="shared" si="77"/>
+        <v>179</v>
+      </c>
+      <c r="K13" s="5">
+        <f t="shared" si="77"/>
+        <v>196.2</v>
+      </c>
+      <c r="L13" s="5">
+        <f t="shared" si="77"/>
+        <v>189.10000000000002</v>
+      </c>
+      <c r="M13" s="5">
+        <f t="shared" ref="M13:AL13" si="78">M10+M11+M12</f>
+        <v>202.9</v>
+      </c>
+      <c r="N13" s="5">
         <f t="shared" si="78"/>
-        <v>77.900000000000006</v>
-      </c>
-      <c r="E13" s="5">
+        <v>240.3</v>
+      </c>
+      <c r="O13" s="5">
         <f t="shared" si="78"/>
-        <v>90.8</v>
-      </c>
-      <c r="F13" s="5">
+        <v>251</v>
+      </c>
+      <c r="P13" s="5">
+        <f t="shared" ref="P13:Q13" si="79">P10+P11+P12</f>
+        <v>269.2</v>
+      </c>
+      <c r="Q13" s="5">
+        <f t="shared" si="79"/>
+        <v>295.10000000000002</v>
+      </c>
+      <c r="R13" s="5">
         <f t="shared" si="78"/>
-        <v>106.8</v>
-      </c>
-      <c r="G13" s="5">
+        <v>358.3</v>
+      </c>
+      <c r="S13" s="5">
+        <f t="shared" ref="S13:T13" si="80">S10+S11+S12</f>
+        <v>388.3</v>
+      </c>
+      <c r="T13" s="5">
+        <f t="shared" si="80"/>
+        <v>465.70000000000005</v>
+      </c>
+      <c r="U13" s="5">
+        <f t="shared" ref="U13" si="81">U10+U11+U12</f>
+        <v>503.8</v>
+      </c>
+      <c r="V13" s="5">
+        <f t="shared" ref="V13" si="82">V10+V11+V12</f>
+        <v>614.29999999999995</v>
+      </c>
+      <c r="W13" s="5">
+        <f t="shared" ref="W13:X13" si="83">W10+W11+W12</f>
+        <v>550.1</v>
+      </c>
+      <c r="X13" s="5">
+        <f t="shared" si="83"/>
+        <v>504.3</v>
+      </c>
+      <c r="Y13" s="5">
+        <f t="shared" ref="Y13" si="84">Y10+Y11+Y12</f>
+        <v>718.59999999999991</v>
+      </c>
+      <c r="Z13" s="5">
+        <f t="shared" ref="Z13:AA13" si="85">Z10+Z11+Z12</f>
+        <v>542.1</v>
+      </c>
+      <c r="AA13" s="5">
+        <f t="shared" si="85"/>
+        <v>460.2</v>
+      </c>
+      <c r="AB13" s="5">
+        <f t="shared" ref="AB13:AD13" si="86">AB10+AB11+AB12</f>
+        <v>496</v>
+      </c>
+      <c r="AC13" s="5">
+        <f t="shared" si="86"/>
+        <v>515.79999999999995</v>
+      </c>
+      <c r="AD13" s="5">
+        <f t="shared" si="86"/>
+        <v>551.69999999999993</v>
+      </c>
+      <c r="AE13" s="5">
+        <f t="shared" ref="AE13:AH13" si="87">AE10+AE11+AE12</f>
+        <v>502.79999999999995</v>
+      </c>
+      <c r="AF13" s="5">
+        <f t="shared" si="87"/>
+        <v>521</v>
+      </c>
+      <c r="AG13" s="5">
+        <f t="shared" si="87"/>
+        <v>515.4</v>
+      </c>
+      <c r="AH13" s="5">
+        <f t="shared" si="87"/>
+        <v>571.97203999999999</v>
+      </c>
+      <c r="AJ13" s="5">
         <f t="shared" si="78"/>
-        <v>111.6</v>
-      </c>
-      <c r="H13" s="5">
+        <v>345.5</v>
+      </c>
+      <c r="AK13" s="5">
         <f t="shared" si="78"/>
-        <v>124.6</v>
-      </c>
-      <c r="I13" s="5">
+        <v>560.29999999999995</v>
+      </c>
+      <c r="AL13" s="5">
         <f t="shared" si="78"/>
-        <v>145.1</v>
-      </c>
-      <c r="J13" s="5">
-        <f t="shared" si="78"/>
-        <v>179</v>
-      </c>
-      <c r="K13" s="5">
-        <f t="shared" si="78"/>
-        <v>196.2</v>
-      </c>
-      <c r="L13" s="5">
-        <f t="shared" si="78"/>
-        <v>189.10000000000002</v>
-      </c>
-      <c r="M13" s="5">
-        <f t="shared" ref="M13:AL13" si="79">M10+M11+M12</f>
-        <v>202.9</v>
-      </c>
-      <c r="N13" s="5">
-        <f t="shared" si="79"/>
-        <v>240.3</v>
-      </c>
-      <c r="O13" s="5">
-        <f t="shared" si="79"/>
-        <v>251</v>
-      </c>
-      <c r="P13" s="5">
-        <f t="shared" ref="P13:Q13" si="80">P10+P11+P12</f>
-        <v>269.2</v>
-      </c>
-      <c r="Q13" s="5">
-        <f t="shared" si="80"/>
-        <v>295.10000000000002</v>
-      </c>
-      <c r="R13" s="5">
-        <f t="shared" si="79"/>
-        <v>358.3</v>
-      </c>
-      <c r="S13" s="5">
-        <f t="shared" ref="S13:T13" si="81">S10+S11+S12</f>
-        <v>388.3</v>
-      </c>
-      <c r="T13" s="5">
-        <f t="shared" si="81"/>
-        <v>465.70000000000005</v>
-      </c>
-      <c r="U13" s="5">
-        <f t="shared" ref="U13" si="82">U10+U11+U12</f>
-        <v>503.8</v>
-      </c>
-      <c r="V13" s="5">
-        <f t="shared" ref="V13" si="83">V10+V11+V12</f>
-        <v>614.29999999999995</v>
-      </c>
-      <c r="W13" s="5">
-        <f t="shared" ref="W13:X13" si="84">W10+W11+W12</f>
-        <v>550.1</v>
-      </c>
-      <c r="X13" s="5">
-        <f t="shared" si="84"/>
-        <v>504.3</v>
-      </c>
-      <c r="Y13" s="5">
-        <f t="shared" ref="Y13" si="85">Y10+Y11+Y12</f>
-        <v>718.59999999999991</v>
-      </c>
-      <c r="Z13" s="5">
-        <f t="shared" ref="Z13:AA13" si="86">Z10+Z11+Z12</f>
-        <v>542.1</v>
-      </c>
-      <c r="AA13" s="5">
-        <f t="shared" si="86"/>
-        <v>460.2</v>
-      </c>
-      <c r="AB13" s="5">
-        <f t="shared" ref="AB13:AD13" si="87">AB10+AB11+AB12</f>
-        <v>496</v>
-      </c>
-      <c r="AC13" s="5">
-        <f t="shared" si="87"/>
-        <v>515.79999999999995</v>
-      </c>
-      <c r="AD13" s="5">
-        <f t="shared" si="87"/>
-        <v>551.69999999999993</v>
-      </c>
-      <c r="AE13" s="5">
-        <f t="shared" ref="AE13:AH13" si="88">AE10+AE11+AE12</f>
-        <v>502.79999999999995</v>
-      </c>
-      <c r="AF13" s="5">
-        <f t="shared" si="88"/>
-        <v>521</v>
-      </c>
-      <c r="AG13" s="5">
-        <f t="shared" si="88"/>
-        <v>552.52531999999997</v>
-      </c>
-      <c r="AH13" s="5">
-        <f t="shared" si="88"/>
-        <v>578.19733999999994</v>
-      </c>
-      <c r="AJ13" s="5">
-        <f t="shared" si="79"/>
-        <v>345.5</v>
-      </c>
-      <c r="AK13" s="5">
-        <f t="shared" si="79"/>
-        <v>560.29999999999995</v>
-      </c>
-      <c r="AL13" s="5">
-        <f t="shared" si="79"/>
         <v>828.5</v>
       </c>
       <c r="AM13" s="5">
-        <f t="shared" ref="AM13" si="89">AM10+AM11+AM12</f>
+        <f t="shared" ref="AM13" si="88">AM10+AM11+AM12</f>
         <v>1173.6000000000001</v>
       </c>
       <c r="AN13" s="5">
-        <f t="shared" ref="AN13" si="90">AN10+AN11+AN12</f>
+        <f t="shared" ref="AN13" si="89">AN10+AN11+AN12</f>
         <v>1972.1000000000001</v>
       </c>
       <c r="AO13" s="5">
-        <f t="shared" ref="AO13" si="91">AO10+AO11+AO12</f>
+        <f t="shared" ref="AO13" si="90">AO10+AO11+AO12</f>
         <v>2315.1</v>
       </c>
       <c r="AP13" s="5">
-        <f t="shared" ref="AP13" si="92">AP10+AP11+AP12</f>
+        <f t="shared" ref="AP13" si="91">AP10+AP11+AP12</f>
         <v>2023.6999999999998</v>
       </c>
       <c r="AQ13" s="5">
-        <f t="shared" ref="AQ13" si="93">AQ10+AQ11+AQ12</f>
-        <v>2154.5226599999996</v>
+        <f t="shared" ref="AQ13" si="92">AQ10+AQ11+AQ12</f>
+        <v>2111.1720399999999</v>
       </c>
       <c r="AR13" s="5">
-        <f t="shared" ref="AR13" si="94">AR10+AR11+AR12</f>
-        <v>2229.8648121000001</v>
+        <f t="shared" ref="AR13" si="93">AR10+AR11+AR12</f>
+        <v>2232.3969557999999</v>
       </c>
       <c r="AS13" s="5">
-        <f t="shared" ref="AS13" si="95">AS10+AS11+AS12</f>
-        <v>2269.8699687600001</v>
+        <f t="shared" ref="AS13" si="94">AS10+AS11+AS12</f>
+        <v>2271.7713859200003</v>
       </c>
       <c r="AT13" s="5">
-        <f t="shared" ref="AT13" si="96">AT10+AT11+AT12</f>
-        <v>2288.5522847883599</v>
+        <f t="shared" ref="AT13" si="95">AT10+AT11+AT12</f>
+        <v>2289.3669184748401</v>
       </c>
       <c r="AU13" s="5">
-        <f t="shared" ref="AU13" si="97">AU10+AU11+AU12</f>
-        <v>2346.0598382767612</v>
+        <f t="shared" ref="AU13" si="96">AU10+AU11+AU12</f>
+        <v>2342.3090508743726</v>
       </c>
       <c r="AV13" s="5">
-        <f t="shared" ref="AV13:AW13" si="98">AV10+AV11+AV12</f>
-        <v>2395.2954046016839</v>
+        <f t="shared" ref="AV13:AW13" si="97">AV10+AV11+AV12</f>
+        <v>2386.5657425453664</v>
       </c>
       <c r="AW13" s="5">
+        <f t="shared" si="97"/>
+        <v>2421.160704569379</v>
+      </c>
+      <c r="AX13" s="5">
+        <f t="shared" ref="AX13:BA13" si="98">AX10+AX11+AX12</f>
+        <v>2456.3162023056034</v>
+      </c>
+      <c r="AY13" s="5">
         <f t="shared" si="98"/>
-        <v>2434.0304678117132</v>
-      </c>
-      <c r="AX13" s="5">
-        <f t="shared" ref="AX13:BA13" si="99">AX10+AX11+AX12</f>
-        <v>2473.448523837123</v>
-      </c>
-      <c r="AY13" s="5">
-        <f t="shared" si="99"/>
-        <v>2513.5623154497325</v>
+        <v>2492.0421328329994</v>
       </c>
       <c r="AZ13" s="5">
-        <f t="shared" si="99"/>
-        <v>2554.3848311059537</v>
+        <f t="shared" si="98"/>
+        <v>2528.3485780357573</v>
       </c>
       <c r="BA13" s="5">
-        <f t="shared" si="99"/>
-        <v>2595.929309768771</v>
+        <f t="shared" si="98"/>
+        <v>2565.2458081680306</v>
       </c>
     </row>
     <row r="14" spans="2:53" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3095,204 +3085,204 @@
         <v>32</v>
       </c>
       <c r="C14" s="8">
-        <f t="shared" ref="C14:L14" si="100">C9-C13</f>
+        <f t="shared" ref="C14:L14" si="99">C9-C13</f>
         <v>-6.9000000000000057</v>
       </c>
       <c r="D14" s="8">
+        <f t="shared" si="99"/>
+        <v>-9.9999999999994316E-2</v>
+      </c>
+      <c r="E14" s="8">
+        <f t="shared" si="99"/>
+        <v>-11.800000000000026</v>
+      </c>
+      <c r="F14" s="8">
+        <f t="shared" si="99"/>
+        <v>5.4999999999999858</v>
+      </c>
+      <c r="G14" s="8">
+        <f t="shared" si="99"/>
+        <v>-10.700000000000017</v>
+      </c>
+      <c r="H14" s="8">
+        <f t="shared" si="99"/>
+        <v>-10.400000000000006</v>
+      </c>
+      <c r="I14" s="8">
+        <f t="shared" si="99"/>
+        <v>-26.700000000000017</v>
+      </c>
+      <c r="J14" s="8">
+        <f t="shared" si="99"/>
+        <v>-17.299999999999955</v>
+      </c>
+      <c r="K14" s="8">
+        <f t="shared" si="99"/>
+        <v>-55</v>
+      </c>
+      <c r="L14" s="8">
+        <f t="shared" si="99"/>
+        <v>-42.199999999999989</v>
+      </c>
+      <c r="M14" s="8">
+        <f t="shared" ref="M14:AL14" si="100">M9-M13</f>
+        <v>11.80000000000004</v>
+      </c>
+      <c r="N14" s="8">
         <f t="shared" si="100"/>
-        <v>-9.9999999999994316E-2</v>
-      </c>
-      <c r="E14" s="8">
+        <v>65.199999999999989</v>
+      </c>
+      <c r="O14" s="8">
         <f t="shared" si="100"/>
-        <v>-11.800000000000026</v>
-      </c>
-      <c r="F14" s="8">
+        <v>75.800000000000068</v>
+      </c>
+      <c r="P14" s="8">
+        <f t="shared" ref="P14:Q14" si="101">P9-P13</f>
+        <v>69.099999999999909</v>
+      </c>
+      <c r="Q14" s="8">
+        <f t="shared" si="101"/>
+        <v>68.799999999999955</v>
+      </c>
+      <c r="R14" s="8">
         <f t="shared" si="100"/>
-        <v>5.4999999999999858</v>
-      </c>
-      <c r="G14" s="8">
+        <v>21.299999999999955</v>
+      </c>
+      <c r="S14" s="8">
+        <f t="shared" ref="S14:T14" si="102">S9-S13</f>
+        <v>-23.500000000000057</v>
+      </c>
+      <c r="T14" s="8">
+        <f t="shared" si="102"/>
+        <v>-110.50000000000006</v>
+      </c>
+      <c r="U14" s="8">
+        <f t="shared" ref="U14" si="103">U9-U13</f>
+        <v>-146.99999999999994</v>
+      </c>
+      <c r="V14" s="8">
+        <f t="shared" ref="V14" si="104">V9-V13</f>
+        <v>-249.90000000000009</v>
+      </c>
+      <c r="W14" s="8">
+        <f t="shared" ref="W14:X14" si="105">W9-W13</f>
+        <v>-212.50000000000006</v>
+      </c>
+      <c r="X14" s="8">
+        <f t="shared" si="105"/>
+        <v>-125.90000000000003</v>
+      </c>
+      <c r="Y14" s="8">
+        <f t="shared" ref="Y14" si="106">Y9-Y13</f>
+        <v>-349.79999999999995</v>
+      </c>
+      <c r="Z14" s="8">
+        <f t="shared" ref="Z14:AA14" si="107">Z9-Z13</f>
+        <v>-104.10000000000002</v>
+      </c>
+      <c r="AA14" s="8">
+        <f t="shared" si="107"/>
+        <v>-72.000000000000057</v>
+      </c>
+      <c r="AB14" s="8">
+        <f t="shared" ref="AB14:AD14" si="108">AB9-AB13</f>
+        <v>-71.400000000000091</v>
+      </c>
+      <c r="AC14" s="8">
+        <f t="shared" si="108"/>
+        <v>-35.699999999999818</v>
+      </c>
+      <c r="AD14" s="8">
+        <f t="shared" si="108"/>
+        <v>-39.199999999999932</v>
+      </c>
+      <c r="AE14" s="8">
+        <f t="shared" ref="AE14:AH14" si="109">AE9-AE13</f>
+        <v>-57.700000000000045</v>
+      </c>
+      <c r="AF14" s="8">
+        <f t="shared" si="109"/>
+        <v>-23.300000000000068</v>
+      </c>
+      <c r="AG14" s="8">
+        <f t="shared" si="109"/>
+        <v>9.3999999999999773</v>
+      </c>
+      <c r="AH14" s="8">
+        <f t="shared" si="109"/>
+        <v>38.803459999999973</v>
+      </c>
+      <c r="AJ14" s="8">
         <f t="shared" si="100"/>
-        <v>-10.700000000000017</v>
-      </c>
-      <c r="H14" s="8">
+        <v>-13.300000000000011</v>
+      </c>
+      <c r="AK14" s="8">
         <f t="shared" si="100"/>
-        <v>-10.400000000000006</v>
-      </c>
-      <c r="I14" s="8">
+        <v>-65.099999999999909</v>
+      </c>
+      <c r="AL14" s="8">
         <f t="shared" si="100"/>
-        <v>-26.700000000000017</v>
-      </c>
-      <c r="J14" s="8">
-        <f t="shared" si="100"/>
-        <v>-17.299999999999955</v>
-      </c>
-      <c r="K14" s="8">
-        <f t="shared" si="100"/>
-        <v>-55</v>
-      </c>
-      <c r="L14" s="8">
-        <f t="shared" si="100"/>
-        <v>-42.199999999999989</v>
-      </c>
-      <c r="M14" s="8">
-        <f t="shared" ref="M14:AL14" si="101">M9-M13</f>
-        <v>11.80000000000004</v>
-      </c>
-      <c r="N14" s="8">
-        <f t="shared" si="101"/>
-        <v>65.199999999999989</v>
-      </c>
-      <c r="O14" s="8">
-        <f t="shared" si="101"/>
-        <v>75.800000000000068</v>
-      </c>
-      <c r="P14" s="8">
-        <f t="shared" ref="P14:Q14" si="102">P9-P13</f>
-        <v>69.099999999999909</v>
-      </c>
-      <c r="Q14" s="8">
-        <f t="shared" si="102"/>
-        <v>68.799999999999955</v>
-      </c>
-      <c r="R14" s="8">
-        <f t="shared" si="101"/>
-        <v>21.299999999999955</v>
-      </c>
-      <c r="S14" s="8">
-        <f t="shared" ref="S14:T14" si="103">S9-S13</f>
-        <v>-23.500000000000057</v>
-      </c>
-      <c r="T14" s="8">
-        <f t="shared" si="103"/>
-        <v>-110.50000000000006</v>
-      </c>
-      <c r="U14" s="8">
-        <f t="shared" ref="U14" si="104">U9-U13</f>
-        <v>-146.99999999999994</v>
-      </c>
-      <c r="V14" s="8">
-        <f t="shared" ref="V14" si="105">V9-V13</f>
-        <v>-249.90000000000009</v>
-      </c>
-      <c r="W14" s="8">
-        <f t="shared" ref="W14:X14" si="106">W9-W13</f>
-        <v>-212.50000000000006</v>
-      </c>
-      <c r="X14" s="8">
-        <f t="shared" si="106"/>
-        <v>-125.90000000000003</v>
-      </c>
-      <c r="Y14" s="8">
-        <f t="shared" ref="Y14" si="107">Y9-Y13</f>
-        <v>-349.79999999999995</v>
-      </c>
-      <c r="Z14" s="8">
-        <f t="shared" ref="Z14:AA14" si="108">Z9-Z13</f>
-        <v>-104.10000000000002</v>
-      </c>
-      <c r="AA14" s="8">
-        <f t="shared" si="108"/>
-        <v>-72.000000000000057</v>
-      </c>
-      <c r="AB14" s="8">
-        <f t="shared" ref="AB14:AD14" si="109">AB9-AB13</f>
-        <v>-71.400000000000091</v>
-      </c>
-      <c r="AC14" s="8">
-        <f t="shared" si="109"/>
-        <v>-35.699999999999818</v>
-      </c>
-      <c r="AD14" s="8">
-        <f t="shared" si="109"/>
-        <v>-39.199999999999932</v>
-      </c>
-      <c r="AE14" s="8">
-        <f t="shared" ref="AE14:AH14" si="110">AE9-AE13</f>
-        <v>-57.700000000000045</v>
-      </c>
-      <c r="AF14" s="8">
-        <f t="shared" si="110"/>
-        <v>-23.300000000000068</v>
-      </c>
-      <c r="AG14" s="8">
-        <f t="shared" si="110"/>
-        <v>-12.340280000000121</v>
-      </c>
-      <c r="AH14" s="8">
-        <f t="shared" si="110"/>
-        <v>8.5586799999999812</v>
-      </c>
-      <c r="AJ14" s="8">
-        <f t="shared" si="101"/>
-        <v>-13.300000000000011</v>
-      </c>
-      <c r="AK14" s="8">
-        <f t="shared" si="101"/>
-        <v>-65.099999999999909</v>
-      </c>
-      <c r="AL14" s="8">
-        <f t="shared" si="101"/>
         <v>-20.200000000000045</v>
       </c>
       <c r="AM14" s="8">
-        <f t="shared" ref="AM14" si="111">AM9-AM13</f>
+        <f t="shared" ref="AM14" si="110">AM9-AM13</f>
         <v>234.99999999999977</v>
       </c>
       <c r="AN14" s="8">
-        <f t="shared" ref="AN14" si="112">AN9-AN13</f>
+        <f t="shared" ref="AN14" si="111">AN9-AN13</f>
         <v>-530.90000000000032</v>
       </c>
       <c r="AO14" s="8">
-        <f t="shared" ref="AO14" si="113">AO9-AO13</f>
+        <f t="shared" ref="AO14" si="112">AO9-AO13</f>
         <v>-792.29999999999973</v>
       </c>
       <c r="AP14" s="8">
-        <f t="shared" ref="AP14" si="114">AP9-AP13</f>
+        <f t="shared" ref="AP14" si="113">AP9-AP13</f>
         <v>-218.30000000000018</v>
       </c>
       <c r="AQ14" s="8">
-        <f t="shared" ref="AQ14" si="115">AQ9-AQ13</f>
-        <v>-84.781599999999344</v>
+        <f t="shared" ref="AQ14" si="114">AQ9-AQ13</f>
+        <v>-32.796540000000277</v>
       </c>
       <c r="AR14" s="8">
-        <f t="shared" ref="AR14" si="116">AR9-AR13</f>
-        <v>200.61517140000024</v>
+        <f t="shared" ref="AR14" si="115">AR9-AR13</f>
+        <v>178.4927972000005</v>
       </c>
       <c r="AS14" s="8">
-        <f t="shared" ref="AS14" si="117">AS9-AS13</f>
-        <v>382.05744401399988</v>
+        <f t="shared" ref="AS14" si="116">AS9-AS13</f>
+        <v>407.73385364400019</v>
       </c>
       <c r="AT14" s="8">
-        <f t="shared" ref="AT14" si="118">AT9-AT13</f>
-        <v>535.73199635495985</v>
+        <f t="shared" ref="AT14" si="117">AT9-AT13</f>
+        <v>563.44768223112033</v>
       </c>
       <c r="AU14" s="8">
-        <f t="shared" ref="AU14" si="119">AU9-AU13</f>
-        <v>591.06594826541823</v>
+        <f t="shared" ref="AU14" si="118">AU9-AU13</f>
+        <v>624.43459129119128</v>
       </c>
       <c r="AV14" s="8">
-        <f t="shared" ref="AV14:AW14" si="120">AV9-AV13</f>
-        <v>629.8779239548544</v>
+        <f t="shared" ref="AV14:AW14" si="119">AV9-AV13</f>
+        <v>669.05662355561662</v>
       </c>
       <c r="AW14" s="8">
+        <f t="shared" si="119"/>
+        <v>695.51169826220303</v>
+      </c>
+      <c r="AX14" s="8">
+        <f t="shared" ref="AX14:BA14" si="120">AX9-AX13</f>
+        <v>722.62661388527522</v>
+      </c>
+      <c r="AY14" s="8">
         <f t="shared" si="120"/>
-        <v>651.57877110241225</v>
-      </c>
-      <c r="AX14" s="8">
-        <f t="shared" ref="AX14:BA14" si="121">AX9-AX13</f>
-        <v>673.80466807960511</v>
-      </c>
-      <c r="AY14" s="8">
-        <f t="shared" si="121"/>
-        <v>696.56702621189334</v>
+        <v>750.41587463738688</v>
       </c>
       <c r="AZ14" s="8">
-        <f t="shared" si="121"/>
-        <v>719.87749415453436</v>
+        <f t="shared" si="120"/>
+        <v>778.89428788928535</v>
       </c>
       <c r="BA14" s="8">
-        <f t="shared" si="121"/>
-        <v>743.74796273021229</v>
+        <f t="shared" si="120"/>
+        <v>808.07697036381251</v>
       </c>
     </row>
     <row r="15" spans="2:53" x14ac:dyDescent="0.3">
@@ -3409,11 +3399,10 @@
         <v>-28</v>
       </c>
       <c r="AG15" s="5">
-        <f t="shared" ref="AF15:AH15" si="122">AC15*1.01</f>
-        <v>-31.209</v>
+        <v>-28.6</v>
       </c>
       <c r="AH15" s="5">
-        <f t="shared" si="122"/>
+        <f t="shared" ref="AG15:AH15" si="121">AD15*1.01</f>
         <v>-13.433000000000002</v>
       </c>
       <c r="AJ15" s="5">
@@ -3446,47 +3435,47 @@
       </c>
       <c r="AQ15" s="5">
         <f>SUM(AE15:AH15)</f>
-        <v>-89.842000000000013</v>
+        <v>-87.233000000000018</v>
       </c>
       <c r="AR15" s="5">
-        <f t="shared" ref="AR15:BA15" si="123">AQ15*1.03</f>
-        <v>-92.537260000000018</v>
+        <f t="shared" ref="AR15:BA15" si="122">AQ15*1.03</f>
+        <v>-89.84999000000002</v>
       </c>
       <c r="AS15" s="5">
-        <f t="shared" si="123"/>
-        <v>-95.313377800000026</v>
+        <f t="shared" si="122"/>
+        <v>-92.545489700000019</v>
       </c>
       <c r="AT15" s="5">
-        <f t="shared" si="123"/>
-        <v>-98.172779134000024</v>
+        <f t="shared" si="122"/>
+        <v>-95.321854391000016</v>
       </c>
       <c r="AU15" s="5">
-        <f t="shared" si="123"/>
-        <v>-101.11796250802003</v>
+        <f t="shared" si="122"/>
+        <v>-98.181510022730023</v>
       </c>
       <c r="AV15" s="5">
-        <f t="shared" si="123"/>
-        <v>-104.15150138326064</v>
+        <f t="shared" si="122"/>
+        <v>-101.12695532341192</v>
       </c>
       <c r="AW15" s="5">
-        <f t="shared" si="123"/>
-        <v>-107.27604642475846</v>
+        <f t="shared" si="122"/>
+        <v>-104.16076398311428</v>
       </c>
       <c r="AX15" s="5">
-        <f t="shared" si="123"/>
-        <v>-110.49432781750122</v>
+        <f t="shared" si="122"/>
+        <v>-107.2855869026077</v>
       </c>
       <c r="AY15" s="5">
-        <f t="shared" si="123"/>
-        <v>-113.80915765202626</v>
+        <f t="shared" si="122"/>
+        <v>-110.50415450968593</v>
       </c>
       <c r="AZ15" s="5">
-        <f t="shared" si="123"/>
-        <v>-117.22343238158705</v>
+        <f t="shared" si="122"/>
+        <v>-113.81927914497652</v>
       </c>
       <c r="BA15" s="5">
-        <f t="shared" si="123"/>
-        <v>-120.74013535303466</v>
+        <f t="shared" si="122"/>
+        <v>-117.23385751932582</v>
       </c>
     </row>
     <row r="16" spans="2:53" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3494,204 +3483,204 @@
         <v>34</v>
       </c>
       <c r="C16" s="8">
-        <f t="shared" ref="C16:L16" si="124">C14-C15</f>
+        <f t="shared" ref="C16:L16" si="123">C14-C15</f>
         <v>-6.5000000000000053</v>
       </c>
       <c r="D16" s="8">
+        <f t="shared" si="123"/>
+        <v>0.20000000000000573</v>
+      </c>
+      <c r="E16" s="8">
+        <f t="shared" si="123"/>
+        <v>-9.7000000000000259</v>
+      </c>
+      <c r="F16" s="8">
+        <f t="shared" si="123"/>
+        <v>6.699999999999986</v>
+      </c>
+      <c r="G16" s="8">
+        <f t="shared" si="123"/>
+        <v>-9.8000000000000167</v>
+      </c>
+      <c r="H16" s="8">
+        <f t="shared" si="123"/>
+        <v>-9.8600000000000065</v>
+      </c>
+      <c r="I16" s="8">
+        <f t="shared" si="123"/>
+        <v>-24.700000000000017</v>
+      </c>
+      <c r="J16" s="8">
+        <f t="shared" si="123"/>
+        <v>-15.999999999999954</v>
+      </c>
+      <c r="K16" s="8">
+        <f t="shared" si="123"/>
+        <v>-54.6</v>
+      </c>
+      <c r="L16" s="8">
+        <f t="shared" si="123"/>
+        <v>-42.599999999999987</v>
+      </c>
+      <c r="M16" s="8">
+        <f t="shared" ref="M16:AL16" si="124">M14-M15</f>
+        <v>12.20000000000004</v>
+      </c>
+      <c r="N16" s="8">
         <f t="shared" si="124"/>
-        <v>0.20000000000000573</v>
-      </c>
-      <c r="E16" s="8">
+        <v>66.649999999999991</v>
+      </c>
+      <c r="O16" s="8">
         <f t="shared" si="124"/>
-        <v>-9.7000000000000259</v>
-      </c>
-      <c r="F16" s="8">
+        <v>75.500000000000071</v>
+      </c>
+      <c r="P16" s="8">
+        <f t="shared" ref="P16:Q16" si="125">P14-P15</f>
+        <v>69.899999999999906</v>
+      </c>
+      <c r="Q16" s="8">
+        <f t="shared" si="125"/>
+        <v>68.599999999999952</v>
+      </c>
+      <c r="R16" s="8">
         <f t="shared" si="124"/>
-        <v>6.699999999999986</v>
-      </c>
-      <c r="G16" s="8">
+        <v>22.599999999999955</v>
+      </c>
+      <c r="S16" s="8">
+        <f t="shared" ref="S16:T16" si="126">S14-S15</f>
+        <v>-24.200000000000056</v>
+      </c>
+      <c r="T16" s="8">
+        <f t="shared" si="126"/>
+        <v>-109.80000000000005</v>
+      </c>
+      <c r="U16" s="8">
+        <f t="shared" ref="U16" si="127">U14-U15</f>
+        <v>-120.29999999999994</v>
+      </c>
+      <c r="V16" s="8">
+        <f t="shared" ref="V16" si="128">V14-V15</f>
+        <v>-238.2000000000001</v>
+      </c>
+      <c r="W16" s="8">
+        <f t="shared" ref="W16:X16" si="129">W14-W15</f>
+        <v>-189.50000000000006</v>
+      </c>
+      <c r="X16" s="8">
+        <f t="shared" si="129"/>
+        <v>-105.90000000000003</v>
+      </c>
+      <c r="Y16" s="8">
+        <f t="shared" ref="Y16" si="130">Y14-Y15</f>
+        <v>-326.89999999999998</v>
+      </c>
+      <c r="Z16" s="8">
+        <f t="shared" ref="Z16:AH16" si="131">Z14-Z15</f>
+        <v>-76.40000000000002</v>
+      </c>
+      <c r="AA16" s="8">
+        <f t="shared" si="131"/>
+        <v>-46.000000000000057</v>
+      </c>
+      <c r="AB16" s="8">
+        <f t="shared" si="131"/>
+        <v>-43.30000000000009</v>
+      </c>
+      <c r="AC16" s="8">
+        <f t="shared" si="131"/>
+        <v>-4.7999999999998195</v>
+      </c>
+      <c r="AD16" s="8">
+        <f t="shared" si="131"/>
+        <v>-25.899999999999931</v>
+      </c>
+      <c r="AE16" s="8">
+        <f t="shared" si="131"/>
+        <v>-40.500000000000043</v>
+      </c>
+      <c r="AF16" s="8">
+        <f t="shared" si="131"/>
+        <v>4.6999999999999318</v>
+      </c>
+      <c r="AG16" s="8">
+        <f t="shared" si="131"/>
+        <v>37.999999999999979</v>
+      </c>
+      <c r="AH16" s="8">
+        <f t="shared" si="131"/>
+        <v>52.236459999999973</v>
+      </c>
+      <c r="AJ16" s="8">
         <f t="shared" si="124"/>
-        <v>-9.8000000000000167</v>
-      </c>
-      <c r="H16" s="8">
+        <v>-9.3000000000000114</v>
+      </c>
+      <c r="AK16" s="8">
         <f t="shared" si="124"/>
-        <v>-9.8600000000000065</v>
-      </c>
-      <c r="I16" s="8">
+        <v>-60.359999999999907</v>
+      </c>
+      <c r="AL16" s="8">
         <f t="shared" si="124"/>
-        <v>-24.700000000000017</v>
-      </c>
-      <c r="J16" s="8">
-        <f t="shared" si="124"/>
-        <v>-15.999999999999954</v>
-      </c>
-      <c r="K16" s="8">
-        <f t="shared" si="124"/>
-        <v>-54.6</v>
-      </c>
-      <c r="L16" s="8">
-        <f t="shared" si="124"/>
-        <v>-42.599999999999987</v>
-      </c>
-      <c r="M16" s="8">
-        <f t="shared" ref="M16:AL16" si="125">M14-M15</f>
-        <v>12.20000000000004</v>
-      </c>
-      <c r="N16" s="8">
-        <f t="shared" si="125"/>
-        <v>66.649999999999991</v>
-      </c>
-      <c r="O16" s="8">
-        <f t="shared" si="125"/>
-        <v>75.500000000000071</v>
-      </c>
-      <c r="P16" s="8">
-        <f t="shared" ref="P16:Q16" si="126">P14-P15</f>
-        <v>69.899999999999906</v>
-      </c>
-      <c r="Q16" s="8">
-        <f t="shared" si="126"/>
-        <v>68.599999999999952</v>
-      </c>
-      <c r="R16" s="8">
-        <f t="shared" si="125"/>
-        <v>22.599999999999955</v>
-      </c>
-      <c r="S16" s="8">
-        <f t="shared" ref="S16:T16" si="127">S14-S15</f>
-        <v>-24.200000000000056</v>
-      </c>
-      <c r="T16" s="8">
-        <f t="shared" si="127"/>
-        <v>-109.80000000000005</v>
-      </c>
-      <c r="U16" s="8">
-        <f t="shared" ref="U16" si="128">U14-U15</f>
-        <v>-120.29999999999994</v>
-      </c>
-      <c r="V16" s="8">
-        <f t="shared" ref="V16" si="129">V14-V15</f>
-        <v>-238.2000000000001</v>
-      </c>
-      <c r="W16" s="8">
-        <f t="shared" ref="W16:X16" si="130">W14-W15</f>
-        <v>-189.50000000000006</v>
-      </c>
-      <c r="X16" s="8">
-        <f t="shared" si="130"/>
-        <v>-105.90000000000003</v>
-      </c>
-      <c r="Y16" s="8">
-        <f t="shared" ref="Y16" si="131">Y14-Y15</f>
-        <v>-326.89999999999998</v>
-      </c>
-      <c r="Z16" s="8">
-        <f t="shared" ref="Z16:AH16" si="132">Z14-Z15</f>
-        <v>-76.40000000000002</v>
-      </c>
-      <c r="AA16" s="8">
-        <f t="shared" si="132"/>
-        <v>-46.000000000000057</v>
-      </c>
-      <c r="AB16" s="8">
-        <f t="shared" si="132"/>
-        <v>-43.30000000000009</v>
-      </c>
-      <c r="AC16" s="8">
-        <f t="shared" si="132"/>
-        <v>-4.7999999999998195</v>
-      </c>
-      <c r="AD16" s="8">
-        <f t="shared" si="132"/>
-        <v>-25.899999999999931</v>
-      </c>
-      <c r="AE16" s="8">
-        <f t="shared" si="132"/>
-        <v>-40.500000000000043</v>
-      </c>
-      <c r="AF16" s="8">
-        <f t="shared" si="132"/>
-        <v>4.6999999999999318</v>
-      </c>
-      <c r="AG16" s="8">
-        <f t="shared" si="132"/>
-        <v>18.868719999999879</v>
-      </c>
-      <c r="AH16" s="8">
-        <f t="shared" si="132"/>
-        <v>21.991679999999981</v>
-      </c>
-      <c r="AJ16" s="8">
-        <f t="shared" si="125"/>
-        <v>-9.3000000000000114</v>
-      </c>
-      <c r="AK16" s="8">
-        <f t="shared" si="125"/>
-        <v>-60.359999999999907</v>
-      </c>
-      <c r="AL16" s="8">
-        <f t="shared" si="125"/>
         <v>-18.350000000000044</v>
       </c>
       <c r="AM16" s="8">
-        <f t="shared" ref="AM16" si="133">AM14-AM15</f>
+        <f t="shared" ref="AM16" si="132">AM14-AM15</f>
         <v>236.59999999999977</v>
       </c>
       <c r="AN16" s="8">
-        <f t="shared" ref="AN16" si="134">AN14-AN15</f>
+        <f t="shared" ref="AN16" si="133">AN14-AN15</f>
         <v>-492.50000000000034</v>
       </c>
       <c r="AO16" s="8">
-        <f t="shared" ref="AO16" si="135">AO14-AO15</f>
+        <f t="shared" ref="AO16" si="134">AO14-AO15</f>
         <v>-698.6999999999997</v>
       </c>
       <c r="AP16" s="8">
-        <f t="shared" ref="AP16" si="136">AP14-AP15</f>
+        <f t="shared" ref="AP16" si="135">AP14-AP15</f>
         <v>-120.00000000000018</v>
       </c>
       <c r="AQ16" s="8">
-        <f t="shared" ref="AQ16" si="137">AQ14-AQ15</f>
-        <v>5.0604000000006693</v>
+        <f t="shared" ref="AQ16" si="136">AQ14-AQ15</f>
+        <v>54.436459999999741</v>
       </c>
       <c r="AR16" s="8">
-        <f t="shared" ref="AR16" si="138">AR14-AR15</f>
-        <v>293.15243140000024</v>
+        <f t="shared" ref="AR16" si="137">AR14-AR15</f>
+        <v>268.34278720000054</v>
       </c>
       <c r="AS16" s="8">
-        <f t="shared" ref="AS16" si="139">AS14-AS15</f>
-        <v>477.3708218139999</v>
+        <f t="shared" ref="AS16" si="138">AS14-AS15</f>
+        <v>500.27934334400021</v>
       </c>
       <c r="AT16" s="8">
-        <f t="shared" ref="AT16" si="140">AT14-AT15</f>
-        <v>633.9047754889599</v>
+        <f t="shared" ref="AT16" si="139">AT14-AT15</f>
+        <v>658.76953662212031</v>
       </c>
       <c r="AU16" s="8">
-        <f t="shared" ref="AU16" si="141">AU14-AU15</f>
-        <v>692.18391077343824</v>
+        <f t="shared" ref="AU16" si="140">AU14-AU15</f>
+        <v>722.61610131392126</v>
       </c>
       <c r="AV16" s="8">
-        <f t="shared" ref="AV16:AW16" si="142">AV14-AV15</f>
-        <v>734.02942533811506</v>
+        <f t="shared" ref="AV16:AW16" si="141">AV14-AV15</f>
+        <v>770.18357887902857</v>
       </c>
       <c r="AW16" s="8">
+        <f t="shared" si="141"/>
+        <v>799.67246224531732</v>
+      </c>
+      <c r="AX16" s="8">
+        <f t="shared" ref="AX16:BA16" si="142">AX14-AX15</f>
+        <v>829.91220078788297</v>
+      </c>
+      <c r="AY16" s="8">
         <f t="shared" si="142"/>
-        <v>758.85481752717067</v>
-      </c>
-      <c r="AX16" s="8">
-        <f t="shared" ref="AX16:BA16" si="143">AX14-AX15</f>
-        <v>784.29899589710635</v>
-      </c>
-      <c r="AY16" s="8">
-        <f t="shared" si="143"/>
-        <v>810.37618386391955</v>
+        <v>860.9200291470728</v>
       </c>
       <c r="AZ16" s="8">
-        <f t="shared" si="143"/>
-        <v>837.10092653612139</v>
+        <f t="shared" si="142"/>
+        <v>892.71356703426181</v>
       </c>
       <c r="BA16" s="8">
-        <f t="shared" si="143"/>
-        <v>864.488098083247</v>
+        <f t="shared" si="142"/>
+        <v>925.31082788313836</v>
       </c>
     </row>
     <row r="17" spans="2:163" x14ac:dyDescent="0.3">
@@ -3789,12 +3778,11 @@
         <v>-5.8</v>
       </c>
       <c r="AG17" s="5">
-        <f t="shared" ref="AF17:AH17" si="144">AG16*0.2</f>
-        <v>3.7737439999999758</v>
+        <v>13.2</v>
       </c>
       <c r="AH17" s="5">
-        <f t="shared" si="144"/>
-        <v>4.398335999999996</v>
+        <f t="shared" ref="AG17:AH17" si="143">AH16*0.2</f>
+        <v>10.447291999999996</v>
       </c>
       <c r="AJ17" s="5">
         <f>SUM(C17:F17)</f>
@@ -3826,47 +3814,47 @@
       </c>
       <c r="AQ17" s="5">
         <f>SUM(AE17:AH17)</f>
-        <v>-10.727920000000026</v>
+        <v>4.7472919999999963</v>
       </c>
       <c r="AR17" s="5">
         <f>AR16*0.2</f>
-        <v>58.630486280000049</v>
+        <v>53.668557440000114</v>
       </c>
       <c r="AS17" s="5">
-        <f t="shared" ref="AS17:AV17" si="145">AS16*0.2</f>
-        <v>95.474164362799982</v>
+        <f t="shared" ref="AS17:AV17" si="144">AS16*0.2</f>
+        <v>100.05586866880004</v>
       </c>
       <c r="AT17" s="5">
+        <f t="shared" si="144"/>
+        <v>131.75390732442406</v>
+      </c>
+      <c r="AU17" s="5">
+        <f t="shared" si="144"/>
+        <v>144.52322026278426</v>
+      </c>
+      <c r="AV17" s="5">
+        <f t="shared" si="144"/>
+        <v>154.03671577580573</v>
+      </c>
+      <c r="AW17" s="5">
+        <f t="shared" ref="AW17:BA17" si="145">AW16*0.2</f>
+        <v>159.93449244906347</v>
+      </c>
+      <c r="AX17" s="5">
         <f t="shared" si="145"/>
-        <v>126.78095509779199</v>
-      </c>
-      <c r="AU17" s="5">
+        <v>165.9824401575766</v>
+      </c>
+      <c r="AY17" s="5">
         <f t="shared" si="145"/>
-        <v>138.43678215468765</v>
-      </c>
-      <c r="AV17" s="5">
+        <v>172.18400582941456</v>
+      </c>
+      <c r="AZ17" s="5">
         <f t="shared" si="145"/>
-        <v>146.80588506762302</v>
-      </c>
-      <c r="AW17" s="5">
-        <f t="shared" ref="AW17:BA17" si="146">AW16*0.2</f>
-        <v>151.77096350543414</v>
-      </c>
-      <c r="AX17" s="5">
-        <f t="shared" si="146"/>
-        <v>156.85979917942129</v>
-      </c>
-      <c r="AY17" s="5">
-        <f t="shared" si="146"/>
-        <v>162.07523677278391</v>
-      </c>
-      <c r="AZ17" s="5">
-        <f t="shared" si="146"/>
-        <v>167.4201853072243</v>
+        <v>178.54271340685239</v>
       </c>
       <c r="BA17" s="5">
-        <f t="shared" si="146"/>
-        <v>172.89761961664942</v>
+        <f t="shared" si="145"/>
+        <v>185.06216557662768</v>
       </c>
     </row>
     <row r="18" spans="2:163" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3874,644 +3862,644 @@
         <v>36</v>
       </c>
       <c r="C18" s="8">
-        <f t="shared" ref="C18:L18" si="147">C16-C17</f>
+        <f t="shared" ref="C18:L18" si="146">C16-C17</f>
         <v>-6.600000000000005</v>
       </c>
       <c r="D18" s="8">
+        <f t="shared" si="146"/>
+        <v>0.60000000000000575</v>
+      </c>
+      <c r="E18" s="8">
+        <f t="shared" si="146"/>
+        <v>-9.5000000000000266</v>
+      </c>
+      <c r="F18" s="8">
+        <f t="shared" si="146"/>
+        <v>6.7999999999999856</v>
+      </c>
+      <c r="G18" s="8">
+        <f t="shared" si="146"/>
+        <v>-9.7000000000000171</v>
+      </c>
+      <c r="H18" s="8">
+        <f t="shared" si="146"/>
+        <v>-9.4600000000000062</v>
+      </c>
+      <c r="I18" s="8">
+        <f t="shared" si="146"/>
+        <v>-24.600000000000016</v>
+      </c>
+      <c r="J18" s="8">
+        <f t="shared" si="146"/>
+        <v>-15.599999999999953</v>
+      </c>
+      <c r="K18" s="8">
+        <f t="shared" si="146"/>
+        <v>-54.4</v>
+      </c>
+      <c r="L18" s="8">
+        <f t="shared" si="146"/>
+        <v>-43.099999999999987</v>
+      </c>
+      <c r="M18" s="8">
+        <f t="shared" ref="M18:AL18" si="147">M16-M17</f>
+        <v>13.20000000000004</v>
+      </c>
+      <c r="N18" s="8">
         <f t="shared" si="147"/>
-        <v>0.60000000000000575</v>
-      </c>
-      <c r="E18" s="8">
+        <v>67.349999999999994</v>
+      </c>
+      <c r="O18" s="8">
+        <f t="shared" ref="O18:R18" si="148">O16-O17</f>
+        <v>76.300000000000068</v>
+      </c>
+      <c r="P18" s="8">
+        <f t="shared" ref="P18:Q18" si="149">P16-P17</f>
+        <v>73.499999999999901</v>
+      </c>
+      <c r="Q18" s="8">
+        <f t="shared" si="149"/>
+        <v>68.899999999999949</v>
+      </c>
+      <c r="R18" s="8">
+        <f t="shared" si="148"/>
+        <v>23.699999999999957</v>
+      </c>
+      <c r="S18" s="8">
+        <f t="shared" ref="S18:T18" si="150">S16-S17</f>
+        <v>-26.400000000000055</v>
+      </c>
+      <c r="T18" s="8">
+        <f t="shared" si="150"/>
+        <v>-112.40000000000005</v>
+      </c>
+      <c r="U18" s="8">
+        <f t="shared" ref="U18" si="151">U16-U17</f>
+        <v>-122.29999999999994</v>
+      </c>
+      <c r="V18" s="8">
+        <f t="shared" ref="V18" si="152">V16-V17</f>
+        <v>-237.2000000000001</v>
+      </c>
+      <c r="W18" s="8">
+        <f t="shared" ref="W18:X18" si="153">W16-W17</f>
+        <v>-193.10000000000005</v>
+      </c>
+      <c r="X18" s="8">
+        <f t="shared" si="153"/>
+        <v>-107.50000000000003</v>
+      </c>
+      <c r="Y18" s="8">
+        <f t="shared" ref="Y18" si="154">Y16-Y17</f>
+        <v>-330.09999999999997</v>
+      </c>
+      <c r="Z18" s="8">
+        <f t="shared" ref="Z18:AA18" si="155">Z16-Z17</f>
+        <v>-78.200000000000017</v>
+      </c>
+      <c r="AA18" s="8">
+        <f t="shared" si="155"/>
+        <v>-50.800000000000054</v>
+      </c>
+      <c r="AB18" s="8">
+        <f t="shared" ref="AB18:AD18" si="156">AB16-AB17</f>
+        <v>-34.100000000000094</v>
+      </c>
+      <c r="AC18" s="8">
+        <f t="shared" si="156"/>
+        <v>-8.8999999999998192</v>
+      </c>
+      <c r="AD18" s="8">
+        <f t="shared" si="156"/>
+        <v>-35.59999999999993</v>
+      </c>
+      <c r="AE18" s="8">
+        <f t="shared" ref="AE18:AH18" si="157">AE16-AE17</f>
+        <v>-27.400000000000041</v>
+      </c>
+      <c r="AF18" s="8">
+        <f t="shared" si="157"/>
+        <v>10.499999999999932</v>
+      </c>
+      <c r="AG18" s="8">
+        <f t="shared" si="157"/>
+        <v>24.799999999999979</v>
+      </c>
+      <c r="AH18" s="8">
+        <f t="shared" si="157"/>
+        <v>41.789167999999975</v>
+      </c>
+      <c r="AJ18" s="8">
         <f t="shared" si="147"/>
-        <v>-9.5000000000000266</v>
-      </c>
-      <c r="F18" s="8">
+        <v>-8.7000000000000117</v>
+      </c>
+      <c r="AK18" s="8">
         <f t="shared" si="147"/>
-        <v>6.7999999999999856</v>
-      </c>
-      <c r="G18" s="8">
+        <v>-59.359999999999907</v>
+      </c>
+      <c r="AL18" s="8">
         <f t="shared" si="147"/>
-        <v>-9.7000000000000171</v>
-      </c>
-      <c r="H18" s="8">
-        <f t="shared" si="147"/>
-        <v>-9.4600000000000062</v>
-      </c>
-      <c r="I18" s="8">
-        <f t="shared" si="147"/>
-        <v>-24.600000000000016</v>
-      </c>
-      <c r="J18" s="8">
-        <f t="shared" si="147"/>
-        <v>-15.599999999999953</v>
-      </c>
-      <c r="K18" s="8">
-        <f t="shared" si="147"/>
-        <v>-54.4</v>
-      </c>
-      <c r="L18" s="8">
-        <f t="shared" si="147"/>
-        <v>-43.099999999999987</v>
-      </c>
-      <c r="M18" s="8">
-        <f t="shared" ref="M18:AL18" si="148">M16-M17</f>
-        <v>13.20000000000004</v>
-      </c>
-      <c r="N18" s="8">
-        <f t="shared" si="148"/>
-        <v>67.349999999999994</v>
-      </c>
-      <c r="O18" s="8">
-        <f t="shared" ref="O18:R18" si="149">O16-O17</f>
-        <v>76.300000000000068</v>
-      </c>
-      <c r="P18" s="8">
-        <f t="shared" ref="P18:Q18" si="150">P16-P17</f>
-        <v>73.499999999999901</v>
-      </c>
-      <c r="Q18" s="8">
-        <f t="shared" si="150"/>
-        <v>68.899999999999949</v>
-      </c>
-      <c r="R18" s="8">
-        <f t="shared" si="149"/>
-        <v>23.699999999999957</v>
-      </c>
-      <c r="S18" s="8">
-        <f t="shared" ref="S18:T18" si="151">S16-S17</f>
-        <v>-26.400000000000055</v>
-      </c>
-      <c r="T18" s="8">
-        <f t="shared" si="151"/>
-        <v>-112.40000000000005</v>
-      </c>
-      <c r="U18" s="8">
-        <f t="shared" ref="U18" si="152">U16-U17</f>
-        <v>-122.29999999999994</v>
-      </c>
-      <c r="V18" s="8">
-        <f t="shared" ref="V18" si="153">V16-V17</f>
-        <v>-237.2000000000001</v>
-      </c>
-      <c r="W18" s="8">
-        <f t="shared" ref="W18:X18" si="154">W16-W17</f>
-        <v>-193.10000000000005</v>
-      </c>
-      <c r="X18" s="8">
-        <f t="shared" si="154"/>
-        <v>-107.50000000000003</v>
-      </c>
-      <c r="Y18" s="8">
-        <f t="shared" ref="Y18" si="155">Y16-Y17</f>
-        <v>-330.09999999999997</v>
-      </c>
-      <c r="Z18" s="8">
-        <f t="shared" ref="Z18:AA18" si="156">Z16-Z17</f>
-        <v>-78.200000000000017</v>
-      </c>
-      <c r="AA18" s="8">
-        <f t="shared" si="156"/>
-        <v>-50.800000000000054</v>
-      </c>
-      <c r="AB18" s="8">
-        <f t="shared" ref="AB18:AD18" si="157">AB16-AB17</f>
-        <v>-34.100000000000094</v>
-      </c>
-      <c r="AC18" s="8">
-        <f t="shared" si="157"/>
-        <v>-8.8999999999998192</v>
-      </c>
-      <c r="AD18" s="8">
-        <f t="shared" si="157"/>
-        <v>-35.59999999999993</v>
-      </c>
-      <c r="AE18" s="8">
-        <f t="shared" ref="AE18:AH18" si="158">AE16-AE17</f>
-        <v>-27.400000000000041</v>
-      </c>
-      <c r="AF18" s="8">
-        <f t="shared" si="158"/>
-        <v>10.499999999999932</v>
-      </c>
-      <c r="AG18" s="8">
-        <f t="shared" si="158"/>
-        <v>15.094975999999903</v>
-      </c>
-      <c r="AH18" s="8">
-        <f t="shared" si="158"/>
-        <v>17.593343999999984</v>
-      </c>
-      <c r="AJ18" s="8">
-        <f t="shared" si="148"/>
-        <v>-8.7000000000000117</v>
-      </c>
-      <c r="AK18" s="8">
-        <f t="shared" si="148"/>
-        <v>-59.359999999999907</v>
-      </c>
-      <c r="AL18" s="8">
-        <f t="shared" si="148"/>
         <v>-16.950000000000045</v>
       </c>
       <c r="AM18" s="8">
-        <f t="shared" ref="AM18" si="159">AM16-AM17</f>
+        <f t="shared" ref="AM18" si="158">AM16-AM17</f>
         <v>242.39999999999978</v>
       </c>
       <c r="AN18" s="8">
-        <f t="shared" ref="AN18" si="160">AN16-AN17</f>
+        <f t="shared" ref="AN18" si="159">AN16-AN17</f>
         <v>-498.30000000000035</v>
       </c>
       <c r="AO18" s="8">
-        <f t="shared" ref="AO18" si="161">AO16-AO17</f>
+        <f t="shared" ref="AO18" si="160">AO16-AO17</f>
         <v>-708.89999999999975</v>
       </c>
       <c r="AP18" s="8">
-        <f t="shared" ref="AP18" si="162">AP16-AP17</f>
+        <f t="shared" ref="AP18" si="161">AP16-AP17</f>
         <v>-129.40000000000018</v>
       </c>
       <c r="AQ18" s="8">
-        <f t="shared" ref="AQ18" si="163">AQ16-AQ17</f>
-        <v>15.788320000000695</v>
+        <f t="shared" ref="AQ18" si="162">AQ16-AQ17</f>
+        <v>49.689167999999746</v>
       </c>
       <c r="AR18" s="8">
-        <f t="shared" ref="AR18" si="164">AR16-AR17</f>
-        <v>234.5219451200002</v>
+        <f t="shared" ref="AR18" si="163">AR16-AR17</f>
+        <v>214.67422976000043</v>
       </c>
       <c r="AS18" s="8">
-        <f t="shared" ref="AS18" si="165">AS16-AS17</f>
-        <v>381.89665745119993</v>
+        <f t="shared" ref="AS18" si="164">AS16-AS17</f>
+        <v>400.22347467520018</v>
       </c>
       <c r="AT18" s="8">
-        <f t="shared" ref="AT18" si="166">AT16-AT17</f>
-        <v>507.1238203911679</v>
+        <f t="shared" ref="AT18" si="165">AT16-AT17</f>
+        <v>527.01562929769625</v>
       </c>
       <c r="AU18" s="8">
-        <f t="shared" ref="AU18" si="167">AU16-AU17</f>
-        <v>553.74712861875059</v>
+        <f t="shared" ref="AU18" si="166">AU16-AU17</f>
+        <v>578.09288105113706</v>
       </c>
       <c r="AV18" s="8">
-        <f t="shared" ref="AV18:AW18" si="168">AV16-AV17</f>
-        <v>587.22354027049209</v>
+        <f t="shared" ref="AV18:AW18" si="167">AV16-AV17</f>
+        <v>616.14686310322281</v>
       </c>
       <c r="AW18" s="8">
+        <f t="shared" si="167"/>
+        <v>639.73796979625388</v>
+      </c>
+      <c r="AX18" s="8">
+        <f t="shared" ref="AX18:BA18" si="168">AX16-AX17</f>
+        <v>663.92976063030642</v>
+      </c>
+      <c r="AY18" s="8">
         <f t="shared" si="168"/>
-        <v>607.08385402173656</v>
-      </c>
-      <c r="AX18" s="8">
-        <f t="shared" ref="AX18:BA18" si="169">AX16-AX17</f>
-        <v>627.43919671768504</v>
-      </c>
-      <c r="AY18" s="8">
-        <f t="shared" si="169"/>
-        <v>648.30094709113564</v>
+        <v>688.73602331765824</v>
       </c>
       <c r="AZ18" s="8">
-        <f t="shared" si="169"/>
-        <v>669.68074122889709</v>
+        <f t="shared" si="168"/>
+        <v>714.17085362740943</v>
       </c>
       <c r="BA18" s="8">
-        <f t="shared" si="169"/>
-        <v>691.59047846659757</v>
+        <f t="shared" si="168"/>
+        <v>740.24866230651071</v>
       </c>
       <c r="BB18" s="1">
         <f>BA18*(1+$BD$25)</f>
-        <v>684.67457368193163</v>
+        <v>732.84617568344561</v>
       </c>
       <c r="BC18" s="1">
-        <f t="shared" ref="BC18:DN18" si="170">BB18*(1+$BD$25)</f>
-        <v>677.82782794511229</v>
+        <f t="shared" ref="BC18:DN18" si="169">BB18*(1+$BD$25)</f>
+        <v>725.51771392661112</v>
       </c>
       <c r="BD18" s="1">
+        <f t="shared" si="169"/>
+        <v>718.26253678734497</v>
+      </c>
+      <c r="BE18" s="1">
+        <f t="shared" si="169"/>
+        <v>711.0799114194715</v>
+      </c>
+      <c r="BF18" s="1">
+        <f t="shared" si="169"/>
+        <v>703.96911230527678</v>
+      </c>
+      <c r="BG18" s="1">
+        <f t="shared" si="169"/>
+        <v>696.92942118222402</v>
+      </c>
+      <c r="BH18" s="1">
+        <f t="shared" si="169"/>
+        <v>689.9601269704018</v>
+      </c>
+      <c r="BI18" s="1">
+        <f t="shared" si="169"/>
+        <v>683.06052570069778</v>
+      </c>
+      <c r="BJ18" s="1">
+        <f t="shared" si="169"/>
+        <v>676.22992044369084</v>
+      </c>
+      <c r="BK18" s="1">
+        <f t="shared" si="169"/>
+        <v>669.46762123925396</v>
+      </c>
+      <c r="BL18" s="1">
+        <f t="shared" si="169"/>
+        <v>662.77294502686141</v>
+      </c>
+      <c r="BM18" s="1">
+        <f t="shared" si="169"/>
+        <v>656.14521557659282</v>
+      </c>
+      <c r="BN18" s="1">
+        <f t="shared" si="169"/>
+        <v>649.58376342082693</v>
+      </c>
+      <c r="BO18" s="1">
+        <f t="shared" si="169"/>
+        <v>643.0879257866186</v>
+      </c>
+      <c r="BP18" s="1">
+        <f t="shared" si="169"/>
+        <v>636.6570465287524</v>
+      </c>
+      <c r="BQ18" s="1">
+        <f t="shared" si="169"/>
+        <v>630.29047606346489</v>
+      </c>
+      <c r="BR18" s="1">
+        <f t="shared" si="169"/>
+        <v>623.98757130283025</v>
+      </c>
+      <c r="BS18" s="1">
+        <f t="shared" si="169"/>
+        <v>617.74769558980199</v>
+      </c>
+      <c r="BT18" s="1">
+        <f t="shared" si="169"/>
+        <v>611.57021863390401</v>
+      </c>
+      <c r="BU18" s="1">
+        <f t="shared" si="169"/>
+        <v>605.45451644756497</v>
+      </c>
+      <c r="BV18" s="1">
+        <f t="shared" si="169"/>
+        <v>599.39997128308937</v>
+      </c>
+      <c r="BW18" s="1">
+        <f t="shared" si="169"/>
+        <v>593.40597157025843</v>
+      </c>
+      <c r="BX18" s="1">
+        <f t="shared" si="169"/>
+        <v>587.47191185455586</v>
+      </c>
+      <c r="BY18" s="1">
+        <f t="shared" si="169"/>
+        <v>581.59719273601024</v>
+      </c>
+      <c r="BZ18" s="1">
+        <f t="shared" si="169"/>
+        <v>575.78122080865012</v>
+      </c>
+      <c r="CA18" s="1">
+        <f t="shared" si="169"/>
+        <v>570.02340860056358</v>
+      </c>
+      <c r="CB18" s="1">
+        <f t="shared" si="169"/>
+        <v>564.32317451455799</v>
+      </c>
+      <c r="CC18" s="1">
+        <f t="shared" si="169"/>
+        <v>558.67994276941238</v>
+      </c>
+      <c r="CD18" s="1">
+        <f t="shared" si="169"/>
+        <v>553.09314334171825</v>
+      </c>
+      <c r="CE18" s="1">
+        <f t="shared" si="169"/>
+        <v>547.56221190830104</v>
+      </c>
+      <c r="CF18" s="1">
+        <f t="shared" si="169"/>
+        <v>542.08658978921801</v>
+      </c>
+      <c r="CG18" s="1">
+        <f t="shared" si="169"/>
+        <v>536.6657238913258</v>
+      </c>
+      <c r="CH18" s="1">
+        <f t="shared" si="169"/>
+        <v>531.29906665241253</v>
+      </c>
+      <c r="CI18" s="1">
+        <f t="shared" si="169"/>
+        <v>525.98607598588842</v>
+      </c>
+      <c r="CJ18" s="1">
+        <f t="shared" si="169"/>
+        <v>520.72621522602958</v>
+      </c>
+      <c r="CK18" s="1">
+        <f t="shared" si="169"/>
+        <v>515.51895307376924</v>
+      </c>
+      <c r="CL18" s="1">
+        <f t="shared" si="169"/>
+        <v>510.36376354303155</v>
+      </c>
+      <c r="CM18" s="1">
+        <f t="shared" si="169"/>
+        <v>505.26012590760121</v>
+      </c>
+      <c r="CN18" s="1">
+        <f t="shared" si="169"/>
+        <v>500.20752464852518</v>
+      </c>
+      <c r="CO18" s="1">
+        <f t="shared" si="169"/>
+        <v>495.2054494020399</v>
+      </c>
+      <c r="CP18" s="1">
+        <f t="shared" si="169"/>
+        <v>490.25339490801952</v>
+      </c>
+      <c r="CQ18" s="1">
+        <f t="shared" si="169"/>
+        <v>485.35086095893934</v>
+      </c>
+      <c r="CR18" s="1">
+        <f t="shared" si="169"/>
+        <v>480.49735234934991</v>
+      </c>
+      <c r="CS18" s="1">
+        <f t="shared" si="169"/>
+        <v>475.69237882585639</v>
+      </c>
+      <c r="CT18" s="1">
+        <f t="shared" si="169"/>
+        <v>470.93545503759782</v>
+      </c>
+      <c r="CU18" s="1">
+        <f t="shared" si="169"/>
+        <v>466.22610048722186</v>
+      </c>
+      <c r="CV18" s="1">
+        <f t="shared" si="169"/>
+        <v>461.56383948234964</v>
+      </c>
+      <c r="CW18" s="1">
+        <f t="shared" si="169"/>
+        <v>456.94820108752612</v>
+      </c>
+      <c r="CX18" s="1">
+        <f t="shared" si="169"/>
+        <v>452.37871907665084</v>
+      </c>
+      <c r="CY18" s="1">
+        <f t="shared" si="169"/>
+        <v>447.8549318858843</v>
+      </c>
+      <c r="CZ18" s="1">
+        <f t="shared" si="169"/>
+        <v>443.37638256702547</v>
+      </c>
+      <c r="DA18" s="1">
+        <f t="shared" si="169"/>
+        <v>438.9426187413552</v>
+      </c>
+      <c r="DB18" s="1">
+        <f t="shared" si="169"/>
+        <v>434.55319255394164</v>
+      </c>
+      <c r="DC18" s="1">
+        <f t="shared" si="169"/>
+        <v>430.20766062840221</v>
+      </c>
+      <c r="DD18" s="1">
+        <f t="shared" si="169"/>
+        <v>425.90558402211821</v>
+      </c>
+      <c r="DE18" s="1">
+        <f t="shared" si="169"/>
+        <v>421.646528181897</v>
+      </c>
+      <c r="DF18" s="1">
+        <f t="shared" si="169"/>
+        <v>417.43006290007804</v>
+      </c>
+      <c r="DG18" s="1">
+        <f t="shared" si="169"/>
+        <v>413.25576227107723</v>
+      </c>
+      <c r="DH18" s="1">
+        <f t="shared" si="169"/>
+        <v>409.12320464836648</v>
+      </c>
+      <c r="DI18" s="1">
+        <f t="shared" si="169"/>
+        <v>405.03197260188279</v>
+      </c>
+      <c r="DJ18" s="1">
+        <f t="shared" si="169"/>
+        <v>400.98165287586397</v>
+      </c>
+      <c r="DK18" s="1">
+        <f t="shared" si="169"/>
+        <v>396.97183634710535</v>
+      </c>
+      <c r="DL18" s="1">
+        <f t="shared" si="169"/>
+        <v>393.00211798363432</v>
+      </c>
+      <c r="DM18" s="1">
+        <f t="shared" si="169"/>
+        <v>389.07209680379799</v>
+      </c>
+      <c r="DN18" s="1">
+        <f t="shared" si="169"/>
+        <v>385.18137583575998</v>
+      </c>
+      <c r="DO18" s="1">
+        <f t="shared" ref="DO18:FG18" si="170">DN18*(1+$BD$25)</f>
+        <v>381.32956207740239</v>
+      </c>
+      <c r="DP18" s="1">
         <f t="shared" si="170"/>
-        <v>671.04954966566117</v>
-      </c>
-      <c r="BE18" s="1">
+        <v>377.51626645662839</v>
+      </c>
+      <c r="DQ18" s="1">
         <f t="shared" si="170"/>
-        <v>664.33905416900461</v>
-      </c>
-      <c r="BF18" s="1">
+        <v>373.74110379206212</v>
+      </c>
+      <c r="DR18" s="1">
         <f t="shared" si="170"/>
-        <v>657.69566362731462</v>
-      </c>
-      <c r="BG18" s="1">
+        <v>370.00369275414147</v>
+      </c>
+      <c r="DS18" s="1">
         <f t="shared" si="170"/>
-        <v>651.11870699104145</v>
-      </c>
-      <c r="BH18" s="1">
+        <v>366.30365582660005</v>
+      </c>
+      <c r="DT18" s="1">
         <f t="shared" si="170"/>
-        <v>644.60751992113103</v>
-      </c>
-      <c r="BI18" s="1">
+        <v>362.64061926833404</v>
+      </c>
+      <c r="DU18" s="1">
         <f t="shared" si="170"/>
-        <v>638.16144472191968</v>
-      </c>
-      <c r="BJ18" s="1">
+        <v>359.01421307565067</v>
+      </c>
+      <c r="DV18" s="1">
         <f t="shared" si="170"/>
-        <v>631.77983027470043</v>
-      </c>
-      <c r="BK18" s="1">
+        <v>355.42407094489414</v>
+      </c>
+      <c r="DW18" s="1">
         <f t="shared" si="170"/>
-        <v>625.46203197195337</v>
-      </c>
-      <c r="BL18" s="1">
+        <v>351.86983023544519</v>
+      </c>
+      <c r="DX18" s="1">
         <f t="shared" si="170"/>
-        <v>619.20741165223387</v>
-      </c>
-      <c r="BM18" s="1">
+        <v>348.35113193309076</v>
+      </c>
+      <c r="DY18" s="1">
         <f t="shared" si="170"/>
-        <v>613.01533753571152</v>
-      </c>
-      <c r="BN18" s="1">
+        <v>344.86762061375987</v>
+      </c>
+      <c r="DZ18" s="1">
         <f t="shared" si="170"/>
-        <v>606.88518416035436</v>
-      </c>
-      <c r="BO18" s="1">
+        <v>341.41894440762229</v>
+      </c>
+      <c r="EA18" s="1">
         <f t="shared" si="170"/>
-        <v>600.81633231875082</v>
-      </c>
-      <c r="BP18" s="1">
+        <v>338.00475496354608</v>
+      </c>
+      <c r="EB18" s="1">
         <f t="shared" si="170"/>
-        <v>594.80816899556328</v>
-      </c>
-      <c r="BQ18" s="1">
+        <v>334.62470741391058</v>
+      </c>
+      <c r="EC18" s="1">
         <f t="shared" si="170"/>
-        <v>588.86008730560764</v>
-      </c>
-      <c r="BR18" s="1">
+        <v>331.27846033977147</v>
+      </c>
+      <c r="ED18" s="1">
         <f t="shared" si="170"/>
-        <v>582.9714864325515</v>
-      </c>
-      <c r="BS18" s="1">
+        <v>327.96567573637373</v>
+      </c>
+      <c r="EE18" s="1">
         <f t="shared" si="170"/>
-        <v>577.14177156822598</v>
-      </c>
-      <c r="BT18" s="1">
+        <v>324.68601897900999</v>
+      </c>
+      <c r="EF18" s="1">
         <f t="shared" si="170"/>
-        <v>571.37035385254376</v>
-      </c>
-      <c r="BU18" s="1">
+        <v>321.4391587892199</v>
+      </c>
+      <c r="EG18" s="1">
         <f t="shared" si="170"/>
-        <v>565.65665031401829</v>
-      </c>
-      <c r="BV18" s="1">
+        <v>318.22476720132772</v>
+      </c>
+      <c r="EH18" s="1">
         <f t="shared" si="170"/>
-        <v>560.0000838108781</v>
-      </c>
-      <c r="BW18" s="1">
+        <v>315.04251952931446</v>
+      </c>
+      <c r="EI18" s="1">
         <f t="shared" si="170"/>
-        <v>554.40008297276927</v>
-      </c>
-      <c r="BX18" s="1">
+        <v>311.89209433402129</v>
+      </c>
+      <c r="EJ18" s="1">
         <f t="shared" si="170"/>
-        <v>548.85608214304159</v>
-      </c>
-      <c r="BY18" s="1">
+        <v>308.77317339068105</v>
+      </c>
+      <c r="EK18" s="1">
         <f t="shared" si="170"/>
-        <v>543.36752132161121</v>
-      </c>
-      <c r="BZ18" s="1">
+        <v>305.68544165677423</v>
+      </c>
+      <c r="EL18" s="1">
         <f t="shared" si="170"/>
-        <v>537.93384610839507</v>
-      </c>
-      <c r="CA18" s="1">
+        <v>302.62858724020651</v>
+      </c>
+      <c r="EM18" s="1">
         <f t="shared" si="170"/>
-        <v>532.55450764731108</v>
-      </c>
-      <c r="CB18" s="1">
+        <v>299.60230136780444</v>
+      </c>
+      <c r="EN18" s="1">
         <f t="shared" si="170"/>
-        <v>527.22896257083801</v>
-      </c>
-      <c r="CC18" s="1">
+        <v>296.6062783541264</v>
+      </c>
+      <c r="EO18" s="1">
         <f t="shared" si="170"/>
-        <v>521.95667294512964</v>
-      </c>
-      <c r="CD18" s="1">
+        <v>293.64021557058516</v>
+      </c>
+      <c r="EP18" s="1">
         <f t="shared" si="170"/>
-        <v>516.7371062156783</v>
-      </c>
-      <c r="CE18" s="1">
+        <v>290.70381341487928</v>
+      </c>
+      <c r="EQ18" s="1">
         <f t="shared" si="170"/>
-        <v>511.56973515352149</v>
-      </c>
-      <c r="CF18" s="1">
+        <v>287.79677528073046</v>
+      </c>
+      <c r="ER18" s="1">
         <f t="shared" si="170"/>
-        <v>506.45403780198626</v>
-      </c>
-      <c r="CG18" s="1">
+        <v>284.91880752792315</v>
+      </c>
+      <c r="ES18" s="1">
         <f t="shared" si="170"/>
-        <v>501.38949742396642</v>
-      </c>
-      <c r="CH18" s="1">
+        <v>282.06961945264391</v>
+      </c>
+      <c r="ET18" s="1">
         <f t="shared" si="170"/>
-        <v>496.37560244972673</v>
-      </c>
-      <c r="CI18" s="1">
+        <v>279.24892325811749</v>
+      </c>
+      <c r="EU18" s="1">
         <f t="shared" si="170"/>
-        <v>491.41184642522944</v>
-      </c>
-      <c r="CJ18" s="1">
+        <v>276.45643402553628</v>
+      </c>
+      <c r="EV18" s="1">
         <f t="shared" si="170"/>
-        <v>486.49772796097716</v>
-      </c>
-      <c r="CK18" s="1">
+        <v>273.69186968528089</v>
+      </c>
+      <c r="EW18" s="1">
         <f t="shared" si="170"/>
-        <v>481.63275068136738</v>
-      </c>
-      <c r="CL18" s="1">
+        <v>270.9549509884281</v>
+      </c>
+      <c r="EX18" s="1">
         <f t="shared" si="170"/>
-        <v>476.81642317455373</v>
-      </c>
-      <c r="CM18" s="1">
+        <v>268.24540147854378</v>
+      </c>
+      <c r="EY18" s="1">
         <f t="shared" si="170"/>
-        <v>472.04825894280822</v>
-      </c>
-      <c r="CN18" s="1">
+        <v>265.56294746375835</v>
+      </c>
+      <c r="EZ18" s="1">
         <f t="shared" si="170"/>
-        <v>467.32777635338016</v>
-      </c>
-      <c r="CO18" s="1">
+        <v>262.90731798912077</v>
+      </c>
+      <c r="FA18" s="1">
         <f t="shared" si="170"/>
-        <v>462.65449858984636</v>
-      </c>
-      <c r="CP18" s="1">
+        <v>260.27824480922953</v>
+      </c>
+      <c r="FB18" s="1">
         <f t="shared" si="170"/>
-        <v>458.02795360394788</v>
-      </c>
-      <c r="CQ18" s="1">
+        <v>257.67546236113725</v>
+      </c>
+      <c r="FC18" s="1">
         <f t="shared" si="170"/>
-        <v>453.44767406790839</v>
-      </c>
-      <c r="CR18" s="1">
+        <v>255.09870773752587</v>
+      </c>
+      <c r="FD18" s="1">
         <f t="shared" si="170"/>
-        <v>448.91319732722928</v>
-      </c>
-      <c r="CS18" s="1">
+        <v>252.54772066015062</v>
+      </c>
+      <c r="FE18" s="1">
         <f t="shared" si="170"/>
-        <v>444.42406535395696</v>
-      </c>
-      <c r="CT18" s="1">
+        <v>250.02224345354909</v>
+      </c>
+      <c r="FF18" s="1">
         <f t="shared" si="170"/>
-        <v>439.9798247004174</v>
-      </c>
-      <c r="CU18" s="1">
+        <v>247.52202101901361</v>
+      </c>
+      <c r="FG18" s="1">
         <f t="shared" si="170"/>
-        <v>435.58002645341321</v>
-      </c>
-      <c r="CV18" s="1">
-        <f t="shared" si="170"/>
-        <v>431.22422618887907</v>
-      </c>
-      <c r="CW18" s="1">
-        <f t="shared" si="170"/>
-        <v>426.91198392699027</v>
-      </c>
-      <c r="CX18" s="1">
-        <f t="shared" si="170"/>
-        <v>422.64286408772034</v>
-      </c>
-      <c r="CY18" s="1">
-        <f t="shared" si="170"/>
-        <v>418.41643544684314</v>
-      </c>
-      <c r="CZ18" s="1">
-        <f t="shared" si="170"/>
-        <v>414.23227109237473</v>
-      </c>
-      <c r="DA18" s="1">
-        <f t="shared" si="170"/>
-        <v>410.08994838145099</v>
-      </c>
-      <c r="DB18" s="1">
-        <f t="shared" si="170"/>
-        <v>405.98904889763651</v>
-      </c>
-      <c r="DC18" s="1">
-        <f t="shared" si="170"/>
-        <v>401.92915840866016</v>
-      </c>
-      <c r="DD18" s="1">
-        <f t="shared" si="170"/>
-        <v>397.90986682457356</v>
-      </c>
-      <c r="DE18" s="1">
-        <f t="shared" si="170"/>
-        <v>393.93076815632782</v>
-      </c>
-      <c r="DF18" s="1">
-        <f t="shared" si="170"/>
-        <v>389.99146047476455</v>
-      </c>
-      <c r="DG18" s="1">
-        <f t="shared" si="170"/>
-        <v>386.09154587001689</v>
-      </c>
-      <c r="DH18" s="1">
-        <f t="shared" si="170"/>
-        <v>382.23063041131672</v>
-      </c>
-      <c r="DI18" s="1">
-        <f t="shared" si="170"/>
-        <v>378.40832410720355</v>
-      </c>
-      <c r="DJ18" s="1">
-        <f t="shared" si="170"/>
-        <v>374.62424086613152</v>
-      </c>
-      <c r="DK18" s="1">
-        <f t="shared" si="170"/>
-        <v>370.8779984574702</v>
-      </c>
-      <c r="DL18" s="1">
-        <f t="shared" si="170"/>
-        <v>367.16921847289547</v>
-      </c>
-      <c r="DM18" s="1">
-        <f t="shared" si="170"/>
-        <v>363.49752628816651</v>
-      </c>
-      <c r="DN18" s="1">
-        <f t="shared" si="170"/>
-        <v>359.86255102528486</v>
-      </c>
-      <c r="DO18" s="1">
-        <f t="shared" ref="DO18:FG18" si="171">DN18*(1+$BD$25)</f>
-        <v>356.26392551503199</v>
-      </c>
-      <c r="DP18" s="1">
-        <f t="shared" si="171"/>
-        <v>352.70128625988167</v>
-      </c>
-      <c r="DQ18" s="1">
-        <f t="shared" si="171"/>
-        <v>349.17427339728283</v>
-      </c>
-      <c r="DR18" s="1">
-        <f t="shared" si="171"/>
-        <v>345.68253066330999</v>
-      </c>
-      <c r="DS18" s="1">
-        <f t="shared" si="171"/>
-        <v>342.22570535667688</v>
-      </c>
-      <c r="DT18" s="1">
-        <f t="shared" si="171"/>
-        <v>338.80344830311009</v>
-      </c>
-      <c r="DU18" s="1">
-        <f t="shared" si="171"/>
-        <v>335.41541382007898</v>
-      </c>
-      <c r="DV18" s="1">
-        <f t="shared" si="171"/>
-        <v>332.0612596818782</v>
-      </c>
-      <c r="DW18" s="1">
-        <f t="shared" si="171"/>
-        <v>328.74064708505944</v>
-      </c>
-      <c r="DX18" s="1">
-        <f t="shared" si="171"/>
-        <v>325.45324061420882</v>
-      </c>
-      <c r="DY18" s="1">
-        <f t="shared" si="171"/>
-        <v>322.19870820806671</v>
-      </c>
-      <c r="DZ18" s="1">
-        <f t="shared" si="171"/>
-        <v>318.97672112598605</v>
-      </c>
-      <c r="EA18" s="1">
-        <f t="shared" si="171"/>
-        <v>315.78695391472615</v>
-      </c>
-      <c r="EB18" s="1">
-        <f t="shared" si="171"/>
-        <v>312.62908437557888</v>
-      </c>
-      <c r="EC18" s="1">
-        <f t="shared" si="171"/>
-        <v>309.5027935318231</v>
-      </c>
-      <c r="ED18" s="1">
-        <f t="shared" si="171"/>
-        <v>306.40776559650487</v>
-      </c>
-      <c r="EE18" s="1">
-        <f t="shared" si="171"/>
-        <v>303.34368794053984</v>
-      </c>
-      <c r="EF18" s="1">
-        <f t="shared" si="171"/>
-        <v>300.31025106113441</v>
-      </c>
-      <c r="EG18" s="1">
-        <f t="shared" si="171"/>
-        <v>297.30714855052304</v>
-      </c>
-      <c r="EH18" s="1">
-        <f t="shared" si="171"/>
-        <v>294.33407706501782</v>
-      </c>
-      <c r="EI18" s="1">
-        <f t="shared" si="171"/>
-        <v>291.39073629436763</v>
-      </c>
-      <c r="EJ18" s="1">
-        <f t="shared" si="171"/>
-        <v>288.47682893142394</v>
-      </c>
-      <c r="EK18" s="1">
-        <f t="shared" si="171"/>
-        <v>285.59206064210969</v>
-      </c>
-      <c r="EL18" s="1">
-        <f t="shared" si="171"/>
-        <v>282.73614003568861</v>
-      </c>
-      <c r="EM18" s="1">
-        <f t="shared" si="171"/>
-        <v>279.90877863533171</v>
-      </c>
-      <c r="EN18" s="1">
-        <f t="shared" si="171"/>
-        <v>277.1096908489784</v>
-      </c>
-      <c r="EO18" s="1">
-        <f t="shared" si="171"/>
-        <v>274.33859394048864</v>
-      </c>
-      <c r="EP18" s="1">
-        <f t="shared" si="171"/>
-        <v>271.59520800108373</v>
-      </c>
-      <c r="EQ18" s="1">
-        <f t="shared" si="171"/>
-        <v>268.87925592107291</v>
-      </c>
-      <c r="ER18" s="1">
-        <f t="shared" si="171"/>
-        <v>266.19046336186216</v>
-      </c>
-      <c r="ES18" s="1">
-        <f t="shared" si="171"/>
-        <v>263.52855872824352</v>
-      </c>
-      <c r="ET18" s="1">
-        <f t="shared" si="171"/>
-        <v>260.89327314096107</v>
-      </c>
-      <c r="EU18" s="1">
-        <f t="shared" si="171"/>
-        <v>258.28434040955148</v>
-      </c>
-      <c r="EV18" s="1">
-        <f t="shared" si="171"/>
-        <v>255.70149700545596</v>
-      </c>
-      <c r="EW18" s="1">
-        <f t="shared" si="171"/>
-        <v>253.14448203540141</v>
-      </c>
-      <c r="EX18" s="1">
-        <f t="shared" si="171"/>
-        <v>250.6130372150474</v>
-      </c>
-      <c r="EY18" s="1">
-        <f t="shared" si="171"/>
-        <v>248.10690684289693</v>
-      </c>
-      <c r="EZ18" s="1">
-        <f t="shared" si="171"/>
-        <v>245.62583777446795</v>
-      </c>
-      <c r="FA18" s="1">
-        <f t="shared" si="171"/>
-        <v>243.16957939672326</v>
-      </c>
-      <c r="FB18" s="1">
-        <f t="shared" si="171"/>
-        <v>240.73788360275603</v>
-      </c>
-      <c r="FC18" s="1">
-        <f t="shared" si="171"/>
-        <v>238.33050476672847</v>
-      </c>
-      <c r="FD18" s="1">
-        <f t="shared" si="171"/>
-        <v>235.94719971906119</v>
-      </c>
-      <c r="FE18" s="1">
-        <f t="shared" si="171"/>
-        <v>233.58772772187058</v>
-      </c>
-      <c r="FF18" s="1">
-        <f t="shared" si="171"/>
-        <v>231.25185044465186</v>
-      </c>
-      <c r="FG18" s="1">
-        <f t="shared" si="171"/>
-        <v>228.93933194020534</v>
+        <v>245.04680080882346</v>
       </c>
     </row>
     <row r="19" spans="2:163" x14ac:dyDescent="0.3">
@@ -4612,12 +4600,12 @@
         <v>146.9</v>
       </c>
       <c r="AG19" s="5">
-        <f>146.9</f>
-        <v>146.9</v>
+        <f>147.5</f>
+        <v>147.5</v>
       </c>
       <c r="AH19" s="5">
-        <f>146.9</f>
-        <v>146.9</v>
+        <f>147.5</f>
+        <v>147.5</v>
       </c>
       <c r="AJ19">
         <v>125</v>
@@ -4638,52 +4626,52 @@
         <v>125</v>
       </c>
       <c r="AP19" s="5">
-        <f t="shared" ref="AP19" si="172">128.7+17.2</f>
+        <f t="shared" ref="AP19" si="171">128.7+17.2</f>
         <v>145.89999999999998</v>
       </c>
       <c r="AQ19" s="5">
-        <f>146.9</f>
-        <v>146.9</v>
+        <f>147.5</f>
+        <v>147.5</v>
       </c>
       <c r="AR19" s="5">
-        <f>146.9</f>
-        <v>146.9</v>
+        <f>147.5</f>
+        <v>147.5</v>
       </c>
       <c r="AS19" s="5">
-        <f>146.9</f>
-        <v>146.9</v>
+        <f>147.5</f>
+        <v>147.5</v>
       </c>
       <c r="AT19" s="5">
-        <f>146.9</f>
-        <v>146.9</v>
+        <f>147.5</f>
+        <v>147.5</v>
       </c>
       <c r="AU19" s="5">
-        <f>146.9</f>
-        <v>146.9</v>
+        <f>147.5</f>
+        <v>147.5</v>
       </c>
       <c r="AV19" s="5">
-        <f>146.9</f>
-        <v>146.9</v>
+        <f>147.5</f>
+        <v>147.5</v>
       </c>
       <c r="AW19" s="5">
-        <f>146.9</f>
-        <v>146.9</v>
+        <f>147.5</f>
+        <v>147.5</v>
       </c>
       <c r="AX19" s="5">
-        <f>146.9</f>
-        <v>146.9</v>
+        <f>147.5</f>
+        <v>147.5</v>
       </c>
       <c r="AY19" s="5">
-        <f>146.9</f>
-        <v>146.9</v>
+        <f>147.5</f>
+        <v>147.5</v>
       </c>
       <c r="AZ19" s="5">
-        <f>146.9</f>
-        <v>146.9</v>
+        <f>147.5</f>
+        <v>147.5</v>
       </c>
       <c r="BA19" s="5">
-        <f>146.9</f>
-        <v>146.9</v>
+        <f>147.5</f>
+        <v>147.5</v>
       </c>
     </row>
     <row r="20" spans="2:163" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4691,204 +4679,204 @@
         <v>37</v>
       </c>
       <c r="C20" s="6">
-        <f t="shared" ref="C20:L20" si="173">C18/C19</f>
+        <f t="shared" ref="C20:L20" si="172">C18/C19</f>
         <v>-5.2800000000000041E-2</v>
       </c>
       <c r="D20" s="6">
+        <f t="shared" si="172"/>
+        <v>4.8000000000000464E-3</v>
+      </c>
+      <c r="E20" s="6">
+        <f t="shared" si="172"/>
+        <v>-7.6000000000000206E-2</v>
+      </c>
+      <c r="F20" s="6">
+        <f t="shared" si="172"/>
+        <v>5.4399999999999886E-2</v>
+      </c>
+      <c r="G20" s="6">
+        <f t="shared" si="172"/>
+        <v>-7.7600000000000141E-2</v>
+      </c>
+      <c r="H20" s="6">
+        <f t="shared" si="172"/>
+        <v>-7.5680000000000053E-2</v>
+      </c>
+      <c r="I20" s="6">
+        <f t="shared" si="172"/>
+        <v>-0.19680000000000011</v>
+      </c>
+      <c r="J20" s="6">
+        <f t="shared" si="172"/>
+        <v>-0.12479999999999963</v>
+      </c>
+      <c r="K20" s="6">
+        <f t="shared" si="172"/>
+        <v>-0.43519999999999998</v>
+      </c>
+      <c r="L20" s="6">
+        <f t="shared" si="172"/>
+        <v>-0.34479999999999988</v>
+      </c>
+      <c r="M20" s="6">
+        <f t="shared" ref="M20:AL20" si="173">M18/M19</f>
+        <v>0.10560000000000032</v>
+      </c>
+      <c r="N20" s="6">
         <f t="shared" si="173"/>
-        <v>4.8000000000000464E-3</v>
-      </c>
-      <c r="E20" s="6">
+        <v>0.53879999999999995</v>
+      </c>
+      <c r="O20" s="6">
+        <f t="shared" ref="O20:R20" si="174">O18/O19</f>
+        <v>0.6104000000000005</v>
+      </c>
+      <c r="P20" s="6">
+        <f t="shared" ref="P20:Q20" si="175">P18/P19</f>
+        <v>0.51148225469728537</v>
+      </c>
+      <c r="Q20" s="6">
+        <f t="shared" si="175"/>
+        <v>0.47947112038970047</v>
+      </c>
+      <c r="R20" s="6">
+        <f t="shared" si="174"/>
+        <v>0.16492693110647152</v>
+      </c>
+      <c r="S20" s="6">
+        <f t="shared" ref="S20:T20" si="176">S18/S19</f>
+        <v>-0.18371607515657659</v>
+      </c>
+      <c r="T20" s="6">
+        <f t="shared" si="176"/>
+        <v>-0.78218510786360518</v>
+      </c>
+      <c r="U20" s="6">
+        <f t="shared" ref="U20" si="177">U18/U19</f>
+        <v>-0.85107863604732048</v>
+      </c>
+      <c r="V20" s="6">
+        <f t="shared" ref="V20" si="178">V18/V19</f>
+        <v>-1.650661099512875</v>
+      </c>
+      <c r="W20" s="6">
+        <f t="shared" ref="W20:X20" si="179">W18/W19</f>
+        <v>-1.3437717466945029</v>
+      </c>
+      <c r="X20" s="6">
+        <f t="shared" si="179"/>
+        <v>-0.74808629088378598</v>
+      </c>
+      <c r="Y20" s="6">
+        <f t="shared" ref="Y20" si="180">Y18/Y19</f>
+        <v>-2.2971468336812806</v>
+      </c>
+      <c r="Z20" s="6">
+        <f t="shared" ref="Z20:AA20" si="181">Z18/Z19</f>
+        <v>-0.54418928322894933</v>
+      </c>
+      <c r="AA20" s="6">
+        <f t="shared" si="181"/>
+        <v>-0.35351426583159401</v>
+      </c>
+      <c r="AB20" s="6">
+        <f t="shared" ref="AB20:AD20" si="182">AB18/AB19</f>
+        <v>-0.23729993041057826</v>
+      </c>
+      <c r="AC20" s="6">
+        <f t="shared" si="182"/>
+        <v>-6.1421670117321039E-2</v>
+      </c>
+      <c r="AD20" s="6">
+        <f t="shared" si="182"/>
+        <v>-0.24400274160383781</v>
+      </c>
+      <c r="AE20" s="6">
+        <f t="shared" ref="AE20:AH20" si="183">AE18/AE19</f>
+        <v>-0.18690313778990478</v>
+      </c>
+      <c r="AF20" s="6">
+        <f t="shared" si="183"/>
+        <v>7.1477195371000224E-2</v>
+      </c>
+      <c r="AG20" s="6">
+        <f t="shared" si="183"/>
+        <v>0.16813559322033883</v>
+      </c>
+      <c r="AH20" s="6">
+        <f t="shared" si="183"/>
+        <v>0.2833163932203388</v>
+      </c>
+      <c r="AJ20" s="6">
         <f t="shared" si="173"/>
-        <v>-7.6000000000000206E-2</v>
-      </c>
-      <c r="F20" s="6">
+        <v>-6.9600000000000092E-2</v>
+      </c>
+      <c r="AK20" s="6">
         <f t="shared" si="173"/>
-        <v>5.4399999999999886E-2</v>
-      </c>
-      <c r="G20" s="6">
+        <v>-0.47487999999999925</v>
+      </c>
+      <c r="AL20" s="6">
         <f t="shared" si="173"/>
-        <v>-7.7600000000000141E-2</v>
-      </c>
-      <c r="H20" s="6">
-        <f t="shared" si="173"/>
-        <v>-7.5680000000000053E-2</v>
-      </c>
-      <c r="I20" s="6">
-        <f t="shared" si="173"/>
-        <v>-0.19680000000000011</v>
-      </c>
-      <c r="J20" s="6">
-        <f t="shared" si="173"/>
-        <v>-0.12479999999999963</v>
-      </c>
-      <c r="K20" s="6">
-        <f t="shared" si="173"/>
-        <v>-0.43519999999999998</v>
-      </c>
-      <c r="L20" s="6">
-        <f t="shared" si="173"/>
-        <v>-0.34479999999999988</v>
-      </c>
-      <c r="M20" s="6">
-        <f t="shared" ref="M20:AL20" si="174">M18/M19</f>
-        <v>0.10560000000000032</v>
-      </c>
-      <c r="N20" s="6">
-        <f t="shared" si="174"/>
-        <v>0.53879999999999995</v>
-      </c>
-      <c r="O20" s="6">
-        <f t="shared" ref="O20:R20" si="175">O18/O19</f>
-        <v>0.6104000000000005</v>
-      </c>
-      <c r="P20" s="6">
-        <f t="shared" ref="P20:Q20" si="176">P18/P19</f>
-        <v>0.51148225469728537</v>
-      </c>
-      <c r="Q20" s="6">
-        <f t="shared" si="176"/>
-        <v>0.47947112038970047</v>
-      </c>
-      <c r="R20" s="6">
-        <f t="shared" si="175"/>
-        <v>0.16492693110647152</v>
-      </c>
-      <c r="S20" s="6">
-        <f t="shared" ref="S20:T20" si="177">S18/S19</f>
-        <v>-0.18371607515657659</v>
-      </c>
-      <c r="T20" s="6">
-        <f t="shared" si="177"/>
-        <v>-0.78218510786360518</v>
-      </c>
-      <c r="U20" s="6">
-        <f t="shared" ref="U20" si="178">U18/U19</f>
-        <v>-0.85107863604732048</v>
-      </c>
-      <c r="V20" s="6">
-        <f t="shared" ref="V20" si="179">V18/V19</f>
-        <v>-1.650661099512875</v>
-      </c>
-      <c r="W20" s="6">
-        <f t="shared" ref="W20:X20" si="180">W18/W19</f>
-        <v>-1.3437717466945029</v>
-      </c>
-      <c r="X20" s="6">
-        <f t="shared" si="180"/>
-        <v>-0.74808629088378598</v>
-      </c>
-      <c r="Y20" s="6">
-        <f t="shared" ref="Y20" si="181">Y18/Y19</f>
-        <v>-2.2971468336812806</v>
-      </c>
-      <c r="Z20" s="6">
-        <f t="shared" ref="Z20:AA20" si="182">Z18/Z19</f>
-        <v>-0.54418928322894933</v>
-      </c>
-      <c r="AA20" s="6">
-        <f t="shared" si="182"/>
-        <v>-0.35351426583159401</v>
-      </c>
-      <c r="AB20" s="6">
-        <f t="shared" ref="AB20:AD20" si="183">AB18/AB19</f>
-        <v>-0.23729993041057826</v>
-      </c>
-      <c r="AC20" s="6">
-        <f t="shared" si="183"/>
-        <v>-6.1421670117321039E-2</v>
-      </c>
-      <c r="AD20" s="6">
-        <f t="shared" si="183"/>
-        <v>-0.24400274160383781</v>
-      </c>
-      <c r="AE20" s="6">
-        <f t="shared" ref="AE20:AH20" si="184">AE18/AE19</f>
-        <v>-0.18690313778990478</v>
-      </c>
-      <c r="AF20" s="6">
-        <f t="shared" si="184"/>
-        <v>7.1477195371000224E-2</v>
-      </c>
-      <c r="AG20" s="6">
-        <f t="shared" si="184"/>
-        <v>0.10275681415929137</v>
-      </c>
-      <c r="AH20" s="6">
-        <f t="shared" si="184"/>
-        <v>0.11976408441116394</v>
-      </c>
-      <c r="AJ20" s="6">
-        <f t="shared" si="174"/>
-        <v>-6.9600000000000092E-2</v>
-      </c>
-      <c r="AK20" s="6">
-        <f t="shared" si="174"/>
-        <v>-0.47487999999999925</v>
-      </c>
-      <c r="AL20" s="6">
-        <f t="shared" si="174"/>
         <v>-0.13560000000000036</v>
       </c>
       <c r="AM20" s="6">
-        <f t="shared" ref="AM20" si="185">AM18/AM19</f>
+        <f t="shared" ref="AM20" si="184">AM18/AM19</f>
         <v>1.9391999999999983</v>
       </c>
       <c r="AN20" s="6">
-        <f t="shared" ref="AN20" si="186">AN18/AN19</f>
+        <f t="shared" ref="AN20" si="185">AN18/AN19</f>
         <v>-3.9864000000000028</v>
       </c>
       <c r="AO20" s="6">
-        <f t="shared" ref="AO20" si="187">AO18/AO19</f>
+        <f t="shared" ref="AO20" si="186">AO18/AO19</f>
         <v>-5.671199999999998</v>
       </c>
       <c r="AP20" s="6">
-        <f t="shared" ref="AP20" si="188">AP18/AP19</f>
+        <f t="shared" ref="AP20" si="187">AP18/AP19</f>
         <v>-0.88690884167237971</v>
       </c>
       <c r="AQ20" s="6">
-        <f t="shared" ref="AQ20" si="189">AQ18/AQ19</f>
-        <v>0.10747665078285019</v>
+        <f t="shared" ref="AQ20" si="188">AQ18/AQ19</f>
+        <v>0.33687571525423554</v>
       </c>
       <c r="AR20" s="6">
-        <f t="shared" ref="AR20" si="190">AR18/AR19</f>
-        <v>1.5964734181075575</v>
+        <f t="shared" ref="AR20" si="189">AR18/AR19</f>
+        <v>1.4554185068474605</v>
       </c>
       <c r="AS20" s="6">
-        <f t="shared" ref="AS20" si="191">AS18/AS19</f>
-        <v>2.5997049520163369</v>
+        <f t="shared" ref="AS20" si="190">AS18/AS19</f>
+        <v>2.7133794893233909</v>
       </c>
       <c r="AT20" s="6">
-        <f t="shared" ref="AT20" si="192">AT18/AT19</f>
-        <v>3.4521703226083584</v>
+        <f t="shared" ref="AT20" si="191">AT18/AT19</f>
+        <v>3.5729873172725171</v>
       </c>
       <c r="AU20" s="6">
-        <f t="shared" ref="AU20" si="193">AU18/AU19</f>
-        <v>3.7695515903250549</v>
+        <f t="shared" ref="AU20" si="192">AU18/AU19</f>
+        <v>3.9192737698382172</v>
       </c>
       <c r="AV20" s="6">
-        <f t="shared" ref="AV20:AW20" si="194">AV18/AV19</f>
-        <v>3.9974373061299664</v>
+        <f t="shared" ref="AV20:AW20" si="193">AV18/AV19</f>
+        <v>4.1772668684964263</v>
       </c>
       <c r="AW20" s="6">
+        <f t="shared" si="193"/>
+        <v>4.3372065748898567</v>
+      </c>
+      <c r="AX20" s="6">
+        <f t="shared" ref="AX20:BA20" si="194">AX18/AX19</f>
+        <v>4.5012187161376707</v>
+      </c>
+      <c r="AY20" s="6">
         <f t="shared" si="194"/>
-        <v>4.1326334514754022</v>
-      </c>
-      <c r="AX20" s="6">
-        <f t="shared" ref="AX20:BA20" si="195">AX18/AX19</f>
-        <v>4.2711994330679719</v>
-      </c>
-      <c r="AY20" s="6">
-        <f t="shared" si="195"/>
-        <v>4.413212709946464</v>
+        <v>4.6693967682553099</v>
       </c>
       <c r="AZ20" s="6">
-        <f t="shared" si="195"/>
-        <v>4.5587524930489929</v>
+        <f t="shared" si="194"/>
+        <v>4.8418362957790473</v>
       </c>
       <c r="BA20" s="6">
-        <f t="shared" si="195"/>
-        <v>4.7078997853410316</v>
+        <f t="shared" si="194"/>
+        <v>5.0186349986882082</v>
       </c>
     </row>
     <row r="22" spans="2:163" x14ac:dyDescent="0.3">
@@ -4896,116 +4884,116 @@
         <v>45</v>
       </c>
       <c r="G22" s="9">
-        <f t="shared" ref="G22:N22" si="196">G3/C3-1</f>
+        <f t="shared" ref="G22:N22" si="195">G3/C3-1</f>
         <v>0.78695073235685742</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" si="196"/>
+        <f t="shared" si="195"/>
         <v>0.85714285714285698</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" si="196"/>
+        <f t="shared" si="195"/>
         <v>0.79120879120879151</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="196"/>
+        <f t="shared" si="195"/>
         <v>0.71466314398943198</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="196"/>
+        <f t="shared" si="195"/>
         <v>0.73323397913561861</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" si="196"/>
+        <f t="shared" si="195"/>
         <v>0.45974955277280882</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="196"/>
+        <f t="shared" si="195"/>
         <v>0.78025655326268795</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="196"/>
+        <f t="shared" si="195"/>
         <v>0.8151001540832048</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" ref="O22:O24" si="197">O3/K3-1</f>
+        <f t="shared" ref="O22:O24" si="196">O3/K3-1</f>
         <v>1.0055889939810836</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" ref="P22:P24" si="198">P3/L3-1</f>
+        <f t="shared" ref="P22:P24" si="197">P3/L3-1</f>
         <v>1.174428104575163</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" ref="Q22:Q24" si="199">Q3/M3-1</f>
+        <f t="shared" ref="Q22:Q24" si="198">Q3/M3-1</f>
         <v>0.82487468671679198</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" ref="R22:R24" si="200">R3/N3-1</f>
+        <f t="shared" ref="R22:R24" si="199">R3/N3-1</f>
         <v>0.49320882852292036</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" ref="S22:S24" si="201">S3/O3-1</f>
+        <f t="shared" ref="S22:S24" si="200">S3/O3-1</f>
         <v>0.38670953912111461</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" ref="T22:T24" si="202">T3/P3-1</f>
+        <f t="shared" ref="T22:T24" si="201">T3/P3-1</f>
         <v>0.25737366146909646</v>
       </c>
       <c r="U22" s="9">
-        <f t="shared" ref="U22:U24" si="203">U3/Q3-1</f>
+        <f t="shared" ref="U22:U24" si="202">U3/Q3-1</f>
         <v>0.14540772532188839</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" ref="V22:V24" si="204">V3/R3-1</f>
+        <f t="shared" ref="V22:V24" si="203">V3/R3-1</f>
         <v>3.9368959636156831E-2</v>
       </c>
       <c r="W22" s="9">
-        <f t="shared" ref="W22:W24" si="205">W3/S3-1</f>
+        <f t="shared" ref="W22:W24" si="204">W3/S3-1</f>
         <v>-1.9013757922399011E-2</v>
       </c>
       <c r="X22" s="9">
-        <f t="shared" ref="X22:X24" si="206">X3/T3-1</f>
+        <f t="shared" ref="X22:X24" si="205">X3/T3-1</f>
         <v>0.11145973405050058</v>
       </c>
       <c r="Y22" s="9">
-        <f t="shared" ref="Y22:Y24" si="207">Y3/U3-1</f>
+        <f t="shared" ref="Y22:Y24" si="206">Y3/U3-1</f>
         <v>0.1792565947242204</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" ref="Z22:Z24" si="208">Z3/V3-1</f>
+        <f t="shared" ref="Z22:Z24" si="207">Z3/V3-1</f>
         <v>0.13346095993436347</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" ref="AA22:AA24" si="209">AA3/W3-1</f>
+        <f t="shared" ref="AA22:AA24" si="208">AA3/W3-1</f>
         <v>0.18956823195713834</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" ref="AB22:AB24" si="210">AB3/X3-1</f>
+        <f t="shared" ref="AB22:AB24" si="209">AB3/X3-1</f>
         <v>0.10807904288210768</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" ref="AC22:AC24" si="211">AC3/Y3-1</f>
+        <f t="shared" ref="AC22:AC24" si="210">AC3/Y3-1</f>
         <v>0.15429588205388933</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" ref="AD22:AD24" si="212">AD3/Z3-1</f>
+        <f t="shared" ref="AD22:AD24" si="211">AD3/Z3-1</f>
         <v>0.24900470503076355</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" ref="AE22:AE24" si="213">AE3/AA3-1</f>
+        <f t="shared" ref="AE22:AE24" si="212">AE3/AA3-1</f>
         <v>0.16677705656378317</v>
       </c>
       <c r="AF22" s="9">
-        <f t="shared" ref="AF22:AF24" si="214">AF3/AB3-1</f>
+        <f t="shared" ref="AF22:AF24" si="213">AF3/AB3-1</f>
         <v>0.18342836345990543</v>
       </c>
       <c r="AG22" s="9">
-        <f t="shared" ref="AG22:AG24" si="215">AG3/AC3-1</f>
-        <v>0.12999999999999967</v>
+        <f t="shared" ref="AG22:AG24" si="214">AG3/AC3-1</f>
+        <v>0.17220876458929735</v>
       </c>
       <c r="AH22" s="9">
-        <f t="shared" ref="AH22:AH24" si="216">AH3/AD3-1</f>
-        <v>0.1100000000000001</v>
+        <f t="shared" ref="AH22:AH24" si="215">AH3/AD3-1</f>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AK22" s="9">
         <f>AK3/AJ3-1</f>
@@ -5016,63 +5004,63 @@
         <v>0.71139308855291583</v>
       </c>
       <c r="AM22" s="9">
-        <f t="shared" ref="AM22:AW22" si="217">AM3/AL3-1</f>
+        <f t="shared" ref="AM22:AW22" si="216">AM3/AL3-1</f>
         <v>0.80225587632118645</v>
       </c>
       <c r="AN22" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="216"/>
         <v>0.1881045122324827</v>
       </c>
       <c r="AO22" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="216"/>
         <v>0.10295796957306536</v>
       </c>
       <c r="AP22" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="216"/>
         <v>0.17650791530291876</v>
       </c>
       <c r="AQ22" s="9">
-        <f t="shared" si="217"/>
-        <v>0.14450535100916917</v>
+        <f t="shared" si="216"/>
+        <v>0.16714310046271308</v>
       </c>
       <c r="AR22" s="9">
-        <f t="shared" si="217"/>
-        <v>0.1100000000000001</v>
+        <f t="shared" si="216"/>
+        <v>0.12000000000000011</v>
       </c>
       <c r="AS22" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="216"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AT22" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="216"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AU22" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="216"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AV22" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="216"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AW22" s="9">
-        <f t="shared" si="217"/>
+        <f t="shared" si="216"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AX22" s="9">
-        <f t="shared" ref="AX22:AX24" si="218">AX3/AW3-1</f>
+        <f t="shared" ref="AX22:AX24" si="217">AX3/AW3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AY22" s="9">
-        <f t="shared" ref="AY22:AY24" si="219">AY3/AX3-1</f>
+        <f t="shared" ref="AY22:AY24" si="218">AY3/AX3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AZ22" s="9">
-        <f t="shared" ref="AZ22:AZ24" si="220">AZ3/AY3-1</f>
+        <f t="shared" ref="AZ22:AZ24" si="219">AZ3/AY3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BA22" s="9">
-        <f t="shared" ref="BA22:BA24" si="221">BA3/AZ3-1</f>
+        <f t="shared" ref="BA22:BA24" si="220">BA3/AZ3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -5081,183 +5069,183 @@
         <v>46</v>
       </c>
       <c r="G23" s="9">
-        <f t="shared" ref="G23:N23" si="222">G4/C4-1</f>
+        <f t="shared" ref="G23:N23" si="221">G4/C4-1</f>
         <v>0.17886178861788626</v>
       </c>
       <c r="H23" s="9">
+        <f t="shared" si="221"/>
+        <v>0.23909774436090236</v>
+      </c>
+      <c r="I23" s="9">
+        <f t="shared" si="221"/>
+        <v>0.11323328785811726</v>
+      </c>
+      <c r="J23" s="9">
+        <f t="shared" si="221"/>
+        <v>0.21962992759452926</v>
+      </c>
+      <c r="K23" s="9">
+        <f t="shared" si="221"/>
+        <v>0.21655172413793111</v>
+      </c>
+      <c r="L23" s="9">
+        <f t="shared" si="221"/>
+        <v>0.35072815533980561</v>
+      </c>
+      <c r="M23" s="9">
+        <f t="shared" si="221"/>
+        <v>0.62254901960784337</v>
+      </c>
+      <c r="N23" s="9">
+        <f t="shared" si="221"/>
+        <v>0.1787598944591029</v>
+      </c>
+      <c r="O23" s="9">
+        <f t="shared" si="196"/>
+        <v>0.22108843537414957</v>
+      </c>
+      <c r="P23" s="9">
+        <f t="shared" si="197"/>
+        <v>1.3477088948786964E-2</v>
+      </c>
+      <c r="Q23" s="9">
+        <f t="shared" si="198"/>
+        <v>-0.2643504531722054</v>
+      </c>
+      <c r="R23" s="9">
+        <f t="shared" si="199"/>
+        <v>-9.5131505316172316E-2</v>
+      </c>
+      <c r="S23" s="9">
+        <f t="shared" si="200"/>
+        <v>-0.19405756731662027</v>
+      </c>
+      <c r="T23" s="9">
+        <f t="shared" si="201"/>
+        <v>-0.15602836879432624</v>
+      </c>
+      <c r="U23" s="9">
+        <f t="shared" si="202"/>
+        <v>-3.2854209445585258E-2</v>
+      </c>
+      <c r="V23" s="9">
+        <f t="shared" si="203"/>
+        <v>-0.16017316017316008</v>
+      </c>
+      <c r="W23" s="9">
+        <f t="shared" si="204"/>
+        <v>0.22580645161290325</v>
+      </c>
+      <c r="X23" s="9">
+        <f t="shared" si="205"/>
+        <v>8.6134453781512743E-2</v>
+      </c>
+      <c r="Y23" s="9">
+        <f t="shared" si="206"/>
+        <v>0.32908704883227169</v>
+      </c>
+      <c r="Z23" s="9">
+        <f t="shared" si="207"/>
+        <v>0.14580265095729006</v>
+      </c>
+      <c r="AA23" s="9">
+        <f t="shared" si="208"/>
+        <v>0.18890977443609014</v>
+      </c>
+      <c r="AB23" s="9">
+        <f t="shared" si="209"/>
+        <v>0.39071566731141205</v>
+      </c>
+      <c r="AC23" s="9">
+        <f t="shared" si="210"/>
+        <v>0.23003194888178902</v>
+      </c>
+      <c r="AD23" s="9">
+        <f t="shared" si="211"/>
+        <v>6.4910025706940822E-2</v>
+      </c>
+      <c r="AE23" s="9">
+        <f t="shared" si="212"/>
+        <v>0.10592885375494077</v>
+      </c>
+      <c r="AF23" s="9">
+        <f t="shared" si="213"/>
+        <v>-5.7023643949930536E-2</v>
+      </c>
+      <c r="AG23" s="9">
+        <f t="shared" si="214"/>
+        <v>-5.1948051948051965E-2</v>
+      </c>
+      <c r="AH23" s="9">
+        <f t="shared" si="215"/>
+        <v>-3.0000000000000027E-2</v>
+      </c>
+      <c r="AK23" s="9">
+        <f t="shared" ref="AK23:AL23" si="222">AK4/AJ4-1</f>
+        <v>0.19195331695331697</v>
+      </c>
+      <c r="AL23" s="9">
         <f t="shared" si="222"/>
-        <v>0.23909774436090236</v>
-      </c>
-      <c r="I23" s="9">
-        <f t="shared" si="222"/>
-        <v>0.11323328785811726</v>
-      </c>
-      <c r="J23" s="9">
-        <f t="shared" si="222"/>
-        <v>0.21962992759452926</v>
-      </c>
-      <c r="K23" s="9">
-        <f t="shared" si="222"/>
-        <v>0.21655172413793111</v>
-      </c>
-      <c r="L23" s="9">
-        <f t="shared" si="222"/>
-        <v>0.35072815533980561</v>
-      </c>
-      <c r="M23" s="9">
-        <f t="shared" si="222"/>
-        <v>0.62254901960784337</v>
-      </c>
-      <c r="N23" s="9">
-        <f t="shared" si="222"/>
-        <v>0.1787598944591029</v>
-      </c>
-      <c r="O23" s="9">
-        <f t="shared" si="197"/>
-        <v>0.22108843537414957</v>
-      </c>
-      <c r="P23" s="9">
-        <f t="shared" si="198"/>
-        <v>1.3477088948786964E-2</v>
-      </c>
-      <c r="Q23" s="9">
-        <f t="shared" si="199"/>
-        <v>-0.2643504531722054</v>
-      </c>
-      <c r="R23" s="9">
-        <f t="shared" si="200"/>
-        <v>-9.5131505316172316E-2</v>
-      </c>
-      <c r="S23" s="9">
-        <f t="shared" si="201"/>
-        <v>-0.19405756731662027</v>
-      </c>
-      <c r="T23" s="9">
-        <f t="shared" si="202"/>
-        <v>-0.15602836879432624</v>
-      </c>
-      <c r="U23" s="9">
-        <f t="shared" si="203"/>
-        <v>-3.2854209445585258E-2</v>
-      </c>
-      <c r="V23" s="9">
-        <f t="shared" si="204"/>
-        <v>-0.16017316017316008</v>
-      </c>
-      <c r="W23" s="9">
-        <f t="shared" si="205"/>
-        <v>0.22580645161290325</v>
-      </c>
-      <c r="X23" s="9">
-        <f t="shared" si="206"/>
-        <v>8.6134453781512743E-2</v>
-      </c>
-      <c r="Y23" s="9">
-        <f t="shared" si="207"/>
-        <v>0.32908704883227169</v>
-      </c>
-      <c r="Z23" s="9">
-        <f t="shared" si="208"/>
-        <v>0.14580265095729006</v>
-      </c>
-      <c r="AA23" s="9">
-        <f t="shared" si="209"/>
-        <v>0.18890977443609014</v>
-      </c>
-      <c r="AB23" s="9">
-        <f t="shared" si="210"/>
-        <v>0.39071566731141205</v>
-      </c>
-      <c r="AC23" s="9">
-        <f t="shared" si="211"/>
-        <v>0.23003194888178902</v>
-      </c>
-      <c r="AD23" s="9">
-        <f t="shared" si="212"/>
-        <v>6.4910025706940822E-2</v>
-      </c>
-      <c r="AE23" s="9">
-        <f t="shared" si="213"/>
-        <v>0.10592885375494077</v>
-      </c>
-      <c r="AF23" s="9">
-        <f t="shared" si="214"/>
-        <v>-5.7023643949930536E-2</v>
-      </c>
-      <c r="AG23" s="9">
-        <f t="shared" si="215"/>
+        <v>0.31564029889203793</v>
+      </c>
+      <c r="AM23" s="9">
+        <f t="shared" ref="AM23:AW23" si="223">AM4/AL4-1</f>
+        <v>-6.0712886799843324E-2</v>
+      </c>
+      <c r="AN23" s="9">
+        <f t="shared" si="223"/>
+        <v>-0.14095079232693908</v>
+      </c>
+      <c r="AO23" s="9">
+        <f t="shared" si="223"/>
+        <v>0.1907766990291262</v>
+      </c>
+      <c r="AP23" s="9">
+        <f t="shared" si="223"/>
+        <v>0.20260905014268227</v>
+      </c>
+      <c r="AQ23" s="9">
+        <f t="shared" si="223"/>
+        <v>-1.317118644067794E-2</v>
+      </c>
+      <c r="AR23" s="9">
+        <f t="shared" si="223"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AS23" s="9">
+        <f t="shared" si="223"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AT23" s="9">
+        <f t="shared" si="223"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AH23" s="9">
-        <f t="shared" si="216"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AK23" s="9">
-        <f t="shared" ref="AK23:AL23" si="223">AK4/AJ4-1</f>
-        <v>0.19195331695331697</v>
-      </c>
-      <c r="AL23" s="9">
+      <c r="AU23" s="9">
         <f t="shared" si="223"/>
-        <v>0.31564029889203793</v>
-      </c>
-      <c r="AM23" s="9">
-        <f t="shared" ref="AM23:AW23" si="224">AM4/AL4-1</f>
-        <v>-6.0712886799843324E-2</v>
-      </c>
-      <c r="AN23" s="9">
-        <f t="shared" si="224"/>
-        <v>-0.14095079232693908</v>
-      </c>
-      <c r="AO23" s="9">
-        <f t="shared" si="224"/>
-        <v>0.1907766990291262</v>
-      </c>
-      <c r="AP23" s="9">
-        <f t="shared" si="224"/>
-        <v>0.20260905014268227</v>
-      </c>
-      <c r="AQ23" s="9">
-        <f t="shared" si="224"/>
-        <v>1.7040677966101647E-2</v>
-      </c>
-      <c r="AR23" s="9">
-        <f t="shared" si="224"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AS23" s="9">
-        <f t="shared" si="224"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AT23" s="9">
-        <f t="shared" si="224"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AU23" s="9">
-        <f t="shared" si="224"/>
-        <v>2.0000000000000018E-2</v>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AV23" s="9">
-        <f t="shared" si="224"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="223"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AW23" s="9">
-        <f t="shared" si="224"/>
+        <f t="shared" si="223"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX23" s="9">
+        <f t="shared" si="217"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AY23" s="9">
         <f t="shared" si="218"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AY23" s="9">
+      <c r="AZ23" s="9">
         <f t="shared" si="219"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AZ23" s="9">
+      <c r="BA23" s="9">
         <f t="shared" si="220"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="BA23" s="9">
-        <f t="shared" si="221"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -5270,180 +5258,180 @@
         <v>0.51317715959004384</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" ref="H24:N24" si="225">H5/D5-1</f>
+        <f t="shared" ref="H24:N24" si="224">H5/D5-1</f>
         <v>0.59502551020408156</v>
       </c>
       <c r="I24" s="9">
+        <f t="shared" si="224"/>
+        <v>0.50461361014994233</v>
+      </c>
+      <c r="J24" s="9">
+        <f t="shared" si="224"/>
+        <v>0.49147624229234688</v>
+      </c>
+      <c r="K24" s="9">
+        <f t="shared" si="224"/>
+        <v>0.5520077406869861</v>
+      </c>
+      <c r="L24" s="9">
+        <f t="shared" si="224"/>
+        <v>0.42383046781287503</v>
+      </c>
+      <c r="M24" s="9">
+        <f t="shared" si="224"/>
+        <v>0.73093139133767759</v>
+      </c>
+      <c r="N24" s="9">
+        <f t="shared" si="224"/>
+        <v>0.58049610894941606</v>
+      </c>
+      <c r="O24" s="9">
+        <f t="shared" si="196"/>
+        <v>0.78990024937655878</v>
+      </c>
+      <c r="P24" s="9">
+        <f t="shared" si="197"/>
+        <v>0.811569783768604</v>
+      </c>
+      <c r="Q24" s="9">
+        <f t="shared" si="198"/>
+        <v>0.50553587245349862</v>
+      </c>
+      <c r="R24" s="9">
+        <f t="shared" si="199"/>
+        <v>0.33143560547776585</v>
+      </c>
+      <c r="S24" s="9">
+        <f t="shared" si="200"/>
+        <v>0.27777777777777746</v>
+      </c>
+      <c r="T24" s="9">
+        <f t="shared" si="201"/>
+        <v>0.18508758332041553</v>
+      </c>
+      <c r="U24" s="9">
+        <f t="shared" si="202"/>
+        <v>0.11987056920135331</v>
+      </c>
+      <c r="V24" s="9">
+        <f t="shared" si="203"/>
+        <v>2.0802033976654588E-3</v>
+      </c>
+      <c r="W24" s="9">
+        <f t="shared" si="204"/>
+        <v>9.9495706692109831E-3</v>
+      </c>
+      <c r="X24" s="9">
+        <f t="shared" si="205"/>
+        <v>0.10830608240680184</v>
+      </c>
+      <c r="Y24" s="9">
+        <f t="shared" si="206"/>
+        <v>0.19779353821907009</v>
+      </c>
+      <c r="Z24" s="9">
+        <f t="shared" si="207"/>
+        <v>0.13539384154076828</v>
+      </c>
+      <c r="AA24" s="9">
+        <f t="shared" si="208"/>
+        <v>0.18947368421052624</v>
+      </c>
+      <c r="AB24" s="9">
+        <f t="shared" si="209"/>
+        <v>0.14257051811636967</v>
+      </c>
+      <c r="AC24" s="9">
+        <f t="shared" si="210"/>
+        <v>0.1646929824561405</v>
+      </c>
+      <c r="AD24" s="9">
+        <f t="shared" si="211"/>
+        <v>0.21990858303707461</v>
+      </c>
+      <c r="AE24" s="9">
+        <f t="shared" si="212"/>
+        <v>0.15804402087587932</v>
+      </c>
+      <c r="AF24" s="9">
+        <f t="shared" si="213"/>
+        <v>0.14771201322177463</v>
+      </c>
+      <c r="AG24" s="9">
+        <f t="shared" si="214"/>
+        <v>0.1397100357748069</v>
+      </c>
+      <c r="AH24" s="9">
+        <f t="shared" si="215"/>
+        <v>0.12516569525395482</v>
+      </c>
+      <c r="AK24" s="9">
+        <f t="shared" ref="AK24:AL24" si="225">AK5/AJ5-1</f>
+        <v>0.52040404040404042</v>
+      </c>
+      <c r="AL24" s="9">
         <f t="shared" si="225"/>
-        <v>0.50461361014994233</v>
-      </c>
-      <c r="J24" s="9">
-        <f t="shared" si="225"/>
-        <v>0.49147624229234688</v>
-      </c>
-      <c r="K24" s="9">
-        <f t="shared" si="225"/>
-        <v>0.5520077406869861</v>
-      </c>
-      <c r="L24" s="9">
-        <f t="shared" si="225"/>
-        <v>0.42383046781287503</v>
-      </c>
-      <c r="M24" s="9">
-        <f t="shared" si="225"/>
-        <v>0.73093139133767759</v>
-      </c>
-      <c r="N24" s="9">
-        <f t="shared" si="225"/>
-        <v>0.58049610894941606</v>
-      </c>
-      <c r="O24" s="9">
-        <f t="shared" si="197"/>
-        <v>0.78990024937655878</v>
-      </c>
-      <c r="P24" s="9">
-        <f t="shared" si="198"/>
-        <v>0.811569783768604</v>
-      </c>
-      <c r="Q24" s="9">
-        <f t="shared" si="199"/>
-        <v>0.50553587245349862</v>
-      </c>
-      <c r="R24" s="9">
-        <f t="shared" si="200"/>
-        <v>0.33143560547776585</v>
-      </c>
-      <c r="S24" s="9">
-        <f t="shared" si="201"/>
-        <v>0.27777777777777746</v>
-      </c>
-      <c r="T24" s="9">
-        <f t="shared" si="202"/>
-        <v>0.18508758332041553</v>
-      </c>
-      <c r="U24" s="9">
-        <f t="shared" si="203"/>
-        <v>0.11987056920135331</v>
-      </c>
-      <c r="V24" s="9">
-        <f t="shared" si="204"/>
-        <v>2.0802033976654588E-3</v>
-      </c>
-      <c r="W24" s="9">
-        <f t="shared" si="205"/>
-        <v>9.9495706692109831E-3</v>
-      </c>
-      <c r="X24" s="9">
-        <f t="shared" si="206"/>
-        <v>0.10830608240680184</v>
-      </c>
-      <c r="Y24" s="9">
-        <f t="shared" si="207"/>
-        <v>0.19779353821907009</v>
-      </c>
-      <c r="Z24" s="9">
-        <f t="shared" si="208"/>
-        <v>0.13539384154076828</v>
-      </c>
-      <c r="AA24" s="9">
-        <f t="shared" si="209"/>
-        <v>0.18947368421052624</v>
-      </c>
-      <c r="AB24" s="9">
-        <f t="shared" si="210"/>
-        <v>0.14257051811636967</v>
-      </c>
-      <c r="AC24" s="9">
-        <f t="shared" si="211"/>
-        <v>0.1646929824561405</v>
-      </c>
-      <c r="AD24" s="9">
-        <f t="shared" si="212"/>
-        <v>0.21990858303707461</v>
-      </c>
-      <c r="AE24" s="9">
-        <f t="shared" si="213"/>
-        <v>0.15804402087587932</v>
-      </c>
-      <c r="AF24" s="9">
-        <f t="shared" si="214"/>
-        <v>0.14771201322177463</v>
-      </c>
-      <c r="AG24" s="9">
-        <f t="shared" si="215"/>
-        <v>0.11260214648841993</v>
-      </c>
-      <c r="AH24" s="9">
-        <f t="shared" si="216"/>
-        <v>9.7582847626977332E-2</v>
-      </c>
-      <c r="AK24" s="9">
-        <f t="shared" ref="AK24:AL24" si="226">AK5/AJ5-1</f>
-        <v>0.52040404040404042</v>
-      </c>
-      <c r="AL24" s="9">
+        <v>0.5753388254052616</v>
+      </c>
+      <c r="AM24" s="9">
+        <f t="shared" ref="AM24:AW24" si="226">AM5/AL5-1</f>
+        <v>0.55448717948717952</v>
+      </c>
+      <c r="AN24" s="9">
         <f t="shared" si="226"/>
-        <v>0.5753388254052616</v>
-      </c>
-      <c r="AM24" s="9">
-        <f t="shared" ref="AM24:AW24" si="227">AM5/AL5-1</f>
-        <v>0.55448717948717952</v>
-      </c>
-      <c r="AN24" s="9">
-        <f t="shared" si="227"/>
         <v>0.13101826731777888</v>
       </c>
       <c r="AO24" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="226"/>
         <v>0.11452969584546024</v>
       </c>
       <c r="AP24" s="9">
-        <f t="shared" si="227"/>
+        <f t="shared" si="226"/>
         <v>0.18018250688705217</v>
       </c>
       <c r="AQ24" s="9">
-        <f t="shared" si="227"/>
-        <v>0.1262195151603569</v>
+        <f t="shared" si="226"/>
+        <v>0.14127556106693895</v>
       </c>
       <c r="AR24" s="9">
-        <f t="shared" si="227"/>
-        <v>9.9635932270867311E-2</v>
+        <f t="shared" si="226"/>
+        <v>0.10759558508340095</v>
       </c>
       <c r="AS24" s="9">
-        <f t="shared" si="227"/>
-        <v>7.3932656795917095E-2</v>
+        <f t="shared" si="226"/>
+        <v>7.3145962270708242E-2</v>
       </c>
       <c r="AT24" s="9">
-        <f t="shared" si="227"/>
-        <v>5.5344688730222025E-2</v>
+        <f t="shared" si="226"/>
+        <v>5.4571165270406619E-2</v>
       </c>
       <c r="AU24" s="9">
-        <f t="shared" si="227"/>
-        <v>3.7750300188232222E-2</v>
+        <f t="shared" si="226"/>
+        <v>3.6880368101767758E-2</v>
       </c>
       <c r="AV24" s="9">
-        <f t="shared" si="227"/>
-        <v>2.8894390197917952E-2</v>
+        <f t="shared" si="226"/>
+        <v>2.7974161523903307E-2</v>
       </c>
       <c r="AW24" s="9">
-        <f t="shared" si="227"/>
-        <v>1.8903947762892725E-2</v>
+        <f t="shared" si="226"/>
+        <v>1.9004791687651013E-2</v>
       </c>
       <c r="AX24" s="9">
+        <f t="shared" si="217"/>
+        <v>1.9013586193438847E-2</v>
+      </c>
+      <c r="AY24" s="9">
         <f t="shared" si="218"/>
-        <v>1.8913525890336347E-2</v>
-      </c>
-      <c r="AY24" s="9">
+        <v>1.902231142143207E-2</v>
+      </c>
+      <c r="AZ24" s="9">
         <f t="shared" si="219"/>
-        <v>1.8923030440879174E-2</v>
-      </c>
-      <c r="AZ24" s="9">
+        <v>1.9030967768530971E-2</v>
+      </c>
+      <c r="BA24" s="9">
         <f t="shared" si="220"/>
-        <v>1.8932461803085054E-2</v>
-      </c>
-      <c r="BA24" s="9">
-        <f t="shared" si="221"/>
-        <v>1.8941820366606077E-2</v>
+        <v>1.9039555632026417E-2</v>
       </c>
     </row>
     <row r="25" spans="2:163" x14ac:dyDescent="0.3">
@@ -5455,200 +5443,200 @@
         <v>0.71105193075898798</v>
       </c>
       <c r="D25" s="9">
-        <f t="shared" ref="D25:N25" si="228">(D3-D6)/D3</f>
+        <f t="shared" ref="D25:N25" si="227">(D3-D6)/D3</f>
         <v>0.69767441860465118</v>
       </c>
       <c r="E25" s="9">
+        <f t="shared" si="227"/>
+        <v>0.70529470529470528</v>
+      </c>
+      <c r="F25" s="9">
+        <f t="shared" si="227"/>
+        <v>0.72258916776750326</v>
+      </c>
+      <c r="G25" s="9">
+        <f t="shared" si="227"/>
+        <v>0.69895678092399394</v>
+      </c>
+      <c r="H25" s="9">
+        <f t="shared" si="227"/>
+        <v>0.654144305307096</v>
+      </c>
+      <c r="I25" s="9">
+        <f t="shared" si="227"/>
+        <v>0.62576687116564422</v>
+      </c>
+      <c r="J25" s="9">
+        <f t="shared" si="227"/>
+        <v>0.62557781201849005</v>
+      </c>
+      <c r="K25" s="9">
+        <f t="shared" si="227"/>
+        <v>0.56190885640584687</v>
+      </c>
+      <c r="L25" s="9">
+        <f t="shared" si="227"/>
+        <v>0.56576797385620914</v>
+      </c>
+      <c r="M25" s="9">
+        <f t="shared" si="227"/>
+        <v>0.60964912280701755</v>
+      </c>
+      <c r="N25" s="9">
+        <f t="shared" si="227"/>
+        <v>0.63858234295415961</v>
+      </c>
+      <c r="O25" s="9">
+        <f t="shared" ref="O25:R25" si="228">(O3-O6)/O3</f>
+        <v>0.66859592711682736</v>
+      </c>
+      <c r="P25" s="9">
         <f t="shared" si="228"/>
-        <v>0.70529470529470528</v>
-      </c>
-      <c r="F25" s="9">
+        <v>0.6481307533345857</v>
+      </c>
+      <c r="Q25" s="9">
         <f t="shared" si="228"/>
-        <v>0.72258916776750326</v>
-      </c>
-      <c r="G25" s="9">
+        <v>0.6497854077253219</v>
+      </c>
+      <c r="R25" s="9">
         <f t="shared" si="228"/>
-        <v>0.69895678092399394</v>
-      </c>
-      <c r="H25" s="9">
-        <f t="shared" si="228"/>
-        <v>0.654144305307096</v>
-      </c>
-      <c r="I25" s="9">
-        <f t="shared" si="228"/>
-        <v>0.62576687116564422</v>
-      </c>
-      <c r="J25" s="9">
-        <f t="shared" si="228"/>
-        <v>0.62557781201849005</v>
-      </c>
-      <c r="K25" s="9">
-        <f t="shared" si="228"/>
-        <v>0.56190885640584687</v>
-      </c>
-      <c r="L25" s="9">
-        <f t="shared" si="228"/>
-        <v>0.56576797385620914</v>
-      </c>
-      <c r="M25" s="9">
-        <f t="shared" si="228"/>
-        <v>0.60964912280701755</v>
-      </c>
-      <c r="N25" s="9">
-        <f t="shared" si="228"/>
-        <v>0.63858234295415961</v>
-      </c>
-      <c r="O25" s="9">
-        <f t="shared" ref="O25:R25" si="229">(O3-O6)/O3</f>
-        <v>0.66859592711682736</v>
-      </c>
-      <c r="P25" s="9">
+        <v>0.60488914155770324</v>
+      </c>
+      <c r="S25" s="9">
+        <f t="shared" ref="S25:AA25" si="229">(S3-S6)/S3</f>
+        <v>0.58726232802597</v>
+      </c>
+      <c r="T25" s="9">
         <f t="shared" si="229"/>
-        <v>0.6481307533345857</v>
-      </c>
-      <c r="Q25" s="9">
+        <v>0.55909158822650529</v>
+      </c>
+      <c r="U25" s="9">
         <f t="shared" si="229"/>
-        <v>0.6497854077253219</v>
-      </c>
-      <c r="R25" s="9">
+        <v>0.55695443645083931</v>
+      </c>
+      <c r="V25" s="9">
         <f t="shared" si="229"/>
-        <v>0.60488914155770324</v>
-      </c>
-      <c r="S25" s="9">
-        <f t="shared" ref="S25:AA25" si="230">(S3-S6)/S3</f>
-        <v>0.58726232802597</v>
-      </c>
-      <c r="T25" s="9">
+        <v>0.55791057021742096</v>
+      </c>
+      <c r="W25" s="9">
+        <f t="shared" si="229"/>
+        <v>0.52631578947368418</v>
+      </c>
+      <c r="X25" s="9">
+        <f t="shared" si="229"/>
+        <v>0.532195187525205</v>
+      </c>
+      <c r="Y25" s="9">
+        <f t="shared" si="229"/>
+        <v>0.48068124046771726</v>
+      </c>
+      <c r="Z25" s="9">
+        <f t="shared" si="229"/>
+        <v>0.55314271926649783</v>
+      </c>
+      <c r="AA25" s="9">
+        <f t="shared" si="229"/>
+        <v>0.52232083719697964</v>
+      </c>
+      <c r="AB25" s="9">
+        <f t="shared" ref="AB25:AD25" si="230">(AB3-AB6)/AB3</f>
+        <v>0.53354361276234374</v>
+      </c>
+      <c r="AC25" s="9">
         <f t="shared" si="230"/>
-        <v>0.55909158822650529</v>
-      </c>
-      <c r="U25" s="9">
+        <v>0.54151068046685757</v>
+      </c>
+      <c r="AD25" s="9">
         <f t="shared" si="230"/>
-        <v>0.55695443645083931</v>
-      </c>
-      <c r="V25" s="9">
-        <f t="shared" si="230"/>
-        <v>0.55791057021742096</v>
-      </c>
-      <c r="W25" s="9">
-        <f t="shared" si="230"/>
-        <v>0.52631578947368418</v>
-      </c>
-      <c r="X25" s="9">
-        <f t="shared" si="230"/>
-        <v>0.532195187525205</v>
-      </c>
-      <c r="Y25" s="9">
-        <f t="shared" si="230"/>
-        <v>0.48068124046771726</v>
-      </c>
-      <c r="Z25" s="9">
-        <f t="shared" si="230"/>
-        <v>0.55314271926649783</v>
-      </c>
-      <c r="AA25" s="9">
-        <f t="shared" si="230"/>
-        <v>0.52232083719697964</v>
-      </c>
-      <c r="AB25" s="9">
-        <f t="shared" ref="AB25:AD25" si="231">(AB3-AB6)/AB3</f>
-        <v>0.53354361276234374</v>
-      </c>
-      <c r="AC25" s="9">
+        <v>0.54080942721916347</v>
+      </c>
+      <c r="AE25" s="9">
+        <f t="shared" ref="AE25:AH25" si="231">(AE3-AE6)/AE3</f>
+        <v>0.52713442325158943</v>
+      </c>
+      <c r="AF25" s="9">
         <f t="shared" si="231"/>
-        <v>0.54151068046685757</v>
-      </c>
-      <c r="AD25" s="9">
+        <v>0.51019989748846739</v>
+      </c>
+      <c r="AG25" s="9">
         <f t="shared" si="231"/>
-        <v>0.54080942721916347</v>
-      </c>
-      <c r="AE25" s="9">
-        <f t="shared" ref="AE25:AH25" si="232">(AE3-AE6)/AE3</f>
-        <v>0.52713442325158943</v>
-      </c>
-      <c r="AF25" s="9">
-        <f t="shared" si="232"/>
-        <v>0.51019989748846739</v>
-      </c>
-      <c r="AG25" s="9">
-        <f t="shared" si="232"/>
+        <v>0.51446552695848202</v>
+      </c>
+      <c r="AH25" s="9">
+        <f t="shared" si="231"/>
+        <v>0.53999999999999992</v>
+      </c>
+      <c r="AJ25" s="9">
+        <f t="shared" ref="AJ25" si="232">(AJ3-AJ6)/AJ3</f>
+        <v>0.71096186135763972</v>
+      </c>
+      <c r="AK25" s="9">
+        <f t="shared" ref="AK25:AL25" si="233">(AK3-AK6)/AK3</f>
+        <v>0.64538336933045359</v>
+      </c>
+      <c r="AL25" s="9">
+        <f t="shared" si="233"/>
+        <v>0.60317084713677238</v>
+      </c>
+      <c r="AM25" s="9">
+        <f t="shared" ref="AM25:AV25" si="234">(AM3-AM6)/AM3</f>
+        <v>0.63941529169766731</v>
+      </c>
+      <c r="AN25" s="9">
+        <f t="shared" si="234"/>
+        <v>0.56496113751059041</v>
+      </c>
+      <c r="AO25" s="9">
+        <f t="shared" si="234"/>
+        <v>0.52321154231514266</v>
+      </c>
+      <c r="AP25" s="9">
+        <f t="shared" si="234"/>
+        <v>0.53532801544270014</v>
+      </c>
+      <c r="AQ25" s="9">
+        <f t="shared" si="234"/>
+        <v>0.52356169714422607</v>
+      </c>
+      <c r="AR25" s="9">
+        <f t="shared" si="234"/>
+        <v>0.53</v>
+      </c>
+      <c r="AS25" s="9">
+        <f t="shared" si="234"/>
         <v>0.54</v>
       </c>
-      <c r="AH25" s="9">
-        <f t="shared" si="232"/>
+      <c r="AT25" s="9">
+        <f t="shared" si="234"/>
+        <v>0.54</v>
+      </c>
+      <c r="AU25" s="9">
+        <f t="shared" si="234"/>
         <v>0.53999999999999992</v>
       </c>
-      <c r="AJ25" s="9">
-        <f t="shared" ref="AJ25" si="233">(AJ3-AJ6)/AJ3</f>
-        <v>0.71096186135763972</v>
-      </c>
-      <c r="AK25" s="9">
-        <f t="shared" ref="AK25:AL25" si="234">(AK3-AK6)/AK3</f>
-        <v>0.64538336933045359</v>
-      </c>
-      <c r="AL25" s="9">
+      <c r="AV25" s="9">
         <f t="shared" si="234"/>
-        <v>0.60317084713677238</v>
-      </c>
-      <c r="AM25" s="9">
-        <f t="shared" ref="AM25:AV25" si="235">(AM3-AM6)/AM3</f>
-        <v>0.63941529169766731</v>
-      </c>
-      <c r="AN25" s="9">
+        <v>0.54</v>
+      </c>
+      <c r="AW25" s="9">
+        <f t="shared" ref="AW25:BA25" si="235">(AW3-AW6)/AW3</f>
+        <v>0.53999999999999992</v>
+      </c>
+      <c r="AX25" s="9">
         <f t="shared" si="235"/>
-        <v>0.56496113751059041</v>
-      </c>
-      <c r="AO25" s="9">
+        <v>0.54</v>
+      </c>
+      <c r="AY25" s="9">
         <f t="shared" si="235"/>
-        <v>0.52321154231514266</v>
-      </c>
-      <c r="AP25" s="9">
+        <v>0.54</v>
+      </c>
+      <c r="AZ25" s="9">
         <f t="shared" si="235"/>
-        <v>0.53532801544270014</v>
-      </c>
-      <c r="AQ25" s="9">
+        <v>0.54</v>
+      </c>
+      <c r="BA25" s="9">
         <f t="shared" si="235"/>
-        <v>0.52997903887369979</v>
-      </c>
-      <c r="AR25" s="9">
-        <f t="shared" si="235"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="AS25" s="9">
-        <f t="shared" si="235"/>
-        <v>0.54999999999999993</v>
-      </c>
-      <c r="AT25" s="9">
-        <f t="shared" si="235"/>
-        <v>0.54999999999999993</v>
-      </c>
-      <c r="AU25" s="9">
-        <f t="shared" si="235"/>
-        <v>0.54999999999999993</v>
-      </c>
-      <c r="AV25" s="9">
-        <f t="shared" si="235"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="AW25" s="9">
-        <f t="shared" ref="AW25:BA25" si="236">(AW3-AW6)/AW3</f>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="AX25" s="9">
-        <f t="shared" si="236"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="AY25" s="9">
-        <f t="shared" si="236"/>
-        <v>0.54999999999999993</v>
-      </c>
-      <c r="AZ25" s="9">
-        <f t="shared" si="236"/>
-        <v>0.54999999999999993</v>
-      </c>
-      <c r="BA25" s="9">
-        <f t="shared" si="236"/>
-        <v>0.55000000000000004</v>
+        <v>0.54</v>
       </c>
       <c r="BC25" t="s">
         <v>47</v>
@@ -5662,204 +5650,204 @@
         <v>44</v>
       </c>
       <c r="C26" s="9">
-        <f t="shared" ref="C26:N26" si="237">(C4-C7)/C4</f>
+        <f t="shared" ref="C26:N26" si="236">(C4-C7)/C4</f>
         <v>0.15772357723577241</v>
       </c>
       <c r="D26" s="9">
+        <f t="shared" si="236"/>
+        <v>0.22255639097744356</v>
+      </c>
+      <c r="E26" s="9">
+        <f t="shared" si="236"/>
+        <v>0.11459754433833549</v>
+      </c>
+      <c r="F26" s="9">
+        <f t="shared" si="236"/>
+        <v>2.3330651649235652E-2</v>
+      </c>
+      <c r="G26" s="9">
+        <f t="shared" si="236"/>
+        <v>9.7931034482758542E-2</v>
+      </c>
+      <c r="H26" s="9">
+        <f t="shared" si="236"/>
+        <v>5.461165048543689E-2</v>
+      </c>
+      <c r="I26" s="9">
+        <f t="shared" si="236"/>
+        <v>7.5980392156862614E-2</v>
+      </c>
+      <c r="J26" s="9">
+        <f t="shared" si="236"/>
+        <v>-4.617414248021221E-3</v>
+      </c>
+      <c r="K26" s="9">
+        <f t="shared" si="236"/>
+        <v>0.11904761904761904</v>
+      </c>
+      <c r="L26" s="9">
+        <f t="shared" si="236"/>
+        <v>7.5471698113207475E-2</v>
+      </c>
+      <c r="M26" s="9">
+        <f t="shared" si="236"/>
+        <v>0.15181268882175233</v>
+      </c>
+      <c r="N26" s="9">
+        <f t="shared" si="236"/>
+        <v>2.5741466144376019E-2</v>
+      </c>
+      <c r="O26" s="9">
+        <f t="shared" ref="O26:R26" si="237">(O4-O7)/O4</f>
+        <v>0.13834726090993504</v>
+      </c>
+      <c r="P26" s="9">
         <f t="shared" si="237"/>
-        <v>0.22255639097744356</v>
-      </c>
-      <c r="E26" s="9">
+        <v>-5.9397163120567399E-2</v>
+      </c>
+      <c r="Q26" s="9">
         <f t="shared" si="237"/>
-        <v>0.11459754433833549</v>
-      </c>
-      <c r="F26" s="9">
+        <v>-0.14989733059548249</v>
+      </c>
+      <c r="R26" s="9">
         <f t="shared" si="237"/>
-        <v>2.3330651649235652E-2</v>
-      </c>
-      <c r="G26" s="9">
-        <f t="shared" si="237"/>
-        <v>9.7931034482758542E-2</v>
-      </c>
-      <c r="H26" s="9">
-        <f t="shared" si="237"/>
-        <v>5.461165048543689E-2</v>
-      </c>
-      <c r="I26" s="9">
-        <f t="shared" si="237"/>
-        <v>7.5980392156862614E-2</v>
-      </c>
-      <c r="J26" s="9">
-        <f t="shared" si="237"/>
-        <v>-4.617414248021221E-3</v>
-      </c>
-      <c r="K26" s="9">
-        <f t="shared" si="237"/>
-        <v>0.11904761904761904</v>
-      </c>
-      <c r="L26" s="9">
-        <f t="shared" si="237"/>
-        <v>7.5471698113207475E-2</v>
-      </c>
-      <c r="M26" s="9">
-        <f t="shared" si="237"/>
-        <v>0.15181268882175233</v>
-      </c>
-      <c r="N26" s="9">
-        <f t="shared" si="237"/>
-        <v>2.5741466144376019E-2</v>
-      </c>
-      <c r="O26" s="9">
-        <f t="shared" ref="O26:R26" si="238">(O4-O7)/O4</f>
-        <v>0.13834726090993504</v>
-      </c>
-      <c r="P26" s="9">
+        <v>-0.28447742733457021</v>
+      </c>
+      <c r="S26" s="9">
+        <f t="shared" ref="S26:AA26" si="238">(S4-S7)/S4</f>
+        <v>-0.1739631336405531</v>
+      </c>
+      <c r="T26" s="9">
         <f t="shared" si="238"/>
-        <v>-5.9397163120567399E-2</v>
-      </c>
-      <c r="Q26" s="9">
+        <v>-0.19957983193277309</v>
+      </c>
+      <c r="U26" s="9">
         <f t="shared" si="238"/>
-        <v>-0.14989733059548249</v>
-      </c>
-      <c r="R26" s="9">
+        <v>-0.1571125265392781</v>
+      </c>
+      <c r="V26" s="9">
         <f t="shared" si="238"/>
-        <v>-0.28447742733457021</v>
-      </c>
-      <c r="S26" s="9">
-        <f t="shared" ref="S26:AA26" si="239">(S4-S7)/S4</f>
-        <v>-0.1739631336405531</v>
-      </c>
-      <c r="T26" s="9">
+        <v>-0.32106038291605293</v>
+      </c>
+      <c r="W26" s="9">
+        <f t="shared" si="238"/>
+        <v>3.3834586466165495E-2</v>
+      </c>
+      <c r="X26" s="9">
+        <f t="shared" si="238"/>
+        <v>-0.16924564796905223</v>
+      </c>
+      <c r="Y26" s="9">
+        <f t="shared" si="238"/>
+        <v>-7.5079872204472778E-2</v>
+      </c>
+      <c r="Z26" s="9">
+        <f t="shared" si="238"/>
+        <v>-0.13174807197943444</v>
+      </c>
+      <c r="AA26" s="9">
+        <f t="shared" si="238"/>
+        <v>-4.8221343873517744E-2</v>
+      </c>
+      <c r="AB26" s="9">
+        <f t="shared" ref="AB26:AD26" si="239">(AB4-AB7)/AB4</f>
+        <v>-0.10570236439499296</v>
+      </c>
+      <c r="AC26" s="9">
         <f t="shared" si="239"/>
-        <v>-0.19957983193277309</v>
-      </c>
-      <c r="U26" s="9">
+        <v>-7.5974025974025902E-2</v>
+      </c>
+      <c r="AD26" s="9">
         <f t="shared" si="239"/>
-        <v>-0.1571125265392781</v>
-      </c>
-      <c r="V26" s="9">
-        <f t="shared" si="239"/>
-        <v>-0.32106038291605293</v>
-      </c>
-      <c r="W26" s="9">
-        <f t="shared" si="239"/>
-        <v>3.3834586466165495E-2</v>
-      </c>
-      <c r="X26" s="9">
-        <f t="shared" si="239"/>
-        <v>-0.16924564796905223</v>
-      </c>
-      <c r="Y26" s="9">
-        <f t="shared" si="239"/>
-        <v>-7.5079872204472778E-2</v>
-      </c>
-      <c r="Z26" s="9">
-        <f t="shared" si="239"/>
-        <v>-0.13174807197943444</v>
-      </c>
-      <c r="AA26" s="9">
-        <f t="shared" si="239"/>
-        <v>-4.8221343873517744E-2</v>
-      </c>
-      <c r="AB26" s="9">
-        <f t="shared" ref="AB26:AD26" si="240">(AB4-AB7)/AB4</f>
-        <v>-0.10570236439499296</v>
-      </c>
-      <c r="AC26" s="9">
+        <v>-0.28605914302957158</v>
+      </c>
+      <c r="AE26" s="9">
+        <f t="shared" ref="AE26:AH26" si="240">(AE4-AE7)/AE4</f>
+        <v>-0.1372408863473909</v>
+      </c>
+      <c r="AF26" s="9">
         <f t="shared" si="240"/>
-        <v>-7.5974025974025902E-2</v>
-      </c>
-      <c r="AD26" s="9">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="9">
         <f t="shared" si="240"/>
-        <v>-0.28605914302957158</v>
-      </c>
-      <c r="AE26" s="9">
-        <f t="shared" ref="AE26:AH26" si="241">(AE4-AE7)/AE4</f>
-        <v>-0.1372408863473909</v>
-      </c>
-      <c r="AF26" s="9">
-        <f t="shared" si="241"/>
-        <v>0</v>
-      </c>
-      <c r="AG26" s="9">
-        <f t="shared" si="241"/>
-        <v>-9.0000000000000066E-2</v>
+        <v>-0.1568493150684932</v>
       </c>
       <c r="AH26" s="9">
-        <f t="shared" si="241"/>
-        <v>-0.19999999999999996</v>
+        <f t="shared" si="240"/>
+        <v>-0.1999999999999999</v>
       </c>
       <c r="AJ26" s="9">
-        <f t="shared" ref="AJ26" si="242">(AJ4-AJ7)/AJ4</f>
+        <f t="shared" ref="AJ26" si="241">(AJ4-AJ7)/AJ4</f>
         <v>0.10995085995085997</v>
       </c>
       <c r="AK26" s="9">
-        <f t="shared" ref="AK26:AL26" si="243">(AK4-AK7)/AK4</f>
+        <f t="shared" ref="AK26:AL26" si="242">(AK4-AK7)/AK4</f>
         <v>4.4060809069827421E-2</v>
       </c>
       <c r="AL26" s="9">
+        <f t="shared" si="242"/>
+        <v>8.538973756365055E-2</v>
+      </c>
+      <c r="AM26" s="9">
+        <f t="shared" ref="AM26:AV26" si="243">(AM4-AM7)/AM4</f>
+        <v>-0.10925771476230199</v>
+      </c>
+      <c r="AN26" s="9">
         <f t="shared" si="243"/>
-        <v>8.538973756365055E-2</v>
-      </c>
-      <c r="AM26" s="9">
-        <f t="shared" ref="AM26:AV26" si="244">(AM4-AM7)/AM4</f>
-        <v>-0.10925771476230199</v>
-      </c>
-      <c r="AN26" s="9">
+        <v>-0.22451456310679613</v>
+      </c>
+      <c r="AO26" s="9">
+        <f t="shared" si="243"/>
+        <v>-8.92784345699143E-2</v>
+      </c>
+      <c r="AP26" s="9">
+        <f t="shared" si="243"/>
+        <v>-0.13627118644067793</v>
+      </c>
+      <c r="AQ26" s="9">
+        <f t="shared" si="243"/>
+        <v>-0.12751992772603205</v>
+      </c>
+      <c r="AR26" s="9">
+        <f t="shared" si="243"/>
+        <v>-4.9999999999999954E-2</v>
+      </c>
+      <c r="AS26" s="9">
+        <f t="shared" si="243"/>
+        <v>-9.9999999999999638E-3</v>
+      </c>
+      <c r="AT26" s="9">
+        <f t="shared" si="243"/>
+        <v>1.0000000000000078E-2</v>
+      </c>
+      <c r="AU26" s="9">
+        <f t="shared" si="243"/>
+        <v>9.9999999999999725E-3</v>
+      </c>
+      <c r="AV26" s="9">
+        <f t="shared" si="243"/>
+        <v>1.0000000000000024E-2</v>
+      </c>
+      <c r="AW26" s="9">
+        <f t="shared" ref="AW26:BA26" si="244">(AW4-AW7)/AW4</f>
+        <v>1.0000000000000002E-2</v>
+      </c>
+      <c r="AX26" s="9">
         <f t="shared" si="244"/>
-        <v>-0.22451456310679613</v>
-      </c>
-      <c r="AO26" s="9">
+        <v>9.9999999999999551E-3</v>
+      </c>
+      <c r="AY26" s="9">
         <f t="shared" si="244"/>
-        <v>-8.92784345699143E-2</v>
-      </c>
-      <c r="AP26" s="9">
+        <v>9.9999999999999256E-3</v>
+      </c>
+      <c r="AZ26" s="9">
         <f t="shared" si="244"/>
-        <v>-0.13627118644067793</v>
-      </c>
-      <c r="AQ26" s="9">
-        <f t="shared" si="244"/>
-        <v>-0.11165895069443749</v>
-      </c>
-      <c r="AR26" s="9">
-        <f t="shared" si="244"/>
-        <v>-5.000000000000001E-2</v>
-      </c>
-      <c r="AS26" s="9">
-        <f t="shared" si="244"/>
-        <v>-1.0000000000000014E-2</v>
-      </c>
-      <c r="AT26" s="9">
+        <v>1.0000000000000063E-2</v>
+      </c>
+      <c r="BA26" s="9">
         <f t="shared" si="244"/>
         <v>9.9999999999999794E-3</v>
-      </c>
-      <c r="AU26" s="9">
-        <f t="shared" si="244"/>
-        <v>9.9999999999999725E-3</v>
-      </c>
-      <c r="AV26" s="9">
-        <f t="shared" si="244"/>
-        <v>1.0000000000000083E-2</v>
-      </c>
-      <c r="AW26" s="9">
-        <f t="shared" ref="AW26:BA26" si="245">(AW4-AW7)/AW4</f>
-        <v>9.999999999999962E-3</v>
-      </c>
-      <c r="AX26" s="9">
-        <f t="shared" si="245"/>
-        <v>1.0000000000000071E-2</v>
-      </c>
-      <c r="AY26" s="9">
-        <f t="shared" si="245"/>
-        <v>9.999999999999936E-3</v>
-      </c>
-      <c r="AZ26" s="9">
-        <f t="shared" si="245"/>
-        <v>9.9999999999999568E-3</v>
-      </c>
-      <c r="BA26" s="9">
-        <f t="shared" si="245"/>
-        <v>1.0000000000000023E-2</v>
       </c>
       <c r="BC26" t="s">
         <v>48</v>
@@ -5877,35 +5865,35 @@
         <v>0.46193265007320644</v>
       </c>
       <c r="D27" s="9">
-        <f t="shared" ref="D27:G27" si="246">D9/D5</f>
+        <f t="shared" ref="D27:G27" si="245">D9/D5</f>
         <v>0.49617346938775514</v>
       </c>
       <c r="E27" s="9">
+        <f t="shared" si="245"/>
+        <v>0.45559400230680497</v>
+      </c>
+      <c r="F27" s="9">
+        <f t="shared" si="245"/>
+        <v>0.4073268044976423</v>
+      </c>
+      <c r="G27" s="9">
+        <f t="shared" si="245"/>
+        <v>0.48814707305273336</v>
+      </c>
+      <c r="H27" s="9">
+        <f t="shared" ref="H27:N27" si="246">H9/H5</f>
+        <v>0.45661735305877643</v>
+      </c>
+      <c r="I27" s="9">
         <f t="shared" si="246"/>
-        <v>0.45559400230680497</v>
-      </c>
-      <c r="F27" s="9">
+        <v>0.45381372173246448</v>
+      </c>
+      <c r="J27" s="9">
         <f t="shared" si="246"/>
-        <v>0.4073268044976423</v>
-      </c>
-      <c r="G27" s="9">
+        <v>0.39323929961089499</v>
+      </c>
+      <c r="K27" s="9">
         <f t="shared" si="246"/>
-        <v>0.48814707305273336</v>
-      </c>
-      <c r="H27" s="9">
-        <f t="shared" ref="H27:N27" si="247">H9/H5</f>
-        <v>0.45661735305877643</v>
-      </c>
-      <c r="I27" s="9">
-        <f t="shared" si="247"/>
-        <v>0.45381372173246448</v>
-      </c>
-      <c r="J27" s="9">
-        <f t="shared" si="247"/>
-        <v>0.39323929961089499</v>
-      </c>
-      <c r="K27" s="9">
-        <f t="shared" si="247"/>
         <v>0.44014962593516205</v>
       </c>
       <c r="L27" s="9">
@@ -5913,171 +5901,171 @@
         <v>0.41252457174950863</v>
       </c>
       <c r="M27" s="9">
+        <f t="shared" si="246"/>
+        <v>0.47542072630646598</v>
+      </c>
+      <c r="N27" s="9">
+        <f t="shared" si="246"/>
+        <v>0.47007231881827977</v>
+      </c>
+      <c r="O27" s="9">
+        <f t="shared" ref="O27:R27" si="247">O9/O5</f>
+        <v>0.56913967258794851</v>
+      </c>
+      <c r="P27" s="9">
         <f t="shared" si="247"/>
-        <v>0.47542072630646598</v>
-      </c>
-      <c r="N27" s="9">
+        <v>0.52441481940784362</v>
+      </c>
+      <c r="Q27" s="9">
         <f t="shared" si="247"/>
-        <v>0.47007231881827977</v>
-      </c>
-      <c r="O27" s="9">
-        <f t="shared" ref="O27:R27" si="248">O9/O5</f>
-        <v>0.56913967258794851</v>
-      </c>
-      <c r="P27" s="9">
+        <v>0.53522576849536696</v>
+      </c>
+      <c r="R27" s="9">
+        <f t="shared" si="247"/>
+        <v>0.4386917831965792</v>
+      </c>
+      <c r="S27" s="9">
+        <f t="shared" ref="S27:AA27" si="248">S9/S5</f>
+        <v>0.4972059424833038</v>
+      </c>
+      <c r="T27" s="9">
         <f t="shared" si="248"/>
-        <v>0.52441481940784362</v>
-      </c>
-      <c r="Q27" s="9">
+        <v>0.46461739699149768</v>
+      </c>
+      <c r="U27" s="9">
         <f t="shared" si="248"/>
-        <v>0.53522576849536696</v>
-      </c>
-      <c r="R27" s="9">
+        <v>0.46861045442605731</v>
+      </c>
+      <c r="V27" s="9">
         <f t="shared" si="248"/>
-        <v>0.4386917831965792</v>
-      </c>
-      <c r="S27" s="9">
-        <f t="shared" ref="S27:AA27" si="249">S9/S5</f>
-        <v>0.4972059424833038</v>
-      </c>
-      <c r="T27" s="9">
+        <v>0.42025141275516076</v>
+      </c>
+      <c r="W27" s="9">
+        <f t="shared" si="248"/>
+        <v>0.45560053981106607</v>
+      </c>
+      <c r="X27" s="9">
+        <f t="shared" si="248"/>
+        <v>0.4465950666824029</v>
+      </c>
+      <c r="Y27" s="9">
+        <f t="shared" si="248"/>
+        <v>0.40438596491228063</v>
+      </c>
+      <c r="Z27" s="9">
+        <f t="shared" si="248"/>
+        <v>0.44489588623666837</v>
+      </c>
+      <c r="AA27" s="9">
+        <f t="shared" si="248"/>
+        <v>0.44043567052416605</v>
+      </c>
+      <c r="AB27" s="9">
+        <f t="shared" ref="AB27:AD27" si="249">AB9/AB5</f>
+        <v>0.43859105464311532</v>
+      </c>
+      <c r="AC27" s="9">
         <f t="shared" si="249"/>
-        <v>0.46461739699149768</v>
-      </c>
-      <c r="U27" s="9">
+        <v>0.45198644323103004</v>
+      </c>
+      <c r="AD27" s="9">
         <f t="shared" si="249"/>
-        <v>0.46861045442605731</v>
-      </c>
-      <c r="V27" s="9">
-        <f t="shared" si="249"/>
-        <v>0.42025141275516076</v>
-      </c>
-      <c r="W27" s="9">
-        <f t="shared" si="249"/>
-        <v>0.45560053981106607</v>
-      </c>
-      <c r="X27" s="9">
-        <f t="shared" si="249"/>
-        <v>0.4465950666824029</v>
-      </c>
-      <c r="Y27" s="9">
-        <f t="shared" si="249"/>
-        <v>0.40438596491228063</v>
-      </c>
-      <c r="Z27" s="9">
-        <f t="shared" si="249"/>
-        <v>0.44489588623666837</v>
-      </c>
-      <c r="AA27" s="9">
-        <f t="shared" si="249"/>
-        <v>0.44043567052416605</v>
-      </c>
-      <c r="AB27" s="9">
-        <f t="shared" ref="AB27:AD27" si="250">AB9/AB5</f>
-        <v>0.43859105464311532</v>
-      </c>
-      <c r="AC27" s="9">
+        <v>0.42672772689425481</v>
+      </c>
+      <c r="AE27" s="9">
+        <f t="shared" ref="AE27:AH27" si="250">AE9/AE5</f>
+        <v>0.4360732830410502</v>
+      </c>
+      <c r="AF27" s="9">
         <f t="shared" si="250"/>
-        <v>0.45198644323103004</v>
-      </c>
-      <c r="AD27" s="9">
+        <v>0.44793447934479341</v>
+      </c>
+      <c r="AG27" s="9">
         <f t="shared" si="250"/>
-        <v>0.42672772689425481</v>
-      </c>
-      <c r="AE27" s="9">
-        <f t="shared" ref="AE27:AH27" si="251">AE9/AE5</f>
-        <v>0.4360732830410502</v>
-      </c>
-      <c r="AF27" s="9">
-        <f t="shared" si="251"/>
-        <v>0.44793447934479341</v>
-      </c>
-      <c r="AG27" s="9">
-        <f t="shared" si="251"/>
-        <v>0.45708436071571806</v>
+        <v>0.43350404757971256</v>
       </c>
       <c r="AH27" s="9">
-        <f t="shared" si="251"/>
-        <v>0.44512012999574418</v>
+        <f t="shared" si="250"/>
+        <v>0.45198301813628711</v>
       </c>
       <c r="AJ27" s="9">
-        <f t="shared" ref="AJ27" si="252">AJ9/AJ5</f>
+        <f t="shared" ref="AJ27" si="251">AJ9/AJ5</f>
         <v>0.44740740740740736</v>
       </c>
       <c r="AK27" s="9">
-        <f t="shared" ref="AK27:AL27" si="253">AK9/AK5</f>
+        <f t="shared" ref="AK27:AL27" si="252">AK9/AK5</f>
         <v>0.4386570998316946</v>
       </c>
       <c r="AL27" s="9">
+        <f t="shared" si="252"/>
+        <v>0.45450967161493477</v>
+      </c>
+      <c r="AM27" s="9">
+        <f t="shared" ref="AM27:AV27" si="253">AM9/AM5</f>
+        <v>0.50953156086091511</v>
+      </c>
+      <c r="AN27" s="9">
         <f t="shared" si="253"/>
-        <v>0.45450967161493477</v>
-      </c>
-      <c r="AM27" s="9">
-        <f t="shared" ref="AM27:AV27" si="254">AM9/AM5</f>
-        <v>0.50953156086091511</v>
-      </c>
-      <c r="AN27" s="9">
+        <v>0.46093325231074295</v>
+      </c>
+      <c r="AO27" s="9">
+        <f t="shared" si="253"/>
+        <v>0.43698347107438018</v>
+      </c>
+      <c r="AP27" s="9">
+        <f t="shared" si="253"/>
+        <v>0.43898169086001887</v>
+      </c>
+      <c r="AQ27" s="9">
+        <f t="shared" si="253"/>
+        <v>0.44279883094958289</v>
+      </c>
+      <c r="AR27" s="9">
+        <f t="shared" si="253"/>
+        <v>0.46374430195017846</v>
+      </c>
+      <c r="AS27" s="9">
+        <f t="shared" si="253"/>
+        <v>0.48028281797447309</v>
+      </c>
+      <c r="AT27" s="9">
+        <f t="shared" si="253"/>
+        <v>0.48488650313122922</v>
+      </c>
+      <c r="AU27" s="9">
+        <f t="shared" si="253"/>
+        <v>0.48631528038344035</v>
+      </c>
+      <c r="AV27" s="9">
+        <f t="shared" si="253"/>
+        <v>0.48725395944549288</v>
+      </c>
+      <c r="AW27" s="9">
+        <f t="shared" ref="AW27:BA27" si="254">AW9/AW5</f>
+        <v>0.48772006825225833</v>
+      </c>
+      <c r="AX27" s="9">
         <f t="shared" si="254"/>
-        <v>0.46093325231074295</v>
-      </c>
-      <c r="AO27" s="9">
+        <v>0.48818250533590479</v>
+      </c>
+      <c r="AY27" s="9">
         <f t="shared" si="254"/>
-        <v>0.43698347107438018</v>
-      </c>
-      <c r="AP27" s="9">
+        <v>0.48864129173213749</v>
+      </c>
+      <c r="AZ27" s="9">
         <f t="shared" si="254"/>
-        <v>0.43898169086001887</v>
-      </c>
-      <c r="AQ27" s="9">
+        <v>0.48909644849740852</v>
+      </c>
+      <c r="BA27" s="9">
         <f t="shared" si="254"/>
-        <v>0.44685429410534089</v>
-      </c>
-      <c r="AR27" s="9">
-        <f t="shared" si="254"/>
-        <v>0.47719188155100351</v>
-      </c>
-      <c r="AS27" s="9">
-        <f t="shared" si="254"/>
-        <v>0.48482564222311098</v>
-      </c>
-      <c r="AT27" s="9">
-        <f t="shared" si="254"/>
-        <v>0.48925810508226569</v>
-      </c>
-      <c r="AU27" s="9">
-        <f t="shared" si="254"/>
-        <v>0.49029707068757206</v>
-      </c>
-      <c r="AV27" s="9">
-        <f t="shared" si="254"/>
-        <v>0.49081317919620265</v>
-      </c>
-      <c r="AW27" s="9">
-        <f t="shared" ref="AW27:BA27" si="255">AW9/AW5</f>
-        <v>0.49133039807816481</v>
-      </c>
-      <c r="AX27" s="9">
-        <f t="shared" si="255"/>
-        <v>0.49184364380748125</v>
-      </c>
-      <c r="AY27" s="9">
-        <f t="shared" si="255"/>
-        <v>0.49235293736659519</v>
-      </c>
-      <c r="AZ27" s="9">
-        <f t="shared" si="255"/>
-        <v>0.49285829979672308</v>
-      </c>
-      <c r="BA27" s="9">
-        <f t="shared" si="255"/>
-        <v>0.49335975219414874</v>
+        <v>0.48954799670584875</v>
       </c>
       <c r="BC27" t="s">
         <v>49</v>
       </c>
       <c r="BD27" s="5">
         <f>NPV(BD26,AP18:FG18)</f>
-        <v>5134.237396951924</v>
+        <v>5459.7680771539344</v>
       </c>
     </row>
     <row r="28" spans="2:163" x14ac:dyDescent="0.3">
@@ -6089,200 +6077,200 @@
         <v>-5.0512445095168418E-2</v>
       </c>
       <c r="D28" s="9">
-        <f t="shared" ref="D28:G28" si="256">D14/D5</f>
+        <f t="shared" ref="D28:G28" si="255">D14/D5</f>
         <v>-6.3775510204078006E-4</v>
       </c>
       <c r="E28" s="9">
+        <f t="shared" si="255"/>
+        <v>-6.8050749711649525E-2</v>
+      </c>
+      <c r="F28" s="9">
+        <f t="shared" si="255"/>
+        <v>1.9949220166847973E-2</v>
+      </c>
+      <c r="G28" s="9">
+        <f t="shared" si="255"/>
+        <v>-5.1765844218674494E-2</v>
+      </c>
+      <c r="H28" s="9">
+        <f t="shared" ref="H28:N28" si="256">H14/H5</f>
+        <v>-4.1583366653338685E-2</v>
+      </c>
+      <c r="I28" s="9">
         <f t="shared" si="256"/>
-        <v>-6.8050749711649525E-2</v>
-      </c>
-      <c r="F28" s="9">
+        <v>-0.10233806055960146</v>
+      </c>
+      <c r="J28" s="9">
         <f t="shared" si="256"/>
-        <v>1.9949220166847973E-2</v>
-      </c>
-      <c r="G28" s="9">
+        <v>-4.2071984435797551E-2</v>
+      </c>
+      <c r="K28" s="9">
         <f t="shared" si="256"/>
-        <v>-5.1765844218674494E-2</v>
-      </c>
-      <c r="H28" s="9">
-        <f t="shared" ref="H28:N28" si="257">H14/H5</f>
-        <v>-4.1583366653338685E-2</v>
-      </c>
-      <c r="I28" s="9">
+        <v>-0.17144638403990026</v>
+      </c>
+      <c r="L28" s="9">
+        <f t="shared" si="256"/>
+        <v>-0.11850603762987921</v>
+      </c>
+      <c r="M28" s="9">
+        <f t="shared" si="256"/>
+        <v>2.6129317980513815E-2</v>
+      </c>
+      <c r="N28" s="9">
+        <f t="shared" si="256"/>
+        <v>0.10032312663486689</v>
+      </c>
+      <c r="O28" s="9">
+        <f t="shared" ref="O28:R28" si="257">O14/O5</f>
+        <v>0.13200975269940798</v>
+      </c>
+      <c r="P28" s="9">
         <f t="shared" si="257"/>
-        <v>-0.10233806055960146</v>
-      </c>
-      <c r="J28" s="9">
+        <v>0.10711517594171434</v>
+      </c>
+      <c r="Q28" s="9">
         <f t="shared" si="257"/>
-        <v>-4.2071984435797551E-2</v>
-      </c>
-      <c r="K28" s="9">
+        <v>0.10119135166936308</v>
+      </c>
+      <c r="R28" s="9">
         <f t="shared" si="257"/>
-        <v>-0.17144638403990026</v>
-      </c>
-      <c r="L28" s="9">
-        <f t="shared" si="257"/>
-        <v>-0.11850603762987921</v>
-      </c>
-      <c r="M28" s="9">
-        <f t="shared" si="257"/>
-        <v>2.6129317980513815E-2</v>
-      </c>
-      <c r="N28" s="9">
-        <f t="shared" si="257"/>
-        <v>0.10032312663486689</v>
-      </c>
-      <c r="O28" s="9">
-        <f t="shared" ref="O28:R28" si="258">O14/O5</f>
-        <v>0.13200975269940798</v>
-      </c>
-      <c r="P28" s="9">
+        <v>2.461574020570895E-2</v>
+      </c>
+      <c r="S28" s="9">
+        <f t="shared" ref="S28:AA28" si="258">S14/S5</f>
+        <v>-3.2029439825541857E-2</v>
+      </c>
+      <c r="T28" s="9">
         <f t="shared" si="258"/>
-        <v>0.10711517594171434</v>
-      </c>
-      <c r="Q28" s="9">
+        <v>-0.14453891432308705</v>
+      </c>
+      <c r="U28" s="9">
         <f t="shared" si="258"/>
-        <v>0.10119135166936308</v>
-      </c>
-      <c r="R28" s="9">
+        <v>-0.19306540583136317</v>
+      </c>
+      <c r="V28" s="9">
         <f t="shared" si="258"/>
-        <v>2.461574020570895E-2</v>
-      </c>
-      <c r="S28" s="9">
-        <f t="shared" ref="S28:AA28" si="259">S14/S5</f>
-        <v>-3.2029439825541857E-2</v>
-      </c>
-      <c r="T28" s="9">
+        <v>-0.28820205281974409</v>
+      </c>
+      <c r="W28" s="9">
+        <f t="shared" si="258"/>
+        <v>-0.28677462887989214</v>
+      </c>
+      <c r="X28" s="9">
+        <f t="shared" si="258"/>
+        <v>-0.14858963767260716</v>
+      </c>
+      <c r="Y28" s="9">
+        <f t="shared" si="258"/>
+        <v>-0.38355263157894731</v>
+      </c>
+      <c r="Z28" s="9">
+        <f t="shared" si="258"/>
+        <v>-0.10573895378364655</v>
+      </c>
+      <c r="AA28" s="9">
+        <f t="shared" si="258"/>
+        <v>-8.1688223281143696E-2</v>
+      </c>
+      <c r="AB28" s="9">
+        <f t="shared" ref="AB28:AD28" si="259">AB14/AB5</f>
+        <v>-7.3752711496746309E-2</v>
+      </c>
+      <c r="AC28" s="9">
         <f t="shared" si="259"/>
-        <v>-0.14453891432308705</v>
-      </c>
-      <c r="U28" s="9">
+        <v>-3.3609489738278868E-2</v>
+      </c>
+      <c r="AD28" s="9">
         <f t="shared" si="259"/>
-        <v>-0.19306540583136317</v>
-      </c>
-      <c r="V28" s="9">
-        <f t="shared" si="259"/>
-        <v>-0.28820205281974409</v>
-      </c>
-      <c r="W28" s="9">
-        <f t="shared" si="259"/>
-        <v>-0.28677462887989214</v>
-      </c>
-      <c r="X28" s="9">
-        <f t="shared" si="259"/>
-        <v>-0.14858963767260716</v>
-      </c>
-      <c r="Y28" s="9">
-        <f t="shared" si="259"/>
-        <v>-0.38355263157894731</v>
-      </c>
-      <c r="Z28" s="9">
-        <f t="shared" si="259"/>
-        <v>-0.10573895378364655</v>
-      </c>
-      <c r="AA28" s="9">
-        <f t="shared" si="259"/>
-        <v>-8.1688223281143696E-2</v>
-      </c>
-      <c r="AB28" s="9">
-        <f t="shared" ref="AB28:AD28" si="260">AB14/AB5</f>
-        <v>-7.3752711496746309E-2</v>
-      </c>
-      <c r="AC28" s="9">
+        <v>-3.2639467110740991E-2</v>
+      </c>
+      <c r="AE28" s="9">
+        <f t="shared" ref="AE28:AH28" si="260">AE14/AE5</f>
+        <v>-5.6529832467914223E-2</v>
+      </c>
+      <c r="AF28" s="9">
         <f t="shared" si="260"/>
-        <v>-3.3609489738278868E-2</v>
-      </c>
-      <c r="AD28" s="9">
+        <v>-2.0970209702097085E-2</v>
+      </c>
+      <c r="AG28" s="9">
         <f t="shared" si="260"/>
-        <v>-3.2639467110740991E-2</v>
-      </c>
-      <c r="AE28" s="9">
-        <f t="shared" ref="AE28:AH28" si="261">AE14/AE5</f>
-        <v>-5.6529832467914223E-2</v>
-      </c>
-      <c r="AF28" s="9">
-        <f t="shared" si="261"/>
-        <v>-2.0970209702097085E-2</v>
-      </c>
-      <c r="AG28" s="9">
-        <f t="shared" si="261"/>
-        <v>-1.0441883016332735E-2</v>
+        <v>7.7647447546670889E-3</v>
       </c>
       <c r="AH28" s="9">
-        <f t="shared" si="261"/>
-        <v>6.4927169459496432E-3</v>
+        <f t="shared" si="260"/>
+        <v>2.8715141594465855E-2</v>
       </c>
       <c r="AJ28" s="9">
-        <f t="shared" ref="AJ28" si="262">AJ14/AJ5</f>
+        <f t="shared" ref="AJ28" si="261">AJ14/AJ5</f>
         <v>-1.7912457912457928E-2</v>
       </c>
       <c r="AK28" s="9">
-        <f t="shared" ref="AK28:AL28" si="263">AK14/AK5</f>
+        <f t="shared" ref="AK28:AL28" si="262">AK14/AK5</f>
         <v>-5.7666755248471882E-2</v>
       </c>
       <c r="AL28" s="9">
+        <f t="shared" si="262"/>
+        <v>-1.1358524516419279E-2</v>
+      </c>
+      <c r="AM28" s="9">
+        <f t="shared" ref="AM28:AV28" si="263">AM14/AM5</f>
+        <v>8.5006330258636201E-2</v>
+      </c>
+      <c r="AN28" s="9">
         <f t="shared" si="263"/>
-        <v>-1.1358524516419279E-2</v>
-      </c>
-      <c r="AM28" s="9">
-        <f t="shared" ref="AM28:AV28" si="264">AM14/AM5</f>
-        <v>8.5006330258636201E-2</v>
-      </c>
-      <c r="AN28" s="9">
+        <v>-0.16979563117664001</v>
+      </c>
+      <c r="AO28" s="9">
+        <f t="shared" si="263"/>
+        <v>-0.22735881542699715</v>
+      </c>
+      <c r="AP28" s="9">
+        <f t="shared" si="263"/>
+        <v>-5.3079485496146134E-2</v>
+      </c>
+      <c r="AQ28" s="9">
+        <f t="shared" si="263"/>
+        <v>-6.9873175329440507E-3</v>
+      </c>
+      <c r="AR28" s="9">
+        <f t="shared" si="263"/>
+        <v>3.4333804578847944E-2</v>
+      </c>
+      <c r="AS28" s="9">
+        <f t="shared" si="263"/>
+        <v>7.3083478740872385E-2</v>
+      </c>
+      <c r="AT28" s="9">
+        <f t="shared" si="263"/>
+        <v>9.5767939587394005E-2</v>
+      </c>
+      <c r="AU28" s="9">
+        <f t="shared" si="263"/>
+        <v>0.10235872052740976</v>
+      </c>
+      <c r="AV28" s="9">
+        <f t="shared" si="263"/>
+        <v>0.10668873632335923</v>
+      </c>
+      <c r="AW28" s="9">
+        <f t="shared" ref="AW28:BA28" si="264">AW14/AW5</f>
+        <v>0.10883884127138278</v>
+      </c>
+      <c r="AX28" s="9">
         <f t="shared" si="264"/>
-        <v>-0.16979563117664001</v>
-      </c>
-      <c r="AO28" s="9">
+        <v>0.11097200899373869</v>
+      </c>
+      <c r="AY28" s="9">
         <f t="shared" si="264"/>
-        <v>-0.22735881542699715</v>
-      </c>
-      <c r="AP28" s="9">
+        <v>0.11308833652565459</v>
+      </c>
+      <c r="AZ28" s="9">
         <f t="shared" si="264"/>
-        <v>-5.3079485496146134E-2</v>
-      </c>
-      <c r="AQ28" s="9">
+        <v>0.11518792099805884</v>
+      </c>
+      <c r="BA28" s="9">
         <f t="shared" si="264"/>
-        <v>-1.8304232714560473E-2</v>
-      </c>
-      <c r="AR28" s="9">
-        <f t="shared" si="264"/>
-        <v>3.9388076329756438E-2</v>
-      </c>
-      <c r="AS28" s="9">
-        <f t="shared" si="264"/>
-        <v>6.9847781190379571E-2</v>
-      </c>
-      <c r="AT28" s="9">
-        <f t="shared" si="264"/>
-        <v>9.2806245857962891E-2</v>
-      </c>
-      <c r="AU28" s="9">
-        <f t="shared" si="264"/>
-        <v>9.8667174673128313E-2</v>
-      </c>
-      <c r="AV28" s="9">
-        <f t="shared" si="264"/>
-        <v>0.10219328044561934</v>
-      </c>
-      <c r="AW28" s="9">
-        <f t="shared" ref="AW28:BA28" si="265">AW14/AW5</f>
-        <v>0.10375275422032769</v>
-      </c>
-      <c r="AX28" s="9">
-        <f t="shared" si="265"/>
-        <v>0.10530024848777149</v>
-      </c>
-      <c r="AY28" s="9">
-        <f t="shared" si="265"/>
-        <v>0.10683582651240421</v>
-      </c>
-      <c r="AZ28" s="9">
-        <f t="shared" si="265"/>
-        <v>0.10835955173588692</v>
-      </c>
-      <c r="BA28" s="9">
-        <f t="shared" si="265"/>
-        <v>0.10987148776591624</v>
+        <v>0.11727085962343275</v>
       </c>
       <c r="BC28" t="s">
         <v>50</v>
@@ -6301,184 +6289,184 @@
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
       <c r="G29" s="9">
-        <f t="shared" ref="G29:N29" si="266">G10/C10-1</f>
+        <f t="shared" ref="G29:N29" si="265">G10/C10-1</f>
         <v>0.63343108504398837</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" si="266"/>
+        <f t="shared" si="265"/>
         <v>0.54228855721393021</v>
       </c>
       <c r="I29" s="9">
-        <f t="shared" si="266"/>
+        <f t="shared" si="265"/>
         <v>0.50881057268722474</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="266"/>
+        <f t="shared" si="265"/>
         <v>0.54509803921568611</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="266"/>
+        <f t="shared" si="265"/>
         <v>0.58527827648114883</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" si="266"/>
+        <f t="shared" si="265"/>
         <v>0.3612903225806452</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" si="266"/>
+        <f t="shared" si="265"/>
         <v>0.29051094890510964</v>
       </c>
       <c r="N29" s="9">
-        <f t="shared" si="266"/>
+        <f t="shared" si="265"/>
         <v>0.20177664974619303</v>
       </c>
       <c r="O29" s="9">
-        <f t="shared" ref="O29" si="267">O10/K10-1</f>
+        <f t="shared" ref="O29" si="266">O10/K10-1</f>
         <v>0.15062287655719131</v>
       </c>
       <c r="P29" s="9">
-        <f t="shared" ref="P29" si="268">P10/L10-1</f>
+        <f t="shared" ref="P29" si="267">P10/L10-1</f>
         <v>0.3424170616113742</v>
       </c>
       <c r="Q29" s="9">
-        <f t="shared" ref="Q29" si="269">Q10/M10-1</f>
+        <f t="shared" ref="Q29" si="268">Q10/M10-1</f>
         <v>0.36085972850678716</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" ref="R29" si="270">R10/N10-1</f>
+        <f t="shared" ref="R29" si="269">R10/N10-1</f>
         <v>0.33474128827877503</v>
       </c>
       <c r="S29" s="9">
-        <f t="shared" ref="S29" si="271">S10/O10-1</f>
+        <f t="shared" ref="S29" si="270">S10/O10-1</f>
         <v>0.61417322834645671</v>
       </c>
       <c r="T29" s="9">
-        <f t="shared" ref="T29" si="272">T10/P10-1</f>
+        <f t="shared" ref="T29" si="271">T10/P10-1</f>
         <v>0.73521624007060904</v>
       </c>
       <c r="U29" s="9">
-        <f t="shared" ref="U29" si="273">U10/Q10-1</f>
+        <f t="shared" ref="U29" si="272">U10/Q10-1</f>
         <v>0.72568578553615959</v>
       </c>
       <c r="V29" s="9">
-        <f t="shared" ref="V29" si="274">V10/R10-1</f>
+        <f t="shared" ref="V29" si="273">V10/R10-1</f>
         <v>0.74604430379746822</v>
       </c>
       <c r="W29" s="9">
-        <f t="shared" ref="W29" si="275">W10/S10-1</f>
+        <f t="shared" ref="W29" si="274">W10/S10-1</f>
         <v>0.34207317073170729</v>
       </c>
       <c r="X29" s="9">
-        <f t="shared" ref="X29" si="276">X10/T10-1</f>
+        <f t="shared" ref="X29" si="275">X10/T10-1</f>
         <v>-2.1363173957273607E-2</v>
       </c>
       <c r="Y29" s="9">
-        <f t="shared" ref="Y29" si="277">Y10/U10-1</f>
+        <f t="shared" ref="Y29" si="276">Y10/U10-1</f>
         <v>0.359344894026975</v>
       </c>
       <c r="Z29" s="9">
-        <f t="shared" ref="Z29" si="278">Z10/V10-1</f>
+        <f t="shared" ref="Z29" si="277">Z10/V10-1</f>
         <v>-0.16719528772088799</v>
       </c>
       <c r="AA29" s="9">
-        <f t="shared" ref="AA29" si="279">AA10/W10-1</f>
+        <f t="shared" ref="AA29" si="278">AA10/W10-1</f>
         <v>-0.18037255792821438</v>
       </c>
       <c r="AB29" s="9">
-        <f t="shared" ref="AB29" si="280">AB10/X10-1</f>
+        <f t="shared" ref="AB29" si="279">AB10/X10-1</f>
         <v>-8.7837837837837829E-2</v>
       </c>
       <c r="AC29" s="9">
-        <f t="shared" ref="AC29" si="281">AC10/Y10-1</f>
+        <f t="shared" ref="AC29" si="280">AC10/Y10-1</f>
         <v>-0.36640680368532952</v>
       </c>
       <c r="AD29" s="9">
-        <f t="shared" ref="AD29" si="282">AD10/Z10-1</f>
+        <f t="shared" ref="AD29" si="281">AD10/Z10-1</f>
         <v>8.705114254624613E-3</v>
       </c>
       <c r="AE29" s="9">
-        <f t="shared" ref="AE29" si="283">AE10/AA10-1</f>
+        <f t="shared" ref="AE29" si="282">AE10/AA10-1</f>
         <v>2.3281596452328079E-2</v>
       </c>
       <c r="AF29" s="9">
-        <f t="shared" ref="AF29" si="284">AF10/AB10-1</f>
+        <f t="shared" ref="AF29" si="283">AF10/AB10-1</f>
         <v>1.4245014245014342E-2</v>
       </c>
       <c r="AG29" s="9">
-        <f t="shared" ref="AG29" si="285">AG10/AC10-1</f>
-        <v>6.0000000000000053E-2</v>
+        <f t="shared" ref="AG29" si="284">AG10/AC10-1</f>
+        <v>1.9015659955257114E-2</v>
       </c>
       <c r="AH29" s="9">
-        <f t="shared" ref="AH29" si="286">AH10/AD10-1</f>
+        <f t="shared" ref="AH29" si="285">AH10/AD10-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ29" s="9"/>
       <c r="AK29" s="9">
-        <f t="shared" ref="AK29" si="287">AK10/AJ10-1</f>
+        <f t="shared" ref="AK29" si="286">AK10/AJ10-1</f>
         <v>0.55243116578793194</v>
       </c>
       <c r="AL29" s="9">
-        <f t="shared" ref="AL29" si="288">AL10/AK10-1</f>
+        <f t="shared" ref="AL29" si="287">AL10/AK10-1</f>
         <v>0.34264150943396232</v>
       </c>
       <c r="AM29" s="9">
-        <f t="shared" ref="AM29" si="289">AM10/AL10-1</f>
+        <f t="shared" ref="AM29" si="288">AM10/AL10-1</f>
         <v>0.29735806632939865</v>
       </c>
       <c r="AN29" s="9">
-        <f t="shared" ref="AN29" si="290">AN10/AM10-1</f>
+        <f t="shared" ref="AN29" si="289">AN10/AM10-1</f>
         <v>0.70905545927209723</v>
       </c>
       <c r="AO29" s="9">
-        <f t="shared" ref="AO29" si="291">AO10/AN10-1</f>
+        <f t="shared" ref="AO29" si="290">AO10/AN10-1</f>
         <v>0.11357586512866003</v>
       </c>
       <c r="AP29" s="9">
-        <f t="shared" ref="AP29" si="292">AP10/AO10-1</f>
+        <f t="shared" ref="AP29" si="291">AP10/AO10-1</f>
         <v>-0.18030734206033006</v>
       </c>
       <c r="AQ29" s="9">
-        <f t="shared" ref="AQ29" si="293">AQ10/AP10-1</f>
-        <v>3.1926121372031657E-2</v>
+        <f t="shared" ref="AQ29" si="292">AQ10/AP10-1</f>
+        <v>2.1749756978197254E-2</v>
       </c>
       <c r="AR29" s="9">
-        <f t="shared" ref="AR29" si="294">AR10/AQ10-1</f>
+        <f t="shared" ref="AR29" si="293">AR10/AQ10-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AS29" s="9">
-        <f t="shared" ref="AS29" si="295">AS10/AR10-1</f>
+        <f t="shared" ref="AS29" si="294">AS10/AR10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AT29" s="9">
-        <f t="shared" ref="AT29" si="296">AT10/AS10-1</f>
+        <f t="shared" ref="AT29" si="295">AT10/AS10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AU29" s="9">
-        <f t="shared" ref="AU29" si="297">AU10/AT10-1</f>
+        <f t="shared" ref="AU29" si="296">AU10/AT10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AV29" s="9">
-        <f t="shared" ref="AV29:AW29" si="298">AV10/AU10-1</f>
+        <f t="shared" ref="AV29:AW29" si="297">AV10/AU10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AW29" s="9">
-        <f t="shared" si="298"/>
+        <f t="shared" si="297"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX29" s="9">
-        <f t="shared" ref="AX29" si="299">AX10/AW10-1</f>
+        <f t="shared" ref="AX29" si="298">AX10/AW10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY29" s="9">
-        <f t="shared" ref="AY29" si="300">AY10/AX10-1</f>
+        <f t="shared" ref="AY29" si="299">AY10/AX10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ29" s="9">
-        <f t="shared" ref="AZ29" si="301">AZ10/AY10-1</f>
+        <f t="shared" ref="AZ29" si="300">AZ10/AY10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA29" s="9">
-        <f t="shared" ref="BA29" si="302">BA10/AZ10-1</f>
+        <f t="shared" ref="BA29" si="301">BA10/AZ10-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BC29" t="s">
@@ -6486,7 +6474,7 @@
       </c>
       <c r="BD29" s="5">
         <f>BD27+BD28</f>
-        <v>7387.5373969519242</v>
+        <v>7713.0680771539346</v>
       </c>
     </row>
     <row r="30" spans="2:163" x14ac:dyDescent="0.3">
@@ -6498,199 +6486,199 @@
         <v>0.14860907759882871</v>
       </c>
       <c r="D30" s="9">
-        <f t="shared" ref="D30:G30" si="303">D11/D5</f>
+        <f t="shared" ref="D30:G30" si="302">D11/D5</f>
         <v>0.14221938775510204</v>
       </c>
       <c r="E30" s="9">
+        <f t="shared" si="302"/>
+        <v>0.14763552479815459</v>
+      </c>
+      <c r="F30" s="9">
+        <f t="shared" si="302"/>
+        <v>0.12549873050417121</v>
+      </c>
+      <c r="G30" s="9">
+        <f t="shared" si="302"/>
+        <v>0.16352201257861634</v>
+      </c>
+      <c r="H30" s="9">
+        <f t="shared" ref="H30:N30" si="303">H11/H5</f>
+        <v>0.14634146341463417</v>
+      </c>
+      <c r="I30" s="9">
         <f t="shared" si="303"/>
-        <v>0.14763552479815459</v>
-      </c>
-      <c r="F30" s="9">
+        <v>0.17899578382522041</v>
+      </c>
+      <c r="J30" s="9">
         <f t="shared" si="303"/>
-        <v>0.12549873050417121</v>
-      </c>
-      <c r="G30" s="9">
+        <v>0.15029182879377428</v>
+      </c>
+      <c r="K30" s="9">
         <f t="shared" si="303"/>
-        <v>0.16352201257861634</v>
-      </c>
-      <c r="H30" s="9">
-        <f t="shared" ref="H30:N30" si="304">H11/H5</f>
-        <v>0.14634146341463417</v>
-      </c>
-      <c r="I30" s="9">
+        <v>0.21259351620947631</v>
+      </c>
+      <c r="L30" s="9">
+        <f t="shared" si="303"/>
+        <v>0.18028643639427128</v>
+      </c>
+      <c r="M30" s="9">
+        <f t="shared" si="303"/>
+        <v>0.15721877767936226</v>
+      </c>
+      <c r="N30" s="9">
+        <f t="shared" si="303"/>
+        <v>0.1478689029081397</v>
+      </c>
+      <c r="O30" s="9">
+        <f t="shared" ref="O30:R30" si="304">O11/O5</f>
+        <v>0.15482410309996517</v>
+      </c>
+      <c r="P30" s="9">
         <f t="shared" si="304"/>
-        <v>0.17899578382522041</v>
-      </c>
-      <c r="J30" s="9">
+        <v>0.14524879863587042</v>
+      </c>
+      <c r="Q30" s="9">
         <f t="shared" si="304"/>
-        <v>0.15029182879377428</v>
-      </c>
-      <c r="K30" s="9">
+        <v>0.1613472569495514</v>
+      </c>
+      <c r="R30" s="9">
         <f t="shared" si="304"/>
-        <v>0.21259351620947631</v>
-      </c>
-      <c r="L30" s="9">
-        <f t="shared" si="304"/>
-        <v>0.18028643639427128</v>
-      </c>
-      <c r="M30" s="9">
-        <f t="shared" si="304"/>
-        <v>0.15721877767936226</v>
-      </c>
-      <c r="N30" s="9">
-        <f t="shared" si="304"/>
-        <v>0.1478689029081397</v>
-      </c>
-      <c r="O30" s="9">
-        <f t="shared" ref="O30:R30" si="305">O11/O5</f>
-        <v>0.15482410309996517</v>
-      </c>
-      <c r="P30" s="9">
+        <v>0.18883624176586156</v>
+      </c>
+      <c r="S30" s="9">
+        <f t="shared" ref="S30:AA30" si="305">S11/S5</f>
+        <v>0.19967289082731363</v>
+      </c>
+      <c r="T30" s="9">
         <f t="shared" si="305"/>
-        <v>0.14524879863587042</v>
-      </c>
-      <c r="Q30" s="9">
+        <v>0.2419882275997384</v>
+      </c>
+      <c r="U30" s="9">
         <f t="shared" si="305"/>
-        <v>0.1613472569495514</v>
-      </c>
-      <c r="R30" s="9">
+        <v>0.2750197005516154</v>
+      </c>
+      <c r="V30" s="9">
         <f t="shared" si="305"/>
-        <v>0.18883624176586156</v>
-      </c>
-      <c r="S30" s="9">
-        <f t="shared" ref="S30:AA30" si="306">S11/S5</f>
-        <v>0.19967289082731363</v>
-      </c>
-      <c r="T30" s="9">
+        <v>0.34321300888017536</v>
+      </c>
+      <c r="W30" s="9">
+        <f t="shared" si="305"/>
+        <v>0.31565452091767882</v>
+      </c>
+      <c r="X30" s="9">
+        <f t="shared" si="305"/>
+        <v>0.26814587513277471</v>
+      </c>
+      <c r="Y30" s="9">
+        <f t="shared" si="305"/>
+        <v>0.33739035087719299</v>
+      </c>
+      <c r="Z30" s="9">
+        <f t="shared" si="305"/>
+        <v>0.26876587100050792</v>
+      </c>
+      <c r="AA30" s="9">
+        <f t="shared" si="305"/>
+        <v>0.22929430451554345</v>
+      </c>
+      <c r="AB30" s="9">
+        <f t="shared" ref="AB30:AD30" si="306">AB11/AB5</f>
+        <v>0.22900526805082119</v>
+      </c>
+      <c r="AC30" s="9">
         <f t="shared" si="306"/>
-        <v>0.2419882275997384</v>
-      </c>
-      <c r="U30" s="9">
+        <v>0.22312182263227262</v>
+      </c>
+      <c r="AD30" s="9">
         <f t="shared" si="306"/>
-        <v>0.2750197005516154</v>
-      </c>
-      <c r="V30" s="9">
-        <f t="shared" si="306"/>
-        <v>0.34321300888017536</v>
-      </c>
-      <c r="W30" s="9">
-        <f t="shared" si="306"/>
-        <v>0.31565452091767882</v>
-      </c>
-      <c r="X30" s="9">
-        <f t="shared" si="306"/>
-        <v>0.26814587513277471</v>
-      </c>
-      <c r="Y30" s="9">
-        <f t="shared" si="306"/>
-        <v>0.33739035087719299</v>
-      </c>
-      <c r="Z30" s="9">
-        <f t="shared" si="306"/>
-        <v>0.26876587100050792</v>
-      </c>
-      <c r="AA30" s="9">
-        <f t="shared" si="306"/>
-        <v>0.22929430451554345</v>
-      </c>
-      <c r="AB30" s="9">
-        <f t="shared" ref="AB30:AD30" si="307">AB11/AB5</f>
-        <v>0.22900526805082119</v>
-      </c>
-      <c r="AC30" s="9">
+        <v>0.22639467110741046</v>
+      </c>
+      <c r="AE30" s="9">
+        <f t="shared" ref="AE30:AH30" si="307">AE11/AE5</f>
+        <v>0.21916331929068286</v>
+      </c>
+      <c r="AF30" s="9">
         <f t="shared" si="307"/>
-        <v>0.22312182263227262</v>
-      </c>
-      <c r="AD30" s="9">
+        <v>0.21897218972189725</v>
+      </c>
+      <c r="AG30" s="9">
         <f t="shared" si="307"/>
-        <v>0.22639467110741046</v>
-      </c>
-      <c r="AE30" s="9">
-        <f t="shared" ref="AE30:AH30" si="308">AE11/AE5</f>
-        <v>0.21916331929068286</v>
-      </c>
-      <c r="AF30" s="9">
-        <f t="shared" si="308"/>
-        <v>0.21897218972189725</v>
-      </c>
-      <c r="AG30" s="9">
-        <f t="shared" si="308"/>
-        <v>0.22</v>
+        <v>0.19998347926647944</v>
       </c>
       <c r="AH30" s="9">
-        <f t="shared" si="308"/>
-        <v>0.22</v>
+        <f t="shared" si="307"/>
+        <v>0.21000000000000002</v>
       </c>
       <c r="AJ30" s="9">
-        <f t="shared" ref="AJ30" si="309">AJ11/AJ5</f>
+        <f t="shared" ref="AJ30" si="308">AJ11/AJ5</f>
         <v>0.13845117845117846</v>
       </c>
       <c r="AK30" s="9">
-        <f t="shared" ref="AK30:AL30" si="310">AK11/AK5</f>
+        <f t="shared" ref="AK30:AL30" si="309">AK11/AK5</f>
         <v>0.15847284967667641</v>
       </c>
       <c r="AL30" s="9">
+        <f t="shared" si="309"/>
+        <v>0.16840980656770133</v>
+      </c>
+      <c r="AM30" s="9">
+        <f t="shared" ref="AM30:AV30" si="310">AM11/AM5</f>
+        <v>0.16483993488876833</v>
+      </c>
+      <c r="AN30" s="9">
         <f t="shared" si="310"/>
-        <v>0.16840980656770133</v>
-      </c>
-      <c r="AM30" s="9">
-        <f t="shared" ref="AM30:AV30" si="311">AM11/AM5</f>
-        <v>0.16483993488876833</v>
-      </c>
-      <c r="AN30" s="9">
-        <f t="shared" si="311"/>
         <v>0.26817411328237439</v>
       </c>
       <c r="AO30" s="9">
-        <f t="shared" si="311"/>
+        <f t="shared" si="310"/>
         <v>0.29654499540863177</v>
       </c>
       <c r="AP30" s="9">
-        <f t="shared" si="311"/>
+        <f t="shared" si="310"/>
         <v>0.22678532351010283</v>
       </c>
       <c r="AQ30" s="9">
-        <f t="shared" si="311"/>
-        <v>0.21956906630096312</v>
+        <f t="shared" si="310"/>
+        <v>0.2115331110222928</v>
       </c>
       <c r="AR30" s="9">
-        <f t="shared" si="311"/>
-        <v>0.20999999999999996</v>
+        <f t="shared" si="310"/>
+        <v>0.21</v>
       </c>
       <c r="AS30" s="9">
-        <f t="shared" si="311"/>
-        <v>0.2</v>
+        <f t="shared" si="310"/>
+        <v>0.19999999999999998</v>
       </c>
       <c r="AT30" s="9">
+        <f t="shared" si="310"/>
+        <v>0.19</v>
+      </c>
+      <c r="AU30" s="9">
+        <f t="shared" si="310"/>
+        <v>0.19000000000000003</v>
+      </c>
+      <c r="AV30" s="9">
+        <f t="shared" si="310"/>
+        <v>0.19</v>
+      </c>
+      <c r="AW30" s="9">
+        <f t="shared" ref="AW30:BA30" si="311">AW11/AW5</f>
+        <v>0.19</v>
+      </c>
+      <c r="AX30" s="9">
         <f t="shared" si="311"/>
         <v>0.19</v>
       </c>
-      <c r="AU30" s="9">
+      <c r="AY30" s="9">
         <f t="shared" si="311"/>
-        <v>0.18999999999999997</v>
-      </c>
-      <c r="AV30" s="9">
+        <v>0.19</v>
+      </c>
+      <c r="AZ30" s="9">
         <f t="shared" si="311"/>
-        <v>0.18999999999999997</v>
-      </c>
-      <c r="AW30" s="9">
-        <f t="shared" ref="AW30:BA30" si="312">AW11/AW5</f>
         <v>0.19</v>
       </c>
-      <c r="AX30" s="9">
-        <f t="shared" si="312"/>
-        <v>0.19</v>
-      </c>
-      <c r="AY30" s="9">
-        <f t="shared" si="312"/>
-        <v>0.19</v>
-      </c>
-      <c r="AZ30" s="9">
-        <f t="shared" si="312"/>
-        <v>0.19000000000000003</v>
-      </c>
       <c r="BA30" s="9">
-        <f t="shared" si="312"/>
+        <f t="shared" si="311"/>
         <v>0.19</v>
       </c>
       <c r="BC30" t="s">
@@ -6698,7 +6686,7 @@
       </c>
       <c r="BD30" s="11">
         <f>BD29/AV19</f>
-        <v>50.289567031667282</v>
+        <v>52.291986963755491</v>
       </c>
     </row>
     <row r="31" spans="2:163" x14ac:dyDescent="0.3">
@@ -6710,192 +6698,192 @@
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
       <c r="G31" s="9">
-        <f t="shared" ref="G31:N31" si="313">G12/C12-1</f>
+        <f t="shared" ref="G31:N31" si="312">G12/C12-1</f>
         <v>0.41666666666666674</v>
       </c>
       <c r="H31" s="9">
-        <f t="shared" si="313"/>
+        <f t="shared" si="312"/>
         <v>0.68831168831168821</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" si="313"/>
+        <f t="shared" si="312"/>
         <v>0.51010101010100994</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" si="313"/>
+        <f t="shared" si="312"/>
         <v>0.81132075471698117</v>
       </c>
       <c r="K31" s="9">
-        <f t="shared" si="313"/>
+        <f t="shared" si="312"/>
         <v>0.79638009049773761</v>
       </c>
       <c r="L31" s="9">
-        <f t="shared" si="313"/>
+        <f t="shared" si="312"/>
         <v>0.55769230769230771</v>
       </c>
       <c r="M31" s="9">
-        <f t="shared" si="313"/>
+        <f t="shared" si="312"/>
         <v>0.45484949832775934</v>
       </c>
       <c r="N31" s="9">
-        <f t="shared" si="313"/>
+        <f t="shared" si="312"/>
         <v>0.2890625</v>
       </c>
       <c r="O31" s="9">
-        <f t="shared" ref="O31" si="314">O12/K12-1</f>
+        <f t="shared" ref="O31" si="313">O12/K12-1</f>
         <v>0.52392947103274556</v>
       </c>
       <c r="P31" s="9">
-        <f t="shared" ref="P31" si="315">P12/L12-1</f>
+        <f t="shared" ref="P31" si="314">P12/L12-1</f>
         <v>0.53580246913580254</v>
       </c>
       <c r="Q31" s="9">
-        <f t="shared" ref="Q31" si="316">Q12/M12-1</f>
+        <f t="shared" ref="Q31" si="315">Q12/M12-1</f>
         <v>0.49655172413793092</v>
       </c>
       <c r="R31" s="9">
-        <f t="shared" ref="R31" si="317">R12/N12-1</f>
+        <f t="shared" ref="R31" si="316">R12/N12-1</f>
         <v>0.38383838383838387</v>
       </c>
       <c r="S31" s="9">
-        <f t="shared" ref="S31" si="318">S12/O12-1</f>
+        <f t="shared" ref="S31" si="317">S12/O12-1</f>
         <v>0.28595041322314052</v>
       </c>
       <c r="T31" s="9">
-        <f t="shared" ref="T31" si="319">T12/P12-1</f>
+        <f t="shared" ref="T31" si="318">T12/P12-1</f>
         <v>0.35209003215434076</v>
       </c>
       <c r="U31" s="9">
-        <f t="shared" ref="U31" si="320">U12/Q12-1</f>
+        <f t="shared" ref="U31" si="319">U12/Q12-1</f>
         <v>0.33333333333333348</v>
       </c>
       <c r="V31" s="9">
-        <f t="shared" ref="V31" si="321">V12/R12-1</f>
+        <f t="shared" ref="V31" si="320">V12/R12-1</f>
         <v>0.4014598540145986</v>
       </c>
       <c r="W31" s="9">
-        <f t="shared" ref="W31" si="322">W12/S12-1</f>
+        <f t="shared" ref="W31" si="321">W12/S12-1</f>
         <v>0.23521850899742924</v>
       </c>
       <c r="X31" s="9">
-        <f t="shared" ref="X31" si="323">X12/T12-1</f>
+        <f t="shared" ref="X31" si="322">X12/T12-1</f>
         <v>7.1343638525565023E-3</v>
       </c>
       <c r="Y31" s="9">
-        <f t="shared" ref="Y31" si="324">Y12/U12-1</f>
+        <f t="shared" ref="Y31" si="323">Y12/U12-1</f>
         <v>0.48271889400921641</v>
       </c>
       <c r="Z31" s="9">
-        <f t="shared" ref="Z31" si="325">Z12/V12-1</f>
+        <f t="shared" ref="Z31" si="324">Z12/V12-1</f>
         <v>-2.3958333333333304E-2</v>
       </c>
       <c r="AA31" s="9">
-        <f t="shared" ref="AA31" si="326">AA12/W12-1</f>
+        <f t="shared" ref="AA31" si="325">AA12/W12-1</f>
         <v>-0.19146722164412067</v>
       </c>
       <c r="AB31" s="9">
-        <f t="shared" ref="AB31" si="327">AB12/X12-1</f>
+        <f t="shared" ref="AB31" si="326">AB12/X12-1</f>
         <v>0.166469893742621</v>
       </c>
       <c r="AC31" s="9">
-        <f t="shared" ref="AC31" si="328">AC12/Y12-1</f>
+        <f t="shared" ref="AC31" si="327">AC12/Y12-1</f>
         <v>-0.22299922299922292</v>
       </c>
       <c r="AD31" s="9">
-        <f t="shared" ref="AD31" si="329">AD12/Z12-1</f>
+        <f t="shared" ref="AD31" si="328">AD12/Z12-1</f>
         <v>7.4706510138740079E-3</v>
       </c>
       <c r="AE31" s="9">
-        <f t="shared" ref="AE31" si="330">AE12/AA12-1</f>
+        <f t="shared" ref="AE31" si="329">AE12/AA12-1</f>
         <v>0.21621621621621623</v>
       </c>
       <c r="AF31" s="9">
-        <f t="shared" ref="AF31" si="331">AF12/AB12-1</f>
+        <f t="shared" ref="AF31" si="330">AF12/AB12-1</f>
         <v>9.109311740890691E-3</v>
       </c>
       <c r="AG31" s="9">
-        <f t="shared" ref="AG31" si="332">AG12/AC12-1</f>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" ref="AG31" si="331">AG12/AC12-1</f>
+        <v>-8.9000000000000079E-2</v>
       </c>
       <c r="AH31" s="9">
-        <f t="shared" ref="AH31" si="333">AH12/AD12-1</f>
+        <f t="shared" ref="AH31" si="332">AH12/AD12-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ31" s="9"/>
       <c r="AK31" s="9">
-        <f t="shared" ref="AK31" si="334">AK12/AJ12-1</f>
+        <f t="shared" ref="AK31" si="333">AK12/AJ12-1</f>
         <v>0.6166666666666667</v>
       </c>
       <c r="AL31" s="9">
-        <f t="shared" ref="AL31" si="335">AL12/AK12-1</f>
+        <f t="shared" ref="AL31" si="334">AL12/AK12-1</f>
         <v>0.48797250859106511</v>
       </c>
       <c r="AM31" s="9">
-        <f t="shared" ref="AM31" si="336">AM12/AL12-1</f>
+        <f t="shared" ref="AM31" si="335">AM12/AL12-1</f>
         <v>0.47979214780600477</v>
       </c>
       <c r="AN31" s="9">
-        <f t="shared" ref="AN31" si="337">AN12/AM12-1</f>
+        <f t="shared" ref="AN31" si="336">AN12/AM12-1</f>
         <v>0.34490831057354643</v>
       </c>
       <c r="AO31" s="9">
-        <f t="shared" ref="AO31" si="338">AO12/AN12-1</f>
+        <f t="shared" ref="AO31" si="337">AO12/AN12-1</f>
         <v>0.16971279373368153</v>
       </c>
       <c r="AP31" s="9">
-        <f t="shared" ref="AP31" si="339">AP12/AO12-1</f>
+        <f t="shared" ref="AP31" si="338">AP12/AO12-1</f>
         <v>-8.0109126984126977E-2</v>
       </c>
       <c r="AQ31" s="9">
-        <f t="shared" ref="AQ31" si="340">AQ12/AP12-1</f>
-        <v>6.3445672688056121E-2</v>
+        <f t="shared" ref="AQ31" si="339">AQ12/AP12-1</f>
+        <v>3.1361552979239704E-2</v>
       </c>
       <c r="AR31" s="9">
-        <f t="shared" ref="AR31" si="341">AR12/AQ12-1</f>
+        <f t="shared" ref="AR31" si="340">AR12/AQ12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AS31" s="9">
-        <f t="shared" ref="AS31" si="342">AS12/AR12-1</f>
+        <f t="shared" ref="AS31" si="341">AS12/AR12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AT31" s="9">
-        <f t="shared" ref="AT31" si="343">AT12/AS12-1</f>
+        <f t="shared" ref="AT31" si="342">AT12/AS12-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AU31" s="9">
-        <f t="shared" ref="AU31" si="344">AU12/AT12-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="AU31" si="343">AU12/AT12-1</f>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AV31" s="9">
-        <f t="shared" ref="AV31:AW31" si="345">AV12/AU12-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="AV31:AW31" si="344">AV12/AU12-1</f>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AW31" s="9">
-        <f t="shared" si="345"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="344"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX31" s="9">
-        <f t="shared" ref="AX31" si="346">AX12/AW12-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="AX31" si="345">AX12/AW12-1</f>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY31" s="9">
-        <f t="shared" ref="AY31" si="347">AY12/AX12-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="AY31" si="346">AY12/AX12-1</f>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ31" s="9">
-        <f t="shared" ref="AZ31" si="348">AZ12/AY12-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="AZ31" si="347">AZ12/AY12-1</f>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA31" s="9">
-        <f t="shared" ref="BA31" si="349">BA12/AZ12-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="BA31" si="348">BA12/AZ12-1</f>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="BC31" t="s">
         <v>53</v>
       </c>
       <c r="BD31" s="11">
         <f>Main!D3</f>
-        <v>89.5</v>
+        <v>94.56</v>
       </c>
     </row>
     <row r="32" spans="2:163" x14ac:dyDescent="0.3">
@@ -6907,207 +6895,207 @@
         <v>-1.5384615384615373E-2</v>
       </c>
       <c r="D32" s="9">
-        <f t="shared" ref="D32:G32" si="350">D17/D16</f>
+        <f t="shared" ref="D32:G32" si="349">D17/D16</f>
         <v>-1.9999999999999429</v>
       </c>
       <c r="E32" s="9">
+        <f t="shared" si="349"/>
+        <v>2.0618556701030875E-2</v>
+      </c>
+      <c r="F32" s="9">
+        <f t="shared" si="349"/>
+        <v>-1.4925373134328391E-2</v>
+      </c>
+      <c r="G32" s="9">
+        <f t="shared" si="349"/>
+        <v>1.0204081632653045E-2</v>
+      </c>
+      <c r="H32" s="9">
+        <f t="shared" ref="H32:N32" si="350">H17/H16</f>
+        <v>4.0567951318458396E-2</v>
+      </c>
+      <c r="I32" s="9">
         <f t="shared" si="350"/>
-        <v>2.0618556701030875E-2</v>
-      </c>
-      <c r="F32" s="9">
+        <v>4.0485829959514144E-3</v>
+      </c>
+      <c r="J32" s="9">
         <f t="shared" si="350"/>
-        <v>-1.4925373134328391E-2</v>
-      </c>
-      <c r="G32" s="9">
+        <v>2.5000000000000074E-2</v>
+      </c>
+      <c r="K32" s="9">
         <f t="shared" si="350"/>
-        <v>1.0204081632653045E-2</v>
-      </c>
-      <c r="H32" s="9">
-        <f t="shared" ref="H32:N32" si="351">H17/H16</f>
-        <v>4.0567951318458396E-2</v>
-      </c>
-      <c r="I32" s="9">
+        <v>3.663003663003663E-3</v>
+      </c>
+      <c r="L32" s="9">
+        <f t="shared" si="350"/>
+        <v>-1.1737089201877937E-2</v>
+      </c>
+      <c r="M32" s="9">
+        <f t="shared" si="350"/>
+        <v>-8.1967213114753829E-2</v>
+      </c>
+      <c r="N32" s="9">
+        <f t="shared" si="350"/>
+        <v>-1.0502625656414103E-2</v>
+      </c>
+      <c r="O32" s="9">
+        <f t="shared" ref="O32:R32" si="351">O17/O16</f>
+        <v>-1.0596026490066216E-2</v>
+      </c>
+      <c r="P32" s="9">
         <f t="shared" si="351"/>
-        <v>4.0485829959514144E-3</v>
-      </c>
-      <c r="J32" s="9">
+        <v>-5.150214592274685E-2</v>
+      </c>
+      <c r="Q32" s="9">
         <f t="shared" si="351"/>
-        <v>2.5000000000000074E-2</v>
-      </c>
-      <c r="K32" s="9">
+        <v>-4.3731778425656004E-3</v>
+      </c>
+      <c r="R32" s="9">
         <f t="shared" si="351"/>
-        <v>3.663003663003663E-3</v>
-      </c>
-      <c r="L32" s="9">
-        <f t="shared" si="351"/>
-        <v>-1.1737089201877937E-2</v>
-      </c>
-      <c r="M32" s="9">
-        <f t="shared" si="351"/>
-        <v>-8.1967213114753829E-2</v>
-      </c>
-      <c r="N32" s="9">
-        <f t="shared" si="351"/>
-        <v>-1.0502625656414103E-2</v>
-      </c>
-      <c r="O32" s="9">
-        <f t="shared" ref="O32:R32" si="352">O17/O16</f>
-        <v>-1.0596026490066216E-2</v>
-      </c>
-      <c r="P32" s="9">
+        <v>-4.8672566371681519E-2</v>
+      </c>
+      <c r="S32" s="9">
+        <f t="shared" ref="S32:AA32" si="352">S17/S16</f>
+        <v>-9.0909090909090703E-2</v>
+      </c>
+      <c r="T32" s="9">
         <f t="shared" si="352"/>
-        <v>-5.150214592274685E-2</v>
-      </c>
-      <c r="Q32" s="9">
+        <v>-2.3679417122040063E-2</v>
+      </c>
+      <c r="U32" s="9">
         <f t="shared" si="352"/>
-        <v>-4.3731778425656004E-3</v>
-      </c>
-      <c r="R32" s="9">
+        <v>-1.6625103906899426E-2</v>
+      </c>
+      <c r="V32" s="9">
         <f t="shared" si="352"/>
-        <v>-4.8672566371681519E-2</v>
-      </c>
-      <c r="S32" s="9">
-        <f t="shared" ref="S32:AA32" si="353">S17/S16</f>
-        <v>-9.0909090909090703E-2</v>
-      </c>
-      <c r="T32" s="9">
+        <v>4.1981528127623827E-3</v>
+      </c>
+      <c r="W32" s="9">
+        <f t="shared" si="352"/>
+        <v>-1.8997361477572555E-2</v>
+      </c>
+      <c r="X32" s="9">
+        <f t="shared" si="352"/>
+        <v>-1.5108593012275727E-2</v>
+      </c>
+      <c r="Y32" s="9">
+        <f t="shared" si="352"/>
+        <v>-9.7889262771489773E-3</v>
+      </c>
+      <c r="Z32" s="9">
+        <f t="shared" si="352"/>
+        <v>-2.3560209424083763E-2</v>
+      </c>
+      <c r="AA32" s="9">
+        <f t="shared" si="352"/>
+        <v>-0.10434782608695639</v>
+      </c>
+      <c r="AB32" s="9">
+        <f t="shared" ref="AB32:AD32" si="353">AB17/AB16</f>
+        <v>0.21247113163972242</v>
+      </c>
+      <c r="AC32" s="9">
         <f t="shared" si="353"/>
-        <v>-2.3679417122040063E-2</v>
-      </c>
-      <c r="U32" s="9">
+        <v>-0.85416666666669872</v>
+      </c>
+      <c r="AD32" s="9">
         <f t="shared" si="353"/>
-        <v>-1.6625103906899426E-2</v>
-      </c>
-      <c r="V32" s="9">
-        <f t="shared" si="353"/>
-        <v>4.1981528127623827E-3</v>
-      </c>
-      <c r="W32" s="9">
-        <f t="shared" si="353"/>
-        <v>-1.8997361477572555E-2</v>
-      </c>
-      <c r="X32" s="9">
-        <f t="shared" si="353"/>
-        <v>-1.5108593012275727E-2</v>
-      </c>
-      <c r="Y32" s="9">
-        <f t="shared" si="353"/>
-        <v>-9.7889262771489773E-3</v>
-      </c>
-      <c r="Z32" s="9">
-        <f t="shared" si="353"/>
-        <v>-2.3560209424083763E-2</v>
-      </c>
-      <c r="AA32" s="9">
-        <f t="shared" si="353"/>
-        <v>-0.10434782608695639</v>
-      </c>
-      <c r="AB32" s="9">
-        <f t="shared" ref="AB32:AD32" si="354">AB17/AB16</f>
-        <v>0.21247113163972242</v>
-      </c>
-      <c r="AC32" s="9">
+        <v>-0.37451737451737549</v>
+      </c>
+      <c r="AE32" s="9">
+        <f t="shared" ref="AE32:AH32" si="354">AE17/AE16</f>
+        <v>0.32345679012345646</v>
+      </c>
+      <c r="AF32" s="9">
         <f t="shared" si="354"/>
-        <v>-0.85416666666669872</v>
-      </c>
-      <c r="AD32" s="9">
+        <v>-1.2340425531915071</v>
+      </c>
+      <c r="AG32" s="9">
         <f t="shared" si="354"/>
-        <v>-0.37451737451737549</v>
-      </c>
-      <c r="AE32" s="9">
-        <f t="shared" ref="AE32:AH32" si="355">AE17/AE16</f>
-        <v>0.32345679012345646</v>
-      </c>
-      <c r="AF32" s="9">
-        <f t="shared" si="355"/>
-        <v>-1.2340425531915071</v>
-      </c>
-      <c r="AG32" s="9">
-        <f t="shared" si="355"/>
+        <v>0.34736842105263177</v>
+      </c>
+      <c r="AH32" s="9">
+        <f t="shared" si="354"/>
         <v>0.2</v>
       </c>
-      <c r="AH32" s="9">
-        <f t="shared" si="355"/>
-        <v>0.19999999999999998</v>
-      </c>
       <c r="AJ32" s="9">
-        <f t="shared" ref="AJ32" si="356">AJ17/AJ16</f>
+        <f t="shared" ref="AJ32" si="355">AJ17/AJ16</f>
         <v>6.4516129032257979E-2</v>
       </c>
       <c r="AK32" s="9">
-        <f t="shared" ref="AK32:AL32" si="357">AK17/AK16</f>
+        <f t="shared" ref="AK32:AL32" si="356">AK17/AK16</f>
         <v>1.6567263088137864E-2</v>
       </c>
       <c r="AL32" s="9">
+        <f t="shared" si="356"/>
+        <v>7.6294277929155122E-2</v>
+      </c>
+      <c r="AM32" s="9">
+        <f t="shared" ref="AM32:AV32" si="357">AM17/AM16</f>
+        <v>-2.4513947590870694E-2</v>
+      </c>
+      <c r="AN32" s="9">
         <f t="shared" si="357"/>
-        <v>7.6294277929155122E-2</v>
-      </c>
-      <c r="AM32" s="9">
-        <f t="shared" ref="AM32:AV32" si="358">AM17/AM16</f>
-        <v>-2.4513947590870694E-2</v>
-      </c>
-      <c r="AN32" s="9">
-        <f t="shared" si="358"/>
         <v>-1.1776649746192887E-2</v>
       </c>
       <c r="AO32" s="9">
-        <f t="shared" si="358"/>
+        <f t="shared" si="357"/>
         <v>-1.459854014598541E-2</v>
       </c>
       <c r="AP32" s="9">
-        <f t="shared" si="358"/>
+        <f t="shared" si="357"/>
         <v>-7.8333333333333199E-2</v>
       </c>
       <c r="AQ32" s="9">
-        <f t="shared" si="358"/>
-        <v>-2.1199747055565976</v>
+        <f t="shared" si="357"/>
+        <v>8.720794849628391E-2</v>
       </c>
       <c r="AR32" s="9">
+        <f t="shared" si="357"/>
+        <v>0.2</v>
+      </c>
+      <c r="AS32" s="9">
+        <f t="shared" si="357"/>
+        <v>0.2</v>
+      </c>
+      <c r="AT32" s="9">
+        <f t="shared" si="357"/>
+        <v>0.2</v>
+      </c>
+      <c r="AU32" s="9">
+        <f t="shared" si="357"/>
+        <v>0.2</v>
+      </c>
+      <c r="AV32" s="9">
+        <f t="shared" si="357"/>
+        <v>0.2</v>
+      </c>
+      <c r="AW32" s="9">
+        <f t="shared" ref="AW32:BA32" si="358">AW17/AW16</f>
+        <v>0.2</v>
+      </c>
+      <c r="AX32" s="9">
         <f t="shared" si="358"/>
         <v>0.2</v>
       </c>
-      <c r="AS32" s="9">
+      <c r="AY32" s="9">
         <f t="shared" si="358"/>
         <v>0.2</v>
       </c>
-      <c r="AT32" s="9">
+      <c r="AZ32" s="9">
+        <f t="shared" si="358"/>
+        <v>0.20000000000000004</v>
+      </c>
+      <c r="BA32" s="9">
         <f t="shared" si="358"/>
         <v>0.2</v>
       </c>
-      <c r="AU32" s="9">
-        <f t="shared" si="358"/>
-        <v>0.2</v>
-      </c>
-      <c r="AV32" s="9">
-        <f t="shared" si="358"/>
-        <v>0.2</v>
-      </c>
-      <c r="AW32" s="9">
-        <f t="shared" ref="AW32:BA32" si="359">AW17/AW16</f>
-        <v>0.2</v>
-      </c>
-      <c r="AX32" s="9">
-        <f t="shared" si="359"/>
-        <v>0.2</v>
-      </c>
-      <c r="AY32" s="9">
-        <f t="shared" si="359"/>
-        <v>0.2</v>
-      </c>
-      <c r="AZ32" s="9">
-        <f t="shared" si="359"/>
-        <v>0.20000000000000004</v>
-      </c>
-      <c r="BA32" s="9">
-        <f t="shared" si="359"/>
-        <v>0.20000000000000004</v>
-      </c>
       <c r="BC32" s="1" t="s">
         <v>54</v>
       </c>
       <c r="BD32" s="10">
         <f>BD30/BD31-1</f>
-        <v>-0.4381053962942203</v>
+        <v>-0.44699675376739123</v>
       </c>
     </row>
     <row r="33" spans="2:56" x14ac:dyDescent="0.3">
@@ -7119,210 +7107,205 @@
         <v>-4.831625183016109E-2</v>
       </c>
       <c r="D33" s="9">
-        <f t="shared" ref="D33:AW33" si="360">D18/D5</f>
+        <f t="shared" ref="D33:AW33" si="359">D18/D5</f>
         <v>3.8265306122449343E-3</v>
       </c>
       <c r="E33" s="9">
+        <f t="shared" si="359"/>
+        <v>-5.4786620530565329E-2</v>
+      </c>
+      <c r="F33" s="9">
+        <f t="shared" si="359"/>
+        <v>2.466449038810296E-2</v>
+      </c>
+      <c r="G33" s="9">
+        <f t="shared" si="359"/>
+        <v>-4.6927914852443242E-2</v>
+      </c>
+      <c r="H33" s="9">
+        <f t="shared" si="359"/>
+        <v>-3.7824870051979237E-2</v>
+      </c>
+      <c r="I33" s="9">
+        <f t="shared" si="359"/>
+        <v>-9.4288999616711458E-2</v>
+      </c>
+      <c r="J33" s="9">
+        <f t="shared" si="359"/>
+        <v>-3.7937743190661365E-2</v>
+      </c>
+      <c r="K33" s="9">
+        <f t="shared" si="359"/>
+        <v>-0.16957605985037405</v>
+      </c>
+      <c r="L33" s="9">
+        <f t="shared" si="359"/>
+        <v>-0.1210334175793316</v>
+      </c>
+      <c r="M33" s="9">
+        <f t="shared" si="359"/>
+        <v>2.9229406554473071E-2</v>
+      </c>
+      <c r="N33" s="9">
+        <f t="shared" si="359"/>
+        <v>0.10363132789659947</v>
+      </c>
+      <c r="O33" s="9">
+        <f t="shared" si="359"/>
+        <v>0.13288052943225367</v>
+      </c>
+      <c r="P33" s="9">
+        <f t="shared" si="359"/>
+        <v>0.11393582390327067</v>
+      </c>
+      <c r="Q33" s="9">
+        <f t="shared" si="359"/>
+        <v>0.10133843212237087</v>
+      </c>
+      <c r="R33" s="9">
+        <f t="shared" si="359"/>
+        <v>2.7389344735929688E-2</v>
+      </c>
+      <c r="S33" s="9">
+        <f t="shared" ref="S33:AA33" si="360">S18/S5</f>
+        <v>-3.5982008995502329E-2</v>
+      </c>
+      <c r="T33" s="9">
         <f t="shared" si="360"/>
-        <v>-5.4786620530565329E-2</v>
-      </c>
-      <c r="F33" s="9">
+        <v>-0.14702419882276005</v>
+      </c>
+      <c r="U33" s="9">
         <f t="shared" si="360"/>
-        <v>2.466449038810296E-2</v>
-      </c>
-      <c r="G33" s="9">
+        <v>-0.16062516417126335</v>
+      </c>
+      <c r="V33" s="9">
         <f t="shared" si="360"/>
-        <v>-4.6927914852443242E-2</v>
-      </c>
-      <c r="H33" s="9">
+        <v>-0.27355552992734417</v>
+      </c>
+      <c r="W33" s="9">
         <f t="shared" si="360"/>
-        <v>-3.7824870051979237E-2</v>
-      </c>
-      <c r="I33" s="9">
+        <v>-0.26059379217273959</v>
+      </c>
+      <c r="X33" s="9">
         <f t="shared" si="360"/>
-        <v>-9.4288999616711458E-2</v>
-      </c>
-      <c r="J33" s="9">
+        <v>-0.12687359848931906</v>
+      </c>
+      <c r="Y33" s="9">
         <f t="shared" si="360"/>
-        <v>-3.7937743190661365E-2</v>
-      </c>
-      <c r="K33" s="9">
+        <v>-0.36195175438596489</v>
+      </c>
+      <c r="Z33" s="9">
         <f t="shared" si="360"/>
-        <v>-0.16957605985037405</v>
-      </c>
-      <c r="L33" s="9">
+        <v>-7.9431183341797884E-2</v>
+      </c>
+      <c r="AA33" s="9">
         <f t="shared" si="360"/>
-        <v>-0.1210334175793316</v>
-      </c>
-      <c r="M33" s="9">
-        <f t="shared" si="360"/>
-        <v>2.9229406554473071E-2</v>
-      </c>
-      <c r="N33" s="9">
-        <f t="shared" si="360"/>
-        <v>0.10363132789659947</v>
-      </c>
-      <c r="O33" s="9">
-        <f t="shared" si="360"/>
-        <v>0.13288052943225367</v>
-      </c>
-      <c r="P33" s="9">
-        <f t="shared" si="360"/>
-        <v>0.11393582390327067</v>
-      </c>
-      <c r="Q33" s="9">
-        <f t="shared" si="360"/>
-        <v>0.10133843212237087</v>
-      </c>
-      <c r="R33" s="9">
-        <f t="shared" si="360"/>
-        <v>2.7389344735929688E-2</v>
-      </c>
-      <c r="S33" s="9">
-        <f t="shared" ref="S33:AA33" si="361">S18/S5</f>
-        <v>-3.5982008995502329E-2</v>
-      </c>
-      <c r="T33" s="9">
+        <v>-5.7635579759473629E-2</v>
+      </c>
+      <c r="AB33" s="9">
+        <f t="shared" ref="AB33:AD33" si="361">AB18/AB5</f>
+        <v>-3.5223633922115583E-2</v>
+      </c>
+      <c r="AC33" s="9">
         <f t="shared" si="361"/>
-        <v>-0.14702419882276005</v>
-      </c>
-      <c r="U33" s="9">
+        <v>-8.3788363773298988E-3</v>
+      </c>
+      <c r="AD33" s="9">
         <f t="shared" si="361"/>
-        <v>-0.16062516417126335</v>
-      </c>
-      <c r="V33" s="9">
-        <f t="shared" si="361"/>
-        <v>-0.27355552992734417</v>
-      </c>
-      <c r="W33" s="9">
-        <f t="shared" si="361"/>
-        <v>-0.26059379217273959</v>
-      </c>
-      <c r="X33" s="9">
-        <f t="shared" si="361"/>
-        <v>-0.12687359848931906</v>
-      </c>
-      <c r="Y33" s="9">
-        <f t="shared" si="361"/>
-        <v>-0.36195175438596489</v>
-      </c>
-      <c r="Z33" s="9">
-        <f t="shared" si="361"/>
-        <v>-7.9431183341797884E-2</v>
-      </c>
-      <c r="AA33" s="9">
-        <f t="shared" si="361"/>
-        <v>-5.7635579759473629E-2</v>
-      </c>
-      <c r="AB33" s="9">
-        <f t="shared" ref="AB33:AD33" si="362">AB18/AB5</f>
-        <v>-3.5223633922115583E-2</v>
-      </c>
-      <c r="AC33" s="9">
+        <v>-2.9641965029142323E-2</v>
+      </c>
+      <c r="AE33" s="9">
+        <f t="shared" ref="AE33:AH33" si="362">AE18/AE5</f>
+        <v>-2.6844322523758249E-2</v>
+      </c>
+      <c r="AF33" s="9">
         <f t="shared" si="362"/>
-        <v>-8.3788363773298988E-3</v>
-      </c>
-      <c r="AD33" s="9">
+        <v>9.4500945009449496E-3</v>
+      </c>
+      <c r="AG33" s="9">
         <f t="shared" si="362"/>
-        <v>-2.9641965029142323E-2</v>
-      </c>
-      <c r="AE33" s="9">
-        <f t="shared" ref="AE33:AH33" si="363">AE18/AE5</f>
-        <v>-2.6844322523758249E-2</v>
-      </c>
-      <c r="AF33" s="9">
+        <v>2.0485709565504693E-2</v>
+      </c>
+      <c r="AH33" s="9">
+        <f t="shared" si="362"/>
+        <v>3.0924610234111125E-2</v>
+      </c>
+      <c r="AJ33" s="9">
+        <f t="shared" si="359"/>
+        <v>-1.1717171717171734E-2</v>
+      </c>
+      <c r="AK33" s="9">
+        <f t="shared" si="359"/>
+        <v>-5.2582159624413059E-2</v>
+      </c>
+      <c r="AL33" s="9">
+        <f t="shared" si="359"/>
+        <v>-9.53103913630232E-3</v>
+      </c>
+      <c r="AM33" s="9">
+        <f t="shared" si="359"/>
+        <v>8.7683125339120913E-2</v>
+      </c>
+      <c r="AN33" s="9">
+        <f t="shared" si="359"/>
+        <v>-0.15936930309911421</v>
+      </c>
+      <c r="AO33" s="9">
+        <f t="shared" si="359"/>
+        <v>-0.20342630853994481</v>
+      </c>
+      <c r="AP33" s="9">
+        <f t="shared" si="359"/>
+        <v>-3.1463515452136111E-2</v>
+      </c>
+      <c r="AQ33" s="9">
+        <f t="shared" si="359"/>
+        <v>1.0586299492684222E-2</v>
+      </c>
+      <c r="AR33" s="9">
+        <f t="shared" si="359"/>
+        <v>4.1293448073626456E-2</v>
+      </c>
+      <c r="AS33" s="9">
+        <f t="shared" si="359"/>
+        <v>7.1737295153719405E-2</v>
+      </c>
+      <c r="AT33" s="9">
+        <f t="shared" si="359"/>
+        <v>8.9575665212323033E-2</v>
+      </c>
+      <c r="AU33" s="9">
+        <f t="shared" si="359"/>
+        <v>9.4762283313040416E-2</v>
+      </c>
+      <c r="AV33" s="9">
+        <f t="shared" si="359"/>
+        <v>9.825166943978432E-2</v>
+      </c>
+      <c r="AW33" s="9">
+        <f t="shared" si="359"/>
+        <v>0.10011095359560977</v>
+      </c>
+      <c r="AX33" s="9">
+        <f t="shared" ref="AX33:BA33" si="363">AX18/AX5</f>
+        <v>0.10195807620721571</v>
+      </c>
+      <c r="AY33" s="9">
         <f t="shared" si="363"/>
-        <v>9.4500945009449496E-3</v>
-      </c>
-      <c r="AG33" s="9">
+        <v>0.10379312833690409</v>
+      </c>
+      <c r="AZ33" s="9">
         <f t="shared" si="363"/>
-        <v>1.2772803658129935E-2</v>
-      </c>
-      <c r="AH33" s="9">
+        <v>0.10561620125585457</v>
+      </c>
+      <c r="BA33" s="9">
         <f t="shared" si="363"/>
-        <v>1.3346521043516246E-2</v>
-      </c>
-      <c r="AJ33" s="9">
-        <f t="shared" si="360"/>
-        <v>-1.1717171717171734E-2</v>
-      </c>
-      <c r="AK33" s="9">
-        <f t="shared" si="360"/>
-        <v>-5.2582159624413059E-2</v>
-      </c>
-      <c r="AL33" s="9">
-        <f t="shared" si="360"/>
-        <v>-9.53103913630232E-3</v>
-      </c>
-      <c r="AM33" s="9">
-        <f t="shared" si="360"/>
-        <v>8.7683125339120913E-2</v>
-      </c>
-      <c r="AN33" s="9">
-        <f t="shared" si="360"/>
-        <v>-0.15936930309911421</v>
-      </c>
-      <c r="AO33" s="9">
-        <f t="shared" si="360"/>
-        <v>-0.20342630853994481</v>
-      </c>
-      <c r="AP33" s="9">
-        <f t="shared" si="360"/>
-        <v>-3.1463515452136111E-2</v>
-      </c>
-      <c r="AQ33" s="9">
-        <f t="shared" si="360"/>
-        <v>3.4086769234357973E-3</v>
-      </c>
-      <c r="AR33" s="9">
-        <f t="shared" si="360"/>
-        <v>4.6045212886573872E-2</v>
-      </c>
-      <c r="AS33" s="9">
-        <f t="shared" si="360"/>
-        <v>6.9818386174439528E-2</v>
-      </c>
-      <c r="AT33" s="9">
-        <f t="shared" si="360"/>
-        <v>8.7850377195818619E-2</v>
-      </c>
-      <c r="AU33" s="9">
-        <f t="shared" si="360"/>
-        <v>9.2437510271924705E-2</v>
-      </c>
-      <c r="AV33" s="9">
-        <f t="shared" si="360"/>
-        <v>9.5272905515312201E-2</v>
-      </c>
-      <c r="AW33" s="9">
-        <f t="shared" si="360"/>
-        <v>9.6667701114446794E-2</v>
-      </c>
-      <c r="AX33" s="9">
-        <f t="shared" ref="AX33:BA33" si="364">AX18/AX5</f>
-        <v>9.8054386464319271E-2</v>
-      </c>
-      <c r="AY33" s="9">
-        <f t="shared" si="364"/>
-        <v>9.9433026406545277E-2</v>
-      </c>
-      <c r="AZ33" s="9">
-        <f t="shared" si="364"/>
-        <v>0.10080368606459329</v>
-      </c>
-      <c r="BA33" s="9">
-        <f t="shared" si="364"/>
-        <v>0.10216643083623501</v>
+        <v>0.10742738643411316</v>
       </c>
       <c r="BC33" t="s">
         <v>55</v>
       </c>
       <c r="BD33" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="35" spans="2:56" x14ac:dyDescent="0.3">
-      <c r="BD35" t="s">
         <v>80</v>
       </c>
     </row>
